--- a/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEBD344-B214-4663-A45A-6859BF558856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED855C92-DA3A-43A7-A7D2-C830730D1A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="486">
   <si>
     <t>Date</t>
   </si>
@@ -1320,6 +1320,174 @@
   <si>
     <t>Shadra</t>
   </si>
+  <si>
+    <t>Chanda Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UF Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadab Super Mart </t>
+  </si>
+  <si>
+    <t>Al Karam Super Store</t>
+  </si>
+  <si>
+    <t>Roshan Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaudry Cash &amp; carry </t>
+  </si>
+  <si>
+    <t>Umair</t>
+  </si>
+  <si>
+    <t>Shadab Colony</t>
+  </si>
+  <si>
+    <t>Zeshan</t>
+  </si>
+  <si>
+    <t>Fakher Store</t>
+  </si>
+  <si>
+    <t>Toheed Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luqman Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sakuf Mart </t>
+  </si>
+  <si>
+    <t>Hikma Store</t>
+  </si>
+  <si>
+    <t>Family Store</t>
+  </si>
+  <si>
+    <t>The Hotpot Souces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shehwar Mega Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy Mart </t>
+  </si>
+  <si>
+    <t>Velencia Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faziya Adda Block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jublee Town </t>
+  </si>
+  <si>
+    <t>Behria Orchard</t>
+  </si>
+  <si>
+    <t>Nespak Society Wapda Town</t>
+  </si>
+  <si>
+    <t>Sana Cash &amp; Carry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iqbal Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem  </t>
+  </si>
+  <si>
+    <t>Adnan Store</t>
+  </si>
+  <si>
+    <t>Shehzad Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Sweet </t>
+  </si>
+  <si>
+    <t>Data store</t>
+  </si>
+  <si>
+    <t>RA GS</t>
+  </si>
+  <si>
+    <t>Umer Store</t>
+  </si>
+  <si>
+    <t>Ajmal Bakery</t>
+  </si>
+  <si>
+    <t>Furqan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadman </t>
+  </si>
+  <si>
+    <t>Smart Pharmacy</t>
+  </si>
+  <si>
+    <t>Cant Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best One Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Super Mart </t>
+  </si>
+  <si>
+    <t>Askari 9</t>
+  </si>
+  <si>
+    <t>Shabaz SB</t>
+  </si>
+  <si>
+    <t>Iftakhar GS</t>
+  </si>
+  <si>
+    <t>Somoro Sweet</t>
+  </si>
+  <si>
+    <t>Karachi Kareyana Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK Mart </t>
+  </si>
+  <si>
+    <t>Khan GS</t>
+  </si>
+  <si>
+    <t>Haji Kreyana Store</t>
+  </si>
+  <si>
+    <t>Hamza Store</t>
+  </si>
+  <si>
+    <t>Jamshad Store</t>
+  </si>
+  <si>
+    <t>Numan GS</t>
+  </si>
+  <si>
+    <t>Muaz GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazrat Karman Wla </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sherry Mart </t>
+  </si>
+  <si>
+    <t>Rise Store</t>
+  </si>
+  <si>
+    <t>Jameel Store</t>
+  </si>
+  <si>
+    <t>Saad Store</t>
+  </si>
 </sst>
 </file>
 
@@ -1377,11 +1545,13 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1403,13 +1573,13 @@
     <font>
       <sz val="11"/>
       <name val="Arial Unicode MS"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial Unicode MS"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2255,6 +2425,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2296,12 +2472,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2669,114 +2839,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="116" t="s">
+      <c r="A1" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="116" t="s">
+      <c r="C1" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="116" t="s">
+      <c r="E1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="116" t="s">
+      <c r="F1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="116" t="s">
+      <c r="G1" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="116" t="s">
+      <c r="H1" s="118" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="42"/>
-      <c r="K1" s="116" t="s">
+      <c r="K1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="117" t="s">
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="119" t="s">
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="121" t="s">
+      <c r="T1" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121" t="s">
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
+      <c r="X1" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="119" t="s">
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="123"/>
+      <c r="AB1" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="119" t="s">
+      <c r="AC1" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="119" t="s">
+      <c r="AD1" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="119" t="s">
+      <c r="AE1" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="119" t="s">
+      <c r="AF1" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="119" t="s">
+      <c r="AG1" s="121" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="84">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="119" t="s">
+      <c r="AI1" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="119" t="s">
+      <c r="AJ1" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="119" t="s">
+      <c r="AK1" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="119" t="s">
+      <c r="AL1" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="119" t="s">
+      <c r="AM1" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="122" t="s">
+      <c r="AN1" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="122" t="s">
+      <c r="AO1" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="119" t="s">
+      <c r="AP1" s="121" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="116"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -2807,7 +2977,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="120"/>
+      <c r="S2" s="122"/>
       <c r="T2" s="83" t="s">
         <v>73</v>
       </c>
@@ -2832,23 +3002,23 @@
       <c r="AA2" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="120"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="120"/>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="120"/>
-      <c r="AG2" s="120"/>
+      <c r="AB2" s="122"/>
+      <c r="AC2" s="122"/>
+      <c r="AD2" s="122"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="122"/>
+      <c r="AG2" s="122"/>
       <c r="AH2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="120"/>
-      <c r="AJ2" s="120"/>
-      <c r="AK2" s="120"/>
-      <c r="AL2" s="120"/>
-      <c r="AM2" s="120"/>
-      <c r="AN2" s="123"/>
-      <c r="AO2" s="123"/>
-      <c r="AP2" s="120"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
+      <c r="AK2" s="122"/>
+      <c r="AL2" s="122"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="122"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="85">
@@ -34414,13 +34584,13 @@
       <c r="F314" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="G314" s="130" t="s">
+      <c r="G314" s="116" t="s">
         <v>277</v>
       </c>
       <c r="H314" s="86" t="s">
         <v>424</v>
       </c>
-      <c r="I314" s="131" t="s">
+      <c r="I314" s="117" t="s">
         <v>425</v>
       </c>
       <c r="J314" s="52">
@@ -43874,16 +44044,36 @@
       <c r="AP434" s="7"/>
     </row>
     <row r="435" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A435" s="94"/>
-      <c r="B435" s="76"/>
-      <c r="C435" s="94"/>
-      <c r="D435" s="102"/>
-      <c r="E435" s="94"/>
-      <c r="F435" s="94"/>
-      <c r="G435" s="94"/>
-      <c r="H435" s="94"/>
-      <c r="I435" s="94"/>
-      <c r="J435" s="52"/>
+      <c r="A435" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B435" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C435" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D435" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E435" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F435" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G435" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="H435" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I435" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="J435" s="52">
+        <v>40</v>
+      </c>
       <c r="K435" s="52"/>
       <c r="L435" s="52"/>
       <c r="M435" s="52"/>
@@ -43891,16 +44081,22 @@
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="O435" s="52"/>
-      <c r="P435" s="52"/>
-      <c r="Q435" s="52"/>
+      <c r="O435" s="52">
+        <v>10</v>
+      </c>
+      <c r="P435" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q435" s="52">
+        <v>20</v>
+      </c>
       <c r="R435" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S435" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB435" s="88">
         <v>39.270000000000003</v>
@@ -43913,47 +44109,67 @@
       </c>
       <c r="AE435" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF435" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG435" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>479.83000000000004</v>
       </c>
       <c r="AH435" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI435" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>6902.17</v>
       </c>
       <c r="AJ435" s="91">
         <v>0.18</v>
       </c>
       <c r="AK435" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>1242.3905999999999</v>
       </c>
       <c r="AL435" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>8144.5605999999998</v>
       </c>
       <c r="AP435" s="7"/>
     </row>
     <row r="436" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A436" s="94"/>
-      <c r="B436" s="76"/>
-      <c r="C436" s="94"/>
-      <c r="D436" s="102"/>
-      <c r="E436" s="94"/>
-      <c r="F436" s="94"/>
-      <c r="G436" s="94"/>
-      <c r="H436" s="94"/>
-      <c r="I436" s="94"/>
-      <c r="J436" s="52"/>
+      <c r="A436" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B436" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C436" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D436" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E436" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F436" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G436" s="94" t="s">
+        <v>430</v>
+      </c>
+      <c r="H436" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I436" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="J436" s="52">
+        <v>12</v>
+      </c>
       <c r="K436" s="52"/>
       <c r="L436" s="52"/>
       <c r="M436" s="52"/>
@@ -43970,7 +44186,7 @@
       </c>
       <c r="S436" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB436" s="88">
         <v>39.270000000000003</v>
@@ -43983,46 +44199,64 @@
       </c>
       <c r="AE436" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF436" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG436" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>87.289800000000014</v>
       </c>
       <c r="AH436" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI436" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1255.6302000000001</v>
       </c>
       <c r="AJ436" s="91">
         <v>0.18</v>
       </c>
       <c r="AK436" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>226.01343600000001</v>
       </c>
       <c r="AL436" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1481.643636</v>
       </c>
       <c r="AP436" s="7"/>
     </row>
     <row r="437" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A437" s="94"/>
-      <c r="B437" s="76"/>
-      <c r="C437" s="94"/>
-      <c r="D437" s="102"/>
-      <c r="E437" s="94"/>
-      <c r="F437" s="94"/>
-      <c r="G437" s="94"/>
-      <c r="H437" s="94"/>
-      <c r="I437" s="94"/>
+      <c r="A437" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B437" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C437" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D437" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E437" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F437" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G437" s="94" t="s">
+        <v>431</v>
+      </c>
+      <c r="H437" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I437" s="94" t="s">
+        <v>437</v>
+      </c>
       <c r="J437" s="52"/>
       <c r="K437" s="52"/>
       <c r="L437" s="52"/>
@@ -44031,16 +44265,22 @@
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="O437" s="52"/>
-      <c r="P437" s="52"/>
-      <c r="Q437" s="52"/>
+      <c r="O437" s="52">
+        <v>10</v>
+      </c>
+      <c r="P437" s="52">
+        <v>15</v>
+      </c>
+      <c r="Q437" s="52">
+        <v>15</v>
+      </c>
       <c r="R437" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S437" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB437" s="88">
         <v>39.270000000000003</v>
@@ -44053,14 +44293,14 @@
       </c>
       <c r="AE437" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF437" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG437" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH437" s="49">
         <f t="shared" si="127"/>
@@ -44068,49 +44308,77 @@
       </c>
       <c r="AI437" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ437" s="91">
         <v>0.18</v>
       </c>
       <c r="AK437" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL437" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP437" s="7"/>
     </row>
     <row r="438" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A438" s="94"/>
-      <c r="B438" s="76"/>
-      <c r="C438" s="94"/>
-      <c r="D438" s="102"/>
-      <c r="E438" s="94"/>
-      <c r="F438" s="94"/>
-      <c r="G438" s="94"/>
-      <c r="H438" s="94"/>
-      <c r="I438" s="94"/>
+      <c r="A438" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B438" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C438" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D438" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E438" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F438" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G438" s="94" t="s">
+        <v>432</v>
+      </c>
+      <c r="H438" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I438" s="94" t="s">
+        <v>437</v>
+      </c>
       <c r="J438" s="52"/>
-      <c r="K438" s="52"/>
-      <c r="L438" s="52"/>
+      <c r="K438" s="52">
+        <v>40</v>
+      </c>
+      <c r="L438" s="52">
+        <v>40</v>
+      </c>
       <c r="M438" s="52"/>
       <c r="N438" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="O438" s="52"/>
-      <c r="P438" s="52"/>
-      <c r="Q438" s="52"/>
+        <v>80</v>
+      </c>
+      <c r="O438" s="52">
+        <v>40</v>
+      </c>
+      <c r="P438" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q438" s="52">
+        <v>40</v>
+      </c>
       <c r="R438" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S438" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB438" s="88">
         <v>39.270000000000003</v>
@@ -44123,14 +44391,14 @@
       </c>
       <c r="AE438" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>18725</v>
       </c>
       <c r="AF438" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG438" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1217.125</v>
       </c>
       <c r="AH438" s="49">
         <f t="shared" si="127"/>
@@ -44138,32 +44406,52 @@
       </c>
       <c r="AI438" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ438" s="91">
         <v>0.18</v>
       </c>
       <c r="AK438" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL438" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP438" s="7"/>
     </row>
     <row r="439" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A439" s="94"/>
-      <c r="B439" s="76"/>
-      <c r="C439" s="94"/>
-      <c r="D439" s="102"/>
-      <c r="E439" s="94"/>
-      <c r="F439" s="94"/>
-      <c r="G439" s="94"/>
-      <c r="H439" s="94"/>
-      <c r="I439" s="94"/>
-      <c r="J439" s="52"/>
+      <c r="A439" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B439" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C439" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D439" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E439" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F439" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G439" s="94" t="s">
+        <v>210</v>
+      </c>
+      <c r="H439" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I439" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="J439" s="52">
+        <v>40</v>
+      </c>
       <c r="K439" s="52"/>
       <c r="L439" s="52"/>
       <c r="M439" s="52"/>
@@ -44180,7 +44468,7 @@
       </c>
       <c r="S439" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB439" s="88">
         <v>39.270000000000003</v>
@@ -44193,53 +44481,75 @@
       </c>
       <c r="AE439" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF439" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG439" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH439" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI439" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ439" s="91">
         <v>0.18</v>
       </c>
       <c r="AK439" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL439" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP439" s="7"/>
     </row>
     <row r="440" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A440" s="94"/>
-      <c r="B440" s="76"/>
-      <c r="C440" s="94"/>
-      <c r="D440" s="102"/>
-      <c r="E440" s="94"/>
-      <c r="F440" s="94"/>
-      <c r="G440" s="94"/>
-      <c r="H440" s="94"/>
-      <c r="I440" s="94"/>
+      <c r="A440" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B440" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C440" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D440" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E440" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F440" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G440" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="H440" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I440" s="94" t="s">
+        <v>437</v>
+      </c>
       <c r="J440" s="52"/>
-      <c r="K440" s="52"/>
-      <c r="L440" s="52"/>
+      <c r="K440" s="52">
+        <v>6</v>
+      </c>
+      <c r="L440" s="52">
+        <v>6</v>
+      </c>
       <c r="M440" s="52"/>
       <c r="N440" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O440" s="52"/>
       <c r="P440" s="52"/>
@@ -44250,7 +44560,7 @@
       </c>
       <c r="S440" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB440" s="88">
         <v>39.270000000000003</v>
@@ -44263,14 +44573,14 @@
       </c>
       <c r="AE440" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1501.23</v>
       </c>
       <c r="AF440" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG440" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>97.579950000000011</v>
       </c>
       <c r="AH440" s="49">
         <f t="shared" si="127"/>
@@ -44278,32 +44588,52 @@
       </c>
       <c r="AI440" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1403.65005</v>
       </c>
       <c r="AJ440" s="91">
         <v>0.18</v>
       </c>
       <c r="AK440" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>252.65700899999999</v>
       </c>
       <c r="AL440" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1656.307059</v>
       </c>
       <c r="AP440" s="7"/>
     </row>
     <row r="441" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A441" s="94"/>
-      <c r="B441" s="76"/>
-      <c r="C441" s="94"/>
-      <c r="D441" s="102"/>
-      <c r="E441" s="94"/>
-      <c r="F441" s="94"/>
-      <c r="G441" s="94"/>
-      <c r="H441" s="94"/>
-      <c r="I441" s="94"/>
-      <c r="J441" s="52"/>
+      <c r="A441" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B441" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C441" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D441" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E441" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F441" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G441" s="94" t="s">
+        <v>194</v>
+      </c>
+      <c r="H441" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I441" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="J441" s="52">
+        <v>40</v>
+      </c>
       <c r="K441" s="52"/>
       <c r="L441" s="52"/>
       <c r="M441" s="52"/>
@@ -44320,7 +44650,7 @@
       </c>
       <c r="S441" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB441" s="88">
         <v>39.270000000000003</v>
@@ -44333,47 +44663,67 @@
       </c>
       <c r="AE441" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF441" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG441" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH441" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI441" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ441" s="91">
         <v>0.18</v>
       </c>
       <c r="AK441" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL441" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP441" s="7"/>
     </row>
     <row r="442" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A442" s="94"/>
-      <c r="B442" s="76"/>
-      <c r="C442" s="94"/>
-      <c r="D442" s="102"/>
-      <c r="E442" s="94"/>
-      <c r="F442" s="94"/>
-      <c r="G442" s="94"/>
-      <c r="H442" s="94"/>
-      <c r="I442" s="94"/>
-      <c r="J442" s="52"/>
+      <c r="A442" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B442" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C442" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D442" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E442" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F442" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G442" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="H442" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I442" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="J442" s="52">
+        <v>40</v>
+      </c>
       <c r="K442" s="52"/>
       <c r="L442" s="52"/>
       <c r="M442" s="52"/>
@@ -44381,16 +44731,22 @@
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="O442" s="52"/>
-      <c r="P442" s="52"/>
-      <c r="Q442" s="52"/>
+      <c r="O442" s="52">
+        <v>40</v>
+      </c>
+      <c r="P442" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q442" s="52">
+        <v>40</v>
+      </c>
       <c r="R442" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S442" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB442" s="88">
         <v>39.270000000000003</v>
@@ -44403,47 +44759,67 @@
       </c>
       <c r="AE442" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>13193.2</v>
       </c>
       <c r="AF442" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG442" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>857.55800000000011</v>
       </c>
       <c r="AH442" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI442" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>12335.642</v>
       </c>
       <c r="AJ442" s="91">
         <v>0.18</v>
       </c>
       <c r="AK442" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2220.4155599999999</v>
       </c>
       <c r="AL442" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>14556.057559999999</v>
       </c>
       <c r="AP442" s="7"/>
     </row>
     <row r="443" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A443" s="94"/>
-      <c r="B443" s="76"/>
-      <c r="C443" s="94"/>
-      <c r="D443" s="102"/>
-      <c r="E443" s="94"/>
-      <c r="F443" s="94"/>
-      <c r="G443" s="94"/>
-      <c r="H443" s="94"/>
-      <c r="I443" s="94"/>
-      <c r="J443" s="52"/>
+      <c r="A443" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B443" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C443" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D443" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E443" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F443" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G443" s="94" t="s">
+        <v>434</v>
+      </c>
+      <c r="H443" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I443" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="J443" s="52">
+        <v>10</v>
+      </c>
       <c r="K443" s="52"/>
       <c r="L443" s="52"/>
       <c r="M443" s="52"/>
@@ -44451,16 +44827,22 @@
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="O443" s="52"/>
-      <c r="P443" s="52"/>
-      <c r="Q443" s="52"/>
+      <c r="O443" s="52">
+        <v>15</v>
+      </c>
+      <c r="P443" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q443" s="52">
+        <v>15</v>
+      </c>
       <c r="R443" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S443" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB443" s="88">
         <v>39.270000000000003</v>
@@ -44473,46 +44855,64 @@
       </c>
       <c r="AE443" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4024.7</v>
       </c>
       <c r="AF443" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG443" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>261.60550000000001</v>
       </c>
       <c r="AH443" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI443" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>3763.0944999999997</v>
       </c>
       <c r="AJ443" s="91">
         <v>0.18</v>
       </c>
       <c r="AK443" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>677.35700999999995</v>
       </c>
       <c r="AL443" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4440.4515099999999</v>
       </c>
       <c r="AP443" s="7"/>
     </row>
     <row r="444" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A444" s="94"/>
-      <c r="B444" s="76"/>
-      <c r="C444" s="94"/>
-      <c r="D444" s="102"/>
-      <c r="E444" s="94"/>
-      <c r="F444" s="94"/>
-      <c r="G444" s="94"/>
-      <c r="H444" s="94"/>
-      <c r="I444" s="94"/>
+      <c r="A444" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B444" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C444" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D444" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E444" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F444" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G444" s="94" t="s">
+        <v>439</v>
+      </c>
+      <c r="H444" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I444" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J444" s="52"/>
       <c r="K444" s="52"/>
       <c r="L444" s="52"/>
@@ -44523,14 +44923,16 @@
       </c>
       <c r="O444" s="52"/>
       <c r="P444" s="52"/>
-      <c r="Q444" s="52"/>
+      <c r="Q444" s="52">
+        <v>10</v>
+      </c>
       <c r="R444" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S444" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB444" s="88">
         <v>39.270000000000003</v>
@@ -44543,14 +44945,14 @@
       </c>
       <c r="AE444" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF444" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG444" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH444" s="49">
         <f t="shared" si="127"/>
@@ -44558,31 +44960,49 @@
       </c>
       <c r="AI444" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ444" s="91">
         <v>0.18</v>
       </c>
       <c r="AK444" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL444" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP444" s="7"/>
     </row>
     <row r="445" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A445" s="94"/>
-      <c r="B445" s="76"/>
-      <c r="C445" s="94"/>
-      <c r="D445" s="102"/>
-      <c r="E445" s="94"/>
-      <c r="F445" s="94"/>
-      <c r="G445" s="94"/>
-      <c r="H445" s="94"/>
-      <c r="I445" s="94"/>
+      <c r="A445" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B445" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C445" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D445" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E445" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F445" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G445" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="H445" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I445" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J445" s="52"/>
       <c r="K445" s="52"/>
       <c r="L445" s="52"/>
@@ -44593,14 +45013,16 @@
       </c>
       <c r="O445" s="52"/>
       <c r="P445" s="52"/>
-      <c r="Q445" s="52"/>
+      <c r="Q445" s="52">
+        <v>10</v>
+      </c>
       <c r="R445" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S445" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB445" s="88">
         <v>39.270000000000003</v>
@@ -44613,14 +45035,14 @@
       </c>
       <c r="AE445" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF445" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG445" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH445" s="49">
         <f t="shared" si="127"/>
@@ -44628,49 +45050,77 @@
       </c>
       <c r="AI445" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ445" s="91">
         <v>0.18</v>
       </c>
       <c r="AK445" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL445" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP445" s="7"/>
     </row>
     <row r="446" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A446" s="94"/>
-      <c r="B446" s="76"/>
-      <c r="C446" s="94"/>
-      <c r="D446" s="102"/>
-      <c r="E446" s="94"/>
-      <c r="F446" s="94"/>
-      <c r="G446" s="94"/>
-      <c r="H446" s="94"/>
-      <c r="I446" s="94"/>
-      <c r="J446" s="52"/>
-      <c r="K446" s="52"/>
+      <c r="A446" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B446" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C446" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D446" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E446" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F446" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G446" s="94" t="s">
+        <v>440</v>
+      </c>
+      <c r="H446" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I446" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J446" s="52">
+        <v>40</v>
+      </c>
+      <c r="K446" s="52">
+        <v>23</v>
+      </c>
       <c r="L446" s="52"/>
       <c r="M446" s="52"/>
       <c r="N446" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="O446" s="52"/>
-      <c r="P446" s="52"/>
-      <c r="Q446" s="52"/>
+        <v>23</v>
+      </c>
+      <c r="O446" s="52">
+        <v>40</v>
+      </c>
+      <c r="P446" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q446" s="52">
+        <v>40</v>
+      </c>
       <c r="R446" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S446" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="AB446" s="88">
         <v>39.270000000000003</v>
@@ -44683,46 +45133,64 @@
       </c>
       <c r="AE446" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>16070.557500000001</v>
       </c>
       <c r="AF446" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG446" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1044.5862375000002</v>
       </c>
       <c r="AH446" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI446" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>15025.971262500001</v>
       </c>
       <c r="AJ446" s="91">
         <v>0.18</v>
       </c>
       <c r="AK446" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2704.6748272499999</v>
       </c>
       <c r="AL446" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>17730.64608975</v>
       </c>
       <c r="AP446" s="7"/>
     </row>
     <row r="447" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A447" s="94"/>
-      <c r="B447" s="76"/>
-      <c r="C447" s="94"/>
-      <c r="D447" s="102"/>
-      <c r="E447" s="94"/>
-      <c r="F447" s="94"/>
-      <c r="G447" s="94"/>
-      <c r="H447" s="94"/>
-      <c r="I447" s="94"/>
+      <c r="A447" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B447" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C447" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D447" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E447" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F447" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G447" s="94" t="s">
+        <v>441</v>
+      </c>
+      <c r="H447" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I447" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J447" s="52"/>
       <c r="K447" s="52"/>
       <c r="L447" s="52"/>
@@ -44733,14 +45201,16 @@
       </c>
       <c r="O447" s="52"/>
       <c r="P447" s="52"/>
-      <c r="Q447" s="52"/>
+      <c r="Q447" s="52">
+        <v>40</v>
+      </c>
       <c r="R447" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S447" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB447" s="88">
         <v>39.270000000000003</v>
@@ -44753,14 +45223,14 @@
       </c>
       <c r="AE447" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF447" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG447" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH447" s="49">
         <f t="shared" si="127"/>
@@ -44768,49 +45238,79 @@
       </c>
       <c r="AI447" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ447" s="91">
         <v>0.18</v>
       </c>
       <c r="AK447" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL447" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP447" s="7"/>
     </row>
     <row r="448" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A448" s="94"/>
-      <c r="B448" s="76"/>
-      <c r="C448" s="94"/>
-      <c r="D448" s="102"/>
-      <c r="E448" s="94"/>
-      <c r="F448" s="94"/>
-      <c r="G448" s="94"/>
-      <c r="H448" s="94"/>
-      <c r="I448" s="94"/>
-      <c r="J448" s="52"/>
-      <c r="K448" s="52"/>
-      <c r="L448" s="52"/>
+      <c r="A448" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B448" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C448" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D448" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E448" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F448" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G448" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="H448" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I448" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J448" s="52">
+        <v>20</v>
+      </c>
+      <c r="K448" s="52">
+        <v>20</v>
+      </c>
+      <c r="L448" s="52">
+        <v>20</v>
+      </c>
       <c r="M448" s="52"/>
       <c r="N448" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="O448" s="52"/>
-      <c r="P448" s="52"/>
-      <c r="Q448" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O448" s="52">
+        <v>15</v>
+      </c>
+      <c r="P448" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q448" s="52">
+        <v>15</v>
+      </c>
       <c r="R448" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S448" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB448" s="88">
         <v>39.270000000000003</v>
@@ -44823,64 +45323,94 @@
       </c>
       <c r="AE448" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>10147.9</v>
       </c>
       <c r="AF448" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG448" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>659.61350000000004</v>
       </c>
       <c r="AH448" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI448" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>9488.2865000000002</v>
       </c>
       <c r="AJ448" s="91">
         <v>0.18</v>
       </c>
       <c r="AK448" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>1707.89157</v>
       </c>
       <c r="AL448" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>11196.17807</v>
       </c>
       <c r="AP448" s="7"/>
     </row>
     <row r="449" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A449" s="94"/>
-      <c r="B449" s="76"/>
-      <c r="C449" s="94"/>
-      <c r="D449" s="102"/>
-      <c r="E449" s="94"/>
-      <c r="F449" s="94"/>
-      <c r="G449" s="94"/>
-      <c r="H449" s="94"/>
-      <c r="I449" s="94"/>
-      <c r="J449" s="52"/>
-      <c r="K449" s="52"/>
-      <c r="L449" s="52"/>
+      <c r="A449" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B449" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C449" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D449" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E449" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F449" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G449" s="94" t="s">
+        <v>442</v>
+      </c>
+      <c r="H449" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I449" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J449" s="52">
+        <v>15</v>
+      </c>
+      <c r="K449" s="52">
+        <v>10</v>
+      </c>
+      <c r="L449" s="52">
+        <v>10</v>
+      </c>
       <c r="M449" s="52"/>
       <c r="N449" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="O449" s="52"/>
-      <c r="P449" s="52"/>
-      <c r="Q449" s="52"/>
+        <v>20</v>
+      </c>
+      <c r="O449" s="52">
+        <v>15</v>
+      </c>
+      <c r="P449" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q449" s="52">
+        <v>15</v>
+      </c>
       <c r="R449" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S449" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB449" s="88">
         <v>39.270000000000003</v>
@@ -44893,46 +45423,64 @@
       </c>
       <c r="AE449" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>7086.3</v>
       </c>
       <c r="AF449" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG449" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>460.60950000000003</v>
       </c>
       <c r="AH449" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>20.616750000000003</v>
       </c>
       <c r="AI449" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>6625.6905000000006</v>
       </c>
       <c r="AJ449" s="91">
         <v>0.18</v>
       </c>
       <c r="AK449" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>1192.62429</v>
       </c>
       <c r="AL449" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>7818.3147900000004</v>
       </c>
       <c r="AP449" s="7"/>
     </row>
     <row r="450" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A450" s="94"/>
-      <c r="B450" s="76"/>
-      <c r="C450" s="94"/>
-      <c r="D450" s="102"/>
-      <c r="E450" s="94"/>
-      <c r="F450" s="94"/>
-      <c r="G450" s="94"/>
-      <c r="H450" s="94"/>
-      <c r="I450" s="94"/>
+      <c r="A450" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B450" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C450" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D450" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E450" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F450" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G450" s="94" t="s">
+        <v>270</v>
+      </c>
+      <c r="H450" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I450" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J450" s="52"/>
       <c r="K450" s="52"/>
       <c r="L450" s="52"/>
@@ -44941,16 +45489,18 @@
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="O450" s="52"/>
+      <c r="O450" s="52">
+        <v>10</v>
+      </c>
       <c r="P450" s="52"/>
       <c r="Q450" s="52"/>
       <c r="R450" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S450" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB450" s="88">
         <v>39.270000000000003</v>
@@ -44963,14 +45513,14 @@
       </c>
       <c r="AE450" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF450" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG450" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH450" s="49">
         <f t="shared" si="127"/>
@@ -44978,32 +45528,52 @@
       </c>
       <c r="AI450" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ450" s="91">
         <v>0.18</v>
       </c>
       <c r="AK450" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL450" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP450" s="7"/>
     </row>
     <row r="451" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A451" s="94"/>
-      <c r="B451" s="76"/>
-      <c r="C451" s="94"/>
-      <c r="D451" s="102"/>
-      <c r="E451" s="94"/>
-      <c r="F451" s="94"/>
-      <c r="G451" s="94"/>
-      <c r="H451" s="94"/>
-      <c r="I451" s="94"/>
-      <c r="J451" s="52"/>
+      <c r="A451" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B451" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C451" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D451" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E451" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F451" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G451" s="94" t="s">
+        <v>443</v>
+      </c>
+      <c r="H451" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I451" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J451" s="52">
+        <v>80</v>
+      </c>
       <c r="K451" s="52"/>
       <c r="L451" s="52"/>
       <c r="M451" s="52"/>
@@ -45011,16 +45581,22 @@
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="O451" s="52"/>
-      <c r="P451" s="52"/>
-      <c r="Q451" s="52"/>
+      <c r="O451" s="52">
+        <v>120</v>
+      </c>
+      <c r="P451" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q451" s="52">
+        <v>160</v>
+      </c>
       <c r="R451" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="S451" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AB451" s="88">
         <v>39.270000000000003</v>
@@ -45033,64 +45609,92 @@
       </c>
       <c r="AE451" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>32197.599999999999</v>
       </c>
       <c r="AF451" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG451" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>2092.8440000000001</v>
       </c>
       <c r="AH451" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI451" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>30104.755999999998</v>
       </c>
       <c r="AJ451" s="91">
         <v>0.18</v>
       </c>
       <c r="AK451" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>5418.8560799999996</v>
       </c>
       <c r="AL451" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>35523.612079999999</v>
       </c>
       <c r="AP451" s="7"/>
     </row>
     <row r="452" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A452" s="94"/>
-      <c r="B452" s="76"/>
-      <c r="C452" s="94"/>
-      <c r="D452" s="102"/>
-      <c r="E452" s="94"/>
-      <c r="F452" s="94"/>
-      <c r="G452" s="94"/>
-      <c r="H452" s="94"/>
-      <c r="I452" s="94"/>
+      <c r="A452" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B452" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C452" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D452" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E452" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F452" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G452" s="94" t="s">
+        <v>444</v>
+      </c>
+      <c r="H452" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I452" s="94" t="s">
+        <v>448</v>
+      </c>
       <c r="J452" s="52"/>
-      <c r="K452" s="52"/>
-      <c r="L452" s="52"/>
+      <c r="K452" s="52">
+        <v>20</v>
+      </c>
+      <c r="L452" s="52">
+        <v>80</v>
+      </c>
       <c r="M452" s="52"/>
       <c r="N452" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="O452" s="52"/>
-      <c r="P452" s="52"/>
-      <c r="Q452" s="52"/>
+        <v>100</v>
+      </c>
+      <c r="O452" s="52">
+        <v>20</v>
+      </c>
+      <c r="P452" s="52">
+        <v>80</v>
+      </c>
+      <c r="Q452" s="52">
+        <v>80</v>
+      </c>
       <c r="R452" s="104">
         <f t="shared" ref="R452:R515" si="131">SUM(O452:Q452)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="S452" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB452" s="88">
         <v>39.270000000000003</v>
@@ -45103,14 +45707,14 @@
       </c>
       <c r="AE452" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>25585.45</v>
       </c>
       <c r="AF452" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG452" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1663.0542500000001</v>
       </c>
       <c r="AH452" s="49">
         <f t="shared" si="127"/>
@@ -45118,31 +45722,49 @@
       </c>
       <c r="AI452" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>23922.39575</v>
       </c>
       <c r="AJ452" s="91">
         <v>0.18</v>
       </c>
       <c r="AK452" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>4306.0312349999995</v>
       </c>
       <c r="AL452" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>28228.426984999998</v>
       </c>
       <c r="AP452" s="7"/>
     </row>
     <row r="453" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A453" s="94"/>
-      <c r="B453" s="76"/>
-      <c r="C453" s="94"/>
-      <c r="D453" s="102"/>
-      <c r="E453" s="94"/>
-      <c r="F453" s="94"/>
-      <c r="G453" s="94"/>
-      <c r="H453" s="94"/>
-      <c r="I453" s="94"/>
+      <c r="A453" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B453" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C453" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D453" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E453" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F453" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G453" s="94" t="s">
+        <v>445</v>
+      </c>
+      <c r="H453" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I453" s="94" t="s">
+        <v>449</v>
+      </c>
       <c r="J453" s="52"/>
       <c r="K453" s="52"/>
       <c r="L453" s="52"/>
@@ -45151,16 +45773,18 @@
         <f t="shared" ref="N453:N516" si="132">K453+L453+M453</f>
         <v>0</v>
       </c>
-      <c r="O453" s="52"/>
+      <c r="O453" s="52">
+        <v>200</v>
+      </c>
       <c r="P453" s="52"/>
       <c r="Q453" s="52"/>
       <c r="R453" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S453" s="86">
         <f t="shared" ref="S453:S516" si="133">R453+N453+J453</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB453" s="88">
         <v>39.270000000000003</v>
@@ -45173,14 +45797,14 @@
       </c>
       <c r="AE453" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>14528</v>
       </c>
       <c r="AF453" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG453" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>944.32</v>
       </c>
       <c r="AH453" s="49">
         <f t="shared" si="127"/>
@@ -45188,49 +45812,79 @@
       </c>
       <c r="AI453" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>13583.68</v>
       </c>
       <c r="AJ453" s="91">
         <v>0.18</v>
       </c>
       <c r="AK453" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2445.0623999999998</v>
       </c>
       <c r="AL453" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>16028.742399999999</v>
       </c>
       <c r="AP453" s="7"/>
     </row>
     <row r="454" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A454" s="94"/>
-      <c r="B454" s="76"/>
-      <c r="C454" s="94"/>
-      <c r="D454" s="102"/>
-      <c r="E454" s="94"/>
-      <c r="F454" s="94"/>
-      <c r="G454" s="94"/>
-      <c r="H454" s="94"/>
-      <c r="I454" s="94"/>
-      <c r="J454" s="52"/>
-      <c r="K454" s="52"/>
-      <c r="L454" s="52"/>
+      <c r="A454" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B454" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C454" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D454" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E454" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F454" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G454" s="94" t="s">
+        <v>446</v>
+      </c>
+      <c r="H454" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I454" s="94" t="s">
+        <v>450</v>
+      </c>
+      <c r="J454" s="52">
+        <v>160</v>
+      </c>
+      <c r="K454" s="52">
+        <v>120</v>
+      </c>
+      <c r="L454" s="52">
+        <v>120</v>
+      </c>
       <c r="M454" s="52"/>
       <c r="N454" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O454" s="52"/>
-      <c r="P454" s="52"/>
-      <c r="Q454" s="52"/>
+        <v>240</v>
+      </c>
+      <c r="O454" s="52">
+        <v>120</v>
+      </c>
+      <c r="P454" s="52">
+        <v>120</v>
+      </c>
+      <c r="Q454" s="52">
+        <v>200</v>
+      </c>
       <c r="R454" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="S454" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="AB454" s="88">
         <v>39.270000000000003</v>
@@ -45243,47 +45897,67 @@
       </c>
       <c r="AE454" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>79891.8</v>
       </c>
       <c r="AF454" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG454" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>5192.9670000000006</v>
       </c>
       <c r="AH454" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>219.91200000000003</v>
       </c>
       <c r="AI454" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>74698.832999999999</v>
       </c>
       <c r="AJ454" s="91">
         <v>0.18</v>
       </c>
       <c r="AK454" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>13445.789939999999</v>
       </c>
       <c r="AL454" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>88144.622940000001</v>
       </c>
       <c r="AP454" s="7"/>
     </row>
     <row r="455" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A455" s="94"/>
-      <c r="B455" s="76"/>
-      <c r="C455" s="94"/>
-      <c r="D455" s="102"/>
-      <c r="E455" s="94"/>
-      <c r="F455" s="94"/>
-      <c r="G455" s="94"/>
-      <c r="H455" s="94"/>
-      <c r="I455" s="94"/>
-      <c r="J455" s="52"/>
+      <c r="A455" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B455" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C455" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D455" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E455" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F455" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G455" s="94" t="s">
+        <v>447</v>
+      </c>
+      <c r="H455" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I455" s="94" t="s">
+        <v>245</v>
+      </c>
+      <c r="J455" s="52">
+        <v>80</v>
+      </c>
       <c r="K455" s="52"/>
       <c r="L455" s="52"/>
       <c r="M455" s="52"/>
@@ -45291,16 +45965,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O455" s="52"/>
-      <c r="P455" s="52"/>
-      <c r="Q455" s="52"/>
+      <c r="O455" s="52">
+        <v>80</v>
+      </c>
+      <c r="P455" s="52">
+        <v>80</v>
+      </c>
+      <c r="Q455" s="52">
+        <v>80</v>
+      </c>
       <c r="R455" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S455" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AB455" s="88">
         <v>39.270000000000003</v>
@@ -45313,46 +45993,64 @@
       </c>
       <c r="AE455" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>26386.400000000001</v>
       </c>
       <c r="AF455" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG455" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1715.1160000000002</v>
       </c>
       <c r="AH455" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI455" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>24671.284</v>
       </c>
       <c r="AJ455" s="91">
         <v>0.18</v>
       </c>
       <c r="AK455" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>4440.8311199999998</v>
       </c>
       <c r="AL455" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>29112.115119999999</v>
       </c>
       <c r="AP455" s="7"/>
     </row>
     <row r="456" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A456" s="94"/>
-      <c r="B456" s="76"/>
-      <c r="C456" s="94"/>
-      <c r="D456" s="102"/>
-      <c r="E456" s="94"/>
-      <c r="F456" s="94"/>
-      <c r="G456" s="94"/>
-      <c r="H456" s="94"/>
-      <c r="I456" s="94"/>
+      <c r="A456" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B456" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C456" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D456" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E456" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F456" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G456" s="94" t="s">
+        <v>412</v>
+      </c>
+      <c r="H456" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I456" s="94" t="s">
+        <v>451</v>
+      </c>
       <c r="J456" s="52"/>
       <c r="K456" s="52"/>
       <c r="L456" s="52"/>
@@ -45361,16 +46059,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O456" s="52"/>
-      <c r="P456" s="52"/>
-      <c r="Q456" s="52"/>
+      <c r="O456" s="52">
+        <v>40</v>
+      </c>
+      <c r="P456" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q456" s="52">
+        <v>80</v>
+      </c>
       <c r="R456" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="S456" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB456" s="88">
         <v>39.270000000000003</v>
@@ -45383,14 +46087,14 @@
       </c>
       <c r="AE456" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>11622.4</v>
       </c>
       <c r="AF456" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG456" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>755.45600000000002</v>
       </c>
       <c r="AH456" s="49">
         <f t="shared" si="127"/>
@@ -45398,49 +46102,73 @@
       </c>
       <c r="AI456" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>10866.944</v>
       </c>
       <c r="AJ456" s="91">
         <v>0.18</v>
       </c>
       <c r="AK456" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>1956.0499199999999</v>
       </c>
       <c r="AL456" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12822.993919999999</v>
       </c>
       <c r="AP456" s="7"/>
     </row>
     <row r="457" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A457" s="94"/>
-      <c r="B457" s="76"/>
-      <c r="C457" s="94"/>
-      <c r="D457" s="102"/>
-      <c r="E457" s="94"/>
-      <c r="F457" s="94"/>
-      <c r="G457" s="94"/>
-      <c r="H457" s="94"/>
-      <c r="I457" s="94"/>
+      <c r="A457" s="85">
+        <v>46216</v>
+      </c>
+      <c r="B457" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C457" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D457" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E457" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F457" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G457" s="94" t="s">
+        <v>453</v>
+      </c>
+      <c r="H457" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I457" s="94" t="s">
+        <v>452</v>
+      </c>
       <c r="J457" s="52"/>
       <c r="K457" s="52"/>
-      <c r="L457" s="52"/>
+      <c r="L457" s="52">
+        <v>80</v>
+      </c>
       <c r="M457" s="52"/>
       <c r="N457" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O457" s="52"/>
+        <v>80</v>
+      </c>
+      <c r="O457" s="52">
+        <v>40</v>
+      </c>
       <c r="P457" s="52"/>
-      <c r="Q457" s="52"/>
+      <c r="Q457" s="52">
+        <v>40</v>
+      </c>
       <c r="R457" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S457" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB457" s="88">
         <v>39.270000000000003</v>
@@ -45453,14 +46181,14 @@
       </c>
       <c r="AE457" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>15819.4</v>
       </c>
       <c r="AF457" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG457" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1028.261</v>
       </c>
       <c r="AH457" s="49">
         <f t="shared" si="127"/>
@@ -45468,49 +46196,75 @@
       </c>
       <c r="AI457" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>14791.138999999999</v>
       </c>
       <c r="AJ457" s="91">
         <v>0.18</v>
       </c>
       <c r="AK457" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2662.4050199999997</v>
       </c>
       <c r="AL457" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>17453.544019999998</v>
       </c>
       <c r="AP457" s="7"/>
     </row>
     <row r="458" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A458" s="94"/>
-      <c r="B458" s="76"/>
-      <c r="C458" s="94"/>
-      <c r="D458" s="102"/>
-      <c r="E458" s="94"/>
-      <c r="F458" s="94"/>
-      <c r="G458" s="94"/>
-      <c r="H458" s="94"/>
-      <c r="I458" s="94"/>
+      <c r="A458" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B458" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C458" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D458" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E458" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F458" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G458" s="94" t="s">
+        <v>455</v>
+      </c>
+      <c r="H458" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I458" s="94" t="s">
+        <v>454</v>
+      </c>
       <c r="J458" s="52"/>
-      <c r="K458" s="52"/>
+      <c r="K458" s="52">
+        <v>120</v>
+      </c>
       <c r="L458" s="52"/>
       <c r="M458" s="52"/>
       <c r="N458" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O458" s="52"/>
-      <c r="P458" s="52"/>
-      <c r="Q458" s="52"/>
+        <v>120</v>
+      </c>
+      <c r="O458" s="52">
+        <v>360</v>
+      </c>
+      <c r="P458" s="52">
+        <v>600</v>
+      </c>
+      <c r="Q458" s="52">
+        <v>320</v>
+      </c>
       <c r="R458" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="S458" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="AB458" s="88">
         <v>39.270000000000003</v>
@@ -45523,14 +46277,14 @@
       </c>
       <c r="AE458" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>107991.5</v>
       </c>
       <c r="AF458" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG458" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>7019.4475000000002</v>
       </c>
       <c r="AH458" s="49">
         <f t="shared" si="127"/>
@@ -45538,38 +46292,58 @@
       </c>
       <c r="AI458" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>100972.05250000001</v>
       </c>
       <c r="AJ458" s="91">
         <v>0.18</v>
       </c>
       <c r="AK458" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>18174.969450000001</v>
       </c>
       <c r="AL458" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>119147.02195000001</v>
       </c>
       <c r="AP458" s="7"/>
     </row>
     <row r="459" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A459" s="94"/>
-      <c r="B459" s="76"/>
-      <c r="C459" s="94"/>
-      <c r="D459" s="102"/>
-      <c r="E459" s="94"/>
+      <c r="A459" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B459" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C459" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D459" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E459" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F459" s="94"/>
-      <c r="G459" s="94"/>
-      <c r="H459" s="94"/>
-      <c r="I459" s="94"/>
-      <c r="J459" s="52"/>
-      <c r="K459" s="52"/>
+      <c r="G459" s="94" t="s">
+        <v>456</v>
+      </c>
+      <c r="H459" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I459" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J459" s="52">
+        <v>12</v>
+      </c>
+      <c r="K459" s="52">
+        <v>12</v>
+      </c>
       <c r="L459" s="52"/>
       <c r="M459" s="52"/>
       <c r="N459" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O459" s="52"/>
       <c r="P459" s="52"/>
@@ -45580,7 +46354,7 @@
       </c>
       <c r="S459" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB459" s="88">
         <v>39.270000000000003</v>
@@ -45593,47 +46367,65 @@
       </c>
       <c r="AE459" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2844.15</v>
       </c>
       <c r="AF459" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG459" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>184.86975000000001</v>
       </c>
       <c r="AH459" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI459" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2659.2802500000003</v>
       </c>
       <c r="AJ459" s="91">
         <v>0.18</v>
       </c>
       <c r="AK459" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>478.67044500000003</v>
       </c>
       <c r="AL459" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3137.9506950000005</v>
       </c>
       <c r="AP459" s="7"/>
     </row>
     <row r="460" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A460" s="94"/>
-      <c r="B460" s="76"/>
-      <c r="C460" s="94"/>
-      <c r="D460" s="102"/>
-      <c r="E460" s="94"/>
+      <c r="A460" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B460" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C460" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D460" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E460" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F460" s="94"/>
-      <c r="G460" s="94"/>
-      <c r="H460" s="94"/>
-      <c r="I460" s="94"/>
-      <c r="J460" s="52"/>
+      <c r="G460" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="H460" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I460" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J460" s="52">
+        <v>6</v>
+      </c>
       <c r="K460" s="52"/>
       <c r="L460" s="52"/>
       <c r="M460" s="52"/>
@@ -45641,16 +46433,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O460" s="52"/>
-      <c r="P460" s="52"/>
-      <c r="Q460" s="52"/>
+      <c r="O460" s="52">
+        <v>6</v>
+      </c>
+      <c r="P460" s="52">
+        <v>6</v>
+      </c>
+      <c r="Q460" s="52">
+        <v>12</v>
+      </c>
       <c r="R460" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S460" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB460" s="88">
         <v>39.270000000000003</v>
@@ -45663,47 +46461,65 @@
       </c>
       <c r="AE460" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2414.8199999999997</v>
       </c>
       <c r="AF460" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG460" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>156.96329999999998</v>
       </c>
       <c r="AH460" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>8.2467000000000006</v>
       </c>
       <c r="AI460" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2257.8566999999998</v>
       </c>
       <c r="AJ460" s="91">
         <v>0.18</v>
       </c>
       <c r="AK460" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>406.41420599999998</v>
       </c>
       <c r="AL460" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2664.2709059999997</v>
       </c>
       <c r="AP460" s="7"/>
     </row>
     <row r="461" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A461" s="94"/>
-      <c r="B461" s="76"/>
-      <c r="C461" s="94"/>
-      <c r="D461" s="102"/>
-      <c r="E461" s="94"/>
+      <c r="A461" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B461" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C461" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D461" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E461" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F461" s="94"/>
-      <c r="G461" s="94"/>
-      <c r="H461" s="94"/>
-      <c r="I461" s="94"/>
-      <c r="J461" s="52"/>
+      <c r="G461" s="94" t="s">
+        <v>457</v>
+      </c>
+      <c r="H461" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I461" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J461" s="52">
+        <v>24</v>
+      </c>
       <c r="K461" s="52"/>
       <c r="L461" s="52"/>
       <c r="M461" s="52"/>
@@ -45720,7 +46536,7 @@
       </c>
       <c r="S461" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB461" s="88">
         <v>39.270000000000003</v>
@@ -45733,47 +46549,65 @@
       </c>
       <c r="AE461" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2685.84</v>
       </c>
       <c r="AF461" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG461" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>174.57960000000003</v>
       </c>
       <c r="AH461" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>32.986800000000002</v>
       </c>
       <c r="AI461" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2511.2604000000001</v>
       </c>
       <c r="AJ461" s="91">
         <v>0.18</v>
       </c>
       <c r="AK461" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>452.02687200000003</v>
       </c>
       <c r="AL461" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2963.287272</v>
       </c>
       <c r="AP461" s="7"/>
     </row>
     <row r="462" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A462" s="94"/>
-      <c r="B462" s="76"/>
-      <c r="C462" s="94"/>
-      <c r="D462" s="102"/>
-      <c r="E462" s="94"/>
+      <c r="A462" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B462" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C462" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D462" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E462" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F462" s="94"/>
-      <c r="G462" s="94"/>
-      <c r="H462" s="94"/>
-      <c r="I462" s="94"/>
-      <c r="J462" s="52"/>
+      <c r="G462" s="94" t="s">
+        <v>458</v>
+      </c>
+      <c r="H462" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I462" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J462" s="52">
+        <v>24</v>
+      </c>
       <c r="K462" s="52"/>
       <c r="L462" s="52"/>
       <c r="M462" s="52"/>
@@ -45783,14 +46617,16 @@
       </c>
       <c r="O462" s="52"/>
       <c r="P462" s="52"/>
-      <c r="Q462" s="52"/>
+      <c r="Q462" s="52">
+        <v>24</v>
+      </c>
       <c r="R462" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S462" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB462" s="88">
         <v>39.270000000000003</v>
@@ -45803,47 +46639,65 @@
       </c>
       <c r="AE462" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4429.2000000000007</v>
       </c>
       <c r="AF462" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG462" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>287.89800000000008</v>
       </c>
       <c r="AH462" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>32.986800000000002</v>
       </c>
       <c r="AI462" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4141.3020000000006</v>
       </c>
       <c r="AJ462" s="91">
         <v>0.18</v>
       </c>
       <c r="AK462" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>745.43436000000008</v>
       </c>
       <c r="AL462" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4886.7363600000008</v>
       </c>
       <c r="AP462" s="7"/>
     </row>
     <row r="463" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A463" s="94"/>
-      <c r="B463" s="76"/>
-      <c r="C463" s="94"/>
-      <c r="D463" s="102"/>
-      <c r="E463" s="94"/>
+      <c r="A463" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B463" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C463" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D463" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E463" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F463" s="94"/>
-      <c r="G463" s="94"/>
-      <c r="H463" s="94"/>
-      <c r="I463" s="94"/>
-      <c r="J463" s="52"/>
+      <c r="G463" s="94" t="s">
+        <v>459</v>
+      </c>
+      <c r="H463" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I463" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J463" s="52">
+        <v>24</v>
+      </c>
       <c r="K463" s="52"/>
       <c r="L463" s="52"/>
       <c r="M463" s="52"/>
@@ -45860,7 +46714,7 @@
       </c>
       <c r="S463" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB463" s="88">
         <v>39.270000000000003</v>
@@ -45873,47 +46727,65 @@
       </c>
       <c r="AE463" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2685.84</v>
       </c>
       <c r="AF463" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG463" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>174.57960000000003</v>
       </c>
       <c r="AH463" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>32.986800000000002</v>
       </c>
       <c r="AI463" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2511.2604000000001</v>
       </c>
       <c r="AJ463" s="91">
         <v>0.18</v>
       </c>
       <c r="AK463" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>452.02687200000003</v>
       </c>
       <c r="AL463" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2963.287272</v>
       </c>
       <c r="AP463" s="7"/>
     </row>
     <row r="464" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A464" s="94"/>
-      <c r="B464" s="76"/>
-      <c r="C464" s="94"/>
-      <c r="D464" s="102"/>
-      <c r="E464" s="94"/>
+      <c r="A464" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B464" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C464" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D464" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E464" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F464" s="94"/>
-      <c r="G464" s="94"/>
-      <c r="H464" s="94"/>
-      <c r="I464" s="94"/>
-      <c r="J464" s="52"/>
+      <c r="G464" s="94" t="s">
+        <v>460</v>
+      </c>
+      <c r="H464" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I464" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J464" s="52">
+        <v>40</v>
+      </c>
       <c r="K464" s="52"/>
       <c r="L464" s="52"/>
       <c r="M464" s="52"/>
@@ -45921,16 +46793,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O464" s="52"/>
-      <c r="P464" s="52"/>
-      <c r="Q464" s="52"/>
+      <c r="O464" s="52">
+        <v>3</v>
+      </c>
+      <c r="P464" s="52">
+        <v>3</v>
+      </c>
+      <c r="Q464" s="52">
+        <v>3</v>
+      </c>
       <c r="R464" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S464" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AB464" s="88">
         <v>39.270000000000003</v>
@@ -45943,46 +46821,62 @@
       </c>
       <c r="AE464" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>5130.16</v>
       </c>
       <c r="AF464" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG464" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>333.46039999999999</v>
       </c>
       <c r="AH464" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI464" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4796.6995999999999</v>
       </c>
       <c r="AJ464" s="91">
         <v>0.18</v>
       </c>
       <c r="AK464" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>863.4059279999999</v>
       </c>
       <c r="AL464" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>5660.105528</v>
       </c>
       <c r="AP464" s="7"/>
     </row>
     <row r="465" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A465" s="94"/>
-      <c r="B465" s="76"/>
-      <c r="C465" s="94"/>
-      <c r="D465" s="102"/>
-      <c r="E465" s="94"/>
+      <c r="A465" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B465" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C465" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D465" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E465" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F465" s="94"/>
-      <c r="G465" s="94"/>
-      <c r="H465" s="94"/>
-      <c r="I465" s="94"/>
+      <c r="G465" s="94" t="s">
+        <v>184</v>
+      </c>
+      <c r="H465" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I465" s="94" t="s">
+        <v>464</v>
+      </c>
       <c r="J465" s="52"/>
       <c r="K465" s="52"/>
       <c r="L465" s="52"/>
@@ -45991,16 +46885,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O465" s="52"/>
-      <c r="P465" s="52"/>
-      <c r="Q465" s="52"/>
+      <c r="O465" s="52">
+        <v>6</v>
+      </c>
+      <c r="P465" s="52">
+        <v>6</v>
+      </c>
+      <c r="Q465" s="52">
+        <v>6</v>
+      </c>
       <c r="R465" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S465" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB465" s="88">
         <v>39.270000000000003</v>
@@ -46013,14 +46913,14 @@
       </c>
       <c r="AE465" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1307.52</v>
       </c>
       <c r="AF465" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG465" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>84.988799999999998</v>
       </c>
       <c r="AH465" s="49">
         <f t="shared" si="127"/>
@@ -46028,31 +46928,47 @@
       </c>
       <c r="AI465" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1222.5311999999999</v>
       </c>
       <c r="AJ465" s="91">
         <v>0.18</v>
       </c>
       <c r="AK465" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>220.05561599999999</v>
       </c>
       <c r="AL465" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1442.586816</v>
       </c>
       <c r="AP465" s="7"/>
     </row>
     <row r="466" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A466" s="94"/>
-      <c r="B466" s="76"/>
-      <c r="C466" s="94"/>
-      <c r="D466" s="102"/>
-      <c r="E466" s="94"/>
+      <c r="A466" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B466" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C466" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D466" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E466" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F466" s="94"/>
-      <c r="G466" s="94"/>
-      <c r="H466" s="94"/>
-      <c r="I466" s="94"/>
+      <c r="G466" s="94" t="s">
+        <v>461</v>
+      </c>
+      <c r="H466" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I466" s="94" t="s">
+        <v>464</v>
+      </c>
       <c r="J466" s="52"/>
       <c r="K466" s="52"/>
       <c r="L466" s="52"/>
@@ -46061,16 +46977,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O466" s="52"/>
-      <c r="P466" s="52"/>
-      <c r="Q466" s="52"/>
+      <c r="O466" s="52">
+        <v>15</v>
+      </c>
+      <c r="P466" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q466" s="52">
+        <v>15</v>
+      </c>
       <c r="R466" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S466" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB466" s="88">
         <v>39.270000000000003</v>
@@ -46083,14 +47005,14 @@
       </c>
       <c r="AE466" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF466" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG466" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH466" s="49">
         <f t="shared" si="127"/>
@@ -46098,18 +47020,18 @@
       </c>
       <c r="AI466" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ466" s="91">
         <v>0.18</v>
       </c>
       <c r="AK466" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL466" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP466" s="7"/>
     </row>
@@ -46120,10 +47042,18 @@
       <c r="D467" s="102"/>
       <c r="E467" s="94"/>
       <c r="F467" s="94"/>
-      <c r="G467" s="94"/>
-      <c r="H467" s="94"/>
-      <c r="I467" s="94"/>
-      <c r="J467" s="52"/>
+      <c r="G467" s="94" t="s">
+        <v>462</v>
+      </c>
+      <c r="H467" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I467" s="94" t="s">
+        <v>464</v>
+      </c>
+      <c r="J467" s="52">
+        <v>12</v>
+      </c>
       <c r="K467" s="52"/>
       <c r="L467" s="52"/>
       <c r="M467" s="52"/>
@@ -46140,7 +47070,7 @@
       </c>
       <c r="S467" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB467" s="88">
         <v>39.270000000000003</v>
@@ -46153,33 +47083,33 @@
       </c>
       <c r="AE467" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF467" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG467" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>87.289800000000014</v>
       </c>
       <c r="AH467" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI467" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1255.6302000000001</v>
       </c>
       <c r="AJ467" s="91">
         <v>0.18</v>
       </c>
       <c r="AK467" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>226.01343600000001</v>
       </c>
       <c r="AL467" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1481.643636</v>
       </c>
       <c r="AP467" s="7"/>
     </row>
@@ -46190,16 +47120,26 @@
       <c r="D468" s="102"/>
       <c r="E468" s="94"/>
       <c r="F468" s="94"/>
-      <c r="G468" s="94"/>
-      <c r="H468" s="94"/>
-      <c r="I468" s="94"/>
-      <c r="J468" s="52"/>
-      <c r="K468" s="52"/>
+      <c r="G468" s="94" t="s">
+        <v>204</v>
+      </c>
+      <c r="H468" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I468" s="94" t="s">
+        <v>469</v>
+      </c>
+      <c r="J468" s="52">
+        <v>15</v>
+      </c>
+      <c r="K468" s="52">
+        <v>1</v>
+      </c>
       <c r="L468" s="52"/>
       <c r="M468" s="52"/>
       <c r="N468" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O468" s="52"/>
       <c r="P468" s="52"/>
@@ -46210,7 +47150,7 @@
       </c>
       <c r="S468" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB468" s="88">
         <v>39.270000000000003</v>
@@ -46223,33 +47163,33 @@
       </c>
       <c r="AE468" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1803.7525000000001</v>
       </c>
       <c r="AF468" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG468" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>117.24391250000001</v>
       </c>
       <c r="AH468" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>20.616750000000003</v>
       </c>
       <c r="AI468" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1686.5085875</v>
       </c>
       <c r="AJ468" s="91">
         <v>0.18</v>
       </c>
       <c r="AK468" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>303.57154574999998</v>
       </c>
       <c r="AL468" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1990.08013325</v>
       </c>
       <c r="AP468" s="7"/>
     </row>
@@ -46260,9 +47200,15 @@
       <c r="D469" s="102"/>
       <c r="E469" s="94"/>
       <c r="F469" s="94"/>
-      <c r="G469" s="94"/>
-      <c r="H469" s="94"/>
-      <c r="I469" s="94"/>
+      <c r="G469" s="94" t="s">
+        <v>465</v>
+      </c>
+      <c r="H469" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I469" s="94" t="s">
+        <v>469</v>
+      </c>
       <c r="J469" s="52"/>
       <c r="K469" s="52"/>
       <c r="L469" s="52"/>
@@ -46271,16 +47217,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O469" s="52"/>
-      <c r="P469" s="52"/>
-      <c r="Q469" s="52"/>
+      <c r="O469" s="52">
+        <v>4</v>
+      </c>
+      <c r="P469" s="52">
+        <v>4</v>
+      </c>
+      <c r="Q469" s="52">
+        <v>12</v>
+      </c>
       <c r="R469" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S469" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB469" s="88">
         <v>39.270000000000003</v>
@@ -46293,14 +47245,14 @@
       </c>
       <c r="AE469" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="AF469" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG469" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>94.432000000000002</v>
       </c>
       <c r="AH469" s="49">
         <f t="shared" si="127"/>
@@ -46308,18 +47260,18 @@
       </c>
       <c r="AI469" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1358.3679999999999</v>
       </c>
       <c r="AJ469" s="91">
         <v>0.18</v>
       </c>
       <c r="AK469" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>244.50623999999999</v>
       </c>
       <c r="AL469" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1602.8742399999999</v>
       </c>
       <c r="AP469" s="7"/>
     </row>
@@ -46330,10 +47282,18 @@
       <c r="D470" s="102"/>
       <c r="E470" s="94"/>
       <c r="F470" s="94"/>
-      <c r="G470" s="94"/>
-      <c r="H470" s="94"/>
-      <c r="I470" s="94"/>
-      <c r="J470" s="52"/>
+      <c r="G470" s="94" t="s">
+        <v>466</v>
+      </c>
+      <c r="H470" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I470" s="94" t="s">
+        <v>469</v>
+      </c>
+      <c r="J470" s="52">
+        <v>80</v>
+      </c>
       <c r="K470" s="52"/>
       <c r="L470" s="52"/>
       <c r="M470" s="52"/>
@@ -46343,14 +47303,16 @@
       </c>
       <c r="O470" s="52"/>
       <c r="P470" s="52"/>
-      <c r="Q470" s="52"/>
+      <c r="Q470" s="52">
+        <v>77</v>
+      </c>
       <c r="R470" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="S470" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="AB470" s="88">
         <v>39.270000000000003</v>
@@ -46363,33 +47325,33 @@
       </c>
       <c r="AE470" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>14546.08</v>
       </c>
       <c r="AF470" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG470" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>945.49520000000007</v>
       </c>
       <c r="AH470" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI470" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>13600.584800000001</v>
       </c>
       <c r="AJ470" s="91">
         <v>0.18</v>
       </c>
       <c r="AK470" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2448.1052639999998</v>
       </c>
       <c r="AL470" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>16048.690064</v>
       </c>
       <c r="AP470" s="7"/>
     </row>
@@ -46400,10 +47362,18 @@
       <c r="D471" s="102"/>
       <c r="E471" s="94"/>
       <c r="F471" s="94"/>
-      <c r="G471" s="94"/>
-      <c r="H471" s="94"/>
-      <c r="I471" s="94"/>
-      <c r="J471" s="52"/>
+      <c r="G471" s="94" t="s">
+        <v>203</v>
+      </c>
+      <c r="H471" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I471" s="94" t="s">
+        <v>469</v>
+      </c>
+      <c r="J471" s="52">
+        <v>39</v>
+      </c>
       <c r="K471" s="52"/>
       <c r="L471" s="52"/>
       <c r="M471" s="52"/>
@@ -46420,7 +47390,7 @@
       </c>
       <c r="S471" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AB471" s="88">
         <v>39.270000000000003</v>
@@ -46433,33 +47403,33 @@
       </c>
       <c r="AE471" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4364.49</v>
       </c>
       <c r="AF471" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG471" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>283.69184999999999</v>
       </c>
       <c r="AH471" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>53.603550000000013</v>
       </c>
       <c r="AI471" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4080.7981499999996</v>
       </c>
       <c r="AJ471" s="91">
         <v>0.18</v>
       </c>
       <c r="AK471" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>734.54366699999991</v>
       </c>
       <c r="AL471" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4815.3418169999995</v>
       </c>
       <c r="AP471" s="7"/>
     </row>
@@ -46470,27 +47440,39 @@
       <c r="D472" s="102"/>
       <c r="E472" s="94"/>
       <c r="F472" s="94"/>
-      <c r="G472" s="94"/>
-      <c r="H472" s="94"/>
-      <c r="I472" s="94"/>
-      <c r="J472" s="52"/>
-      <c r="K472" s="52"/>
+      <c r="G472" s="94" t="s">
+        <v>467</v>
+      </c>
+      <c r="H472" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I472" s="94" t="s">
+        <v>469</v>
+      </c>
+      <c r="J472" s="52">
+        <v>40</v>
+      </c>
+      <c r="K472" s="52">
+        <v>40</v>
+      </c>
       <c r="L472" s="52"/>
       <c r="M472" s="52"/>
       <c r="N472" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O472" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O472" s="52">
+        <v>40</v>
+      </c>
       <c r="P472" s="52"/>
       <c r="Q472" s="52"/>
       <c r="R472" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S472" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB472" s="88">
         <v>39.270000000000003</v>
@@ -46503,33 +47485,33 @@
       </c>
       <c r="AE472" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>12386.099999999999</v>
       </c>
       <c r="AF472" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG472" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>805.09649999999988</v>
       </c>
       <c r="AH472" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI472" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>11581.003499999999</v>
       </c>
       <c r="AJ472" s="91">
         <v>0.18</v>
       </c>
       <c r="AK472" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2084.5806299999999</v>
       </c>
       <c r="AL472" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>13665.584129999999</v>
       </c>
       <c r="AP472" s="7"/>
     </row>
@@ -46540,9 +47522,15 @@
       <c r="D473" s="102"/>
       <c r="E473" s="94"/>
       <c r="F473" s="94"/>
-      <c r="G473" s="94"/>
-      <c r="H473" s="94"/>
-      <c r="I473" s="94"/>
+      <c r="G473" s="94" t="s">
+        <v>468</v>
+      </c>
+      <c r="H473" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I473" s="94" t="s">
+        <v>469</v>
+      </c>
       <c r="J473" s="52"/>
       <c r="K473" s="52"/>
       <c r="L473" s="52"/>
@@ -46551,16 +47539,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O473" s="52"/>
-      <c r="P473" s="52"/>
-      <c r="Q473" s="52"/>
+      <c r="O473" s="52">
+        <v>13</v>
+      </c>
+      <c r="P473" s="52">
+        <v>12</v>
+      </c>
+      <c r="Q473" s="52">
+        <v>15</v>
+      </c>
       <c r="R473" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S473" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB473" s="88">
         <v>39.270000000000003</v>
@@ -46573,14 +47567,14 @@
       </c>
       <c r="AE473" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF473" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG473" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH473" s="49">
         <f t="shared" si="127"/>
@@ -46588,18 +47582,18 @@
       </c>
       <c r="AI473" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ473" s="91">
         <v>0.18</v>
       </c>
       <c r="AK473" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL473" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP473" s="7"/>
     </row>
@@ -46610,16 +47604,26 @@
       <c r="D474" s="102"/>
       <c r="E474" s="94"/>
       <c r="F474" s="94"/>
-      <c r="G474" s="94"/>
-      <c r="H474" s="94"/>
-      <c r="I474" s="94"/>
+      <c r="G474" s="94" t="s">
+        <v>423</v>
+      </c>
+      <c r="H474" s="94" t="s">
+        <v>470</v>
+      </c>
+      <c r="I474" s="94" t="s">
+        <v>423</v>
+      </c>
       <c r="J474" s="52"/>
-      <c r="K474" s="52"/>
-      <c r="L474" s="52"/>
+      <c r="K474" s="52">
+        <v>20</v>
+      </c>
+      <c r="L474" s="52">
+        <v>20</v>
+      </c>
       <c r="M474" s="52"/>
       <c r="N474" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O474" s="52"/>
       <c r="P474" s="52"/>
@@ -46630,7 +47634,7 @@
       </c>
       <c r="S474" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB474" s="88">
         <v>39.270000000000003</v>
@@ -46643,14 +47647,14 @@
       </c>
       <c r="AE474" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF474" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG474" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH474" s="49">
         <f t="shared" si="127"/>
@@ -46658,18 +47662,18 @@
       </c>
       <c r="AI474" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ474" s="91">
         <v>0.18</v>
       </c>
       <c r="AK474" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL474" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP474" s="7"/>
     </row>
@@ -46680,9 +47684,15 @@
       <c r="D475" s="102"/>
       <c r="E475" s="94"/>
       <c r="F475" s="94"/>
-      <c r="G475" s="94"/>
-      <c r="H475" s="94"/>
-      <c r="I475" s="94"/>
+      <c r="G475" s="94" t="s">
+        <v>297</v>
+      </c>
+      <c r="H475" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I475" s="94" t="s">
+        <v>298</v>
+      </c>
       <c r="J475" s="52"/>
       <c r="K475" s="52"/>
       <c r="L475" s="52"/>
@@ -46693,14 +47703,16 @@
       </c>
       <c r="O475" s="52"/>
       <c r="P475" s="52"/>
-      <c r="Q475" s="52"/>
+      <c r="Q475" s="52">
+        <v>20</v>
+      </c>
       <c r="R475" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S475" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB475" s="88">
         <v>39.270000000000003</v>
@@ -46713,14 +47725,14 @@
       </c>
       <c r="AE475" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="AF475" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG475" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>94.432000000000002</v>
       </c>
       <c r="AH475" s="49">
         <f t="shared" si="127"/>
@@ -46728,18 +47740,18 @@
       </c>
       <c r="AI475" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1358.3679999999999</v>
       </c>
       <c r="AJ475" s="91">
         <v>0.18</v>
       </c>
       <c r="AK475" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>244.50623999999999</v>
       </c>
       <c r="AL475" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1602.8742399999999</v>
       </c>
       <c r="AP475" s="7"/>
     </row>
@@ -46750,10 +47762,18 @@
       <c r="D476" s="102"/>
       <c r="E476" s="94"/>
       <c r="F476" s="94"/>
-      <c r="G476" s="94"/>
-      <c r="H476" s="94"/>
-      <c r="I476" s="94"/>
-      <c r="J476" s="52"/>
+      <c r="G476" s="94" t="s">
+        <v>471</v>
+      </c>
+      <c r="H476" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I476" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J476" s="52">
+        <v>40</v>
+      </c>
       <c r="K476" s="52"/>
       <c r="L476" s="52"/>
       <c r="M476" s="52"/>
@@ -46770,7 +47790,7 @@
       </c>
       <c r="S476" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB476" s="88">
         <v>39.270000000000003</v>
@@ -46783,33 +47803,33 @@
       </c>
       <c r="AE476" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF476" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG476" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH476" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI476" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ476" s="91">
         <v>0.18</v>
       </c>
       <c r="AK476" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL476" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP476" s="7"/>
     </row>
@@ -46820,10 +47840,18 @@
       <c r="D477" s="102"/>
       <c r="E477" s="94"/>
       <c r="F477" s="94"/>
-      <c r="G477" s="94"/>
-      <c r="H477" s="94"/>
-      <c r="I477" s="94"/>
-      <c r="J477" s="52"/>
+      <c r="G477" s="94" t="s">
+        <v>294</v>
+      </c>
+      <c r="H477" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I477" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J477" s="52">
+        <v>12</v>
+      </c>
       <c r="K477" s="52"/>
       <c r="L477" s="52"/>
       <c r="M477" s="52"/>
@@ -46840,7 +47868,7 @@
       </c>
       <c r="S477" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB477" s="88">
         <v>39.270000000000003</v>
@@ -46853,33 +47881,33 @@
       </c>
       <c r="AE477" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF477" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG477" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>87.289800000000014</v>
       </c>
       <c r="AH477" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI477" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1255.6302000000001</v>
       </c>
       <c r="AJ477" s="91">
         <v>0.18</v>
       </c>
       <c r="AK477" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>226.01343600000001</v>
       </c>
       <c r="AL477" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1481.643636</v>
       </c>
       <c r="AP477" s="7"/>
     </row>
@@ -46890,10 +47918,18 @@
       <c r="D478" s="102"/>
       <c r="E478" s="94"/>
       <c r="F478" s="94"/>
-      <c r="G478" s="94"/>
-      <c r="H478" s="94"/>
-      <c r="I478" s="94"/>
-      <c r="J478" s="52"/>
+      <c r="G478" s="94" t="s">
+        <v>194</v>
+      </c>
+      <c r="H478" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I478" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J478" s="52">
+        <v>5</v>
+      </c>
       <c r="K478" s="52"/>
       <c r="L478" s="52"/>
       <c r="M478" s="52"/>
@@ -46910,7 +47946,7 @@
       </c>
       <c r="S478" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB478" s="88">
         <v>39.270000000000003</v>
@@ -46923,33 +47959,33 @@
       </c>
       <c r="AE478" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>559.54999999999995</v>
       </c>
       <c r="AF478" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG478" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>36.370750000000001</v>
       </c>
       <c r="AH478" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>6.8722500000000011</v>
       </c>
       <c r="AI478" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>523.17924999999991</v>
       </c>
       <c r="AJ478" s="91">
         <v>0.18</v>
       </c>
       <c r="AK478" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>94.172264999999982</v>
       </c>
       <c r="AL478" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>617.35151499999984</v>
       </c>
       <c r="AP478" s="7"/>
     </row>
@@ -46960,10 +47996,18 @@
       <c r="D479" s="102"/>
       <c r="E479" s="94"/>
       <c r="F479" s="94"/>
-      <c r="G479" s="94"/>
-      <c r="H479" s="94"/>
-      <c r="I479" s="94"/>
-      <c r="J479" s="52"/>
+      <c r="G479" s="94" t="s">
+        <v>472</v>
+      </c>
+      <c r="H479" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I479" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J479" s="52">
+        <v>12</v>
+      </c>
       <c r="K479" s="52"/>
       <c r="L479" s="52"/>
       <c r="M479" s="52"/>
@@ -46980,7 +48024,7 @@
       </c>
       <c r="S479" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB479" s="88">
         <v>39.270000000000003</v>
@@ -46993,33 +48037,33 @@
       </c>
       <c r="AE479" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF479" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG479" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>87.289800000000014</v>
       </c>
       <c r="AH479" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI479" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1255.6302000000001</v>
       </c>
       <c r="AJ479" s="91">
         <v>0.18</v>
       </c>
       <c r="AK479" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>226.01343600000001</v>
       </c>
       <c r="AL479" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1481.643636</v>
       </c>
       <c r="AP479" s="7"/>
     </row>
@@ -47030,10 +48074,18 @@
       <c r="D480" s="102"/>
       <c r="E480" s="94"/>
       <c r="F480" s="94"/>
-      <c r="G480" s="94"/>
-      <c r="H480" s="94"/>
-      <c r="I480" s="94"/>
-      <c r="J480" s="52"/>
+      <c r="G480" s="94" t="s">
+        <v>473</v>
+      </c>
+      <c r="H480" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I480" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J480" s="52">
+        <v>6</v>
+      </c>
       <c r="K480" s="52"/>
       <c r="L480" s="52"/>
       <c r="M480" s="52"/>
@@ -47050,7 +48102,7 @@
       </c>
       <c r="S480" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB480" s="88">
         <v>39.270000000000003</v>
@@ -47063,33 +48115,33 @@
       </c>
       <c r="AE480" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>671.46</v>
       </c>
       <c r="AF480" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG480" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>43.644900000000007</v>
       </c>
       <c r="AH480" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>8.2467000000000006</v>
       </c>
       <c r="AI480" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>627.81510000000003</v>
       </c>
       <c r="AJ480" s="91">
         <v>0.18</v>
       </c>
       <c r="AK480" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>113.00671800000001</v>
       </c>
       <c r="AL480" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>740.82181800000001</v>
       </c>
       <c r="AP480" s="7"/>
     </row>
@@ -47100,9 +48152,15 @@
       <c r="D481" s="102"/>
       <c r="E481" s="94"/>
       <c r="F481" s="94"/>
-      <c r="G481" s="94"/>
-      <c r="H481" s="94"/>
-      <c r="I481" s="94"/>
+      <c r="G481" s="94" t="s">
+        <v>474</v>
+      </c>
+      <c r="H481" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I481" s="94" t="s">
+        <v>298</v>
+      </c>
       <c r="J481" s="52"/>
       <c r="K481" s="52"/>
       <c r="L481" s="52"/>
@@ -47111,16 +48169,20 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O481" s="52"/>
+      <c r="O481" s="52">
+        <v>20</v>
+      </c>
       <c r="P481" s="52"/>
-      <c r="Q481" s="52"/>
+      <c r="Q481" s="52">
+        <v>20</v>
+      </c>
       <c r="R481" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S481" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB481" s="88">
         <v>39.270000000000003</v>
@@ -47133,14 +48195,14 @@
       </c>
       <c r="AE481" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF481" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG481" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH481" s="49">
         <f t="shared" si="127"/>
@@ -47148,18 +48210,18 @@
       </c>
       <c r="AI481" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ481" s="91">
         <v>0.18</v>
       </c>
       <c r="AK481" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL481" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP481" s="7"/>
     </row>
@@ -47170,10 +48232,18 @@
       <c r="D482" s="102"/>
       <c r="E482" s="94"/>
       <c r="F482" s="94"/>
-      <c r="G482" s="94"/>
-      <c r="H482" s="94"/>
-      <c r="I482" s="94"/>
-      <c r="J482" s="52"/>
+      <c r="G482" s="94" t="s">
+        <v>475</v>
+      </c>
+      <c r="H482" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I482" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J482" s="52">
+        <v>40</v>
+      </c>
       <c r="K482" s="52"/>
       <c r="L482" s="52"/>
       <c r="M482" s="52"/>
@@ -47190,7 +48260,7 @@
       </c>
       <c r="S482" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB482" s="88">
         <v>39.270000000000003</v>
@@ -47203,33 +48273,33 @@
       </c>
       <c r="AE482" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF482" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG482" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH482" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI482" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ482" s="91">
         <v>0.18</v>
       </c>
       <c r="AK482" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL482" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP482" s="7"/>
     </row>
@@ -47240,16 +48310,28 @@
       <c r="D483" s="102"/>
       <c r="E483" s="94"/>
       <c r="F483" s="94"/>
-      <c r="G483" s="94"/>
-      <c r="H483" s="94"/>
-      <c r="I483" s="94"/>
-      <c r="J483" s="52"/>
-      <c r="K483" s="52"/>
-      <c r="L483" s="52"/>
+      <c r="G483" s="94" t="s">
+        <v>476</v>
+      </c>
+      <c r="H483" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I483" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J483" s="52">
+        <v>12</v>
+      </c>
+      <c r="K483" s="52">
+        <v>6</v>
+      </c>
+      <c r="L483" s="52">
+        <v>6</v>
+      </c>
       <c r="M483" s="52"/>
       <c r="N483" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O483" s="52"/>
       <c r="P483" s="52"/>
@@ -47260,7 +48342,7 @@
       </c>
       <c r="S483" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB483" s="88">
         <v>39.270000000000003</v>
@@ -47273,33 +48355,33 @@
       </c>
       <c r="AE483" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2844.15</v>
       </c>
       <c r="AF483" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG483" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>184.86975000000001</v>
       </c>
       <c r="AH483" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI483" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2659.2802500000003</v>
       </c>
       <c r="AJ483" s="91">
         <v>0.18</v>
       </c>
       <c r="AK483" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>478.67044500000003</v>
       </c>
       <c r="AL483" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3137.9506950000005</v>
       </c>
       <c r="AP483" s="7"/>
     </row>
@@ -47310,16 +48392,28 @@
       <c r="D484" s="102"/>
       <c r="E484" s="94"/>
       <c r="F484" s="94"/>
-      <c r="G484" s="94"/>
-      <c r="H484" s="94"/>
-      <c r="I484" s="94"/>
-      <c r="J484" s="52"/>
-      <c r="K484" s="52"/>
-      <c r="L484" s="52"/>
+      <c r="G484" s="94" t="s">
+        <v>477</v>
+      </c>
+      <c r="H484" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I484" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J484" s="52">
+        <v>40</v>
+      </c>
+      <c r="K484" s="52">
+        <v>40</v>
+      </c>
+      <c r="L484" s="52">
+        <v>40</v>
+      </c>
       <c r="M484" s="52"/>
       <c r="N484" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O484" s="52"/>
       <c r="P484" s="52"/>
@@ -47330,7 +48424,7 @@
       </c>
       <c r="S484" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB484" s="88">
         <v>39.270000000000003</v>
@@ -47343,33 +48437,33 @@
       </c>
       <c r="AE484" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>14484.599999999999</v>
       </c>
       <c r="AF484" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG484" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>941.49899999999991</v>
       </c>
       <c r="AH484" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI484" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>13543.100999999999</v>
       </c>
       <c r="AJ484" s="91">
         <v>0.18</v>
       </c>
       <c r="AK484" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2437.7581799999998</v>
       </c>
       <c r="AL484" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>15980.859179999999</v>
       </c>
       <c r="AP484" s="7"/>
     </row>
@@ -47380,10 +48474,18 @@
       <c r="D485" s="102"/>
       <c r="E485" s="94"/>
       <c r="F485" s="94"/>
-      <c r="G485" s="94"/>
-      <c r="H485" s="94"/>
-      <c r="I485" s="94"/>
-      <c r="J485" s="52"/>
+      <c r="G485" s="94" t="s">
+        <v>478</v>
+      </c>
+      <c r="H485" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I485" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J485" s="52">
+        <v>40</v>
+      </c>
       <c r="K485" s="52"/>
       <c r="L485" s="52"/>
       <c r="M485" s="52"/>
@@ -47400,7 +48502,7 @@
       </c>
       <c r="S485" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB485" s="88">
         <v>39.270000000000003</v>
@@ -47413,33 +48515,33 @@
       </c>
       <c r="AE485" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF485" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG485" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH485" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI485" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ485" s="91">
         <v>0.18</v>
       </c>
       <c r="AK485" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL485" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP485" s="7"/>
     </row>
@@ -47450,10 +48552,18 @@
       <c r="D486" s="102"/>
       <c r="E486" s="94"/>
       <c r="F486" s="94"/>
-      <c r="G486" s="94"/>
-      <c r="H486" s="94"/>
-      <c r="I486" s="94"/>
-      <c r="J486" s="52"/>
+      <c r="G486" s="94" t="s">
+        <v>479</v>
+      </c>
+      <c r="H486" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I486" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J486" s="52">
+        <v>40</v>
+      </c>
       <c r="K486" s="52"/>
       <c r="L486" s="52"/>
       <c r="M486" s="52"/>
@@ -47470,7 +48580,7 @@
       </c>
       <c r="S486" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB486" s="88">
         <v>39.270000000000003</v>
@@ -47483,33 +48593,33 @@
       </c>
       <c r="AE486" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF486" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG486" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH486" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI486" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ486" s="91">
         <v>0.18</v>
       </c>
       <c r="AK486" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL486" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP486" s="7"/>
     </row>
@@ -47520,10 +48630,18 @@
       <c r="D487" s="102"/>
       <c r="E487" s="94"/>
       <c r="F487" s="94"/>
-      <c r="G487" s="94"/>
-      <c r="H487" s="94"/>
-      <c r="I487" s="94"/>
-      <c r="J487" s="52"/>
+      <c r="G487" s="94" t="s">
+        <v>480</v>
+      </c>
+      <c r="H487" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I487" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J487" s="52">
+        <v>40</v>
+      </c>
       <c r="K487" s="52"/>
       <c r="L487" s="52"/>
       <c r="M487" s="52"/>
@@ -47540,7 +48658,7 @@
       </c>
       <c r="S487" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB487" s="88">
         <v>39.270000000000003</v>
@@ -47553,33 +48671,33 @@
       </c>
       <c r="AE487" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF487" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG487" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH487" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI487" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ487" s="91">
         <v>0.18</v>
       </c>
       <c r="AK487" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL487" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP487" s="7"/>
     </row>
@@ -47590,10 +48708,18 @@
       <c r="D488" s="102"/>
       <c r="E488" s="94"/>
       <c r="F488" s="94"/>
-      <c r="G488" s="94"/>
-      <c r="H488" s="94"/>
-      <c r="I488" s="94"/>
-      <c r="J488" s="52"/>
+      <c r="G488" s="94" t="s">
+        <v>481</v>
+      </c>
+      <c r="H488" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I488" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="J488" s="52">
+        <v>20</v>
+      </c>
       <c r="K488" s="52"/>
       <c r="L488" s="52"/>
       <c r="M488" s="52"/>
@@ -47610,7 +48736,7 @@
       </c>
       <c r="S488" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB488" s="88">
         <v>39.270000000000003</v>
@@ -47623,33 +48749,33 @@
       </c>
       <c r="AE488" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2238.1999999999998</v>
       </c>
       <c r="AF488" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG488" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>145.483</v>
       </c>
       <c r="AH488" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI488" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2092.7169999999996</v>
       </c>
       <c r="AJ488" s="91">
         <v>0.18</v>
       </c>
       <c r="AK488" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>376.68905999999993</v>
       </c>
       <c r="AL488" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2469.4060599999993</v>
       </c>
       <c r="AP488" s="7"/>
     </row>
@@ -47660,9 +48786,15 @@
       <c r="D489" s="102"/>
       <c r="E489" s="94"/>
       <c r="F489" s="94"/>
-      <c r="G489" s="94"/>
-      <c r="H489" s="94"/>
-      <c r="I489" s="94"/>
+      <c r="G489" s="94" t="s">
+        <v>300</v>
+      </c>
+      <c r="H489" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I489" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J489" s="52"/>
       <c r="K489" s="52"/>
       <c r="L489" s="52"/>
@@ -47673,14 +48805,16 @@
       </c>
       <c r="O489" s="52"/>
       <c r="P489" s="52"/>
-      <c r="Q489" s="52"/>
+      <c r="Q489" s="52">
+        <v>80</v>
+      </c>
       <c r="R489" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S489" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB489" s="88">
         <v>39.270000000000003</v>
@@ -47693,14 +48827,14 @@
       </c>
       <c r="AE489" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>5811.2</v>
       </c>
       <c r="AF489" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG489" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>377.72800000000001</v>
       </c>
       <c r="AH489" s="49">
         <f t="shared" si="127"/>
@@ -47708,18 +48842,18 @@
       </c>
       <c r="AI489" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>5433.4719999999998</v>
       </c>
       <c r="AJ489" s="91">
         <v>0.18</v>
       </c>
       <c r="AK489" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>978.02495999999996</v>
       </c>
       <c r="AL489" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>6411.4969599999995</v>
       </c>
       <c r="AP489" s="7"/>
     </row>
@@ -47730,16 +48864,24 @@
       <c r="D490" s="102"/>
       <c r="E490" s="94"/>
       <c r="F490" s="94"/>
-      <c r="G490" s="94"/>
-      <c r="H490" s="94"/>
-      <c r="I490" s="94"/>
+      <c r="G490" s="94" t="s">
+        <v>271</v>
+      </c>
+      <c r="H490" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I490" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J490" s="52"/>
-      <c r="K490" s="52"/>
+      <c r="K490" s="52">
+        <v>10</v>
+      </c>
       <c r="L490" s="52"/>
       <c r="M490" s="52"/>
       <c r="N490" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O490" s="52"/>
       <c r="P490" s="52"/>
@@ -47750,7 +48892,7 @@
       </c>
       <c r="S490" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB490" s="88">
         <v>39.270000000000003</v>
@@ -47763,14 +48905,14 @@
       </c>
       <c r="AE490" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF490" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG490" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH490" s="49">
         <f t="shared" si="127"/>
@@ -47778,18 +48920,18 @@
       </c>
       <c r="AI490" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ490" s="91">
         <v>0.18</v>
       </c>
       <c r="AK490" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL490" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP490" s="7"/>
     </row>
@@ -47800,16 +48942,24 @@
       <c r="D491" s="102"/>
       <c r="E491" s="94"/>
       <c r="F491" s="94"/>
-      <c r="G491" s="94"/>
-      <c r="H491" s="94"/>
-      <c r="I491" s="94"/>
+      <c r="G491" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="H491" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I491" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J491" s="52"/>
       <c r="K491" s="52"/>
-      <c r="L491" s="52"/>
+      <c r="L491" s="52">
+        <v>10</v>
+      </c>
       <c r="M491" s="52"/>
       <c r="N491" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O491" s="52"/>
       <c r="P491" s="52"/>
@@ -47820,7 +48970,7 @@
       </c>
       <c r="S491" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB491" s="88">
         <v>39.270000000000003</v>
@@ -47833,14 +48983,14 @@
       </c>
       <c r="AE491" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF491" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG491" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH491" s="49">
         <f t="shared" si="127"/>
@@ -47848,18 +48998,18 @@
       </c>
       <c r="AI491" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ491" s="91">
         <v>0.18</v>
       </c>
       <c r="AK491" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL491" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP491" s="7"/>
     </row>
@@ -47870,16 +49020,24 @@
       <c r="D492" s="102"/>
       <c r="E492" s="94"/>
       <c r="F492" s="94"/>
-      <c r="G492" s="94"/>
-      <c r="H492" s="94"/>
-      <c r="I492" s="94"/>
+      <c r="G492" s="94" t="s">
+        <v>303</v>
+      </c>
+      <c r="H492" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I492" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J492" s="52"/>
-      <c r="K492" s="52"/>
+      <c r="K492" s="52">
+        <v>10</v>
+      </c>
       <c r="L492" s="52"/>
       <c r="M492" s="52"/>
       <c r="N492" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O492" s="52"/>
       <c r="P492" s="52"/>
@@ -47890,7 +49048,7 @@
       </c>
       <c r="S492" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB492" s="88">
         <v>39.270000000000003</v>
@@ -47903,14 +49061,14 @@
       </c>
       <c r="AE492" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF492" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG492" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH492" s="49">
         <f t="shared" si="127"/>
@@ -47918,18 +49076,18 @@
       </c>
       <c r="AI492" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ492" s="91">
         <v>0.18</v>
       </c>
       <c r="AK492" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL492" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP492" s="7"/>
     </row>
@@ -47940,16 +49098,24 @@
       <c r="D493" s="102"/>
       <c r="E493" s="94"/>
       <c r="F493" s="94"/>
-      <c r="G493" s="94"/>
-      <c r="H493" s="94"/>
-      <c r="I493" s="94"/>
+      <c r="G493" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="H493" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I493" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J493" s="52"/>
       <c r="K493" s="52"/>
-      <c r="L493" s="52"/>
+      <c r="L493" s="52">
+        <v>10</v>
+      </c>
       <c r="M493" s="52"/>
       <c r="N493" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O493" s="52"/>
       <c r="P493" s="52"/>
@@ -47960,7 +49126,7 @@
       </c>
       <c r="S493" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB493" s="88">
         <v>39.270000000000003</v>
@@ -47973,14 +49139,14 @@
       </c>
       <c r="AE493" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF493" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG493" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH493" s="49">
         <f t="shared" si="127"/>
@@ -47988,18 +49154,18 @@
       </c>
       <c r="AI493" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ493" s="91">
         <v>0.18</v>
       </c>
       <c r="AK493" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL493" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP493" s="7"/>
     </row>
@@ -48010,9 +49176,15 @@
       <c r="D494" s="102"/>
       <c r="E494" s="94"/>
       <c r="F494" s="94"/>
-      <c r="G494" s="94"/>
-      <c r="H494" s="94"/>
-      <c r="I494" s="94"/>
+      <c r="G494" s="94" t="s">
+        <v>482</v>
+      </c>
+      <c r="H494" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I494" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J494" s="52"/>
       <c r="K494" s="52"/>
       <c r="L494" s="52"/>
@@ -48021,16 +49193,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O494" s="52"/>
-      <c r="P494" s="52"/>
-      <c r="Q494" s="52"/>
+      <c r="O494" s="52">
+        <v>15</v>
+      </c>
+      <c r="P494" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q494" s="52">
+        <v>15</v>
+      </c>
       <c r="R494" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S494" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB494" s="88">
         <v>39.270000000000003</v>
@@ -48043,14 +49221,14 @@
       </c>
       <c r="AE494" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF494" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG494" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH494" s="49">
         <f t="shared" si="127"/>
@@ -48058,18 +49236,18 @@
       </c>
       <c r="AI494" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ494" s="91">
         <v>0.18</v>
       </c>
       <c r="AK494" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL494" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP494" s="7"/>
     </row>
@@ -48080,27 +49258,43 @@
       <c r="D495" s="102"/>
       <c r="E495" s="94"/>
       <c r="F495" s="94"/>
-      <c r="G495" s="94"/>
-      <c r="H495" s="94"/>
-      <c r="I495" s="94"/>
+      <c r="G495" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="H495" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I495" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J495" s="52"/>
-      <c r="K495" s="52"/>
-      <c r="L495" s="52"/>
+      <c r="K495" s="52">
+        <v>20</v>
+      </c>
+      <c r="L495" s="52">
+        <v>20</v>
+      </c>
       <c r="M495" s="52"/>
       <c r="N495" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O495" s="52"/>
-      <c r="P495" s="52"/>
-      <c r="Q495" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O495" s="52">
+        <v>15</v>
+      </c>
+      <c r="P495" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q495" s="52">
+        <v>15</v>
+      </c>
       <c r="R495" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S495" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB495" s="88">
         <v>39.270000000000003</v>
@@ -48113,14 +49307,14 @@
       </c>
       <c r="AE495" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>7909.7</v>
       </c>
       <c r="AF495" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG495" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>514.13049999999998</v>
       </c>
       <c r="AH495" s="49">
         <f t="shared" si="127"/>
@@ -48128,18 +49322,18 @@
       </c>
       <c r="AI495" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>7395.5694999999996</v>
       </c>
       <c r="AJ495" s="91">
         <v>0.18</v>
       </c>
       <c r="AK495" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>1331.2025099999998</v>
       </c>
       <c r="AL495" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>8726.7720099999988</v>
       </c>
       <c r="AP495" s="7"/>
     </row>
@@ -48150,27 +49344,45 @@
       <c r="D496" s="102"/>
       <c r="E496" s="94"/>
       <c r="F496" s="94"/>
-      <c r="G496" s="94"/>
-      <c r="H496" s="94"/>
-      <c r="I496" s="94"/>
-      <c r="J496" s="52"/>
-      <c r="K496" s="52"/>
-      <c r="L496" s="52"/>
+      <c r="G496" s="94" t="s">
+        <v>483</v>
+      </c>
+      <c r="H496" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I496" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J496" s="52">
+        <v>80</v>
+      </c>
+      <c r="K496" s="52">
+        <v>40</v>
+      </c>
+      <c r="L496" s="52">
+        <v>40</v>
+      </c>
       <c r="M496" s="52"/>
       <c r="N496" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O496" s="52"/>
-      <c r="P496" s="52"/>
-      <c r="Q496" s="52"/>
+        <v>80</v>
+      </c>
+      <c r="O496" s="52">
+        <v>40</v>
+      </c>
+      <c r="P496" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q496" s="52">
+        <v>40</v>
+      </c>
       <c r="R496" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S496" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB496" s="88">
         <v>39.270000000000003</v>
@@ -48183,33 +49395,33 @@
       </c>
       <c r="AE496" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>27677.800000000003</v>
       </c>
       <c r="AF496" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG496" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1799.0570000000002</v>
       </c>
       <c r="AH496" s="49">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI496" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25878.743000000002</v>
       </c>
       <c r="AJ496" s="91">
         <v>0.18</v>
       </c>
       <c r="AK496" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>4658.1737400000002</v>
       </c>
       <c r="AL496" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>30536.916740000001</v>
       </c>
       <c r="AP496" s="7"/>
     </row>
@@ -48220,16 +49432,24 @@
       <c r="D497" s="102"/>
       <c r="E497" s="94"/>
       <c r="F497" s="94"/>
-      <c r="G497" s="94"/>
-      <c r="H497" s="94"/>
-      <c r="I497" s="94"/>
+      <c r="G497" s="94" t="s">
+        <v>168</v>
+      </c>
+      <c r="H497" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I497" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J497" s="52"/>
-      <c r="K497" s="52"/>
+      <c r="K497" s="52">
+        <v>10</v>
+      </c>
       <c r="L497" s="52"/>
       <c r="M497" s="52"/>
       <c r="N497" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O497" s="52"/>
       <c r="P497" s="52"/>
@@ -48240,7 +49460,7 @@
       </c>
       <c r="S497" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB497" s="88">
         <v>39.270000000000003</v>
@@ -48253,14 +49473,14 @@
       </c>
       <c r="AE497" s="89">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF497" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG497" s="4">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH497" s="49">
         <f t="shared" si="127"/>
@@ -48268,18 +49488,18 @@
       </c>
       <c r="AI497" s="89">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ497" s="91">
         <v>0.18</v>
       </c>
       <c r="AK497" s="5">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL497" s="89">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP497" s="7"/>
     </row>
@@ -48290,16 +49510,24 @@
       <c r="D498" s="102"/>
       <c r="E498" s="94"/>
       <c r="F498" s="94"/>
-      <c r="G498" s="94"/>
-      <c r="H498" s="94"/>
-      <c r="I498" s="94"/>
+      <c r="G498" s="94" t="s">
+        <v>484</v>
+      </c>
+      <c r="H498" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I498" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J498" s="52"/>
-      <c r="K498" s="52"/>
+      <c r="K498" s="52">
+        <v>10</v>
+      </c>
       <c r="L498" s="52"/>
       <c r="M498" s="52"/>
       <c r="N498" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O498" s="52"/>
       <c r="P498" s="52"/>
@@ -48310,7 +49538,7 @@
       </c>
       <c r="S498" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB498" s="88">
         <v>39.270000000000003</v>
@@ -48323,14 +49551,14 @@
       </c>
       <c r="AE498" s="89">
         <f t="shared" ref="AE498:AE561" si="134">(J498*AB498)+(N498*AC498)+(AD498*S498)</f>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF498" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG498" s="4">
         <f t="shared" ref="AG498:AG561" si="135">AE498*AF498</f>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH498" s="49">
         <f t="shared" ref="AH498:AH561" si="136">(AB498*J498)*$AH$1</f>
@@ -48338,18 +49566,18 @@
       </c>
       <c r="AI498" s="89">
         <f t="shared" ref="AI498:AI561" si="137">AE498-AG498</f>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ498" s="91">
         <v>0.18</v>
       </c>
       <c r="AK498" s="5">
         <f t="shared" ref="AK498:AK561" si="138">AI498*AJ498</f>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL498" s="89">
         <f t="shared" ref="AL498:AL561" si="139">AI498+AK498</f>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP498" s="7"/>
     </row>
@@ -48360,16 +49588,24 @@
       <c r="D499" s="102"/>
       <c r="E499" s="94"/>
       <c r="F499" s="94"/>
-      <c r="G499" s="94"/>
-      <c r="H499" s="94"/>
-      <c r="I499" s="94"/>
+      <c r="G499" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="H499" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I499" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J499" s="52"/>
-      <c r="K499" s="52"/>
+      <c r="K499" s="52">
+        <v>10</v>
+      </c>
       <c r="L499" s="52"/>
       <c r="M499" s="52"/>
       <c r="N499" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O499" s="52"/>
       <c r="P499" s="52"/>
@@ -48380,7 +49616,7 @@
       </c>
       <c r="S499" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB499" s="88">
         <v>39.270000000000003</v>
@@ -48393,14 +49629,14 @@
       </c>
       <c r="AE499" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF499" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG499" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH499" s="49">
         <f t="shared" si="136"/>
@@ -48408,18 +49644,18 @@
       </c>
       <c r="AI499" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ499" s="91">
         <v>0.18</v>
       </c>
       <c r="AK499" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL499" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP499" s="7"/>
     </row>
@@ -48430,16 +49666,24 @@
       <c r="D500" s="102"/>
       <c r="E500" s="94"/>
       <c r="F500" s="94"/>
-      <c r="G500" s="94"/>
-      <c r="H500" s="94"/>
-      <c r="I500" s="94"/>
+      <c r="G500" s="94" t="s">
+        <v>485</v>
+      </c>
+      <c r="H500" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I500" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J500" s="52"/>
-      <c r="K500" s="52"/>
+      <c r="K500" s="52">
+        <v>10</v>
+      </c>
       <c r="L500" s="52"/>
       <c r="M500" s="52"/>
       <c r="N500" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O500" s="52"/>
       <c r="P500" s="52"/>
@@ -48450,7 +49694,7 @@
       </c>
       <c r="S500" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB500" s="88">
         <v>39.270000000000003</v>
@@ -48463,14 +49707,14 @@
       </c>
       <c r="AE500" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF500" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG500" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH500" s="49">
         <f t="shared" si="136"/>
@@ -48478,18 +49722,18 @@
       </c>
       <c r="AI500" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ500" s="91">
         <v>0.18</v>
       </c>
       <c r="AK500" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL500" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP500" s="7"/>
     </row>
@@ -48500,9 +49744,15 @@
       <c r="D501" s="102"/>
       <c r="E501" s="94"/>
       <c r="F501" s="94"/>
-      <c r="G501" s="94"/>
-      <c r="H501" s="94"/>
-      <c r="I501" s="94"/>
+      <c r="G501" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="H501" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I501" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J501" s="52"/>
       <c r="K501" s="52"/>
       <c r="L501" s="52"/>
@@ -48513,14 +49763,16 @@
       </c>
       <c r="O501" s="52"/>
       <c r="P501" s="52"/>
-      <c r="Q501" s="52"/>
+      <c r="Q501" s="52">
+        <v>20</v>
+      </c>
       <c r="R501" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S501" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB501" s="88">
         <v>39.270000000000003</v>
@@ -48533,14 +49785,14 @@
       </c>
       <c r="AE501" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="AF501" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG501" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>94.432000000000002</v>
       </c>
       <c r="AH501" s="49">
         <f t="shared" si="136"/>
@@ -48548,18 +49800,18 @@
       </c>
       <c r="AI501" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1358.3679999999999</v>
       </c>
       <c r="AJ501" s="91">
         <v>0.18</v>
       </c>
       <c r="AK501" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>244.50623999999999</v>
       </c>
       <c r="AL501" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1602.8742399999999</v>
       </c>
       <c r="AP501" s="7"/>
     </row>
@@ -54822,15 +56074,15 @@
       <c r="A592" s="3"/>
       <c r="J592" s="107">
         <f>SUM(J3:J591)</f>
-        <v>9923</v>
+        <v>11203</v>
       </c>
       <c r="K592" s="107">
         <f t="shared" ref="K592:S592" si="152">SUM(K3:K591)</f>
-        <v>5247</v>
+        <v>5845</v>
       </c>
       <c r="L592" s="107">
         <f t="shared" si="152"/>
-        <v>4608</v>
+        <v>5110</v>
       </c>
       <c r="M592" s="107">
         <f t="shared" si="152"/>
@@ -54838,27 +56090,27 @@
       </c>
       <c r="N592" s="107">
         <f t="shared" si="152"/>
-        <v>9855</v>
+        <v>10955</v>
       </c>
       <c r="O592" s="107">
         <f t="shared" si="152"/>
-        <v>9369</v>
+        <v>10721</v>
       </c>
       <c r="P592" s="107">
         <f t="shared" si="152"/>
-        <v>8104</v>
+        <v>9340</v>
       </c>
       <c r="Q592" s="107">
         <f t="shared" si="152"/>
-        <v>10494</v>
+        <v>12088</v>
       </c>
       <c r="R592" s="107">
         <f t="shared" si="152"/>
-        <v>27967</v>
+        <v>32149</v>
       </c>
       <c r="S592" s="107">
         <f t="shared" si="152"/>
-        <v>47745</v>
+        <v>54307</v>
       </c>
       <c r="AP592" s="7"/>
     </row>
@@ -54925,15 +56177,15 @@
       </c>
       <c r="J595" s="47">
         <f>J592/40</f>
-        <v>248.07499999999999</v>
+        <v>280.07499999999999</v>
       </c>
       <c r="K595" s="109">
         <f t="shared" ref="K595:S595" si="153">K592/40</f>
-        <v>131.17500000000001</v>
+        <v>146.125</v>
       </c>
       <c r="L595" s="109">
         <f t="shared" si="153"/>
-        <v>115.2</v>
+        <v>127.75</v>
       </c>
       <c r="M595" s="109">
         <f t="shared" si="153"/>
@@ -54941,27 +56193,27 @@
       </c>
       <c r="N595" s="47">
         <f t="shared" si="153"/>
-        <v>246.375</v>
+        <v>273.875</v>
       </c>
       <c r="O595" s="109">
         <f t="shared" si="153"/>
-        <v>234.22499999999999</v>
+        <v>268.02499999999998</v>
       </c>
       <c r="P595" s="109">
         <f t="shared" si="153"/>
-        <v>202.6</v>
+        <v>233.5</v>
       </c>
       <c r="Q595" s="109">
         <f t="shared" si="153"/>
-        <v>262.35000000000002</v>
+        <v>302.2</v>
       </c>
       <c r="R595" s="47">
         <f t="shared" si="153"/>
-        <v>699.17499999999995</v>
+        <v>803.72500000000002</v>
       </c>
       <c r="S595" s="109">
         <f t="shared" si="153"/>
-        <v>1193.625</v>
+        <v>1357.675</v>
       </c>
       <c r="T595" s="54">
         <f t="shared" ref="T595:AF595" si="154">+T433/40</f>
@@ -55026,7 +56278,7 @@
     <row r="597" spans="1:42" x14ac:dyDescent="0.35">
       <c r="S597" s="53">
         <f>S595+W595+AA595</f>
-        <v>1193.625</v>
+        <v>1357.675</v>
       </c>
       <c r="X597" t="s">
         <v>50</v>
@@ -55105,22 +56357,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="124" t="s">
+      <c r="D4" s="126" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="126"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="128"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="10" t="s">
@@ -55151,11 +56403,11 @@
       </c>
       <c r="G7" s="16">
         <f>'STT Report'!Q595+'STT Report'!Z595</f>
-        <v>262.35000000000002</v>
+        <v>302.2</v>
       </c>
       <c r="H7" s="17">
         <f>E7+F7-G7</f>
-        <v>1057.6500000000001</v>
+        <v>1017.8</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -55170,11 +56422,11 @@
       </c>
       <c r="G8" s="16">
         <f>'STT Report'!P595+'STT Report'!Y595</f>
-        <v>202.6</v>
+        <v>233.5</v>
       </c>
       <c r="H8" s="17">
         <f>E8+F8-G8</f>
-        <v>140.4</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -55189,11 +56441,11 @@
       </c>
       <c r="G9" s="16">
         <f>'STT Report'!O595+'STT Report'!X595</f>
-        <v>234.22499999999999</v>
+        <v>268.02499999999998</v>
       </c>
       <c r="H9" s="17">
         <f>E9+F9-G9</f>
-        <v>693.77499999999998</v>
+        <v>659.97500000000002</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -55210,11 +56462,11 @@
       </c>
       <c r="G10" s="22">
         <f>SUM(G7:G9)</f>
-        <v>699.17500000000007</v>
+        <v>803.72500000000002</v>
       </c>
       <c r="H10" s="23">
         <f>SUM(H7:H9)</f>
-        <v>1891.8250000000003</v>
+        <v>1787.2750000000001</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -55227,11 +56479,11 @@
       <c r="F11" s="15"/>
       <c r="G11" s="44">
         <f>'STT Report'!J595</f>
-        <v>248.07499999999999</v>
+        <v>280.07499999999999</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1404.925</v>
+        <v>1372.925</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -55268,11 +56520,11 @@
       </c>
       <c r="G14" s="20">
         <f>SUM(G11:G13)</f>
-        <v>248.07499999999999</v>
+        <v>280.07499999999999</v>
       </c>
       <c r="H14" s="23">
         <f>SUM(H11:H13)</f>
-        <v>1404.925</v>
+        <v>1372.925</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -55302,11 +56554,11 @@
       <c r="F16" s="18"/>
       <c r="G16" s="16">
         <f>'STT Report'!L595+'STT Report'!U595</f>
-        <v>115.2</v>
+        <v>127.75</v>
       </c>
       <c r="H16" s="17">
         <f>E16+F16-G16</f>
-        <v>151.80000000000001</v>
+        <v>139.25</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -55319,11 +56571,11 @@
       <c r="F17" s="18"/>
       <c r="G17" s="16">
         <f>'STT Report'!K595+'STT Report'!T595</f>
-        <v>131.17500000000001</v>
+        <v>146.125</v>
       </c>
       <c r="H17" s="17">
         <f>E17+F17-G17</f>
-        <v>108.82499999999999</v>
+        <v>93.875</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -55340,11 +56592,11 @@
       </c>
       <c r="G18" s="22">
         <f>SUM(G15:G17)</f>
-        <v>246.375</v>
+        <v>273.875</v>
       </c>
       <c r="H18" s="23">
         <f>SUM(H15:H17)</f>
-        <v>260.625</v>
+        <v>233.125</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -55361,11 +56613,11 @@
       </c>
       <c r="G19" s="25">
         <f>G10+G14+G18</f>
-        <v>1193.625</v>
+        <v>1357.675</v>
       </c>
       <c r="H19" s="27">
         <f>H10+H14+H18</f>
-        <v>3557.375</v>
+        <v>3393.3249999999998</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
@@ -55675,10 +56927,10 @@
       </c>
     </row>
     <row r="31" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="128" t="s">
+      <c r="C31" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="129"/>
+      <c r="D31" s="131"/>
       <c r="E31" s="37">
         <f>SUM(E24:E30)</f>
         <v>8000</v>

--- a/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED855C92-DA3A-43A7-A7D2-C830730D1A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7743F9-0951-42F8-9EEA-C8CAEFA3CEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Inventory" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STT Report'!$A$1:$AP$434</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STT Report'!$A$1:$AP$552</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="530">
   <si>
     <t>Date</t>
   </si>
@@ -1488,6 +1488,138 @@
   <si>
     <t>Saad Store</t>
   </si>
+  <si>
+    <t>Amna Dopartment</t>
+  </si>
+  <si>
+    <t>Khalid Super Store</t>
+  </si>
+  <si>
+    <t>Al Madina Store</t>
+  </si>
+  <si>
+    <t>Ghous Bakers</t>
+  </si>
+  <si>
+    <t>Hikma Super Store 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umaima </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick &amp; Pack </t>
+  </si>
+  <si>
+    <t>City Mart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green City </t>
+  </si>
+  <si>
+    <t>Jhore pull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gulshan Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Makkah Kareyana </t>
+  </si>
+  <si>
+    <t>New Idel Bakers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faredia Kareyana </t>
+  </si>
+  <si>
+    <t>Hanif Kareyana Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madina Super Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS Sweet </t>
+  </si>
+  <si>
+    <t>Nishter Bazar</t>
+  </si>
+  <si>
+    <t>Faizan Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imran Bakers </t>
+  </si>
+  <si>
+    <t>Nister Store</t>
+  </si>
+  <si>
+    <t>786 Sweets</t>
+  </si>
+  <si>
+    <t>Chaudry Sons</t>
+  </si>
+  <si>
+    <t>LAL Store</t>
+  </si>
+  <si>
+    <t>Subedar Store</t>
+  </si>
+  <si>
+    <t>RA Bazar</t>
+  </si>
+  <si>
+    <t>Jalal Sons Warehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatri Chowk </t>
+  </si>
+  <si>
+    <t>Ferozpur Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shell Petro Mart </t>
+  </si>
+  <si>
+    <t>Abdullah Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saeed Bakery </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tajpura </t>
+  </si>
+  <si>
+    <t>Makkah Store</t>
+  </si>
+  <si>
+    <t>Kashif Super Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ah mart </t>
+  </si>
+  <si>
+    <t>Ghulam Store 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Falah Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shera Mart </t>
+  </si>
+  <si>
+    <t>Allys Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bravo Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan Mart </t>
+  </si>
+  <si>
+    <t>K Smart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MHT Mart </t>
+  </si>
 </sst>
 </file>
 
@@ -2431,13 +2563,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2446,13 +2575,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2792,7 +2924,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AP597"/>
+  <dimension ref="A1:AP599"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -2839,45 +2971,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="118" t="s">
+      <c r="A1" s="122" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="118" t="s">
+      <c r="C1" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="118" t="s">
+      <c r="D1" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="118" t="s">
+      <c r="G1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="118" t="s">
+      <c r="H1" s="122" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="42"/>
-      <c r="K1" s="118" t="s">
+      <c r="K1" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="119" t="s">
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="121" t="s">
+      <c r="P1" s="125"/>
+      <c r="Q1" s="125"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="120" t="s">
         <v>10</v>
       </c>
       <c r="T1" s="123" t="s">
@@ -2892,61 +3024,61 @@
       <c r="Y1" s="123"/>
       <c r="Z1" s="123"/>
       <c r="AA1" s="123"/>
-      <c r="AB1" s="121" t="s">
+      <c r="AB1" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="121" t="s">
+      <c r="AC1" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="121" t="s">
+      <c r="AD1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="121" t="s">
+      <c r="AE1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="121" t="s">
+      <c r="AF1" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="121" t="s">
+      <c r="AG1" s="120" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="84">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="121" t="s">
+      <c r="AI1" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="121" t="s">
+      <c r="AJ1" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="121" t="s">
+      <c r="AK1" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="121" t="s">
+      <c r="AL1" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="121" t="s">
+      <c r="AM1" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="124" t="s">
+      <c r="AN1" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="124" t="s">
+      <c r="AO1" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="121" t="s">
+      <c r="AP1" s="120" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="118"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -2977,7 +3109,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="122"/>
+      <c r="S2" s="121"/>
       <c r="T2" s="83" t="s">
         <v>73</v>
       </c>
@@ -3002,23 +3134,23 @@
       <c r="AA2" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="121"/>
+      <c r="AG2" s="121"/>
       <c r="AH2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="125"/>
-      <c r="AO2" s="125"/>
-      <c r="AP2" s="122"/>
+      <c r="AI2" s="121"/>
+      <c r="AJ2" s="121"/>
+      <c r="AK2" s="121"/>
+      <c r="AL2" s="121"/>
+      <c r="AM2" s="121"/>
+      <c r="AN2" s="119"/>
+      <c r="AO2" s="119"/>
+      <c r="AP2" s="121"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="85">
@@ -3050,32 +3182,32 @@
       </c>
       <c r="J3" s="103"/>
       <c r="K3" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L3" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M3" s="86"/>
       <c r="N3" s="104">
         <f>K3+L3+M3</f>
+        <v>160</v>
+      </c>
+      <c r="O3" s="105">
         <v>80</v>
       </c>
-      <c r="O3" s="105">
-        <v>40</v>
-      </c>
       <c r="P3" s="105">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q3" s="105">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R3" s="104">
         <f t="shared" ref="R3:R66" si="0">SUM(O3:Q3)</f>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="S3" s="86">
         <f>R3+N3+J3</f>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T3" s="87"/>
       <c r="U3" s="87"/>
@@ -3096,14 +3228,14 @@
       </c>
       <c r="AE3" s="89">
         <f>(J3*AB3)+(N3*AC3)+(AD3*S3)</f>
-        <v>18725</v>
+        <v>37450</v>
       </c>
       <c r="AF3" s="90">
         <v>0.08</v>
       </c>
       <c r="AG3" s="4">
         <f>AE3*AF3</f>
-        <v>1498</v>
+        <v>2996</v>
       </c>
       <c r="AH3" s="49">
         <f>(AB3*J3)*$AH$1</f>
@@ -3111,18 +3243,18 @@
       </c>
       <c r="AI3" s="89">
         <f>AE3-AG3-AH3</f>
-        <v>17227</v>
+        <v>34454</v>
       </c>
       <c r="AJ3" s="91">
         <v>0.18</v>
       </c>
       <c r="AK3" s="5">
         <f>AI3*AJ3</f>
-        <v>3100.8599999999997</v>
+        <v>6201.7199999999993</v>
       </c>
       <c r="AL3" s="89">
         <f>AI3+AK3</f>
-        <v>20327.86</v>
+        <v>40655.72</v>
       </c>
       <c r="AM3" s="92"/>
       <c r="AN3" s="92"/>
@@ -3268,32 +3400,32 @@
       </c>
       <c r="J5" s="103"/>
       <c r="K5" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L5" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M5" s="86"/>
       <c r="N5" s="104">
         <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="O5" s="86">
         <v>80</v>
       </c>
-      <c r="O5" s="86">
-        <v>40</v>
-      </c>
       <c r="P5" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q5" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R5" s="104">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="S5" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T5" s="87"/>
       <c r="U5" s="87"/>
@@ -3314,14 +3446,14 @@
       </c>
       <c r="AE5" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>37450</v>
       </c>
       <c r="AF5" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG5" s="4">
         <f t="shared" si="4"/>
-        <v>1217.125</v>
+        <v>2434.25</v>
       </c>
       <c r="AH5" s="49">
         <f t="shared" si="5"/>
@@ -3329,18 +3461,18 @@
       </c>
       <c r="AI5" s="89">
         <f t="shared" si="6"/>
-        <v>17507.875</v>
+        <v>35015.75</v>
       </c>
       <c r="AJ5" s="91">
         <v>0.18</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" si="7"/>
-        <v>3151.4175</v>
+        <v>6302.835</v>
       </c>
       <c r="AL5" s="89">
         <f t="shared" si="8"/>
-        <v>20659.2925</v>
+        <v>41318.584999999999</v>
       </c>
       <c r="AM5" s="92"/>
       <c r="AN5" s="92"/>
@@ -3377,15 +3509,15 @@
       </c>
       <c r="J6" s="103"/>
       <c r="K6" s="105">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L6" s="105">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M6" s="105"/>
       <c r="N6" s="104">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O6" s="105">
         <v>40</v>
@@ -3402,7 +3534,7 @@
       </c>
       <c r="S6" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="T6" s="87"/>
       <c r="U6" s="87"/>
@@ -3423,14 +3555,14 @@
       </c>
       <c r="AE6" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>28733.200000000001</v>
       </c>
       <c r="AF6" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="4"/>
-        <v>1217.125</v>
+        <v>1867.6580000000001</v>
       </c>
       <c r="AH6" s="49">
         <f t="shared" si="5"/>
@@ -3438,18 +3570,18 @@
       </c>
       <c r="AI6" s="89">
         <f t="shared" si="6"/>
-        <v>17507.875</v>
+        <v>26865.542000000001</v>
       </c>
       <c r="AJ6" s="91">
         <v>0.18</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="7"/>
-        <v>3151.4175</v>
+        <v>4835.79756</v>
       </c>
       <c r="AL6" s="89">
         <f t="shared" si="8"/>
-        <v>20659.2925</v>
+        <v>31701.33956</v>
       </c>
       <c r="AM6" s="92"/>
       <c r="AN6" s="92"/>
@@ -3618,18 +3750,18 @@
         <v>40</v>
       </c>
       <c r="P8" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R8" s="104">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="S8" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="T8" s="87"/>
       <c r="U8" s="87"/>
@@ -3650,14 +3782,14 @@
       </c>
       <c r="AE8" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>24536.2</v>
       </c>
       <c r="AF8" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG8" s="4">
         <f t="shared" si="4"/>
-        <v>1217.125</v>
+        <v>1594.8530000000001</v>
       </c>
       <c r="AH8" s="49">
         <f t="shared" si="5"/>
@@ -3665,18 +3797,18 @@
       </c>
       <c r="AI8" s="89">
         <f t="shared" si="6"/>
-        <v>17507.875</v>
+        <v>22941.347000000002</v>
       </c>
       <c r="AJ8" s="91">
         <v>0.18</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" si="7"/>
-        <v>3151.4175</v>
+        <v>4129.4424600000002</v>
       </c>
       <c r="AL8" s="89">
         <f t="shared" si="8"/>
-        <v>20659.2925</v>
+        <v>27070.78946</v>
       </c>
       <c r="AN8"/>
       <c r="AP8" s="92"/>
@@ -3711,15 +3843,15 @@
       </c>
       <c r="J9" s="52"/>
       <c r="K9" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L9" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M9" s="86"/>
       <c r="N9" s="104">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O9" s="86">
         <v>40</v>
@@ -3736,7 +3868,7 @@
       </c>
       <c r="S9" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="T9" s="87"/>
       <c r="U9" s="87"/>
@@ -3757,14 +3889,14 @@
       </c>
       <c r="AE9" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>28733.200000000001</v>
       </c>
       <c r="AF9" s="90">
         <v>0.1</v>
       </c>
       <c r="AG9" s="4">
         <f t="shared" si="4"/>
-        <v>1872.5</v>
+        <v>2873.32</v>
       </c>
       <c r="AH9" s="49">
         <f t="shared" si="5"/>
@@ -3772,18 +3904,18 @@
       </c>
       <c r="AI9" s="89">
         <f t="shared" si="6"/>
-        <v>16852.5</v>
+        <v>25859.88</v>
       </c>
       <c r="AJ9" s="91">
         <v>0.18</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="7"/>
-        <v>3033.45</v>
+        <v>4654.7784000000001</v>
       </c>
       <c r="AL9" s="89">
         <f t="shared" si="8"/>
-        <v>19885.95</v>
+        <v>30514.6584</v>
       </c>
       <c r="AN9"/>
       <c r="AP9" s="92"/>
@@ -4136,15 +4268,15 @@
       </c>
       <c r="J13" s="52"/>
       <c r="K13" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L13" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M13" s="86"/>
       <c r="N13" s="104">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O13" s="105">
         <v>40</v>
@@ -4161,7 +4293,7 @@
       </c>
       <c r="S13" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="T13" s="87"/>
       <c r="U13" s="87"/>
@@ -4182,14 +4314,14 @@
       </c>
       <c r="AE13" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>28733.200000000001</v>
       </c>
       <c r="AF13" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG13" s="4">
         <f t="shared" si="4"/>
-        <v>1217.125</v>
+        <v>1867.6580000000001</v>
       </c>
       <c r="AH13" s="49">
         <f t="shared" si="5"/>
@@ -4197,18 +4329,18 @@
       </c>
       <c r="AI13" s="89">
         <f t="shared" si="6"/>
-        <v>17507.875</v>
+        <v>26865.542000000001</v>
       </c>
       <c r="AJ13" s="91">
         <v>0.18</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="7"/>
-        <v>3151.4175</v>
+        <v>4835.79756</v>
       </c>
       <c r="AL13" s="89">
         <f t="shared" si="8"/>
-        <v>20659.2925</v>
+        <v>31701.33956</v>
       </c>
       <c r="AP13" s="92"/>
     </row>
@@ -4242,15 +4374,15 @@
       </c>
       <c r="J14" s="52"/>
       <c r="K14" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L14" s="86">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M14" s="86"/>
       <c r="N14" s="104">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O14" s="105">
         <v>40</v>
@@ -4267,7 +4399,7 @@
       </c>
       <c r="S14" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="T14" s="87"/>
       <c r="U14" s="87"/>
@@ -4288,14 +4420,14 @@
       </c>
       <c r="AE14" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>28733.200000000001</v>
       </c>
       <c r="AF14" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG14" s="4">
         <f t="shared" si="4"/>
-        <v>1217.125</v>
+        <v>1867.6580000000001</v>
       </c>
       <c r="AH14" s="49">
         <f t="shared" si="5"/>
@@ -4303,18 +4435,18 @@
       </c>
       <c r="AI14" s="89">
         <f t="shared" si="6"/>
-        <v>17507.875</v>
+        <v>26865.542000000001</v>
       </c>
       <c r="AJ14" s="91">
         <v>0.18</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="7"/>
-        <v>3151.4175</v>
+        <v>4835.79756</v>
       </c>
       <c r="AL14" s="89">
         <f t="shared" si="8"/>
-        <v>20659.2925</v>
+        <v>31701.33956</v>
       </c>
       <c r="AP14" s="92"/>
     </row>
@@ -4348,15 +4480,15 @@
       </c>
       <c r="J15" s="52"/>
       <c r="K15" s="105">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L15" s="105">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M15" s="105"/>
       <c r="N15" s="104">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="O15" s="86">
         <v>40</v>
@@ -4373,7 +4505,7 @@
       </c>
       <c r="S15" s="86">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="T15" s="87"/>
       <c r="U15" s="87"/>
@@ -4394,14 +4526,14 @@
       </c>
       <c r="AE15" s="89">
         <f t="shared" si="3"/>
-        <v>18725</v>
+        <v>28733.200000000001</v>
       </c>
       <c r="AF15" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG15" s="4">
         <f t="shared" si="4"/>
-        <v>1217.125</v>
+        <v>1867.6580000000001</v>
       </c>
       <c r="AH15" s="49">
         <f t="shared" si="5"/>
@@ -4409,18 +4541,18 @@
       </c>
       <c r="AI15" s="89">
         <f t="shared" si="6"/>
-        <v>17507.875</v>
+        <v>26865.542000000001</v>
       </c>
       <c r="AJ15" s="91">
         <v>0.18</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="7"/>
-        <v>3151.4175</v>
+        <v>4835.79756</v>
       </c>
       <c r="AL15" s="89">
         <f t="shared" si="8"/>
-        <v>20659.2925</v>
+        <v>31701.33956</v>
       </c>
       <c r="AP15" s="92"/>
     </row>
@@ -26070,21 +26202,21 @@
         <v>160</v>
       </c>
       <c r="O230" s="86">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="P230" s="86">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="Q230" s="105">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="R230" s="104">
         <f t="shared" si="88"/>
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="S230" s="86">
         <f t="shared" si="90"/>
-        <v>400</v>
+        <v>640</v>
       </c>
       <c r="T230" s="87"/>
       <c r="U230" s="87"/>
@@ -26105,14 +26237,14 @@
       </c>
       <c r="AE230" s="89">
         <f t="shared" si="91"/>
-        <v>37450</v>
+        <v>54883.6</v>
       </c>
       <c r="AF230" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG230" s="4">
         <f t="shared" si="96"/>
-        <v>2434.25</v>
+        <v>3567.4340000000002</v>
       </c>
       <c r="AH230" s="49">
         <f t="shared" si="92"/>
@@ -26120,18 +26252,18 @@
       </c>
       <c r="AI230" s="89">
         <f t="shared" si="93"/>
-        <v>35015.75</v>
+        <v>51316.165999999997</v>
       </c>
       <c r="AJ230" s="91">
         <v>0.18</v>
       </c>
       <c r="AK230" s="5">
         <f t="shared" si="94"/>
-        <v>6302.835</v>
+        <v>9236.9098799999992</v>
       </c>
       <c r="AL230" s="89">
         <f t="shared" si="95"/>
-        <v>41318.584999999999</v>
+        <v>60553.075879999997</v>
       </c>
       <c r="AP230" s="92"/>
     </row>
@@ -34179,32 +34311,32 @@
       </c>
       <c r="J310" s="52"/>
       <c r="K310" s="86">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="L310" s="86">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="M310" s="86"/>
       <c r="N310" s="104">
         <f t="shared" si="98"/>
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="O310" s="86">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="P310" s="86">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="Q310" s="86">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="R310" s="104">
         <f t="shared" si="97"/>
-        <v>360</v>
+        <v>1080</v>
       </c>
       <c r="S310" s="86">
         <f t="shared" si="99"/>
-        <v>600</v>
+        <v>1640</v>
       </c>
       <c r="T310" s="87"/>
       <c r="U310" s="87"/>
@@ -34225,14 +34357,14 @@
       </c>
       <c r="AE310" s="89">
         <f t="shared" si="101"/>
-        <v>56175</v>
+        <v>148508.6</v>
       </c>
       <c r="AF310" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG310" s="4">
         <f t="shared" si="100"/>
-        <v>3651.375</v>
+        <v>9653.0590000000011</v>
       </c>
       <c r="AH310" s="49">
         <f t="shared" si="102"/>
@@ -34240,18 +34372,18 @@
       </c>
       <c r="AI310" s="89">
         <f t="shared" si="103"/>
-        <v>52523.625</v>
+        <v>138855.541</v>
       </c>
       <c r="AJ310" s="91">
         <v>0.18</v>
       </c>
       <c r="AK310" s="5">
         <f t="shared" si="104"/>
-        <v>9454.2525000000005</v>
+        <v>24993.997379999997</v>
       </c>
       <c r="AL310" s="89">
         <f t="shared" si="105"/>
-        <v>61977.877500000002</v>
+        <v>163849.53837999998</v>
       </c>
       <c r="AP310" s="92"/>
     </row>
@@ -43920,12 +44052,12 @@
       <c r="AD433" s="100"/>
       <c r="AE433" s="100">
         <f>SUM(AE3:AE432)</f>
-        <v>3182536.9475000002</v>
+        <v>3385606.3474999992</v>
       </c>
       <c r="AF433" s="78"/>
       <c r="AG433" s="100">
         <f>SUM(AG3:AG432)</f>
-        <v>231924.90965000013</v>
+        <v>245755.58265000008</v>
       </c>
       <c r="AH433" s="100">
         <f>SUM(AH3:AH432)</f>
@@ -43933,15 +44065,15 @@
       </c>
       <c r="AI433" s="100">
         <f>SUM(AI3:AI432)</f>
-        <v>2950612.0378499995</v>
+        <v>3139850.7648500004</v>
       </c>
       <c r="AK433" s="100">
         <f>SUM(AK3:AK432)</f>
-        <v>531110.16681299964</v>
+        <v>565173.13767299964</v>
       </c>
       <c r="AL433" s="100">
         <f>SUM(AL3:AL432)</f>
-        <v>3481722.2046629954</v>
+        <v>3705023.9025229961</v>
       </c>
       <c r="AP433" s="92"/>
     </row>
@@ -46323,7 +46455,9 @@
       <c r="E459" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F459" s="94"/>
+      <c r="F459" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G459" s="94" t="s">
         <v>456</v>
       </c>
@@ -46413,7 +46547,9 @@
       <c r="E460" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F460" s="94"/>
+      <c r="F460" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G460" s="94" t="s">
         <v>139</v>
       </c>
@@ -46507,7 +46643,9 @@
       <c r="E461" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F461" s="94"/>
+      <c r="F461" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G461" s="94" t="s">
         <v>457</v>
       </c>
@@ -46595,7 +46733,9 @@
       <c r="E462" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F462" s="94"/>
+      <c r="F462" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G462" s="94" t="s">
         <v>458</v>
       </c>
@@ -46685,7 +46825,9 @@
       <c r="E463" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F463" s="94"/>
+      <c r="F463" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G463" s="94" t="s">
         <v>459</v>
       </c>
@@ -46773,7 +46915,9 @@
       <c r="E464" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F464" s="94"/>
+      <c r="F464" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G464" s="94" t="s">
         <v>460</v>
       </c>
@@ -46867,7 +47011,9 @@
       <c r="E465" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F465" s="94"/>
+      <c r="F465" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G465" s="94" t="s">
         <v>184</v>
       </c>
@@ -46959,7 +47105,9 @@
       <c r="E466" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F466" s="94"/>
+      <c r="F466" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G466" s="94" t="s">
         <v>461</v>
       </c>
@@ -47036,12 +47184,24 @@
       <c r="AP466" s="7"/>
     </row>
     <row r="467" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A467" s="94"/>
-      <c r="B467" s="76"/>
-      <c r="C467" s="94"/>
-      <c r="D467" s="102"/>
-      <c r="E467" s="94"/>
-      <c r="F467" s="94"/>
+      <c r="A467" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B467" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C467" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D467" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E467" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F467" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G467" s="94" t="s">
         <v>462</v>
       </c>
@@ -47114,12 +47274,24 @@
       <c r="AP467" s="7"/>
     </row>
     <row r="468" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A468" s="94"/>
-      <c r="B468" s="76"/>
-      <c r="C468" s="94"/>
-      <c r="D468" s="102"/>
-      <c r="E468" s="94"/>
-      <c r="F468" s="94"/>
+      <c r="A468" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B468" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C468" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D468" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E468" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F468" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G468" s="94" t="s">
         <v>204</v>
       </c>
@@ -47194,12 +47366,24 @@
       <c r="AP468" s="7"/>
     </row>
     <row r="469" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A469" s="94"/>
-      <c r="B469" s="76"/>
-      <c r="C469" s="94"/>
-      <c r="D469" s="102"/>
-      <c r="E469" s="94"/>
-      <c r="F469" s="94"/>
+      <c r="A469" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B469" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C469" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D469" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E469" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F469" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G469" s="94" t="s">
         <v>465</v>
       </c>
@@ -47276,12 +47460,24 @@
       <c r="AP469" s="7"/>
     </row>
     <row r="470" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A470" s="94"/>
-      <c r="B470" s="76"/>
-      <c r="C470" s="94"/>
-      <c r="D470" s="102"/>
-      <c r="E470" s="94"/>
-      <c r="F470" s="94"/>
+      <c r="A470" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B470" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C470" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D470" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E470" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F470" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G470" s="94" t="s">
         <v>466</v>
       </c>
@@ -47356,12 +47552,24 @@
       <c r="AP470" s="7"/>
     </row>
     <row r="471" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A471" s="94"/>
-      <c r="B471" s="76"/>
-      <c r="C471" s="94"/>
-      <c r="D471" s="102"/>
-      <c r="E471" s="94"/>
-      <c r="F471" s="94"/>
+      <c r="A471" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B471" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C471" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D471" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E471" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F471" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G471" s="94" t="s">
         <v>203</v>
       </c>
@@ -47434,12 +47642,24 @@
       <c r="AP471" s="7"/>
     </row>
     <row r="472" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A472" s="94"/>
-      <c r="B472" s="76"/>
-      <c r="C472" s="94"/>
-      <c r="D472" s="102"/>
-      <c r="E472" s="94"/>
-      <c r="F472" s="94"/>
+      <c r="A472" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B472" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C472" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D472" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E472" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F472" s="94" t="s">
+        <v>109</v>
+      </c>
       <c r="G472" s="94" t="s">
         <v>467</v>
       </c>
@@ -47516,12 +47736,24 @@
       <c r="AP472" s="7"/>
     </row>
     <row r="473" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A473" s="94"/>
-      <c r="B473" s="76"/>
-      <c r="C473" s="94"/>
-      <c r="D473" s="102"/>
-      <c r="E473" s="94"/>
-      <c r="F473" s="94"/>
+      <c r="A473" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B473" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C473" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D473" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E473" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F473" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G473" s="94" t="s">
         <v>468</v>
       </c>
@@ -47598,12 +47830,24 @@
       <c r="AP473" s="7"/>
     </row>
     <row r="474" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A474" s="94"/>
-      <c r="B474" s="76"/>
-      <c r="C474" s="94"/>
-      <c r="D474" s="102"/>
-      <c r="E474" s="94"/>
-      <c r="F474" s="94"/>
+      <c r="A474" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B474" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C474" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D474" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E474" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F474" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G474" s="94" t="s">
         <v>423</v>
       </c>
@@ -47678,12 +47922,24 @@
       <c r="AP474" s="7"/>
     </row>
     <row r="475" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A475" s="94"/>
-      <c r="B475" s="76"/>
-      <c r="C475" s="94"/>
-      <c r="D475" s="102"/>
-      <c r="E475" s="94"/>
-      <c r="F475" s="94"/>
+      <c r="A475" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B475" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C475" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D475" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E475" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F475" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G475" s="94" t="s">
         <v>297</v>
       </c>
@@ -47756,12 +48012,24 @@
       <c r="AP475" s="7"/>
     </row>
     <row r="476" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A476" s="94"/>
-      <c r="B476" s="76"/>
-      <c r="C476" s="94"/>
-      <c r="D476" s="102"/>
-      <c r="E476" s="94"/>
-      <c r="F476" s="94"/>
+      <c r="A476" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B476" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C476" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D476" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E476" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F476" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G476" s="94" t="s">
         <v>471</v>
       </c>
@@ -47834,12 +48102,24 @@
       <c r="AP476" s="7"/>
     </row>
     <row r="477" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A477" s="94"/>
-      <c r="B477" s="76"/>
-      <c r="C477" s="94"/>
-      <c r="D477" s="102"/>
-      <c r="E477" s="94"/>
-      <c r="F477" s="94"/>
+      <c r="A477" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B477" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C477" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D477" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E477" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F477" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G477" s="94" t="s">
         <v>294</v>
       </c>
@@ -47912,12 +48192,24 @@
       <c r="AP477" s="7"/>
     </row>
     <row r="478" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A478" s="94"/>
-      <c r="B478" s="76"/>
-      <c r="C478" s="94"/>
-      <c r="D478" s="102"/>
-      <c r="E478" s="94"/>
-      <c r="F478" s="94"/>
+      <c r="A478" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B478" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C478" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D478" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E478" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F478" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G478" s="94" t="s">
         <v>194</v>
       </c>
@@ -47990,12 +48282,24 @@
       <c r="AP478" s="7"/>
     </row>
     <row r="479" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A479" s="94"/>
-      <c r="B479" s="76"/>
-      <c r="C479" s="94"/>
-      <c r="D479" s="102"/>
-      <c r="E479" s="94"/>
-      <c r="F479" s="94"/>
+      <c r="A479" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B479" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C479" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D479" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E479" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F479" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G479" s="94" t="s">
         <v>472</v>
       </c>
@@ -48068,12 +48372,24 @@
       <c r="AP479" s="7"/>
     </row>
     <row r="480" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A480" s="94"/>
-      <c r="B480" s="76"/>
-      <c r="C480" s="94"/>
-      <c r="D480" s="102"/>
-      <c r="E480" s="94"/>
-      <c r="F480" s="94"/>
+      <c r="A480" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B480" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C480" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D480" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E480" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F480" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G480" s="94" t="s">
         <v>473</v>
       </c>
@@ -48146,12 +48462,24 @@
       <c r="AP480" s="7"/>
     </row>
     <row r="481" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A481" s="94"/>
-      <c r="B481" s="76"/>
-      <c r="C481" s="94"/>
-      <c r="D481" s="102"/>
-      <c r="E481" s="94"/>
-      <c r="F481" s="94"/>
+      <c r="A481" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B481" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C481" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D481" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E481" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F481" s="94" t="s">
+        <v>109</v>
+      </c>
       <c r="G481" s="94" t="s">
         <v>474</v>
       </c>
@@ -48226,12 +48554,24 @@
       <c r="AP481" s="7"/>
     </row>
     <row r="482" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A482" s="94"/>
-      <c r="B482" s="76"/>
-      <c r="C482" s="94"/>
-      <c r="D482" s="102"/>
-      <c r="E482" s="94"/>
-      <c r="F482" s="94"/>
+      <c r="A482" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B482" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C482" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D482" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E482" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F482" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G482" s="94" t="s">
         <v>475</v>
       </c>
@@ -48304,12 +48644,24 @@
       <c r="AP482" s="7"/>
     </row>
     <row r="483" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A483" s="94"/>
-      <c r="B483" s="76"/>
-      <c r="C483" s="94"/>
-      <c r="D483" s="102"/>
-      <c r="E483" s="94"/>
-      <c r="F483" s="94"/>
+      <c r="A483" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B483" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C483" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D483" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E483" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F483" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G483" s="94" t="s">
         <v>476</v>
       </c>
@@ -48386,12 +48738,24 @@
       <c r="AP483" s="7"/>
     </row>
     <row r="484" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A484" s="94"/>
-      <c r="B484" s="76"/>
-      <c r="C484" s="94"/>
-      <c r="D484" s="102"/>
-      <c r="E484" s="94"/>
-      <c r="F484" s="94"/>
+      <c r="A484" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B484" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C484" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D484" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E484" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F484" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G484" s="94" t="s">
         <v>477</v>
       </c>
@@ -48468,12 +48832,24 @@
       <c r="AP484" s="7"/>
     </row>
     <row r="485" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A485" s="94"/>
-      <c r="B485" s="76"/>
-      <c r="C485" s="94"/>
-      <c r="D485" s="102"/>
-      <c r="E485" s="94"/>
-      <c r="F485" s="94"/>
+      <c r="A485" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B485" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C485" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D485" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E485" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F485" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G485" s="94" t="s">
         <v>478</v>
       </c>
@@ -48546,12 +48922,24 @@
       <c r="AP485" s="7"/>
     </row>
     <row r="486" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A486" s="94"/>
-      <c r="B486" s="76"/>
-      <c r="C486" s="94"/>
-      <c r="D486" s="102"/>
-      <c r="E486" s="94"/>
-      <c r="F486" s="94"/>
+      <c r="A486" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B486" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C486" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D486" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E486" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F486" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G486" s="94" t="s">
         <v>479</v>
       </c>
@@ -48624,12 +49012,24 @@
       <c r="AP486" s="7"/>
     </row>
     <row r="487" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A487" s="94"/>
-      <c r="B487" s="76"/>
-      <c r="C487" s="94"/>
-      <c r="D487" s="102"/>
-      <c r="E487" s="94"/>
-      <c r="F487" s="94"/>
+      <c r="A487" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B487" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C487" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D487" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E487" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F487" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G487" s="94" t="s">
         <v>480</v>
       </c>
@@ -48702,12 +49102,24 @@
       <c r="AP487" s="7"/>
     </row>
     <row r="488" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A488" s="94"/>
-      <c r="B488" s="76"/>
-      <c r="C488" s="94"/>
-      <c r="D488" s="102"/>
-      <c r="E488" s="94"/>
-      <c r="F488" s="94"/>
+      <c r="A488" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B488" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C488" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D488" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E488" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F488" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G488" s="94" t="s">
         <v>481</v>
       </c>
@@ -48780,12 +49192,24 @@
       <c r="AP488" s="7"/>
     </row>
     <row r="489" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A489" s="94"/>
-      <c r="B489" s="76"/>
-      <c r="C489" s="94"/>
-      <c r="D489" s="102"/>
-      <c r="E489" s="94"/>
-      <c r="F489" s="94"/>
+      <c r="A489" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B489" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C489" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D489" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E489" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F489" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G489" s="94" t="s">
         <v>300</v>
       </c>
@@ -48858,12 +49282,24 @@
       <c r="AP489" s="7"/>
     </row>
     <row r="490" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A490" s="94"/>
-      <c r="B490" s="76"/>
-      <c r="C490" s="94"/>
-      <c r="D490" s="102"/>
-      <c r="E490" s="94"/>
-      <c r="F490" s="94"/>
+      <c r="A490" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B490" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C490" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D490" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E490" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F490" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G490" s="94" t="s">
         <v>271</v>
       </c>
@@ -48936,12 +49372,24 @@
       <c r="AP490" s="7"/>
     </row>
     <row r="491" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A491" s="94"/>
-      <c r="B491" s="76"/>
-      <c r="C491" s="94"/>
-      <c r="D491" s="102"/>
-      <c r="E491" s="94"/>
-      <c r="F491" s="94"/>
+      <c r="A491" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B491" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C491" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D491" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E491" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F491" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G491" s="94" t="s">
         <v>139</v>
       </c>
@@ -49014,12 +49462,24 @@
       <c r="AP491" s="7"/>
     </row>
     <row r="492" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A492" s="94"/>
-      <c r="B492" s="76"/>
-      <c r="C492" s="94"/>
-      <c r="D492" s="102"/>
-      <c r="E492" s="94"/>
-      <c r="F492" s="94"/>
+      <c r="A492" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B492" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C492" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D492" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E492" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F492" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G492" s="94" t="s">
         <v>303</v>
       </c>
@@ -49092,12 +49552,24 @@
       <c r="AP492" s="7"/>
     </row>
     <row r="493" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A493" s="94"/>
-      <c r="B493" s="76"/>
-      <c r="C493" s="94"/>
-      <c r="D493" s="102"/>
-      <c r="E493" s="94"/>
-      <c r="F493" s="94"/>
+      <c r="A493" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B493" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C493" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D493" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E493" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F493" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G493" s="94" t="s">
         <v>177</v>
       </c>
@@ -49170,12 +49642,24 @@
       <c r="AP493" s="7"/>
     </row>
     <row r="494" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A494" s="94"/>
-      <c r="B494" s="76"/>
-      <c r="C494" s="94"/>
-      <c r="D494" s="102"/>
-      <c r="E494" s="94"/>
-      <c r="F494" s="94"/>
+      <c r="A494" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B494" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C494" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D494" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E494" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F494" s="94" t="s">
+        <v>109</v>
+      </c>
       <c r="G494" s="94" t="s">
         <v>482</v>
       </c>
@@ -49252,12 +49736,24 @@
       <c r="AP494" s="7"/>
     </row>
     <row r="495" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A495" s="94"/>
-      <c r="B495" s="76"/>
-      <c r="C495" s="94"/>
-      <c r="D495" s="102"/>
-      <c r="E495" s="94"/>
-      <c r="F495" s="94"/>
+      <c r="A495" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B495" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C495" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D495" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E495" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F495" s="94" t="s">
+        <v>109</v>
+      </c>
       <c r="G495" s="94" t="s">
         <v>167</v>
       </c>
@@ -49338,12 +49834,24 @@
       <c r="AP495" s="7"/>
     </row>
     <row r="496" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A496" s="94"/>
-      <c r="B496" s="76"/>
-      <c r="C496" s="94"/>
-      <c r="D496" s="102"/>
-      <c r="E496" s="94"/>
-      <c r="F496" s="94"/>
+      <c r="A496" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B496" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C496" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D496" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E496" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F496" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G496" s="94" t="s">
         <v>483</v>
       </c>
@@ -49426,12 +49934,24 @@
       <c r="AP496" s="7"/>
     </row>
     <row r="497" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A497" s="94"/>
-      <c r="B497" s="76"/>
-      <c r="C497" s="94"/>
-      <c r="D497" s="102"/>
-      <c r="E497" s="94"/>
-      <c r="F497" s="94"/>
+      <c r="A497" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B497" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C497" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D497" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E497" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F497" s="94" t="s">
+        <v>109</v>
+      </c>
       <c r="G497" s="94" t="s">
         <v>168</v>
       </c>
@@ -49504,12 +50024,24 @@
       <c r="AP497" s="7"/>
     </row>
     <row r="498" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A498" s="94"/>
-      <c r="B498" s="76"/>
-      <c r="C498" s="94"/>
-      <c r="D498" s="102"/>
-      <c r="E498" s="94"/>
-      <c r="F498" s="94"/>
+      <c r="A498" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B498" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C498" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D498" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E498" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F498" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G498" s="94" t="s">
         <v>484</v>
       </c>
@@ -49582,12 +50114,24 @@
       <c r="AP498" s="7"/>
     </row>
     <row r="499" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A499" s="94"/>
-      <c r="B499" s="76"/>
-      <c r="C499" s="94"/>
-      <c r="D499" s="102"/>
-      <c r="E499" s="94"/>
-      <c r="F499" s="94"/>
+      <c r="A499" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B499" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C499" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D499" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E499" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F499" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G499" s="94" t="s">
         <v>267</v>
       </c>
@@ -49660,12 +50204,24 @@
       <c r="AP499" s="7"/>
     </row>
     <row r="500" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A500" s="94"/>
-      <c r="B500" s="76"/>
-      <c r="C500" s="94"/>
-      <c r="D500" s="102"/>
-      <c r="E500" s="94"/>
-      <c r="F500" s="94"/>
+      <c r="A500" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B500" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C500" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D500" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E500" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F500" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G500" s="94" t="s">
         <v>485</v>
       </c>
@@ -49738,12 +50294,24 @@
       <c r="AP500" s="7"/>
     </row>
     <row r="501" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A501" s="94"/>
-      <c r="B501" s="76"/>
-      <c r="C501" s="94"/>
-      <c r="D501" s="102"/>
-      <c r="E501" s="94"/>
-      <c r="F501" s="94"/>
+      <c r="A501" s="85">
+        <v>46217</v>
+      </c>
+      <c r="B501" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C501" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D501" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E501" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F501" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G501" s="94" t="s">
         <v>302</v>
       </c>
@@ -49816,15 +50384,33 @@
       <c r="AP501" s="7"/>
     </row>
     <row r="502" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A502" s="94"/>
-      <c r="B502" s="76"/>
-      <c r="C502" s="94"/>
-      <c r="D502" s="102"/>
-      <c r="E502" s="94"/>
-      <c r="F502" s="94"/>
-      <c r="G502" s="94"/>
-      <c r="H502" s="94"/>
-      <c r="I502" s="94"/>
+      <c r="A502" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B502" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C502" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D502" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E502" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F502" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G502" s="94" t="s">
+        <v>486</v>
+      </c>
+      <c r="H502" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I502" s="94" t="s">
+        <v>427</v>
+      </c>
       <c r="J502" s="52"/>
       <c r="K502" s="52"/>
       <c r="L502" s="52"/>
@@ -49833,16 +50419,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O502" s="52"/>
-      <c r="P502" s="52"/>
-      <c r="Q502" s="52"/>
+      <c r="O502" s="52">
+        <v>15</v>
+      </c>
+      <c r="P502" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q502" s="52">
+        <v>15</v>
+      </c>
       <c r="R502" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S502" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB502" s="88">
         <v>39.270000000000003</v>
@@ -49855,14 +50447,14 @@
       </c>
       <c r="AE502" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF502" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG502" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH502" s="49">
         <f t="shared" si="136"/>
@@ -49870,31 +50462,49 @@
       </c>
       <c r="AI502" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ502" s="91">
         <v>0.18</v>
       </c>
       <c r="AK502" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL502" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP502" s="7"/>
     </row>
     <row r="503" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A503" s="94"/>
-      <c r="B503" s="76"/>
-      <c r="C503" s="94"/>
-      <c r="D503" s="102"/>
-      <c r="E503" s="94"/>
-      <c r="F503" s="94"/>
-      <c r="G503" s="94"/>
-      <c r="H503" s="94"/>
-      <c r="I503" s="94"/>
+      <c r="A503" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B503" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C503" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D503" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E503" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F503" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G503" s="94" t="s">
+        <v>487</v>
+      </c>
+      <c r="H503" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I503" s="94" t="s">
+        <v>427</v>
+      </c>
       <c r="J503" s="52"/>
       <c r="K503" s="52"/>
       <c r="L503" s="52"/>
@@ -49905,14 +50515,16 @@
       </c>
       <c r="O503" s="52"/>
       <c r="P503" s="52"/>
-      <c r="Q503" s="52"/>
+      <c r="Q503" s="52">
+        <v>40</v>
+      </c>
       <c r="R503" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S503" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB503" s="88">
         <v>39.270000000000003</v>
@@ -49925,14 +50537,14 @@
       </c>
       <c r="AE503" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF503" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG503" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH503" s="49">
         <f t="shared" si="136"/>
@@ -49940,31 +50552,49 @@
       </c>
       <c r="AI503" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ503" s="91">
         <v>0.18</v>
       </c>
       <c r="AK503" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL503" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP503" s="7"/>
     </row>
     <row r="504" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A504" s="94"/>
-      <c r="B504" s="76"/>
-      <c r="C504" s="94"/>
-      <c r="D504" s="102"/>
-      <c r="E504" s="94"/>
-      <c r="F504" s="94"/>
-      <c r="G504" s="94"/>
-      <c r="H504" s="94"/>
-      <c r="I504" s="94"/>
+      <c r="A504" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B504" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C504" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D504" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E504" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F504" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G504" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="H504" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I504" s="94" t="s">
+        <v>427</v>
+      </c>
       <c r="J504" s="52"/>
       <c r="K504" s="52"/>
       <c r="L504" s="52"/>
@@ -49973,16 +50603,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O504" s="52"/>
-      <c r="P504" s="52"/>
-      <c r="Q504" s="52"/>
+      <c r="O504" s="52">
+        <v>16</v>
+      </c>
+      <c r="P504" s="52">
+        <v>12</v>
+      </c>
+      <c r="Q504" s="52">
+        <v>16</v>
+      </c>
       <c r="R504" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S504" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB504" s="88">
         <v>39.270000000000003</v>
@@ -49995,14 +50631,14 @@
       </c>
       <c r="AE504" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>3196.16</v>
       </c>
       <c r="AF504" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG504" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>207.75039999999998</v>
       </c>
       <c r="AH504" s="49">
         <f t="shared" si="136"/>
@@ -50010,31 +50646,49 @@
       </c>
       <c r="AI504" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2988.4096</v>
       </c>
       <c r="AJ504" s="91">
         <v>0.18</v>
       </c>
       <c r="AK504" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>537.91372799999999</v>
       </c>
       <c r="AL504" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3526.3233279999999</v>
       </c>
       <c r="AP504" s="7"/>
     </row>
     <row r="505" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A505" s="94"/>
-      <c r="B505" s="76"/>
-      <c r="C505" s="94"/>
-      <c r="D505" s="102"/>
-      <c r="E505" s="94"/>
-      <c r="F505" s="94"/>
-      <c r="G505" s="94"/>
-      <c r="H505" s="94"/>
-      <c r="I505" s="94"/>
+      <c r="A505" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B505" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C505" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D505" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E505" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F505" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G505" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="H505" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I505" s="94" t="s">
+        <v>427</v>
+      </c>
       <c r="J505" s="52"/>
       <c r="K505" s="52"/>
       <c r="L505" s="52"/>
@@ -50044,15 +50698,19 @@
         <v>0</v>
       </c>
       <c r="O505" s="52"/>
-      <c r="P505" s="52"/>
-      <c r="Q505" s="52"/>
+      <c r="P505" s="52">
+        <v>20</v>
+      </c>
+      <c r="Q505" s="52">
+        <v>20</v>
+      </c>
       <c r="R505" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S505" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB505" s="88">
         <v>39.270000000000003</v>
@@ -50065,14 +50723,14 @@
       </c>
       <c r="AE505" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF505" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG505" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH505" s="49">
         <f t="shared" si="136"/>
@@ -50080,31 +50738,49 @@
       </c>
       <c r="AI505" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ505" s="91">
         <v>0.18</v>
       </c>
       <c r="AK505" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL505" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP505" s="7"/>
     </row>
     <row r="506" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A506" s="94"/>
-      <c r="B506" s="76"/>
-      <c r="C506" s="94"/>
-      <c r="D506" s="102"/>
-      <c r="E506" s="94"/>
-      <c r="F506" s="94"/>
-      <c r="G506" s="94"/>
-      <c r="H506" s="94"/>
-      <c r="I506" s="94"/>
+      <c r="A506" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B506" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C506" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D506" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E506" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F506" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G506" s="94" t="s">
+        <v>488</v>
+      </c>
+      <c r="H506" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I506" s="94" t="s">
+        <v>427</v>
+      </c>
       <c r="J506" s="52"/>
       <c r="K506" s="52"/>
       <c r="L506" s="52"/>
@@ -50113,16 +50789,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O506" s="52"/>
-      <c r="P506" s="52"/>
-      <c r="Q506" s="52"/>
+      <c r="O506" s="52">
+        <v>15</v>
+      </c>
+      <c r="P506" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q506" s="52">
+        <v>15</v>
+      </c>
       <c r="R506" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S506" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB506" s="88">
         <v>39.270000000000003</v>
@@ -50135,14 +50817,14 @@
       </c>
       <c r="AE506" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF506" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG506" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH506" s="49">
         <f t="shared" si="136"/>
@@ -50150,49 +50832,79 @@
       </c>
       <c r="AI506" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ506" s="91">
         <v>0.18</v>
       </c>
       <c r="AK506" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL506" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP506" s="7"/>
     </row>
     <row r="507" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A507" s="94"/>
-      <c r="B507" s="76"/>
-      <c r="C507" s="94"/>
-      <c r="D507" s="102"/>
-      <c r="E507" s="94"/>
-      <c r="F507" s="94"/>
-      <c r="G507" s="94"/>
-      <c r="H507" s="94"/>
-      <c r="I507" s="94"/>
-      <c r="J507" s="52"/>
-      <c r="K507" s="52"/>
-      <c r="L507" s="52"/>
+      <c r="A507" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B507" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C507" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D507" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E507" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F507" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G507" s="94" t="s">
+        <v>489</v>
+      </c>
+      <c r="H507" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I507" s="94" t="s">
+        <v>427</v>
+      </c>
+      <c r="J507" s="52">
+        <v>40</v>
+      </c>
+      <c r="K507" s="52">
+        <v>39</v>
+      </c>
+      <c r="L507" s="52">
+        <v>40</v>
+      </c>
       <c r="M507" s="52"/>
       <c r="N507" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O507" s="52"/>
-      <c r="P507" s="52"/>
-      <c r="Q507" s="52"/>
+        <v>79</v>
+      </c>
+      <c r="O507" s="52">
+        <v>40</v>
+      </c>
+      <c r="P507" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q507" s="52">
+        <v>40</v>
+      </c>
       <c r="R507" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S507" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="AB507" s="88">
         <v>39.270000000000003</v>
@@ -50205,53 +50917,75 @@
       </c>
       <c r="AE507" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>23076.297500000001</v>
       </c>
       <c r="AF507" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG507" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1499.9593375000002</v>
       </c>
       <c r="AH507" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI507" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>21576.3381625</v>
       </c>
       <c r="AJ507" s="91">
         <v>0.18</v>
       </c>
       <c r="AK507" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>3883.7408692499998</v>
       </c>
       <c r="AL507" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>25460.07903175</v>
       </c>
       <c r="AP507" s="7"/>
     </row>
     <row r="508" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A508" s="94"/>
-      <c r="B508" s="76"/>
-      <c r="C508" s="94"/>
-      <c r="D508" s="102"/>
-      <c r="E508" s="94"/>
-      <c r="F508" s="94"/>
-      <c r="G508" s="94"/>
-      <c r="H508" s="94"/>
-      <c r="I508" s="94"/>
+      <c r="A508" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B508" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C508" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D508" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E508" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F508" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G508" s="94" t="s">
+        <v>328</v>
+      </c>
+      <c r="H508" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I508" s="94" t="s">
+        <v>246</v>
+      </c>
       <c r="J508" s="52"/>
-      <c r="K508" s="52"/>
-      <c r="L508" s="52"/>
+      <c r="K508" s="52">
+        <v>40</v>
+      </c>
+      <c r="L508" s="52">
+        <v>40</v>
+      </c>
       <c r="M508" s="52"/>
       <c r="N508" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O508" s="52"/>
       <c r="P508" s="52"/>
@@ -50262,7 +50996,7 @@
       </c>
       <c r="S508" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB508" s="88">
         <v>39.270000000000003</v>
@@ -50275,14 +51009,14 @@
       </c>
       <c r="AE508" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>10008.200000000001</v>
       </c>
       <c r="AF508" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG508" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>650.53300000000002</v>
       </c>
       <c r="AH508" s="49">
         <f t="shared" si="136"/>
@@ -50290,31 +51024,49 @@
       </c>
       <c r="AI508" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>9357.6670000000013</v>
       </c>
       <c r="AJ508" s="91">
         <v>0.18</v>
       </c>
       <c r="AK508" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>1684.3800600000002</v>
       </c>
       <c r="AL508" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>11042.047060000001</v>
       </c>
       <c r="AP508" s="7"/>
     </row>
     <row r="509" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A509" s="94"/>
-      <c r="B509" s="76"/>
-      <c r="C509" s="94"/>
-      <c r="D509" s="102"/>
-      <c r="E509" s="94"/>
-      <c r="F509" s="94"/>
-      <c r="G509" s="94"/>
-      <c r="H509" s="94"/>
-      <c r="I509" s="94"/>
+      <c r="A509" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B509" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C509" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D509" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E509" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F509" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G509" s="94" t="s">
+        <v>490</v>
+      </c>
+      <c r="H509" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I509" s="94" t="s">
+        <v>246</v>
+      </c>
       <c r="J509" s="52"/>
       <c r="K509" s="52"/>
       <c r="L509" s="52"/>
@@ -50323,16 +51075,22 @@
         <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="O509" s="52"/>
-      <c r="P509" s="52"/>
-      <c r="Q509" s="52"/>
+      <c r="O509" s="52">
+        <v>13</v>
+      </c>
+      <c r="P509" s="52">
+        <v>12</v>
+      </c>
+      <c r="Q509" s="52">
+        <v>15</v>
+      </c>
       <c r="R509" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S509" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB509" s="88">
         <v>39.270000000000003</v>
@@ -50345,14 +51103,14 @@
       </c>
       <c r="AE509" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF509" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG509" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH509" s="49">
         <f t="shared" si="136"/>
@@ -50360,38 +51118,62 @@
       </c>
       <c r="AI509" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ509" s="91">
         <v>0.18</v>
       </c>
       <c r="AK509" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL509" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP509" s="7"/>
     </row>
     <row r="510" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A510" s="94"/>
-      <c r="B510" s="76"/>
-      <c r="C510" s="94"/>
-      <c r="D510" s="102"/>
-      <c r="E510" s="94"/>
-      <c r="F510" s="94"/>
-      <c r="G510" s="94"/>
-      <c r="H510" s="94"/>
-      <c r="I510" s="94"/>
-      <c r="J510" s="52"/>
-      <c r="K510" s="52"/>
-      <c r="L510" s="52"/>
+      <c r="A510" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B510" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C510" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D510" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E510" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F510" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G510" s="94" t="s">
+        <v>491</v>
+      </c>
+      <c r="H510" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I510" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="J510" s="52">
+        <v>40</v>
+      </c>
+      <c r="K510" s="52">
+        <v>20</v>
+      </c>
+      <c r="L510" s="52">
+        <v>20</v>
+      </c>
       <c r="M510" s="52"/>
       <c r="N510" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O510" s="52"/>
       <c r="P510" s="52"/>
@@ -50402,7 +51184,7 @@
       </c>
       <c r="S510" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB510" s="88">
         <v>39.270000000000003</v>
@@ -50415,64 +51197,94 @@
       </c>
       <c r="AE510" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>9480.5</v>
       </c>
       <c r="AF510" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG510" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>616.23250000000007</v>
       </c>
       <c r="AH510" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI510" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8864.2674999999999</v>
       </c>
       <c r="AJ510" s="91">
         <v>0.18</v>
       </c>
       <c r="AK510" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>1595.5681499999998</v>
       </c>
       <c r="AL510" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>10459.835649999999</v>
       </c>
       <c r="AP510" s="7"/>
     </row>
     <row r="511" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A511" s="94"/>
-      <c r="B511" s="76"/>
-      <c r="C511" s="94"/>
-      <c r="D511" s="102"/>
-      <c r="E511" s="94"/>
-      <c r="F511" s="94"/>
-      <c r="G511" s="94"/>
-      <c r="H511" s="94"/>
-      <c r="I511" s="94"/>
-      <c r="J511" s="52"/>
-      <c r="K511" s="52"/>
-      <c r="L511" s="52"/>
+      <c r="A511" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B511" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C511" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D511" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E511" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F511" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G511" s="94" t="s">
+        <v>492</v>
+      </c>
+      <c r="H511" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I511" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="J511" s="52">
+        <v>12</v>
+      </c>
+      <c r="K511" s="52">
+        <v>12</v>
+      </c>
+      <c r="L511" s="52">
+        <v>6</v>
+      </c>
       <c r="M511" s="52"/>
       <c r="N511" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O511" s="52"/>
-      <c r="P511" s="52"/>
-      <c r="Q511" s="52"/>
+        <v>18</v>
+      </c>
+      <c r="O511" s="52">
+        <v>6</v>
+      </c>
+      <c r="P511" s="52">
+        <v>12</v>
+      </c>
+      <c r="Q511" s="52">
+        <v>12</v>
+      </c>
       <c r="R511" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S511" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB511" s="88">
         <v>39.270000000000003</v>
@@ -50485,64 +51297,94 @@
       </c>
       <c r="AE511" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>5773.9650000000001</v>
       </c>
       <c r="AF511" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG511" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>375.307725</v>
       </c>
       <c r="AH511" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI511" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>5398.6572750000005</v>
       </c>
       <c r="AJ511" s="91">
         <v>0.18</v>
       </c>
       <c r="AK511" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>971.7583095</v>
       </c>
       <c r="AL511" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>6370.4155845000005</v>
       </c>
       <c r="AP511" s="7"/>
     </row>
     <row r="512" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A512" s="94"/>
-      <c r="B512" s="76"/>
-      <c r="C512" s="94"/>
-      <c r="D512" s="102"/>
-      <c r="E512" s="94"/>
-      <c r="F512" s="94"/>
-      <c r="G512" s="94"/>
-      <c r="H512" s="94"/>
-      <c r="I512" s="94"/>
-      <c r="J512" s="52"/>
-      <c r="K512" s="52"/>
-      <c r="L512" s="52"/>
+      <c r="A512" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B512" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C512" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D512" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E512" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F512" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G512" s="94" t="s">
+        <v>328</v>
+      </c>
+      <c r="H512" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I512" s="94" t="s">
+        <v>494</v>
+      </c>
+      <c r="J512" s="52">
+        <v>10</v>
+      </c>
+      <c r="K512" s="52">
+        <v>20</v>
+      </c>
+      <c r="L512" s="52">
+        <v>20</v>
+      </c>
       <c r="M512" s="52"/>
       <c r="N512" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O512" s="52"/>
-      <c r="P512" s="52"/>
-      <c r="Q512" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O512" s="52">
+        <v>13</v>
+      </c>
+      <c r="P512" s="52">
+        <v>12</v>
+      </c>
+      <c r="Q512" s="52">
+        <v>15</v>
+      </c>
       <c r="R512" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S512" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB512" s="88">
         <v>39.270000000000003</v>
@@ -50555,64 +51397,94 @@
       </c>
       <c r="AE512" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>9028.7999999999993</v>
       </c>
       <c r="AF512" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG512" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>586.87199999999996</v>
       </c>
       <c r="AH512" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI512" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8441.9279999999999</v>
       </c>
       <c r="AJ512" s="91">
         <v>0.18</v>
       </c>
       <c r="AK512" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>1519.5470399999999</v>
       </c>
       <c r="AL512" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>9961.4750399999994</v>
       </c>
       <c r="AP512" s="7"/>
     </row>
     <row r="513" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A513" s="94"/>
-      <c r="B513" s="76"/>
-      <c r="C513" s="94"/>
-      <c r="D513" s="102"/>
-      <c r="E513" s="94"/>
-      <c r="F513" s="94"/>
-      <c r="G513" s="94"/>
-      <c r="H513" s="94"/>
-      <c r="I513" s="94"/>
-      <c r="J513" s="52"/>
-      <c r="K513" s="52"/>
-      <c r="L513" s="52"/>
+      <c r="A513" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B513" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C513" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D513" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E513" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F513" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G513" s="94" t="s">
+        <v>493</v>
+      </c>
+      <c r="H513" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I513" s="94" t="s">
+        <v>495</v>
+      </c>
+      <c r="J513" s="52">
+        <v>40</v>
+      </c>
+      <c r="K513" s="52">
+        <v>40</v>
+      </c>
+      <c r="L513" s="52">
+        <v>40</v>
+      </c>
       <c r="M513" s="52"/>
       <c r="N513" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="O513" s="52"/>
-      <c r="P513" s="52"/>
-      <c r="Q513" s="52"/>
+        <v>80</v>
+      </c>
+      <c r="O513" s="52">
+        <v>40</v>
+      </c>
+      <c r="P513" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q513" s="52">
+        <v>40</v>
+      </c>
       <c r="R513" s="104">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S513" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AB513" s="88">
         <v>39.270000000000003</v>
@@ -50625,53 +51497,75 @@
       </c>
       <c r="AE513" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>23201.399999999998</v>
       </c>
       <c r="AF513" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG513" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1508.0909999999999</v>
       </c>
       <c r="AH513" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI513" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>21693.308999999997</v>
       </c>
       <c r="AJ513" s="91">
         <v>0.18</v>
       </c>
       <c r="AK513" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>3904.7956199999994</v>
       </c>
       <c r="AL513" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>25598.104619999998</v>
       </c>
       <c r="AP513" s="7"/>
     </row>
     <row r="514" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A514" s="94"/>
-      <c r="B514" s="76"/>
-      <c r="C514" s="94"/>
-      <c r="D514" s="102"/>
-      <c r="E514" s="94"/>
-      <c r="F514" s="94"/>
-      <c r="G514" s="94"/>
-      <c r="H514" s="94"/>
-      <c r="I514" s="94"/>
+      <c r="A514" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B514" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C514" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D514" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E514" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F514" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G514" s="94" t="s">
+        <v>496</v>
+      </c>
+      <c r="H514" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I514" s="94" t="s">
+        <v>128</v>
+      </c>
       <c r="J514" s="52"/>
-      <c r="K514" s="52"/>
-      <c r="L514" s="52"/>
+      <c r="K514" s="52">
+        <v>20</v>
+      </c>
+      <c r="L514" s="52">
+        <v>20</v>
+      </c>
       <c r="M514" s="52"/>
       <c r="N514" s="104">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O514" s="52"/>
       <c r="P514" s="52"/>
@@ -50682,7 +51576,7 @@
       </c>
       <c r="S514" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB514" s="88">
         <v>39.270000000000003</v>
@@ -50695,14 +51589,14 @@
       </c>
       <c r="AE514" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF514" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG514" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH514" s="49">
         <f t="shared" si="136"/>
@@ -50710,32 +51604,52 @@
       </c>
       <c r="AI514" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ514" s="91">
         <v>0.18</v>
       </c>
       <c r="AK514" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL514" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP514" s="7"/>
     </row>
     <row r="515" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A515" s="94"/>
-      <c r="B515" s="76"/>
-      <c r="C515" s="94"/>
-      <c r="D515" s="102"/>
-      <c r="E515" s="94"/>
-      <c r="F515" s="94"/>
-      <c r="G515" s="94"/>
-      <c r="H515" s="94"/>
-      <c r="I515" s="94"/>
-      <c r="J515" s="52"/>
+      <c r="A515" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B515" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C515" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D515" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E515" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F515" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G515" s="94" t="s">
+        <v>497</v>
+      </c>
+      <c r="H515" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I515" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="J515" s="52">
+        <v>40</v>
+      </c>
       <c r="K515" s="52"/>
       <c r="L515" s="52"/>
       <c r="M515" s="52"/>
@@ -50752,7 +51666,7 @@
       </c>
       <c r="S515" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB515" s="88">
         <v>39.270000000000003</v>
@@ -50765,47 +51679,67 @@
       </c>
       <c r="AE515" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF515" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG515" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH515" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI515" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ515" s="91">
         <v>0.18</v>
       </c>
       <c r="AK515" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL515" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP515" s="7"/>
     </row>
     <row r="516" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A516" s="94"/>
-      <c r="B516" s="76"/>
-      <c r="C516" s="94"/>
-      <c r="D516" s="102"/>
-      <c r="E516" s="94"/>
-      <c r="F516" s="94"/>
-      <c r="G516" s="94"/>
-      <c r="H516" s="94"/>
-      <c r="I516" s="94"/>
-      <c r="J516" s="52"/>
+      <c r="A516" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B516" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C516" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D516" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E516" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F516" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G516" s="94" t="s">
+        <v>498</v>
+      </c>
+      <c r="H516" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I516" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="J516" s="52">
+        <v>12</v>
+      </c>
       <c r="K516" s="52"/>
       <c r="L516" s="52"/>
       <c r="M516" s="52"/>
@@ -50822,7 +51756,7 @@
       </c>
       <c r="S516" s="86">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB516" s="88">
         <v>39.270000000000003</v>
@@ -50835,46 +51769,64 @@
       </c>
       <c r="AE516" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF516" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG516" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>87.289800000000014</v>
       </c>
       <c r="AH516" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI516" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1255.6302000000001</v>
       </c>
       <c r="AJ516" s="91">
         <v>0.18</v>
       </c>
       <c r="AK516" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>226.01343600000001</v>
       </c>
       <c r="AL516" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1481.643636</v>
       </c>
       <c r="AP516" s="7"/>
     </row>
     <row r="517" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A517" s="94"/>
-      <c r="B517" s="76"/>
-      <c r="C517" s="94"/>
-      <c r="D517" s="102"/>
-      <c r="E517" s="94"/>
-      <c r="F517" s="94"/>
-      <c r="G517" s="94"/>
-      <c r="H517" s="94"/>
-      <c r="I517" s="94"/>
+      <c r="A517" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B517" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C517" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D517" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E517" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F517" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G517" s="94" t="s">
+        <v>499</v>
+      </c>
+      <c r="H517" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I517" s="94" t="s">
+        <v>503</v>
+      </c>
       <c r="J517" s="52"/>
       <c r="K517" s="52"/>
       <c r="L517" s="52"/>
@@ -50883,16 +51835,20 @@
         <f t="shared" ref="N517:N580" si="141">K517+L517+M517</f>
         <v>0</v>
       </c>
-      <c r="O517" s="52"/>
+      <c r="O517" s="52">
+        <v>10</v>
+      </c>
       <c r="P517" s="52"/>
-      <c r="Q517" s="52"/>
+      <c r="Q517" s="52">
+        <v>10</v>
+      </c>
       <c r="R517" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S517" s="86">
         <f t="shared" ref="S517:S580" si="142">R517+N517+J517</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB517" s="88">
         <v>39.270000000000003</v>
@@ -50905,14 +51861,14 @@
       </c>
       <c r="AE517" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="AF517" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG517" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>94.432000000000002</v>
       </c>
       <c r="AH517" s="49">
         <f t="shared" si="136"/>
@@ -50920,32 +51876,52 @@
       </c>
       <c r="AI517" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1358.3679999999999</v>
       </c>
       <c r="AJ517" s="91">
         <v>0.18</v>
       </c>
       <c r="AK517" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>244.50623999999999</v>
       </c>
       <c r="AL517" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1602.8742399999999</v>
       </c>
       <c r="AP517" s="7"/>
     </row>
     <row r="518" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A518" s="94"/>
-      <c r="B518" s="76"/>
-      <c r="C518" s="94"/>
-      <c r="D518" s="102"/>
-      <c r="E518" s="94"/>
-      <c r="F518" s="94"/>
-      <c r="G518" s="94"/>
-      <c r="H518" s="94"/>
-      <c r="I518" s="94"/>
-      <c r="J518" s="52"/>
+      <c r="A518" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B518" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C518" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D518" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E518" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F518" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G518" s="94" t="s">
+        <v>500</v>
+      </c>
+      <c r="H518" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I518" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="J518" s="52">
+        <v>20</v>
+      </c>
       <c r="K518" s="52"/>
       <c r="L518" s="52"/>
       <c r="M518" s="52"/>
@@ -50962,7 +51938,7 @@
       </c>
       <c r="S518" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB518" s="88">
         <v>39.270000000000003</v>
@@ -50975,46 +51951,64 @@
       </c>
       <c r="AE518" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2238.1999999999998</v>
       </c>
       <c r="AF518" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG518" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>145.483</v>
       </c>
       <c r="AH518" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI518" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2092.7169999999996</v>
       </c>
       <c r="AJ518" s="91">
         <v>0.18</v>
       </c>
       <c r="AK518" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>376.68905999999993</v>
       </c>
       <c r="AL518" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2469.4060599999993</v>
       </c>
       <c r="AP518" s="7"/>
     </row>
     <row r="519" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A519" s="94"/>
-      <c r="B519" s="76"/>
-      <c r="C519" s="94"/>
-      <c r="D519" s="102"/>
-      <c r="E519" s="94"/>
-      <c r="F519" s="94"/>
-      <c r="G519" s="94"/>
-      <c r="H519" s="94"/>
-      <c r="I519" s="94"/>
+      <c r="A519" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B519" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C519" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D519" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E519" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F519" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G519" s="94" t="s">
+        <v>501</v>
+      </c>
+      <c r="H519" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I519" s="94" t="s">
+        <v>128</v>
+      </c>
       <c r="J519" s="52"/>
       <c r="K519" s="52"/>
       <c r="L519" s="52"/>
@@ -51023,16 +52017,22 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O519" s="52"/>
-      <c r="P519" s="52"/>
-      <c r="Q519" s="52"/>
+      <c r="O519" s="52">
+        <v>6</v>
+      </c>
+      <c r="P519" s="52">
+        <v>6</v>
+      </c>
+      <c r="Q519" s="52">
+        <v>6</v>
+      </c>
       <c r="R519" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S519" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB519" s="88">
         <v>39.270000000000003</v>
@@ -51045,14 +52045,14 @@
       </c>
       <c r="AE519" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1307.52</v>
       </c>
       <c r="AF519" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG519" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>84.988799999999998</v>
       </c>
       <c r="AH519" s="49">
         <f t="shared" si="136"/>
@@ -51060,31 +52060,49 @@
       </c>
       <c r="AI519" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1222.5311999999999</v>
       </c>
       <c r="AJ519" s="91">
         <v>0.18</v>
       </c>
       <c r="AK519" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>220.05561599999999</v>
       </c>
       <c r="AL519" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1442.586816</v>
       </c>
       <c r="AP519" s="7"/>
     </row>
     <row r="520" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A520" s="94"/>
-      <c r="B520" s="76"/>
-      <c r="C520" s="94"/>
-      <c r="D520" s="102"/>
-      <c r="E520" s="94"/>
-      <c r="F520" s="94"/>
-      <c r="G520" s="94"/>
-      <c r="H520" s="94"/>
-      <c r="I520" s="94"/>
+      <c r="A520" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B520" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C520" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D520" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E520" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F520" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G520" s="94" t="s">
+        <v>502</v>
+      </c>
+      <c r="H520" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I520" s="94" t="s">
+        <v>128</v>
+      </c>
       <c r="J520" s="52"/>
       <c r="K520" s="52"/>
       <c r="L520" s="52"/>
@@ -51093,16 +52111,22 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O520" s="52"/>
-      <c r="P520" s="52"/>
-      <c r="Q520" s="52"/>
+      <c r="O520" s="52">
+        <v>8</v>
+      </c>
+      <c r="P520" s="52">
+        <v>8</v>
+      </c>
+      <c r="Q520" s="52">
+        <v>8</v>
+      </c>
       <c r="R520" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S520" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB520" s="88">
         <v>39.270000000000003</v>
@@ -51115,14 +52139,14 @@
       </c>
       <c r="AE520" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1743.3600000000001</v>
       </c>
       <c r="AF520" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG520" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>113.31840000000001</v>
       </c>
       <c r="AH520" s="49">
         <f t="shared" si="136"/>
@@ -51130,31 +52154,49 @@
       </c>
       <c r="AI520" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1630.0416</v>
       </c>
       <c r="AJ520" s="91">
         <v>0.18</v>
       </c>
       <c r="AK520" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>293.407488</v>
       </c>
       <c r="AL520" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1923.4490880000001</v>
       </c>
       <c r="AP520" s="7"/>
     </row>
     <row r="521" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A521" s="94"/>
-      <c r="B521" s="76"/>
-      <c r="C521" s="94"/>
-      <c r="D521" s="102"/>
-      <c r="E521" s="94"/>
-      <c r="F521" s="94"/>
-      <c r="G521" s="94"/>
-      <c r="H521" s="94"/>
-      <c r="I521" s="94"/>
+      <c r="A521" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B521" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C521" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D521" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E521" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F521" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G521" s="94" t="s">
+        <v>316</v>
+      </c>
+      <c r="H521" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I521" s="94" t="s">
+        <v>128</v>
+      </c>
       <c r="J521" s="52"/>
       <c r="K521" s="52"/>
       <c r="L521" s="52"/>
@@ -51163,16 +52205,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O521" s="52"/>
-      <c r="P521" s="52"/>
+      <c r="O521" s="52">
+        <v>20</v>
+      </c>
+      <c r="P521" s="52">
+        <v>20</v>
+      </c>
       <c r="Q521" s="52"/>
       <c r="R521" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S521" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB521" s="88">
         <v>39.270000000000003</v>
@@ -51185,14 +52231,14 @@
       </c>
       <c r="AE521" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF521" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG521" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH521" s="49">
         <f t="shared" si="136"/>
@@ -51200,31 +52246,49 @@
       </c>
       <c r="AI521" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ521" s="91">
         <v>0.18</v>
       </c>
       <c r="AK521" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL521" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP521" s="7"/>
     </row>
     <row r="522" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A522" s="94"/>
-      <c r="B522" s="76"/>
-      <c r="C522" s="94"/>
-      <c r="D522" s="102"/>
-      <c r="E522" s="94"/>
-      <c r="F522" s="94"/>
-      <c r="G522" s="94"/>
-      <c r="H522" s="94"/>
-      <c r="I522" s="94"/>
+      <c r="A522" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B522" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C522" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D522" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E522" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F522" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G522" s="94" t="s">
+        <v>504</v>
+      </c>
+      <c r="H522" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I522" s="94" t="s">
+        <v>511</v>
+      </c>
       <c r="J522" s="52"/>
       <c r="K522" s="52"/>
       <c r="L522" s="52"/>
@@ -51233,16 +52297,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O522" s="52"/>
-      <c r="P522" s="52"/>
+      <c r="O522" s="52">
+        <v>10</v>
+      </c>
+      <c r="P522" s="52">
+        <v>5</v>
+      </c>
       <c r="Q522" s="52"/>
       <c r="R522" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S522" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB522" s="88">
         <v>39.270000000000003</v>
@@ -51255,14 +52323,14 @@
       </c>
       <c r="AE522" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1089.5999999999999</v>
       </c>
       <c r="AF522" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG522" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>70.823999999999998</v>
       </c>
       <c r="AH522" s="49">
         <f t="shared" si="136"/>
@@ -51270,32 +52338,52 @@
       </c>
       <c r="AI522" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1018.776</v>
       </c>
       <c r="AJ522" s="91">
         <v>0.18</v>
       </c>
       <c r="AK522" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>183.37967999999998</v>
       </c>
       <c r="AL522" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1202.1556799999998</v>
       </c>
       <c r="AP522" s="7"/>
     </row>
     <row r="523" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A523" s="94"/>
-      <c r="B523" s="76"/>
-      <c r="C523" s="94"/>
-      <c r="D523" s="102"/>
-      <c r="E523" s="94"/>
-      <c r="F523" s="94"/>
-      <c r="G523" s="94"/>
-      <c r="H523" s="94"/>
-      <c r="I523" s="94"/>
-      <c r="J523" s="52"/>
+      <c r="A523" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B523" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C523" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D523" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E523" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F523" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G523" s="94" t="s">
+        <v>505</v>
+      </c>
+      <c r="H523" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I523" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J523" s="52">
+        <v>12</v>
+      </c>
       <c r="K523" s="52"/>
       <c r="L523" s="52"/>
       <c r="M523" s="52"/>
@@ -51303,16 +52391,18 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O523" s="52"/>
+      <c r="O523" s="52">
+        <v>3</v>
+      </c>
       <c r="P523" s="52"/>
       <c r="Q523" s="52"/>
       <c r="R523" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S523" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB523" s="88">
         <v>39.270000000000003</v>
@@ -51325,53 +52415,75 @@
       </c>
       <c r="AE523" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1560.84</v>
       </c>
       <c r="AF523" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG523" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>101.4546</v>
       </c>
       <c r="AH523" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI523" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1459.3853999999999</v>
       </c>
       <c r="AJ523" s="91">
         <v>0.18</v>
       </c>
       <c r="AK523" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>262.68937199999999</v>
       </c>
       <c r="AL523" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1722.0747719999999</v>
       </c>
       <c r="AP523" s="7"/>
     </row>
     <row r="524" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A524" s="94"/>
-      <c r="B524" s="76"/>
-      <c r="C524" s="94"/>
-      <c r="D524" s="102"/>
-      <c r="E524" s="94"/>
-      <c r="F524" s="94"/>
-      <c r="G524" s="94"/>
-      <c r="H524" s="94"/>
-      <c r="I524" s="94"/>
+      <c r="A524" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B524" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C524" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D524" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E524" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F524" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G524" s="94" t="s">
+        <v>506</v>
+      </c>
+      <c r="H524" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I524" s="94" t="s">
+        <v>511</v>
+      </c>
       <c r="J524" s="52"/>
-      <c r="K524" s="52"/>
-      <c r="L524" s="52"/>
+      <c r="K524" s="52">
+        <v>15</v>
+      </c>
+      <c r="L524" s="52">
+        <v>15</v>
+      </c>
       <c r="M524" s="52"/>
       <c r="N524" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O524" s="52"/>
       <c r="P524" s="52"/>
@@ -51382,7 +52494,7 @@
       </c>
       <c r="S524" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB524" s="88">
         <v>39.270000000000003</v>
@@ -51395,14 +52507,14 @@
       </c>
       <c r="AE524" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>3753.0749999999998</v>
       </c>
       <c r="AF524" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG524" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>243.94987499999999</v>
       </c>
       <c r="AH524" s="49">
         <f t="shared" si="136"/>
@@ -51410,32 +52522,52 @@
       </c>
       <c r="AI524" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>3509.125125</v>
       </c>
       <c r="AJ524" s="91">
         <v>0.18</v>
       </c>
       <c r="AK524" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>631.64252249999993</v>
       </c>
       <c r="AL524" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4140.7676474999998</v>
       </c>
       <c r="AP524" s="7"/>
     </row>
     <row r="525" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A525" s="94"/>
-      <c r="B525" s="76"/>
-      <c r="C525" s="94"/>
-      <c r="D525" s="102"/>
-      <c r="E525" s="94"/>
-      <c r="F525" s="94"/>
-      <c r="G525" s="94"/>
-      <c r="H525" s="94"/>
-      <c r="I525" s="94"/>
-      <c r="J525" s="52"/>
+      <c r="A525" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B525" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C525" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D525" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E525" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F525" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G525" s="94" t="s">
+        <v>507</v>
+      </c>
+      <c r="H525" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I525" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J525" s="52">
+        <v>40</v>
+      </c>
       <c r="K525" s="52"/>
       <c r="L525" s="52"/>
       <c r="M525" s="52"/>
@@ -51452,7 +52584,7 @@
       </c>
       <c r="S525" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB525" s="88">
         <v>39.270000000000003</v>
@@ -51465,47 +52597,67 @@
       </c>
       <c r="AE525" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF525" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG525" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH525" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI525" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ525" s="91">
         <v>0.18</v>
       </c>
       <c r="AK525" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL525" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP525" s="7"/>
     </row>
     <row r="526" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A526" s="94"/>
-      <c r="B526" s="76"/>
-      <c r="C526" s="94"/>
-      <c r="D526" s="102"/>
-      <c r="E526" s="94"/>
-      <c r="F526" s="94"/>
-      <c r="G526" s="94"/>
-      <c r="H526" s="94"/>
-      <c r="I526" s="94"/>
-      <c r="J526" s="52"/>
+      <c r="A526" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B526" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C526" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D526" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E526" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F526" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G526" s="94" t="s">
+        <v>508</v>
+      </c>
+      <c r="H526" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I526" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J526" s="52">
+        <v>40</v>
+      </c>
       <c r="K526" s="52"/>
       <c r="L526" s="52"/>
       <c r="M526" s="52"/>
@@ -51514,15 +52666,19 @@
         <v>0</v>
       </c>
       <c r="O526" s="52"/>
-      <c r="P526" s="52"/>
-      <c r="Q526" s="52"/>
+      <c r="P526" s="52">
+        <v>6</v>
+      </c>
+      <c r="Q526" s="52">
+        <v>6</v>
+      </c>
       <c r="R526" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S526" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AB526" s="88">
         <v>39.270000000000003</v>
@@ -51535,47 +52691,67 @@
       </c>
       <c r="AE526" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>5348.08</v>
       </c>
       <c r="AF526" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG526" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>347.62520000000001</v>
       </c>
       <c r="AH526" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI526" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>5000.4547999999995</v>
       </c>
       <c r="AJ526" s="91">
         <v>0.18</v>
       </c>
       <c r="AK526" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>900.08186399999988</v>
       </c>
       <c r="AL526" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>5900.5366639999993</v>
       </c>
       <c r="AP526" s="7"/>
     </row>
     <row r="527" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A527" s="94"/>
-      <c r="B527" s="76"/>
-      <c r="C527" s="94"/>
-      <c r="D527" s="102"/>
-      <c r="E527" s="94"/>
-      <c r="F527" s="94"/>
-      <c r="G527" s="94"/>
-      <c r="H527" s="94"/>
-      <c r="I527" s="94"/>
-      <c r="J527" s="52"/>
+      <c r="A527" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B527" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C527" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D527" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E527" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F527" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G527" s="94" t="s">
+        <v>509</v>
+      </c>
+      <c r="H527" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I527" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J527" s="52">
+        <v>40</v>
+      </c>
       <c r="K527" s="52"/>
       <c r="L527" s="52"/>
       <c r="M527" s="52"/>
@@ -51592,7 +52768,7 @@
       </c>
       <c r="S527" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB527" s="88">
         <v>39.270000000000003</v>
@@ -51605,47 +52781,67 @@
       </c>
       <c r="AE527" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF527" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG527" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH527" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI527" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ527" s="91">
         <v>0.18</v>
       </c>
       <c r="AK527" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL527" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP527" s="7"/>
     </row>
     <row r="528" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A528" s="94"/>
-      <c r="B528" s="76"/>
-      <c r="C528" s="94"/>
-      <c r="D528" s="102"/>
-      <c r="E528" s="94"/>
-      <c r="F528" s="94"/>
-      <c r="G528" s="94"/>
-      <c r="H528" s="94"/>
-      <c r="I528" s="94"/>
-      <c r="J528" s="52"/>
+      <c r="A528" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B528" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C528" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D528" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E528" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F528" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G528" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="H528" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I528" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J528" s="52">
+        <v>10</v>
+      </c>
       <c r="K528" s="52"/>
       <c r="L528" s="52"/>
       <c r="M528" s="52"/>
@@ -51662,7 +52858,7 @@
       </c>
       <c r="S528" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB528" s="88">
         <v>39.270000000000003</v>
@@ -51675,47 +52871,67 @@
       </c>
       <c r="AE528" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF528" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG528" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH528" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI528" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ528" s="91">
         <v>0.18</v>
       </c>
       <c r="AK528" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL528" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP528" s="7"/>
     </row>
     <row r="529" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A529" s="94"/>
-      <c r="B529" s="76"/>
-      <c r="C529" s="94"/>
-      <c r="D529" s="102"/>
-      <c r="E529" s="94"/>
-      <c r="F529" s="94"/>
-      <c r="G529" s="94"/>
-      <c r="H529" s="94"/>
-      <c r="I529" s="94"/>
-      <c r="J529" s="52"/>
+      <c r="A529" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B529" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C529" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D529" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E529" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F529" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G529" s="94" t="s">
+        <v>510</v>
+      </c>
+      <c r="H529" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I529" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J529" s="52">
+        <v>10</v>
+      </c>
       <c r="K529" s="52"/>
       <c r="L529" s="52"/>
       <c r="M529" s="52"/>
@@ -51732,7 +52948,7 @@
       </c>
       <c r="S529" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB529" s="88">
         <v>39.270000000000003</v>
@@ -51745,47 +52961,67 @@
       </c>
       <c r="AE529" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF529" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG529" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH529" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI529" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ529" s="91">
         <v>0.18</v>
       </c>
       <c r="AK529" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL529" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP529" s="7"/>
     </row>
     <row r="530" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A530" s="94"/>
-      <c r="B530" s="76"/>
-      <c r="C530" s="94"/>
-      <c r="D530" s="102"/>
-      <c r="E530" s="94"/>
-      <c r="F530" s="94"/>
-      <c r="G530" s="94"/>
-      <c r="H530" s="94"/>
-      <c r="I530" s="94"/>
-      <c r="J530" s="52"/>
+      <c r="A530" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B530" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C530" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D530" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E530" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F530" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G530" s="94" t="s">
+        <v>484</v>
+      </c>
+      <c r="H530" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I530" s="94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J530" s="52">
+        <v>10</v>
+      </c>
       <c r="K530" s="52"/>
       <c r="L530" s="52"/>
       <c r="M530" s="52"/>
@@ -51802,7 +53038,7 @@
       </c>
       <c r="S530" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB530" s="88">
         <v>39.270000000000003</v>
@@ -51815,53 +53051,75 @@
       </c>
       <c r="AE530" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF530" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG530" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH530" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI530" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ530" s="91">
         <v>0.18</v>
       </c>
       <c r="AK530" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL530" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP530" s="7"/>
     </row>
     <row r="531" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A531" s="94"/>
-      <c r="B531" s="76"/>
-      <c r="C531" s="94"/>
-      <c r="D531" s="102"/>
-      <c r="E531" s="94"/>
-      <c r="F531" s="94"/>
-      <c r="G531" s="94"/>
-      <c r="H531" s="94"/>
-      <c r="I531" s="94"/>
+      <c r="A531" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B531" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C531" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D531" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E531" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F531" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G531" s="94" t="s">
+        <v>467</v>
+      </c>
+      <c r="H531" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="I531" s="94" t="s">
+        <v>511</v>
+      </c>
       <c r="J531" s="52"/>
-      <c r="K531" s="52"/>
-      <c r="L531" s="52"/>
+      <c r="K531" s="52">
+        <v>20</v>
+      </c>
+      <c r="L531" s="52">
+        <v>20</v>
+      </c>
       <c r="M531" s="52"/>
       <c r="N531" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O531" s="52"/>
       <c r="P531" s="52"/>
@@ -51872,7 +53130,7 @@
       </c>
       <c r="S531" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB531" s="88">
         <v>39.270000000000003</v>
@@ -51885,14 +53143,14 @@
       </c>
       <c r="AE531" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF531" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG531" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH531" s="49">
         <f t="shared" si="136"/>
@@ -51900,49 +53158,82 @@
       </c>
       <c r="AI531" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ531" s="91">
         <v>0.18</v>
       </c>
       <c r="AK531" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL531" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP531" s="7"/>
     </row>
     <row r="532" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A532" s="94"/>
-      <c r="B532" s="76"/>
-      <c r="C532" s="94"/>
-      <c r="D532" s="102"/>
-      <c r="E532" s="94"/>
-      <c r="F532" s="94"/>
-      <c r="G532" s="94"/>
-      <c r="H532" s="94"/>
-      <c r="I532" s="94"/>
+      <c r="A532" s="85">
+        <v>46218</v>
+      </c>
+      <c r="B532" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C532" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D532" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E532" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F532" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G532" s="94" t="s">
+        <v>512</v>
+      </c>
+      <c r="H532" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I532" s="94" t="s">
+        <v>513</v>
+      </c>
       <c r="J532" s="52"/>
-      <c r="K532" s="52"/>
-      <c r="L532" s="52"/>
+      <c r="K532" s="52">
+        <f>25*40</f>
+        <v>1000</v>
+      </c>
+      <c r="L532" s="52">
+        <f>25*40</f>
+        <v>1000</v>
+      </c>
       <c r="M532" s="52"/>
       <c r="N532" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
-      </c>
-      <c r="O532" s="52"/>
-      <c r="P532" s="52"/>
-      <c r="Q532" s="52"/>
+        <v>2000</v>
+      </c>
+      <c r="O532" s="52">
+        <f>25*40</f>
+        <v>1000</v>
+      </c>
+      <c r="P532" s="52">
+        <f>22*40</f>
+        <v>880</v>
+      </c>
+      <c r="Q532" s="52">
+        <f>25*40</f>
+        <v>1000</v>
+      </c>
       <c r="R532" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="S532" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>4880</v>
       </c>
       <c r="AB532" s="88">
         <v>39.270000000000003</v>
@@ -51955,14 +53246,14 @@
       </c>
       <c r="AE532" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>459408.2</v>
       </c>
       <c r="AF532" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG532" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>29861.533000000003</v>
       </c>
       <c r="AH532" s="49">
         <f t="shared" si="136"/>
@@ -51970,49 +53261,73 @@
       </c>
       <c r="AI532" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>429546.66700000002</v>
       </c>
       <c r="AJ532" s="91">
         <v>0.18</v>
       </c>
       <c r="AK532" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>77318.40006</v>
       </c>
       <c r="AL532" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>506865.06706000003</v>
       </c>
       <c r="AP532" s="7"/>
     </row>
     <row r="533" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A533" s="94"/>
-      <c r="B533" s="76"/>
-      <c r="C533" s="94"/>
-      <c r="D533" s="102"/>
-      <c r="E533" s="94"/>
-      <c r="F533" s="94"/>
-      <c r="G533" s="94"/>
-      <c r="H533" s="94"/>
-      <c r="I533" s="94"/>
+      <c r="A533" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B533" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C533" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D533" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E533" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F533" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G533" s="94" t="s">
+        <v>515</v>
+      </c>
+      <c r="H533" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I533" s="94" t="s">
+        <v>514</v>
+      </c>
       <c r="J533" s="52"/>
-      <c r="K533" s="52"/>
+      <c r="K533" s="52">
+        <v>40</v>
+      </c>
       <c r="L533" s="52"/>
       <c r="M533" s="52"/>
       <c r="N533" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
-      </c>
-      <c r="O533" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O533" s="52">
+        <v>40</v>
+      </c>
       <c r="P533" s="52"/>
-      <c r="Q533" s="52"/>
+      <c r="Q533" s="52">
+        <v>20</v>
+      </c>
       <c r="R533" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S533" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB533" s="88">
         <v>39.270000000000003</v>
@@ -52025,14 +53340,14 @@
       </c>
       <c r="AE533" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>9362.5</v>
       </c>
       <c r="AF533" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG533" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>608.5625</v>
       </c>
       <c r="AH533" s="49">
         <f t="shared" si="136"/>
@@ -52040,32 +53355,52 @@
       </c>
       <c r="AI533" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8753.9375</v>
       </c>
       <c r="AJ533" s="91">
         <v>0.18</v>
       </c>
       <c r="AK533" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>1575.70875</v>
       </c>
       <c r="AL533" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>10329.64625</v>
       </c>
       <c r="AP533" s="7"/>
     </row>
     <row r="534" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A534" s="94"/>
-      <c r="B534" s="76"/>
-      <c r="C534" s="94"/>
-      <c r="D534" s="102"/>
-      <c r="E534" s="94"/>
-      <c r="F534" s="94"/>
-      <c r="G534" s="94"/>
-      <c r="H534" s="94"/>
-      <c r="I534" s="94"/>
-      <c r="J534" s="52"/>
+      <c r="A534" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B534" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C534" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D534" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E534" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F534" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G534" s="94" t="s">
+        <v>516</v>
+      </c>
+      <c r="H534" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I534" s="94" t="s">
+        <v>514</v>
+      </c>
+      <c r="J534" s="52">
+        <v>40</v>
+      </c>
       <c r="K534" s="52"/>
       <c r="L534" s="52"/>
       <c r="M534" s="52"/>
@@ -52082,7 +53417,7 @@
       </c>
       <c r="S534" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB534" s="88">
         <v>39.270000000000003</v>
@@ -52095,46 +53430,64 @@
       </c>
       <c r="AE534" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF534" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG534" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH534" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI534" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ534" s="91">
         <v>0.18</v>
       </c>
       <c r="AK534" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL534" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP534" s="7"/>
     </row>
     <row r="535" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A535" s="94"/>
-      <c r="B535" s="76"/>
-      <c r="C535" s="94"/>
-      <c r="D535" s="102"/>
-      <c r="E535" s="94"/>
-      <c r="F535" s="94"/>
-      <c r="G535" s="94"/>
-      <c r="H535" s="94"/>
-      <c r="I535" s="94"/>
+      <c r="A535" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B535" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C535" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D535" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E535" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F535" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G535" s="94" t="s">
+        <v>517</v>
+      </c>
+      <c r="H535" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I535" s="94" t="s">
+        <v>514</v>
+      </c>
       <c r="J535" s="52"/>
       <c r="K535" s="52"/>
       <c r="L535" s="52"/>
@@ -52143,16 +53496,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O535" s="52"/>
+      <c r="O535" s="52">
+        <v>15</v>
+      </c>
       <c r="P535" s="52"/>
-      <c r="Q535" s="52"/>
+      <c r="Q535" s="52">
+        <v>15</v>
+      </c>
       <c r="R535" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S535" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB535" s="88">
         <v>39.270000000000003</v>
@@ -52165,14 +53522,14 @@
       </c>
       <c r="AE535" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2179.1999999999998</v>
       </c>
       <c r="AF535" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG535" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>141.648</v>
       </c>
       <c r="AH535" s="49">
         <f t="shared" si="136"/>
@@ -52180,31 +53537,49 @@
       </c>
       <c r="AI535" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2037.5519999999999</v>
       </c>
       <c r="AJ535" s="91">
         <v>0.18</v>
       </c>
       <c r="AK535" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>366.75935999999996</v>
       </c>
       <c r="AL535" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2404.3113599999997</v>
       </c>
       <c r="AP535" s="7"/>
     </row>
     <row r="536" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A536" s="94"/>
-      <c r="B536" s="76"/>
-      <c r="C536" s="94"/>
-      <c r="D536" s="102"/>
-      <c r="E536" s="94"/>
-      <c r="F536" s="94"/>
-      <c r="G536" s="94"/>
-      <c r="H536" s="94"/>
-      <c r="I536" s="94"/>
+      <c r="A536" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B536" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C536" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D536" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E536" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F536" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G536" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="H536" s="94" t="s">
+        <v>463</v>
+      </c>
+      <c r="I536" s="94" t="s">
+        <v>514</v>
+      </c>
       <c r="J536" s="52"/>
       <c r="K536" s="52"/>
       <c r="L536" s="52"/>
@@ -52213,16 +53588,18 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O536" s="52"/>
+      <c r="O536" s="52">
+        <v>40</v>
+      </c>
       <c r="P536" s="52"/>
       <c r="Q536" s="52"/>
       <c r="R536" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S536" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB536" s="88">
         <v>39.270000000000003</v>
@@ -52235,14 +53612,14 @@
       </c>
       <c r="AE536" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF536" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG536" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH536" s="49">
         <f t="shared" si="136"/>
@@ -52250,31 +53627,49 @@
       </c>
       <c r="AI536" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ536" s="91">
         <v>0.18</v>
       </c>
       <c r="AK536" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL536" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP536" s="7"/>
     </row>
     <row r="537" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A537" s="94"/>
-      <c r="B537" s="76"/>
-      <c r="C537" s="94"/>
-      <c r="D537" s="102"/>
-      <c r="E537" s="94"/>
-      <c r="F537" s="94"/>
-      <c r="G537" s="94"/>
-      <c r="H537" s="94"/>
-      <c r="I537" s="94"/>
+      <c r="A537" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B537" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C537" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D537" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E537" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F537" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G537" s="94" t="s">
+        <v>519</v>
+      </c>
+      <c r="H537" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I537" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J537" s="52"/>
       <c r="K537" s="52"/>
       <c r="L537" s="52"/>
@@ -52283,16 +53678,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O537" s="52"/>
+      <c r="O537" s="52">
+        <v>13</v>
+      </c>
       <c r="P537" s="52"/>
-      <c r="Q537" s="52"/>
+      <c r="Q537" s="52">
+        <v>14</v>
+      </c>
       <c r="R537" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S537" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB537" s="88">
         <v>39.270000000000003</v>
@@ -52305,14 +53704,14 @@
       </c>
       <c r="AE537" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1961.28</v>
       </c>
       <c r="AF537" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG537" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>127.4832</v>
       </c>
       <c r="AH537" s="49">
         <f t="shared" si="136"/>
@@ -52320,31 +53719,49 @@
       </c>
       <c r="AI537" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1833.7968000000001</v>
       </c>
       <c r="AJ537" s="91">
         <v>0.18</v>
       </c>
       <c r="AK537" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>330.08342399999998</v>
       </c>
       <c r="AL537" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2163.880224</v>
       </c>
       <c r="AP537" s="7"/>
     </row>
     <row r="538" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A538" s="94"/>
-      <c r="B538" s="76"/>
-      <c r="C538" s="94"/>
-      <c r="D538" s="102"/>
-      <c r="E538" s="94"/>
-      <c r="F538" s="94"/>
-      <c r="G538" s="94"/>
-      <c r="H538" s="94"/>
-      <c r="I538" s="94"/>
+      <c r="A538" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B538" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C538" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D538" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E538" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F538" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G538" s="94" t="s">
+        <v>520</v>
+      </c>
+      <c r="H538" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I538" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J538" s="52"/>
       <c r="K538" s="52"/>
       <c r="L538" s="52"/>
@@ -52353,16 +53770,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O538" s="52"/>
+      <c r="O538" s="52">
+        <v>13</v>
+      </c>
       <c r="P538" s="52"/>
-      <c r="Q538" s="52"/>
+      <c r="Q538" s="52">
+        <v>15</v>
+      </c>
       <c r="R538" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S538" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB538" s="88">
         <v>39.270000000000003</v>
@@ -52375,14 +53796,14 @@
       </c>
       <c r="AE538" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2033.92</v>
       </c>
       <c r="AF538" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG538" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>132.20480000000001</v>
       </c>
       <c r="AH538" s="49">
         <f t="shared" si="136"/>
@@ -52390,49 +53811,71 @@
       </c>
       <c r="AI538" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1901.7152000000001</v>
       </c>
       <c r="AJ538" s="91">
         <v>0.18</v>
       </c>
       <c r="AK538" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>342.30873600000001</v>
       </c>
       <c r="AL538" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2244.023936</v>
       </c>
       <c r="AP538" s="7"/>
     </row>
     <row r="539" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A539" s="94"/>
-      <c r="B539" s="76"/>
-      <c r="C539" s="94"/>
-      <c r="D539" s="102"/>
-      <c r="E539" s="94"/>
-      <c r="F539" s="94"/>
-      <c r="G539" s="94"/>
-      <c r="H539" s="94"/>
-      <c r="I539" s="94"/>
+      <c r="A539" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B539" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C539" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D539" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E539" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F539" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G539" s="94" t="s">
+        <v>521</v>
+      </c>
+      <c r="H539" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I539" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J539" s="52"/>
-      <c r="K539" s="52"/>
+      <c r="K539" s="52">
+        <v>40</v>
+      </c>
       <c r="L539" s="52"/>
       <c r="M539" s="52"/>
       <c r="N539" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
-      </c>
-      <c r="O539" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O539" s="52">
+        <v>40</v>
+      </c>
       <c r="P539" s="52"/>
       <c r="Q539" s="52"/>
       <c r="R539" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S539" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB539" s="88">
         <v>39.270000000000003</v>
@@ -52445,14 +53888,14 @@
       </c>
       <c r="AE539" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>7909.7</v>
       </c>
       <c r="AF539" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG539" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>514.13049999999998</v>
       </c>
       <c r="AH539" s="49">
         <f t="shared" si="136"/>
@@ -52460,31 +53903,49 @@
       </c>
       <c r="AI539" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>7395.5694999999996</v>
       </c>
       <c r="AJ539" s="91">
         <v>0.18</v>
       </c>
       <c r="AK539" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>1331.2025099999998</v>
       </c>
       <c r="AL539" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8726.7720099999988</v>
       </c>
       <c r="AP539" s="7"/>
     </row>
     <row r="540" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A540" s="94"/>
-      <c r="B540" s="76"/>
-      <c r="C540" s="94"/>
-      <c r="D540" s="102"/>
-      <c r="E540" s="94"/>
-      <c r="F540" s="94"/>
-      <c r="G540" s="94"/>
-      <c r="H540" s="94"/>
-      <c r="I540" s="94"/>
+      <c r="A540" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B540" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C540" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D540" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E540" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F540" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G540" s="94" t="s">
+        <v>461</v>
+      </c>
+      <c r="H540" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I540" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J540" s="52"/>
       <c r="K540" s="52"/>
       <c r="L540" s="52"/>
@@ -52493,16 +53954,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O540" s="52"/>
+      <c r="O540" s="52">
+        <v>13</v>
+      </c>
       <c r="P540" s="52"/>
-      <c r="Q540" s="52"/>
+      <c r="Q540" s="52">
+        <v>14</v>
+      </c>
       <c r="R540" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S540" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB540" s="88">
         <v>39.270000000000003</v>
@@ -52515,14 +53980,14 @@
       </c>
       <c r="AE540" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1961.28</v>
       </c>
       <c r="AF540" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG540" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>127.4832</v>
       </c>
       <c r="AH540" s="49">
         <f t="shared" si="136"/>
@@ -52530,31 +53995,49 @@
       </c>
       <c r="AI540" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>1833.7968000000001</v>
       </c>
       <c r="AJ540" s="91">
         <v>0.18</v>
       </c>
       <c r="AK540" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>330.08342399999998</v>
       </c>
       <c r="AL540" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2163.880224</v>
       </c>
       <c r="AP540" s="7"/>
     </row>
     <row r="541" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A541" s="94"/>
-      <c r="B541" s="76"/>
-      <c r="C541" s="94"/>
-      <c r="D541" s="102"/>
-      <c r="E541" s="94"/>
-      <c r="F541" s="94"/>
-      <c r="G541" s="94"/>
-      <c r="H541" s="94"/>
-      <c r="I541" s="94"/>
+      <c r="A541" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B541" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C541" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D541" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E541" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F541" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G541" s="94" t="s">
+        <v>522</v>
+      </c>
+      <c r="H541" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I541" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J541" s="52"/>
       <c r="K541" s="52"/>
       <c r="L541" s="52"/>
@@ -52563,16 +54046,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O541" s="52"/>
+      <c r="O541" s="52">
+        <v>20</v>
+      </c>
       <c r="P541" s="52"/>
-      <c r="Q541" s="52"/>
+      <c r="Q541" s="52">
+        <v>20</v>
+      </c>
       <c r="R541" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S541" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB541" s="88">
         <v>39.270000000000003</v>
@@ -52585,14 +54072,14 @@
       </c>
       <c r="AE541" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF541" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG541" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH541" s="49">
         <f t="shared" si="136"/>
@@ -52600,31 +54087,49 @@
       </c>
       <c r="AI541" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ541" s="91">
         <v>0.18</v>
       </c>
       <c r="AK541" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL541" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP541" s="7"/>
     </row>
     <row r="542" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A542" s="94"/>
-      <c r="B542" s="76"/>
-      <c r="C542" s="94"/>
-      <c r="D542" s="102"/>
-      <c r="E542" s="94"/>
-      <c r="F542" s="94"/>
-      <c r="G542" s="94"/>
-      <c r="H542" s="94"/>
-      <c r="I542" s="94"/>
+      <c r="A542" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B542" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C542" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D542" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E542" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F542" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G542" s="94" t="s">
+        <v>523</v>
+      </c>
+      <c r="H542" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I542" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J542" s="52"/>
       <c r="K542" s="52"/>
       <c r="L542" s="52"/>
@@ -52633,16 +54138,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O542" s="52"/>
+      <c r="O542" s="52">
+        <v>10</v>
+      </c>
       <c r="P542" s="52"/>
-      <c r="Q542" s="52"/>
+      <c r="Q542" s="52">
+        <v>20</v>
+      </c>
       <c r="R542" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S542" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB542" s="88">
         <v>39.270000000000003</v>
@@ -52655,14 +54164,14 @@
       </c>
       <c r="AE542" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2179.1999999999998</v>
       </c>
       <c r="AF542" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG542" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>141.648</v>
       </c>
       <c r="AH542" s="49">
         <f t="shared" si="136"/>
@@ -52670,38 +54179,60 @@
       </c>
       <c r="AI542" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2037.5519999999999</v>
       </c>
       <c r="AJ542" s="91">
         <v>0.18</v>
       </c>
       <c r="AK542" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>366.75935999999996</v>
       </c>
       <c r="AL542" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2404.3113599999997</v>
       </c>
       <c r="AP542" s="7"/>
     </row>
     <row r="543" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A543" s="94"/>
-      <c r="B543" s="76"/>
-      <c r="C543" s="94"/>
-      <c r="D543" s="102"/>
-      <c r="E543" s="94"/>
-      <c r="F543" s="94"/>
-      <c r="G543" s="94"/>
-      <c r="H543" s="94"/>
-      <c r="I543" s="94"/>
+      <c r="A543" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B543" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C543" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D543" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E543" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F543" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G543" s="94" t="s">
+        <v>524</v>
+      </c>
+      <c r="H543" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I543" s="94" t="s">
+        <v>518</v>
+      </c>
       <c r="J543" s="52"/>
-      <c r="K543" s="52"/>
-      <c r="L543" s="52"/>
+      <c r="K543" s="52">
+        <v>20</v>
+      </c>
+      <c r="L543" s="52">
+        <v>20</v>
+      </c>
       <c r="M543" s="52"/>
       <c r="N543" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O543" s="52"/>
       <c r="P543" s="52"/>
@@ -52712,7 +54243,7 @@
       </c>
       <c r="S543" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB543" s="88">
         <v>39.270000000000003</v>
@@ -52725,14 +54256,14 @@
       </c>
       <c r="AE543" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF543" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG543" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH543" s="49">
         <f t="shared" si="136"/>
@@ -52740,32 +54271,52 @@
       </c>
       <c r="AI543" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ543" s="91">
         <v>0.18</v>
       </c>
       <c r="AK543" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL543" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP543" s="7"/>
     </row>
     <row r="544" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A544" s="94"/>
-      <c r="B544" s="76"/>
-      <c r="C544" s="94"/>
-      <c r="D544" s="102"/>
-      <c r="E544" s="94"/>
-      <c r="F544" s="94"/>
-      <c r="G544" s="94"/>
-      <c r="H544" s="94"/>
-      <c r="I544" s="94"/>
-      <c r="J544" s="52"/>
+      <c r="A544" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B544" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C544" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D544" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E544" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F544" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G544" s="94" t="s">
+        <v>525</v>
+      </c>
+      <c r="H544" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I544" s="94" t="s">
+        <v>199</v>
+      </c>
+      <c r="J544" s="52">
+        <v>20</v>
+      </c>
       <c r="K544" s="52"/>
       <c r="L544" s="52"/>
       <c r="M544" s="52"/>
@@ -52782,7 +54333,7 @@
       </c>
       <c r="S544" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB544" s="88">
         <v>39.270000000000003</v>
@@ -52795,46 +54346,64 @@
       </c>
       <c r="AE544" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2238.1999999999998</v>
       </c>
       <c r="AF544" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG544" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>145.483</v>
       </c>
       <c r="AH544" s="49">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI544" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2092.7169999999996</v>
       </c>
       <c r="AJ544" s="91">
         <v>0.18</v>
       </c>
       <c r="AK544" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>376.68905999999993</v>
       </c>
       <c r="AL544" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2469.4060599999993</v>
       </c>
       <c r="AP544" s="7"/>
     </row>
     <row r="545" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A545" s="94"/>
-      <c r="B545" s="76"/>
-      <c r="C545" s="94"/>
-      <c r="D545" s="102"/>
-      <c r="E545" s="94"/>
-      <c r="F545" s="94"/>
-      <c r="G545" s="94"/>
-      <c r="H545" s="94"/>
-      <c r="I545" s="94"/>
+      <c r="A545" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B545" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C545" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D545" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E545" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F545" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G545" s="94" t="s">
+        <v>526</v>
+      </c>
+      <c r="H545" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I545" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J545" s="52"/>
       <c r="K545" s="52"/>
       <c r="L545" s="52"/>
@@ -52843,16 +54412,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O545" s="52"/>
+      <c r="O545" s="52">
+        <v>15</v>
+      </c>
       <c r="P545" s="52"/>
-      <c r="Q545" s="52"/>
+      <c r="Q545" s="52">
+        <v>15</v>
+      </c>
       <c r="R545" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S545" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB545" s="88">
         <v>39.270000000000003</v>
@@ -52865,14 +54438,14 @@
       </c>
       <c r="AE545" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2179.1999999999998</v>
       </c>
       <c r="AF545" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG545" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>141.648</v>
       </c>
       <c r="AH545" s="49">
         <f t="shared" si="136"/>
@@ -52880,31 +54453,49 @@
       </c>
       <c r="AI545" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2037.5519999999999</v>
       </c>
       <c r="AJ545" s="91">
         <v>0.18</v>
       </c>
       <c r="AK545" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>366.75935999999996</v>
       </c>
       <c r="AL545" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>2404.3113599999997</v>
       </c>
       <c r="AP545" s="7"/>
     </row>
     <row r="546" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A546" s="94"/>
-      <c r="B546" s="76"/>
-      <c r="C546" s="94"/>
-      <c r="D546" s="102"/>
-      <c r="E546" s="94"/>
-      <c r="F546" s="94"/>
-      <c r="G546" s="94"/>
-      <c r="H546" s="94"/>
-      <c r="I546" s="94"/>
+      <c r="A546" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B546" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C546" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D546" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E546" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F546" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G546" s="94" t="s">
+        <v>527</v>
+      </c>
+      <c r="H546" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I546" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J546" s="52"/>
       <c r="K546" s="52"/>
       <c r="L546" s="52"/>
@@ -52915,14 +54506,16 @@
       </c>
       <c r="O546" s="52"/>
       <c r="P546" s="52"/>
-      <c r="Q546" s="52"/>
+      <c r="Q546" s="52">
+        <v>6</v>
+      </c>
       <c r="R546" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S546" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB546" s="88">
         <v>39.270000000000003</v>
@@ -52935,14 +54528,14 @@
       </c>
       <c r="AE546" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>435.84000000000003</v>
       </c>
       <c r="AF546" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG546" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>28.329600000000003</v>
       </c>
       <c r="AH546" s="49">
         <f t="shared" si="136"/>
@@ -52950,31 +54543,49 @@
       </c>
       <c r="AI546" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>407.5104</v>
       </c>
       <c r="AJ546" s="91">
         <v>0.18</v>
       </c>
       <c r="AK546" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>73.351872</v>
       </c>
       <c r="AL546" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>480.86227200000002</v>
       </c>
       <c r="AP546" s="7"/>
     </row>
     <row r="547" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A547" s="94"/>
-      <c r="B547" s="76"/>
-      <c r="C547" s="94"/>
-      <c r="D547" s="102"/>
-      <c r="E547" s="94"/>
-      <c r="F547" s="94"/>
-      <c r="G547" s="94"/>
-      <c r="H547" s="94"/>
-      <c r="I547" s="94"/>
+      <c r="A547" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B547" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C547" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D547" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E547" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F547" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G547" s="94" t="s">
+        <v>343</v>
+      </c>
+      <c r="H547" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I547" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J547" s="52"/>
       <c r="K547" s="52"/>
       <c r="L547" s="52"/>
@@ -52983,16 +54594,18 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O547" s="52"/>
+      <c r="O547" s="52">
+        <v>6</v>
+      </c>
       <c r="P547" s="52"/>
       <c r="Q547" s="52"/>
       <c r="R547" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S547" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB547" s="88">
         <v>39.270000000000003</v>
@@ -53005,14 +54618,14 @@
       </c>
       <c r="AE547" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>435.84000000000003</v>
       </c>
       <c r="AF547" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG547" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>28.329600000000003</v>
       </c>
       <c r="AH547" s="49">
         <f t="shared" si="136"/>
@@ -53020,31 +54633,49 @@
       </c>
       <c r="AI547" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>407.5104</v>
       </c>
       <c r="AJ547" s="91">
         <v>0.18</v>
       </c>
       <c r="AK547" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>73.351872</v>
       </c>
       <c r="AL547" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>480.86227200000002</v>
       </c>
       <c r="AP547" s="7"/>
     </row>
     <row r="548" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A548" s="94"/>
-      <c r="B548" s="76"/>
-      <c r="C548" s="94"/>
-      <c r="D548" s="102"/>
-      <c r="E548" s="94"/>
-      <c r="F548" s="94"/>
-      <c r="G548" s="94"/>
-      <c r="H548" s="94"/>
-      <c r="I548" s="94"/>
+      <c r="A548" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B548" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C548" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D548" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E548" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F548" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G548" s="94" t="s">
+        <v>516</v>
+      </c>
+      <c r="H548" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I548" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J548" s="52"/>
       <c r="K548" s="52"/>
       <c r="L548" s="52"/>
@@ -53055,14 +54686,16 @@
       </c>
       <c r="O548" s="52"/>
       <c r="P548" s="52"/>
-      <c r="Q548" s="52"/>
+      <c r="Q548" s="52">
+        <v>50</v>
+      </c>
       <c r="R548" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S548" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB548" s="88">
         <v>39.270000000000003</v>
@@ -53075,14 +54708,14 @@
       </c>
       <c r="AE548" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="AF548" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG548" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>236.08</v>
       </c>
       <c r="AH548" s="49">
         <f t="shared" si="136"/>
@@ -53090,49 +54723,71 @@
       </c>
       <c r="AI548" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>3395.92</v>
       </c>
       <c r="AJ548" s="91">
         <v>0.18</v>
       </c>
       <c r="AK548" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>611.26559999999995</v>
       </c>
       <c r="AL548" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4007.1855999999998</v>
       </c>
       <c r="AP548" s="7"/>
     </row>
     <row r="549" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A549" s="94"/>
-      <c r="B549" s="76"/>
-      <c r="C549" s="94"/>
-      <c r="D549" s="102"/>
-      <c r="E549" s="94"/>
-      <c r="F549" s="94"/>
-      <c r="G549" s="94"/>
-      <c r="H549" s="94"/>
-      <c r="I549" s="94"/>
+      <c r="A549" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B549" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C549" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D549" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E549" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F549" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G549" s="94" t="s">
+        <v>133</v>
+      </c>
+      <c r="H549" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I549" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J549" s="52"/>
       <c r="K549" s="52"/>
-      <c r="L549" s="52"/>
+      <c r="L549" s="52">
+        <v>40</v>
+      </c>
       <c r="M549" s="52"/>
       <c r="N549" s="104">
         <f t="shared" si="141"/>
-        <v>0</v>
-      </c>
-      <c r="O549" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O549" s="52">
+        <v>40</v>
+      </c>
       <c r="P549" s="52"/>
       <c r="Q549" s="52"/>
       <c r="R549" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S549" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB549" s="88">
         <v>39.270000000000003</v>
@@ -53145,14 +54800,14 @@
       </c>
       <c r="AE549" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>7909.7</v>
       </c>
       <c r="AF549" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG549" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>514.13049999999998</v>
       </c>
       <c r="AH549" s="49">
         <f t="shared" si="136"/>
@@ -53160,31 +54815,49 @@
       </c>
       <c r="AI549" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>7395.5694999999996</v>
       </c>
       <c r="AJ549" s="91">
         <v>0.18</v>
       </c>
       <c r="AK549" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>1331.2025099999998</v>
       </c>
       <c r="AL549" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8726.7720099999988</v>
       </c>
       <c r="AP549" s="7"/>
     </row>
     <row r="550" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A550" s="94"/>
-      <c r="B550" s="76"/>
-      <c r="C550" s="94"/>
-      <c r="D550" s="102"/>
-      <c r="E550" s="94"/>
-      <c r="F550" s="94"/>
-      <c r="G550" s="94"/>
-      <c r="H550" s="94"/>
-      <c r="I550" s="94"/>
+      <c r="A550" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B550" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C550" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D550" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E550" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F550" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G550" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="H550" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I550" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J550" s="52"/>
       <c r="K550" s="52"/>
       <c r="L550" s="52"/>
@@ -53195,14 +54868,16 @@
       </c>
       <c r="O550" s="52"/>
       <c r="P550" s="52"/>
-      <c r="Q550" s="52"/>
+      <c r="Q550" s="52">
+        <v>10</v>
+      </c>
       <c r="R550" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S550" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB550" s="88">
         <v>39.270000000000003</v>
@@ -53215,14 +54890,14 @@
       </c>
       <c r="AE550" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF550" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG550" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH550" s="49">
         <f t="shared" si="136"/>
@@ -53230,31 +54905,49 @@
       </c>
       <c r="AI550" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ550" s="91">
         <v>0.18</v>
       </c>
       <c r="AK550" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL550" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP550" s="7"/>
     </row>
     <row r="551" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A551" s="94"/>
-      <c r="B551" s="76"/>
-      <c r="C551" s="94"/>
-      <c r="D551" s="102"/>
-      <c r="E551" s="94"/>
-      <c r="F551" s="94"/>
-      <c r="G551" s="94"/>
-      <c r="H551" s="94"/>
-      <c r="I551" s="94"/>
+      <c r="A551" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B551" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C551" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D551" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E551" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F551" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G551" s="94" t="s">
+        <v>528</v>
+      </c>
+      <c r="H551" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I551" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J551" s="52"/>
       <c r="K551" s="52"/>
       <c r="L551" s="52"/>
@@ -53263,16 +54956,18 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O551" s="52"/>
+      <c r="O551" s="52">
+        <v>10</v>
+      </c>
       <c r="P551" s="52"/>
       <c r="Q551" s="52"/>
       <c r="R551" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S551" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB551" s="88">
         <v>39.270000000000003</v>
@@ -53285,14 +54980,14 @@
       </c>
       <c r="AE551" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF551" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG551" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH551" s="49">
         <f t="shared" si="136"/>
@@ -53300,31 +54995,49 @@
       </c>
       <c r="AI551" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ551" s="91">
         <v>0.18</v>
       </c>
       <c r="AK551" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL551" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP551" s="7"/>
     </row>
     <row r="552" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A552" s="94"/>
-      <c r="B552" s="76"/>
-      <c r="C552" s="94"/>
-      <c r="D552" s="102"/>
-      <c r="E552" s="94"/>
-      <c r="F552" s="94"/>
-      <c r="G552" s="94"/>
-      <c r="H552" s="94"/>
-      <c r="I552" s="94"/>
+      <c r="A552" s="85">
+        <v>46219</v>
+      </c>
+      <c r="B552" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C552" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D552" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E552" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F552" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G552" s="94" t="s">
+        <v>529</v>
+      </c>
+      <c r="H552" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I552" s="94" t="s">
+        <v>199</v>
+      </c>
       <c r="J552" s="52"/>
       <c r="K552" s="52"/>
       <c r="L552" s="52"/>
@@ -53333,16 +55046,20 @@
         <f t="shared" si="141"/>
         <v>0</v>
       </c>
-      <c r="O552" s="52"/>
+      <c r="O552" s="52">
+        <v>5</v>
+      </c>
       <c r="P552" s="52"/>
-      <c r="Q552" s="52"/>
+      <c r="Q552" s="52">
+        <v>5</v>
+      </c>
       <c r="R552" s="104">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S552" s="86">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB552" s="88">
         <v>39.270000000000003</v>
@@ -53355,14 +55072,14 @@
       </c>
       <c r="AE552" s="89">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF552" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG552" s="4">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH552" s="49">
         <f t="shared" si="136"/>
@@ -53370,18 +55087,18 @@
       </c>
       <c r="AI552" s="89">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ552" s="91">
         <v>0.18</v>
       </c>
       <c r="AK552" s="5">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL552" s="89">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP552" s="7"/>
     </row>
@@ -56074,15 +57791,15 @@
       <c r="A592" s="3"/>
       <c r="J592" s="107">
         <f>SUM(J3:J591)</f>
-        <v>11203</v>
+        <v>11639</v>
       </c>
       <c r="K592" s="107">
         <f t="shared" ref="K592:S592" si="152">SUM(K3:K591)</f>
-        <v>5845</v>
+        <v>7611</v>
       </c>
       <c r="L592" s="107">
         <f t="shared" si="152"/>
-        <v>5110</v>
+        <v>6831</v>
       </c>
       <c r="M592" s="107">
         <f t="shared" si="152"/>
@@ -56090,27 +57807,27 @@
       </c>
       <c r="N592" s="107">
         <f t="shared" si="152"/>
-        <v>10955</v>
+        <v>14442</v>
       </c>
       <c r="O592" s="107">
         <f t="shared" si="152"/>
-        <v>10721</v>
+        <v>12656</v>
       </c>
       <c r="P592" s="107">
         <f t="shared" si="152"/>
-        <v>9340</v>
+        <v>10913</v>
       </c>
       <c r="Q592" s="107">
         <f t="shared" si="152"/>
-        <v>12088</v>
+        <v>13910</v>
       </c>
       <c r="R592" s="107">
         <f t="shared" si="152"/>
-        <v>32149</v>
+        <v>37479</v>
       </c>
       <c r="S592" s="107">
         <f t="shared" si="152"/>
-        <v>54307</v>
+        <v>63560</v>
       </c>
       <c r="AP592" s="7"/>
     </row>
@@ -56177,15 +57894,15 @@
       </c>
       <c r="J595" s="47">
         <f>J592/40</f>
-        <v>280.07499999999999</v>
+        <v>290.97500000000002</v>
       </c>
       <c r="K595" s="109">
         <f t="shared" ref="K595:S595" si="153">K592/40</f>
-        <v>146.125</v>
+        <v>190.27500000000001</v>
       </c>
       <c r="L595" s="109">
         <f t="shared" si="153"/>
-        <v>127.75</v>
+        <v>170.77500000000001</v>
       </c>
       <c r="M595" s="109">
         <f t="shared" si="153"/>
@@ -56193,27 +57910,27 @@
       </c>
       <c r="N595" s="47">
         <f t="shared" si="153"/>
-        <v>273.875</v>
+        <v>361.05</v>
       </c>
       <c r="O595" s="109">
         <f t="shared" si="153"/>
-        <v>268.02499999999998</v>
+        <v>316.39999999999998</v>
       </c>
       <c r="P595" s="109">
         <f t="shared" si="153"/>
-        <v>233.5</v>
+        <v>272.82499999999999</v>
       </c>
       <c r="Q595" s="109">
         <f t="shared" si="153"/>
-        <v>302.2</v>
+        <v>347.75</v>
       </c>
       <c r="R595" s="47">
         <f t="shared" si="153"/>
-        <v>803.72500000000002</v>
+        <v>936.97500000000002</v>
       </c>
       <c r="S595" s="109">
         <f t="shared" si="153"/>
-        <v>1357.675</v>
+        <v>1589</v>
       </c>
       <c r="T595" s="54">
         <f t="shared" ref="T595:AF595" si="154">+T433/40</f>
@@ -56258,7 +57975,7 @@
       </c>
       <c r="AE595" s="43">
         <f t="shared" si="154"/>
-        <v>79563.423687500006</v>
+        <v>84640.158687499978</v>
       </c>
       <c r="AF595" s="43">
         <f t="shared" si="154"/>
@@ -56278,14 +57995,17 @@
     <row r="597" spans="1:42" x14ac:dyDescent="0.35">
       <c r="S597" s="53">
         <f>S595+W595+AA595</f>
-        <v>1357.675</v>
+        <v>1589</v>
       </c>
       <c r="X597" t="s">
         <v>50</v>
       </c>
     </row>
+    <row r="599" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="S599" s="53"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP434" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+  <autoFilter ref="A1:AP552" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -56305,14 +58025,13 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -56325,13 +58044,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -56403,11 +58123,11 @@
       </c>
       <c r="G7" s="16">
         <f>'STT Report'!Q595+'STT Report'!Z595</f>
-        <v>302.2</v>
+        <v>347.75</v>
       </c>
       <c r="H7" s="17">
         <f>E7+F7-G7</f>
-        <v>1017.8</v>
+        <v>972.25</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56422,11 +58142,11 @@
       </c>
       <c r="G8" s="16">
         <f>'STT Report'!P595+'STT Report'!Y595</f>
-        <v>233.5</v>
+        <v>272.82499999999999</v>
       </c>
       <c r="H8" s="17">
         <f>E8+F8-G8</f>
-        <v>109.5</v>
+        <v>70.175000000000011</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56441,11 +58161,11 @@
       </c>
       <c r="G9" s="16">
         <f>'STT Report'!O595+'STT Report'!X595</f>
-        <v>268.02499999999998</v>
+        <v>316.39999999999998</v>
       </c>
       <c r="H9" s="17">
         <f>E9+F9-G9</f>
-        <v>659.97500000000002</v>
+        <v>611.6</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -56462,11 +58182,11 @@
       </c>
       <c r="G10" s="22">
         <f>SUM(G7:G9)</f>
-        <v>803.72500000000002</v>
+        <v>936.97500000000002</v>
       </c>
       <c r="H10" s="23">
         <f>SUM(H7:H9)</f>
-        <v>1787.2750000000001</v>
+        <v>1654.0250000000001</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56479,11 +58199,11 @@
       <c r="F11" s="15"/>
       <c r="G11" s="44">
         <f>'STT Report'!J595</f>
-        <v>280.07499999999999</v>
+        <v>290.97500000000002</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1372.925</v>
+        <v>1362.0250000000001</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56520,11 +58240,11 @@
       </c>
       <c r="G14" s="20">
         <f>SUM(G11:G13)</f>
-        <v>280.07499999999999</v>
+        <v>290.97500000000002</v>
       </c>
       <c r="H14" s="23">
         <f>SUM(H11:H13)</f>
-        <v>1372.925</v>
+        <v>1362.0250000000001</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56554,11 +58274,11 @@
       <c r="F16" s="18"/>
       <c r="G16" s="16">
         <f>'STT Report'!L595+'STT Report'!U595</f>
-        <v>127.75</v>
+        <v>170.77500000000001</v>
       </c>
       <c r="H16" s="17">
         <f>E16+F16-G16</f>
-        <v>139.25</v>
+        <v>96.224999999999994</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -56571,11 +58291,11 @@
       <c r="F17" s="18"/>
       <c r="G17" s="16">
         <f>'STT Report'!K595+'STT Report'!T595</f>
-        <v>146.125</v>
+        <v>190.27500000000001</v>
       </c>
       <c r="H17" s="17">
         <f>E17+F17-G17</f>
-        <v>93.875</v>
+        <v>49.724999999999994</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -56592,11 +58312,11 @@
       </c>
       <c r="G18" s="22">
         <f>SUM(G15:G17)</f>
-        <v>273.875</v>
+        <v>361.05</v>
       </c>
       <c r="H18" s="23">
         <f>SUM(H15:H17)</f>
-        <v>233.125</v>
+        <v>145.94999999999999</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -56613,11 +58333,11 @@
       </c>
       <c r="G19" s="25">
         <f>G10+G14+G18</f>
-        <v>1357.675</v>
+        <v>1589</v>
       </c>
       <c r="H19" s="27">
         <f>H10+H14+H18</f>
-        <v>3393.3249999999998</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">

--- a/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7743F9-0951-42F8-9EEA-C8CAEFA3CEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B994B29-5706-41A3-8ED7-AC3C7A46D1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="527">
   <si>
     <t>Date</t>
   </si>
@@ -865,9 +865,6 @@
     <t>NAGINA Food Store</t>
   </si>
   <si>
-    <t>ASIF SB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Al Noor Town </t>
   </si>
   <si>
@@ -1303,13 +1300,7 @@
     <t>Native</t>
   </si>
   <si>
-    <t>Asif SB</t>
-  </si>
-  <si>
     <t>Al Noor Town</t>
-  </si>
-  <si>
-    <t>Mubeen</t>
   </si>
   <si>
     <t>Mozang</t>
@@ -2248,7 +2239,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2563,10 +2554,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2575,16 +2569,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2604,6 +2595,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2971,45 +2965,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="122" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="122" t="s">
+      <c r="A1" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="122" t="s">
+      <c r="C1" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="122" t="s">
+      <c r="D1" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="122" t="s">
+      <c r="E1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="122" t="s">
+      <c r="G1" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="122" t="s">
+      <c r="H1" s="118" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="42"/>
-      <c r="K1" s="122" t="s">
+      <c r="K1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="124" t="s">
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="120" t="s">
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121" t="s">
         <v>10</v>
       </c>
       <c r="T1" s="123" t="s">
@@ -3024,61 +3018,61 @@
       <c r="Y1" s="123"/>
       <c r="Z1" s="123"/>
       <c r="AA1" s="123"/>
-      <c r="AB1" s="120" t="s">
+      <c r="AB1" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="120" t="s">
+      <c r="AC1" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="120" t="s">
+      <c r="AD1" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="120" t="s">
+      <c r="AE1" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="120" t="s">
+      <c r="AF1" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="120" t="s">
+      <c r="AG1" s="121" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="84">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="120" t="s">
+      <c r="AI1" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="120" t="s">
+      <c r="AJ1" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="120" t="s">
+      <c r="AK1" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="120" t="s">
+      <c r="AL1" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="120" t="s">
+      <c r="AM1" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="118" t="s">
+      <c r="AN1" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="118" t="s">
+      <c r="AO1" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="120" t="s">
+      <c r="AP1" s="121" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="122"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3109,7 +3103,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="121"/>
+      <c r="S2" s="122"/>
       <c r="T2" s="83" t="s">
         <v>73</v>
       </c>
@@ -3134,23 +3128,23 @@
       <c r="AA2" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="121"/>
-      <c r="AC2" s="121"/>
-      <c r="AD2" s="121"/>
-      <c r="AE2" s="121"/>
-      <c r="AF2" s="121"/>
-      <c r="AG2" s="121"/>
+      <c r="AB2" s="122"/>
+      <c r="AC2" s="122"/>
+      <c r="AD2" s="122"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="122"/>
+      <c r="AG2" s="122"/>
       <c r="AH2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="121"/>
-      <c r="AJ2" s="121"/>
-      <c r="AK2" s="121"/>
-      <c r="AL2" s="121"/>
-      <c r="AM2" s="121"/>
-      <c r="AN2" s="119"/>
-      <c r="AO2" s="119"/>
-      <c r="AP2" s="121"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
+      <c r="AK2" s="122"/>
+      <c r="AL2" s="122"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="122"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="85">
@@ -6888,7 +6882,7 @@
         <v>87</v>
       </c>
       <c r="G39" s="95" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H39" s="95" t="s">
         <v>136</v>
@@ -13925,7 +13919,7 @@
       <c r="G108" s="86" t="s">
         <v>200</v>
       </c>
-      <c r="H108" s="86" t="s">
+      <c r="H108" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I108" s="48" t="s">
@@ -14027,7 +14021,7 @@
       <c r="G109" s="86" t="s">
         <v>201</v>
       </c>
-      <c r="H109" s="86" t="s">
+      <c r="H109" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I109" s="48" t="s">
@@ -14129,7 +14123,7 @@
       <c r="G110" s="86" t="s">
         <v>202</v>
       </c>
-      <c r="H110" s="86" t="s">
+      <c r="H110" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I110" s="48" t="s">
@@ -14231,7 +14225,7 @@
       <c r="G111" s="86" t="s">
         <v>203</v>
       </c>
-      <c r="H111" s="86" t="s">
+      <c r="H111" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I111" s="48" t="s">
@@ -14329,7 +14323,7 @@
       <c r="G112" s="86" t="s">
         <v>204</v>
       </c>
-      <c r="H112" s="86" t="s">
+      <c r="H112" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I112" s="48" t="s">
@@ -14433,7 +14427,7 @@
       <c r="G113" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="H113" s="86" t="s">
+      <c r="H113" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I113" s="48" t="s">
@@ -14535,7 +14529,7 @@
       <c r="G114" s="86" t="s">
         <v>203</v>
       </c>
-      <c r="H114" s="86" t="s">
+      <c r="H114" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I114" s="48" t="s">
@@ -14635,7 +14629,7 @@
       <c r="G115" s="86" t="s">
         <v>206</v>
       </c>
-      <c r="H115" s="86" t="s">
+      <c r="H115" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I115" s="48" t="s">
@@ -14737,7 +14731,7 @@
       <c r="G116" s="86" t="s">
         <v>207</v>
       </c>
-      <c r="H116" s="86" t="s">
+      <c r="H116" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I116" s="48" t="s">
@@ -14836,13 +14830,13 @@
         <v>86</v>
       </c>
       <c r="F117" s="95" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G117" s="95" t="s">
+        <v>420</v>
+      </c>
+      <c r="H117" s="95" t="s">
         <v>421</v>
-      </c>
-      <c r="H117" s="95" t="s">
-        <v>422</v>
       </c>
       <c r="I117" s="52"/>
       <c r="J117" s="52">
@@ -17549,7 +17543,7 @@
       <c r="G144" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="H144" s="86" t="s">
+      <c r="H144" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I144" s="48" t="s">
@@ -17651,7 +17645,7 @@
       <c r="G145" s="86" t="s">
         <v>249</v>
       </c>
-      <c r="H145" s="86" t="s">
+      <c r="H145" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I145" s="48" t="s">
@@ -20275,11 +20269,11 @@
       <c r="G171" s="86" t="s">
         <v>277</v>
       </c>
-      <c r="H171" s="86" t="s">
+      <c r="H171" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="I171" s="48" t="s">
         <v>278</v>
-      </c>
-      <c r="I171" s="48" t="s">
-        <v>279</v>
       </c>
       <c r="J171" s="52">
         <v>400</v>
@@ -20383,11 +20377,11 @@
       <c r="G172" s="86" t="s">
         <v>277</v>
       </c>
-      <c r="H172" s="86" t="s">
+      <c r="H172" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="I172" s="48" t="s">
         <v>278</v>
-      </c>
-      <c r="I172" s="48" t="s">
-        <v>279</v>
       </c>
       <c r="J172" s="52">
         <v>5</v>
@@ -20479,13 +20473,13 @@
         <v>108</v>
       </c>
       <c r="G173" s="86" t="s">
-        <v>280</v>
-      </c>
-      <c r="H173" s="86" t="s">
+        <v>279</v>
+      </c>
+      <c r="H173" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I173" s="48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J173" s="52"/>
       <c r="K173" s="86"/>
@@ -20581,13 +20575,13 @@
         <v>108</v>
       </c>
       <c r="G174" s="86" t="s">
-        <v>281</v>
-      </c>
-      <c r="H174" s="86" t="s">
+        <v>280</v>
+      </c>
+      <c r="H174" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I174" s="48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J174" s="52">
         <v>20</v>
@@ -20685,11 +20679,11 @@
       <c r="G175" s="86" t="s">
         <v>225</v>
       </c>
-      <c r="H175" s="86" t="s">
+      <c r="H175" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I175" s="48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J175" s="52"/>
       <c r="K175" s="105"/>
@@ -20785,13 +20779,13 @@
         <v>108</v>
       </c>
       <c r="G176" s="86" t="s">
-        <v>282</v>
-      </c>
-      <c r="H176" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="H176" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I176" s="48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J176" s="52"/>
       <c r="K176" s="105"/>
@@ -20887,13 +20881,13 @@
         <v>109</v>
       </c>
       <c r="G177" s="86" t="s">
-        <v>283</v>
-      </c>
-      <c r="H177" s="86" t="s">
+        <v>282</v>
+      </c>
+      <c r="H177" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I177" s="48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J177" s="52"/>
       <c r="K177" s="105"/>
@@ -20987,13 +20981,13 @@
         <v>108</v>
       </c>
       <c r="G178" s="86" t="s">
-        <v>284</v>
-      </c>
-      <c r="H178" s="86" t="s">
+        <v>283</v>
+      </c>
+      <c r="H178" s="95" t="s">
         <v>176</v>
       </c>
       <c r="I178" s="48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J178" s="52"/>
       <c r="K178" s="105"/>
@@ -21087,13 +21081,13 @@
         <v>108</v>
       </c>
       <c r="G179" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="H179" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="I179" s="48" t="s">
         <v>285</v>
-      </c>
-      <c r="H179" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="I179" s="48" t="s">
-        <v>286</v>
       </c>
       <c r="J179" s="52"/>
       <c r="K179" s="86"/>
@@ -21185,13 +21179,13 @@
         <v>108</v>
       </c>
       <c r="G180" s="86" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H180" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I180" s="48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J180" s="52">
         <v>40</v>
@@ -21293,7 +21287,7 @@
         <v>112</v>
       </c>
       <c r="I181" s="48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J181" s="52">
         <v>40</v>
@@ -21391,13 +21385,13 @@
         <v>108</v>
       </c>
       <c r="G182" s="86" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H182" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I182" s="48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J182" s="52"/>
       <c r="K182" s="105">
@@ -21497,13 +21491,13 @@
         <v>108</v>
       </c>
       <c r="G183" s="86" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H183" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I183" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J183" s="52">
         <v>12</v>
@@ -21599,13 +21593,13 @@
         <v>108</v>
       </c>
       <c r="G184" s="86" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H184" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I184" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J184" s="52">
         <v>6</v>
@@ -21701,13 +21695,13 @@
         <v>108</v>
       </c>
       <c r="G185" s="86" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H185" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I185" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J185" s="52">
         <v>40</v>
@@ -21803,13 +21797,13 @@
         <v>108</v>
       </c>
       <c r="G186" s="86" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H186" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I186" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J186" s="52">
         <v>40</v>
@@ -21901,13 +21895,13 @@
         <v>108</v>
       </c>
       <c r="G187" s="86" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H187" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I187" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J187" s="52">
         <v>12</v>
@@ -22005,7 +21999,7 @@
         <v>127</v>
       </c>
       <c r="I188" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J188" s="52">
         <v>40</v>
@@ -22097,13 +22091,13 @@
         <v>108</v>
       </c>
       <c r="G189" s="86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H189" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I189" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J189" s="52">
         <v>12</v>
@@ -22195,13 +22189,13 @@
         <v>108</v>
       </c>
       <c r="G190" s="86" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H190" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I190" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J190" s="52">
         <v>20</v>
@@ -22305,7 +22299,7 @@
         <v>127</v>
       </c>
       <c r="I191" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J191" s="52">
         <v>20</v>
@@ -22397,13 +22391,13 @@
         <v>108</v>
       </c>
       <c r="G192" s="86" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H192" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I192" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J192" s="52">
         <v>40</v>
@@ -22691,7 +22685,7 @@
         <v>109</v>
       </c>
       <c r="G195" s="86" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H195" s="86" t="s">
         <v>129</v>
@@ -22887,7 +22881,7 @@
         <v>108</v>
       </c>
       <c r="G197" s="86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H197" s="86" t="s">
         <v>129</v>
@@ -23087,7 +23081,7 @@
         <v>108</v>
       </c>
       <c r="G199" s="86" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H199" s="86" t="s">
         <v>129</v>
@@ -23185,7 +23179,7 @@
         <v>108</v>
       </c>
       <c r="G200" s="86" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H200" s="86" t="s">
         <v>129</v>
@@ -23283,7 +23277,7 @@
         <v>108</v>
       </c>
       <c r="G201" s="86" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H201" s="86" t="s">
         <v>129</v>
@@ -23381,13 +23375,13 @@
         <v>108</v>
       </c>
       <c r="G202" s="86" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H202" s="86" t="s">
         <v>110</v>
       </c>
       <c r="I202" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J202" s="52">
         <v>12</v>
@@ -23479,13 +23473,13 @@
         <v>108</v>
       </c>
       <c r="G203" s="86" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H203" s="86" t="s">
         <v>110</v>
       </c>
       <c r="I203" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J203" s="52">
         <v>80</v>
@@ -23577,13 +23571,13 @@
         <v>108</v>
       </c>
       <c r="G204" s="86" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H204" s="86" t="s">
         <v>110</v>
       </c>
       <c r="I204" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J204" s="52"/>
       <c r="K204" s="86"/>
@@ -23683,7 +23677,7 @@
         <v>110</v>
       </c>
       <c r="I205" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J205" s="52"/>
       <c r="K205" s="86"/>
@@ -23779,13 +23773,13 @@
         <v>108</v>
       </c>
       <c r="G206" s="86" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H206" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I206" s="48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J206" s="52">
         <v>40</v>
@@ -23887,7 +23881,7 @@
         <v>112</v>
       </c>
       <c r="I207" s="48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J207" s="52"/>
       <c r="K207" s="86">
@@ -23985,7 +23979,7 @@
         <v>108</v>
       </c>
       <c r="G208" s="86" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H208" s="86" t="s">
         <v>127</v>
@@ -24083,7 +24077,7 @@
         <v>108</v>
       </c>
       <c r="G209" s="86" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H209" s="86" t="s">
         <v>127</v>
@@ -24181,7 +24175,7 @@
         <v>108</v>
       </c>
       <c r="G210" s="86" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H210" s="86" t="s">
         <v>127</v>
@@ -24279,7 +24273,7 @@
         <v>108</v>
       </c>
       <c r="G211" s="86" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H211" s="86" t="s">
         <v>127</v>
@@ -24377,7 +24371,7 @@
         <v>108</v>
       </c>
       <c r="G212" s="86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H212" s="86" t="s">
         <v>127</v>
@@ -24479,7 +24473,7 @@
         <v>108</v>
       </c>
       <c r="G213" s="86" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H213" s="86" t="s">
         <v>127</v>
@@ -24583,7 +24577,7 @@
         <v>108</v>
       </c>
       <c r="G214" s="86" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H214" s="86" t="s">
         <v>127</v>
@@ -24687,7 +24681,7 @@
         <v>108</v>
       </c>
       <c r="G215" s="86" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H215" s="86" t="s">
         <v>127</v>
@@ -24785,7 +24779,7 @@
         <v>108</v>
       </c>
       <c r="G216" s="86" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H216" s="86" t="s">
         <v>127</v>
@@ -24883,7 +24877,7 @@
         <v>108</v>
       </c>
       <c r="G217" s="86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H217" s="86" t="s">
         <v>127</v>
@@ -24985,7 +24979,7 @@
         <v>108</v>
       </c>
       <c r="G218" s="86" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H218" s="86" t="s">
         <v>127</v>
@@ -25185,7 +25179,7 @@
         <v>108</v>
       </c>
       <c r="G220" s="86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H220" s="86" t="s">
         <v>129</v>
@@ -25289,7 +25283,7 @@
         <v>108</v>
       </c>
       <c r="G221" s="86" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H221" s="86" t="s">
         <v>129</v>
@@ -25485,7 +25479,7 @@
         <v>108</v>
       </c>
       <c r="G223" s="86" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H223" s="86" t="s">
         <v>129</v>
@@ -25583,7 +25577,7 @@
         <v>108</v>
       </c>
       <c r="G224" s="86" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H224" s="86" t="s">
         <v>129</v>
@@ -25681,7 +25675,7 @@
         <v>108</v>
       </c>
       <c r="G225" s="86" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H225" s="86" t="s">
         <v>129</v>
@@ -25779,7 +25773,7 @@
         <v>108</v>
       </c>
       <c r="G226" s="86" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H226" s="86" t="s">
         <v>129</v>
@@ -26081,13 +26075,13 @@
         <v>87</v>
       </c>
       <c r="G229" s="86" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H229" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I229" s="48" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J229" s="52"/>
       <c r="K229" s="105"/>
@@ -26287,13 +26281,13 @@
         <v>87</v>
       </c>
       <c r="G231" s="86" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H231" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I231" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J231" s="52"/>
       <c r="K231" s="86"/>
@@ -26389,13 +26383,13 @@
         <v>108</v>
       </c>
       <c r="G232" s="86" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H232" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I232" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J232" s="52">
         <v>40</v>
@@ -26493,7 +26487,7 @@
         <v>112</v>
       </c>
       <c r="I233" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J233" s="52">
         <v>12</v>
@@ -26589,13 +26583,13 @@
         <v>108</v>
       </c>
       <c r="G234" s="86" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H234" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I234" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J234" s="52">
         <v>24</v>
@@ -26689,13 +26683,13 @@
         <v>108</v>
       </c>
       <c r="G235" s="86" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H235" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I235" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J235" s="52">
         <v>10</v>
@@ -26797,13 +26791,13 @@
         <v>108</v>
       </c>
       <c r="G236" s="86" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H236" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I236" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J236" s="52">
         <v>40</v>
@@ -26901,13 +26895,13 @@
         <v>109</v>
       </c>
       <c r="G237" s="86" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H237" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I237" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J237" s="52">
         <v>40</v>
@@ -27001,13 +26995,13 @@
         <v>109</v>
       </c>
       <c r="G238" s="86" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H238" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I238" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J238" s="52"/>
       <c r="K238" s="105"/>
@@ -27103,13 +27097,13 @@
         <v>109</v>
       </c>
       <c r="G239" s="86" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H239" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I239" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J239" s="52"/>
       <c r="K239" s="105"/>
@@ -27205,13 +27199,13 @@
         <v>108</v>
       </c>
       <c r="G240" s="86" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H240" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I240" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J240" s="52"/>
       <c r="K240" s="86">
@@ -27305,13 +27299,13 @@
         <v>108</v>
       </c>
       <c r="G241" s="86" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H241" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I241" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J241" s="52"/>
       <c r="K241" s="86"/>
@@ -27413,7 +27407,7 @@
         <v>127</v>
       </c>
       <c r="I242" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J242" s="52">
         <v>40</v>
@@ -27505,13 +27499,13 @@
         <v>108</v>
       </c>
       <c r="G243" s="86" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H243" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I243" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J243" s="52"/>
       <c r="K243" s="105"/>
@@ -27607,13 +27601,13 @@
         <v>108</v>
       </c>
       <c r="G244" s="86" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H244" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I244" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J244" s="52"/>
       <c r="K244" s="105"/>
@@ -27707,13 +27701,13 @@
         <v>109</v>
       </c>
       <c r="G245" s="86" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H245" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I245" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J245" s="52">
         <v>12</v>
@@ -27805,13 +27799,13 @@
         <v>108</v>
       </c>
       <c r="G246" s="86" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H246" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I246" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J246" s="52">
         <v>40</v>
@@ -27907,13 +27901,13 @@
         <v>109</v>
       </c>
       <c r="G247" s="86" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H247" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I247" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J247" s="52"/>
       <c r="K247" s="86"/>
@@ -28009,13 +28003,13 @@
         <v>108</v>
       </c>
       <c r="G248" s="86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H248" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I248" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J248" s="52"/>
       <c r="K248" s="105"/>
@@ -28111,13 +28105,13 @@
         <v>108</v>
       </c>
       <c r="G249" s="86" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H249" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I249" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J249" s="52">
         <v>10</v>
@@ -28219,7 +28213,7 @@
         <v>129</v>
       </c>
       <c r="I250" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J250" s="52"/>
       <c r="K250" s="86">
@@ -28313,13 +28307,13 @@
         <v>108</v>
       </c>
       <c r="G251" s="86" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H251" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I251" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J251" s="52"/>
       <c r="K251" s="86"/>
@@ -28413,13 +28407,13 @@
         <v>109</v>
       </c>
       <c r="G252" s="86" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H252" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I252" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J252" s="52"/>
       <c r="K252" s="86"/>
@@ -28515,13 +28509,13 @@
         <v>109</v>
       </c>
       <c r="G253" s="86" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H253" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I253" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J253" s="52">
         <v>40</v>
@@ -28619,13 +28613,13 @@
         <v>109</v>
       </c>
       <c r="G254" s="86" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H254" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I254" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J254" s="52">
         <v>40</v>
@@ -28727,7 +28721,7 @@
         <v>129</v>
       </c>
       <c r="I255" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J255" s="52"/>
       <c r="K255" s="105">
@@ -28821,13 +28815,13 @@
         <v>87</v>
       </c>
       <c r="G256" s="86" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H256" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I256" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J256" s="52"/>
       <c r="K256" s="86">
@@ -28927,13 +28921,13 @@
         <v>87</v>
       </c>
       <c r="G257" s="86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H257" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I257" s="48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J257" s="52"/>
       <c r="K257" s="86">
@@ -29033,13 +29027,13 @@
         <v>87</v>
       </c>
       <c r="G258" s="86" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H258" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I258" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J258" s="52"/>
       <c r="K258" s="86"/>
@@ -29135,13 +29129,13 @@
         <v>87</v>
       </c>
       <c r="G259" s="86" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H259" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I259" s="48" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J259" s="52">
         <v>200</v>
@@ -29243,13 +29237,13 @@
         <v>87</v>
       </c>
       <c r="G260" s="86" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H260" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I260" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J260" s="52"/>
       <c r="K260" s="86"/>
@@ -29345,13 +29339,13 @@
         <v>87</v>
       </c>
       <c r="G261" s="86" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H261" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I261" s="48" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J261" s="52"/>
       <c r="K261" s="86"/>
@@ -29447,13 +29441,13 @@
         <v>108</v>
       </c>
       <c r="G262" s="86" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H262" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I262" s="48" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J262" s="52"/>
       <c r="K262" s="86"/>
@@ -29555,7 +29549,7 @@
         <v>112</v>
       </c>
       <c r="I263" s="48" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J263" s="52">
         <v>12</v>
@@ -29647,13 +29641,13 @@
         <v>108</v>
       </c>
       <c r="G264" s="86" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H264" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I264" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J264" s="52">
         <v>10</v>
@@ -29747,13 +29741,13 @@
         <v>108</v>
       </c>
       <c r="G265" s="86" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H265" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I265" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J265" s="52"/>
       <c r="K265" s="86">
@@ -29847,13 +29841,13 @@
         <v>108</v>
       </c>
       <c r="G266" s="86" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H266" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I266" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J266" s="52"/>
       <c r="K266" s="86"/>
@@ -29949,13 +29943,13 @@
         <v>108</v>
       </c>
       <c r="G267" s="86" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H267" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I267" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J267" s="52">
         <v>20</v>
@@ -30057,13 +30051,13 @@
         <v>108</v>
       </c>
       <c r="G268" s="86" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H268" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I268" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J268" s="52"/>
       <c r="K268" s="105"/>
@@ -30159,13 +30153,13 @@
         <v>108</v>
       </c>
       <c r="G269" s="86" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H269" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I269" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J269" s="52"/>
       <c r="K269" s="86"/>
@@ -30261,13 +30255,13 @@
         <v>108</v>
       </c>
       <c r="G270" s="86" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H270" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I270" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J270" s="52"/>
       <c r="K270" s="105"/>
@@ -30365,7 +30359,7 @@
         <v>127</v>
       </c>
       <c r="I271" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J271" s="52">
         <v>40</v>
@@ -30457,13 +30451,13 @@
         <v>108</v>
       </c>
       <c r="G272" s="86" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H272" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I272" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J272" s="52">
         <v>40</v>
@@ -30555,13 +30549,13 @@
         <v>108</v>
       </c>
       <c r="G273" s="86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H273" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I273" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J273" s="52">
         <v>12</v>
@@ -30653,13 +30647,13 @@
         <v>109</v>
       </c>
       <c r="G274" s="86" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H274" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I274" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J274" s="52">
         <v>20</v>
@@ -30751,13 +30745,13 @@
         <v>108</v>
       </c>
       <c r="G275" s="86" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H275" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I275" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J275" s="52">
         <v>40</v>
@@ -30859,13 +30853,13 @@
         <v>108</v>
       </c>
       <c r="G276" s="86" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H276" s="86" t="s">
         <v>127</v>
       </c>
       <c r="I276" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J276" s="52">
         <v>6</v>
@@ -30957,13 +30951,13 @@
         <v>87</v>
       </c>
       <c r="G277" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="H277" s="86" t="s">
+        <v>370</v>
+      </c>
+      <c r="I277" s="48" t="s">
         <v>369</v>
-      </c>
-      <c r="H277" s="86" t="s">
-        <v>371</v>
-      </c>
-      <c r="I277" s="48" t="s">
-        <v>370</v>
       </c>
       <c r="J277" s="52">
         <v>120</v>
@@ -31061,7 +31055,7 @@
         <v>129</v>
       </c>
       <c r="I278" s="48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J278" s="52"/>
       <c r="K278" s="105"/>
@@ -31153,13 +31147,13 @@
         <v>108</v>
       </c>
       <c r="G279" s="86" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H279" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I279" s="48" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J279" s="52">
         <v>14</v>
@@ -31255,13 +31249,13 @@
         <v>108</v>
       </c>
       <c r="G280" s="86" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H280" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I280" s="48" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J280" s="52">
         <v>12</v>
@@ -31361,13 +31355,13 @@
         <v>108</v>
       </c>
       <c r="G281" s="86" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H281" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I281" s="48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J281" s="52">
         <v>20</v>
@@ -31463,7 +31457,7 @@
         <v>109</v>
       </c>
       <c r="G282" s="86" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H282" s="86" t="s">
         <v>112</v>
@@ -31561,7 +31555,7 @@
         <v>108</v>
       </c>
       <c r="G283" s="86" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H283" s="86" t="s">
         <v>112</v>
@@ -31669,7 +31663,7 @@
         <v>109</v>
       </c>
       <c r="G284" s="86" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H284" s="86" t="s">
         <v>112</v>
@@ -31769,13 +31763,13 @@
         <v>108</v>
       </c>
       <c r="G285" s="86" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H285" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I285" s="48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J285" s="52"/>
       <c r="K285" s="86">
@@ -31869,7 +31863,7 @@
         <v>108</v>
       </c>
       <c r="G286" s="86" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H286" s="86" t="s">
         <v>112</v>
@@ -31971,13 +31965,13 @@
         <v>108</v>
       </c>
       <c r="G287" s="86" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H287" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I287" s="48" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J287" s="52">
         <v>20</v>
@@ -32079,13 +32073,13 @@
         <v>109</v>
       </c>
       <c r="G288" s="86" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H288" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I288" s="48" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J288" s="52">
         <v>40</v>
@@ -32187,13 +32181,13 @@
         <v>108</v>
       </c>
       <c r="G289" s="86" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H289" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I289" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J289" s="52"/>
       <c r="K289" s="105"/>
@@ -32289,13 +32283,13 @@
         <v>109</v>
       </c>
       <c r="G290" s="86" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H290" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I290" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J290" s="52"/>
       <c r="K290" s="86"/>
@@ -32391,13 +32385,13 @@
         <v>108</v>
       </c>
       <c r="G291" s="86" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H291" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I291" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J291" s="52"/>
       <c r="K291" s="86"/>
@@ -32493,13 +32487,13 @@
         <v>109</v>
       </c>
       <c r="G292" s="86" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H292" s="86" t="s">
         <v>112</v>
       </c>
       <c r="I292" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J292" s="52"/>
       <c r="K292" s="86"/>
@@ -32595,7 +32589,7 @@
         <v>108</v>
       </c>
       <c r="G293" s="86" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H293" s="86" t="s">
         <v>127</v>
@@ -32801,7 +32795,7 @@
         <v>108</v>
       </c>
       <c r="G295" s="86" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H295" s="86" t="s">
         <v>127</v>
@@ -32901,7 +32895,7 @@
         <v>109</v>
       </c>
       <c r="G296" s="86" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H296" s="86" t="s">
         <v>127</v>
@@ -33001,7 +32995,7 @@
         <v>109</v>
       </c>
       <c r="G297" s="86" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H297" s="86" t="s">
         <v>127</v>
@@ -33105,7 +33099,7 @@
         <v>108</v>
       </c>
       <c r="G298" s="86" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H298" s="86" t="s">
         <v>127</v>
@@ -33203,7 +33197,7 @@
         <v>109</v>
       </c>
       <c r="G299" s="86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H299" s="86" t="s">
         <v>127</v>
@@ -33311,7 +33305,7 @@
         <v>129</v>
       </c>
       <c r="I300" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J300" s="52">
         <v>40</v>
@@ -33413,13 +33407,13 @@
         <v>108</v>
       </c>
       <c r="G301" s="86" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H301" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I301" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J301" s="52"/>
       <c r="K301" s="105"/>
@@ -33521,7 +33515,7 @@
         <v>129</v>
       </c>
       <c r="I302" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J302" s="52"/>
       <c r="K302" s="105">
@@ -33621,7 +33615,7 @@
         <v>129</v>
       </c>
       <c r="I303" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J303" s="52">
         <v>10</v>
@@ -33719,7 +33713,7 @@
         <v>129</v>
       </c>
       <c r="I304" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J304" s="52">
         <v>10</v>
@@ -33811,13 +33805,13 @@
         <v>109</v>
       </c>
       <c r="G305" s="86" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H305" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I305" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J305" s="52">
         <v>10</v>
@@ -33915,7 +33909,7 @@
         <v>129</v>
       </c>
       <c r="I306" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J306" s="52">
         <v>10</v>
@@ -34007,13 +34001,13 @@
         <v>108</v>
       </c>
       <c r="G307" s="86" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H307" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I307" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J307" s="52">
         <v>10</v>
@@ -34111,7 +34105,7 @@
         <v>129</v>
       </c>
       <c r="I308" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J308" s="52">
         <v>10</v>
@@ -34203,13 +34197,13 @@
         <v>108</v>
       </c>
       <c r="G309" s="86" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H309" s="86" t="s">
         <v>129</v>
       </c>
       <c r="I309" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J309" s="52"/>
       <c r="K309" s="86"/>
@@ -34307,7 +34301,7 @@
         <v>89</v>
       </c>
       <c r="I310" s="48" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J310" s="52"/>
       <c r="K310" s="86">
@@ -34407,13 +34401,13 @@
         <v>87</v>
       </c>
       <c r="G311" s="86" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H311" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I311" s="48" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J311" s="52"/>
       <c r="K311" s="86"/>
@@ -34509,13 +34503,13 @@
         <v>87</v>
       </c>
       <c r="G312" s="86" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H312" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I312" s="48" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J312" s="52"/>
       <c r="K312" s="105">
@@ -34615,13 +34609,13 @@
         <v>87</v>
       </c>
       <c r="G313" s="86" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H313" s="86" t="s">
         <v>89</v>
       </c>
       <c r="I313" s="48" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J313" s="52"/>
       <c r="K313" s="105"/>
@@ -34719,11 +34713,11 @@
       <c r="G314" s="116" t="s">
         <v>277</v>
       </c>
-      <c r="H314" s="86" t="s">
-        <v>424</v>
+      <c r="H314" s="95" t="s">
+        <v>136</v>
       </c>
       <c r="I314" s="117" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J314" s="52">
         <v>2000</v>
@@ -34818,10 +34812,10 @@
         <v>159</v>
       </c>
       <c r="H315" s="95" t="s">
-        <v>426</v>
+        <v>176</v>
       </c>
       <c r="I315" s="95" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J315" s="52">
         <v>52</v>
@@ -44093,17 +44087,17 @@
       <c r="E434" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="F434" s="100" t="s">
+      <c r="F434" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="G434" s="94" t="s">
-        <v>428</v>
-      </c>
-      <c r="H434" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="I434" s="94" t="s">
-        <v>429</v>
+      <c r="G434" s="132" t="s">
+        <v>425</v>
+      </c>
+      <c r="H434" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="I434" s="132" t="s">
+        <v>426</v>
       </c>
       <c r="J434" s="52"/>
       <c r="K434" s="52">
@@ -44198,10 +44192,10 @@
         <v>187</v>
       </c>
       <c r="H435" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I435" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J435" s="52">
         <v>40</v>
@@ -44291,13 +44285,13 @@
         <v>108</v>
       </c>
       <c r="G436" s="94" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H436" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I436" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J436" s="52">
         <v>12</v>
@@ -44381,13 +44375,13 @@
         <v>109</v>
       </c>
       <c r="G437" s="94" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H437" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I437" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J437" s="52"/>
       <c r="K437" s="52"/>
@@ -44475,13 +44469,13 @@
         <v>109</v>
       </c>
       <c r="G438" s="94" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H438" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I438" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J438" s="52"/>
       <c r="K438" s="52">
@@ -44576,10 +44570,10 @@
         <v>210</v>
       </c>
       <c r="H439" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I439" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J439" s="52">
         <v>40</v>
@@ -44663,13 +44657,13 @@
         <v>108</v>
       </c>
       <c r="G440" s="94" t="s">
+        <v>430</v>
+      </c>
+      <c r="H440" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="H440" s="94" t="s">
-        <v>436</v>
-      </c>
       <c r="I440" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J440" s="52"/>
       <c r="K440" s="52">
@@ -44758,10 +44752,10 @@
         <v>194</v>
       </c>
       <c r="H441" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I441" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J441" s="52">
         <v>40</v>
@@ -44845,13 +44839,13 @@
         <v>108</v>
       </c>
       <c r="G442" s="94" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H442" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I442" s="94" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J442" s="52">
         <v>40</v>
@@ -44941,13 +44935,13 @@
         <v>109</v>
       </c>
       <c r="G443" s="94" t="s">
+        <v>431</v>
+      </c>
+      <c r="H443" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I443" s="94" t="s">
         <v>434</v>
-      </c>
-      <c r="H443" s="94" t="s">
-        <v>436</v>
-      </c>
-      <c r="I443" s="94" t="s">
-        <v>437</v>
       </c>
       <c r="J443" s="52">
         <v>10</v>
@@ -45037,10 +45031,10 @@
         <v>109</v>
       </c>
       <c r="G444" s="94" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H444" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I444" s="94" t="s">
         <v>273</v>
@@ -45130,7 +45124,7 @@
         <v>267</v>
       </c>
       <c r="H445" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I445" s="94" t="s">
         <v>273</v>
@@ -45217,10 +45211,10 @@
         <v>109</v>
       </c>
       <c r="G446" s="94" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H446" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I446" s="94" t="s">
         <v>273</v>
@@ -45315,10 +45309,10 @@
         <v>108</v>
       </c>
       <c r="G447" s="94" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H447" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I447" s="94" t="s">
         <v>273</v>
@@ -45408,7 +45402,7 @@
         <v>177</v>
       </c>
       <c r="H448" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I448" s="94" t="s">
         <v>273</v>
@@ -45505,10 +45499,10 @@
         <v>109</v>
       </c>
       <c r="G449" s="94" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H449" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I449" s="94" t="s">
         <v>273</v>
@@ -45608,7 +45602,7 @@
         <v>270</v>
       </c>
       <c r="H450" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I450" s="94" t="s">
         <v>273</v>
@@ -45695,10 +45689,10 @@
         <v>108</v>
       </c>
       <c r="G451" s="94" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H451" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I451" s="94" t="s">
         <v>273</v>
@@ -45791,13 +45785,13 @@
         <v>87</v>
       </c>
       <c r="G452" s="94" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H452" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I452" s="94" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J452" s="52"/>
       <c r="K452" s="52">
@@ -45889,13 +45883,13 @@
         <v>87</v>
       </c>
       <c r="G453" s="94" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H453" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I453" s="94" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J453" s="52"/>
       <c r="K453" s="52"/>
@@ -45979,13 +45973,13 @@
         <v>87</v>
       </c>
       <c r="G454" s="94" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H454" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I454" s="94" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J454" s="52">
         <v>160</v>
@@ -46079,7 +46073,7 @@
         <v>87</v>
       </c>
       <c r="G455" s="94" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H455" s="94" t="s">
         <v>89</v>
@@ -46175,13 +46169,13 @@
         <v>87</v>
       </c>
       <c r="G456" s="94" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H456" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I456" s="94" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J456" s="52"/>
       <c r="K456" s="52"/>
@@ -46269,13 +46263,13 @@
         <v>87</v>
       </c>
       <c r="G457" s="94" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H457" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I457" s="94" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J457" s="52"/>
       <c r="K457" s="52"/>
@@ -46363,13 +46357,13 @@
         <v>87</v>
       </c>
       <c r="G458" s="94" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H458" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I458" s="94" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J458" s="52"/>
       <c r="K458" s="52">
@@ -46459,13 +46453,13 @@
         <v>108</v>
       </c>
       <c r="G459" s="94" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H459" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I459" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J459" s="52">
         <v>12</v>
@@ -46554,10 +46548,10 @@
         <v>139</v>
       </c>
       <c r="H460" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I460" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J460" s="52">
         <v>6</v>
@@ -46647,13 +46641,13 @@
         <v>108</v>
       </c>
       <c r="G461" s="94" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H461" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I461" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J461" s="52">
         <v>24</v>
@@ -46737,13 +46731,13 @@
         <v>108</v>
       </c>
       <c r="G462" s="94" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H462" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I462" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J462" s="52">
         <v>24</v>
@@ -46829,13 +46823,13 @@
         <v>108</v>
       </c>
       <c r="G463" s="94" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H463" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I463" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J463" s="52">
         <v>24</v>
@@ -46919,13 +46913,13 @@
         <v>108</v>
       </c>
       <c r="G464" s="94" t="s">
+        <v>457</v>
+      </c>
+      <c r="H464" s="94" t="s">
         <v>460</v>
       </c>
-      <c r="H464" s="94" t="s">
-        <v>463</v>
-      </c>
       <c r="I464" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J464" s="52">
         <v>40</v>
@@ -47018,10 +47012,10 @@
         <v>184</v>
       </c>
       <c r="H465" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I465" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J465" s="52"/>
       <c r="K465" s="52"/>
@@ -47109,13 +47103,13 @@
         <v>108</v>
       </c>
       <c r="G466" s="94" t="s">
+        <v>458</v>
+      </c>
+      <c r="H466" s="94" t="s">
+        <v>460</v>
+      </c>
+      <c r="I466" s="94" t="s">
         <v>461</v>
-      </c>
-      <c r="H466" s="94" t="s">
-        <v>463</v>
-      </c>
-      <c r="I466" s="94" t="s">
-        <v>464</v>
       </c>
       <c r="J466" s="52"/>
       <c r="K466" s="52"/>
@@ -47203,13 +47197,13 @@
         <v>108</v>
       </c>
       <c r="G467" s="94" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="H467" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I467" s="94" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J467" s="52">
         <v>12</v>
@@ -47299,7 +47293,7 @@
         <v>112</v>
       </c>
       <c r="I468" s="94" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J468" s="52">
         <v>15</v>
@@ -47385,13 +47379,13 @@
         <v>108</v>
       </c>
       <c r="G469" s="94" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="H469" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I469" s="94" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J469" s="52"/>
       <c r="K469" s="52"/>
@@ -47479,13 +47473,13 @@
         <v>108</v>
       </c>
       <c r="G470" s="94" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H470" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I470" s="94" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J470" s="52">
         <v>80</v>
@@ -47577,7 +47571,7 @@
         <v>112</v>
       </c>
       <c r="I471" s="94" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J471" s="52">
         <v>39</v>
@@ -47661,13 +47655,13 @@
         <v>109</v>
       </c>
       <c r="G472" s="94" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H472" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I472" s="94" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J472" s="52">
         <v>40</v>
@@ -47755,13 +47749,13 @@
         <v>108</v>
       </c>
       <c r="G473" s="94" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H473" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I473" s="94" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J473" s="52"/>
       <c r="K473" s="52"/>
@@ -47849,13 +47843,13 @@
         <v>108</v>
       </c>
       <c r="G474" s="94" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H474" s="94" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I474" s="94" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J474" s="52"/>
       <c r="K474" s="52">
@@ -47941,13 +47935,13 @@
         <v>108</v>
       </c>
       <c r="G475" s="94" t="s">
+        <v>296</v>
+      </c>
+      <c r="H475" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I475" s="94" t="s">
         <v>297</v>
-      </c>
-      <c r="H475" s="94" t="s">
-        <v>436</v>
-      </c>
-      <c r="I475" s="94" t="s">
-        <v>298</v>
       </c>
       <c r="J475" s="52"/>
       <c r="K475" s="52"/>
@@ -48031,13 +48025,13 @@
         <v>108</v>
       </c>
       <c r="G476" s="94" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H476" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I476" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J476" s="52">
         <v>40</v>
@@ -48121,13 +48115,13 @@
         <v>108</v>
       </c>
       <c r="G477" s="94" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H477" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I477" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J477" s="52">
         <v>12</v>
@@ -48214,10 +48208,10 @@
         <v>194</v>
       </c>
       <c r="H478" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I478" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J478" s="52">
         <v>5</v>
@@ -48301,13 +48295,13 @@
         <v>108</v>
       </c>
       <c r="G479" s="94" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="H479" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I479" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J479" s="52">
         <v>12</v>
@@ -48391,13 +48385,13 @@
         <v>108</v>
       </c>
       <c r="G480" s="94" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H480" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I480" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J480" s="52">
         <v>6</v>
@@ -48481,13 +48475,13 @@
         <v>109</v>
       </c>
       <c r="G481" s="94" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H481" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I481" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J481" s="52"/>
       <c r="K481" s="52"/>
@@ -48573,13 +48567,13 @@
         <v>108</v>
       </c>
       <c r="G482" s="94" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H482" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I482" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J482" s="52">
         <v>40</v>
@@ -48663,13 +48657,13 @@
         <v>108</v>
       </c>
       <c r="G483" s="94" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H483" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I483" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J483" s="52">
         <v>12</v>
@@ -48757,13 +48751,13 @@
         <v>108</v>
       </c>
       <c r="G484" s="94" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H484" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I484" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J484" s="52">
         <v>40</v>
@@ -48851,13 +48845,13 @@
         <v>108</v>
       </c>
       <c r="G485" s="94" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H485" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I485" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J485" s="52">
         <v>40</v>
@@ -48941,13 +48935,13 @@
         <v>108</v>
       </c>
       <c r="G486" s="94" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H486" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I486" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J486" s="52">
         <v>40</v>
@@ -49031,13 +49025,13 @@
         <v>108</v>
       </c>
       <c r="G487" s="94" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H487" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I487" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J487" s="52">
         <v>40</v>
@@ -49121,13 +49115,13 @@
         <v>108</v>
       </c>
       <c r="G488" s="94" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H488" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I488" s="94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J488" s="52">
         <v>20</v>
@@ -49211,10 +49205,10 @@
         <v>108</v>
       </c>
       <c r="G489" s="94" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H489" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I489" s="94" t="s">
         <v>273</v>
@@ -49304,7 +49298,7 @@
         <v>271</v>
       </c>
       <c r="H490" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I490" s="94" t="s">
         <v>273</v>
@@ -49394,7 +49388,7 @@
         <v>139</v>
       </c>
       <c r="H491" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I491" s="94" t="s">
         <v>273</v>
@@ -49481,10 +49475,10 @@
         <v>108</v>
       </c>
       <c r="G492" s="94" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H492" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I492" s="94" t="s">
         <v>273</v>
@@ -49574,7 +49568,7 @@
         <v>177</v>
       </c>
       <c r="H493" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I493" s="94" t="s">
         <v>273</v>
@@ -49661,10 +49655,10 @@
         <v>109</v>
       </c>
       <c r="G494" s="94" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H494" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I494" s="94" t="s">
         <v>273</v>
@@ -49758,7 +49752,7 @@
         <v>167</v>
       </c>
       <c r="H495" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I495" s="94" t="s">
         <v>273</v>
@@ -49853,10 +49847,10 @@
         <v>108</v>
       </c>
       <c r="G496" s="94" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H496" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I496" s="94" t="s">
         <v>273</v>
@@ -49956,7 +49950,7 @@
         <v>168</v>
       </c>
       <c r="H497" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I497" s="94" t="s">
         <v>273</v>
@@ -50043,10 +50037,10 @@
         <v>108</v>
       </c>
       <c r="G498" s="94" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="H498" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I498" s="94" t="s">
         <v>273</v>
@@ -50136,7 +50130,7 @@
         <v>267</v>
       </c>
       <c r="H499" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I499" s="94" t="s">
         <v>273</v>
@@ -50223,10 +50217,10 @@
         <v>108</v>
       </c>
       <c r="G500" s="94" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H500" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I500" s="94" t="s">
         <v>273</v>
@@ -50313,10 +50307,10 @@
         <v>108</v>
       </c>
       <c r="G501" s="94" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H501" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I501" s="94" t="s">
         <v>273</v>
@@ -50403,13 +50397,13 @@
         <v>108</v>
       </c>
       <c r="G502" s="94" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H502" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I502" s="94" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J502" s="52"/>
       <c r="K502" s="52"/>
@@ -50497,13 +50491,13 @@
         <v>108</v>
       </c>
       <c r="G503" s="94" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H503" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I503" s="94" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J503" s="52"/>
       <c r="K503" s="52"/>
@@ -50590,10 +50584,10 @@
         <v>106</v>
       </c>
       <c r="H504" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I504" s="94" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J504" s="52"/>
       <c r="K504" s="52"/>
@@ -50684,10 +50678,10 @@
         <v>142</v>
       </c>
       <c r="H505" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I505" s="94" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J505" s="52"/>
       <c r="K505" s="52"/>
@@ -50773,13 +50767,13 @@
         <v>108</v>
       </c>
       <c r="G506" s="94" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H506" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I506" s="94" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J506" s="52"/>
       <c r="K506" s="52"/>
@@ -50867,13 +50861,13 @@
         <v>108</v>
       </c>
       <c r="G507" s="94" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H507" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I507" s="94" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J507" s="52">
         <v>40</v>
@@ -50967,7 +50961,7 @@
         <v>108</v>
       </c>
       <c r="G508" s="94" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H508" s="94" t="s">
         <v>112</v>
@@ -51059,7 +51053,7 @@
         <v>108</v>
       </c>
       <c r="G509" s="94" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H509" s="94" t="s">
         <v>112</v>
@@ -51153,7 +51147,7 @@
         <v>108</v>
       </c>
       <c r="G510" s="94" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H510" s="94" t="s">
         <v>112</v>
@@ -51247,7 +51241,7 @@
         <v>108</v>
       </c>
       <c r="G511" s="94" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H511" s="94" t="s">
         <v>112</v>
@@ -51347,13 +51341,13 @@
         <v>108</v>
       </c>
       <c r="G512" s="94" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H512" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I512" s="94" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J512" s="52">
         <v>10</v>
@@ -51447,13 +51441,13 @@
         <v>109</v>
       </c>
       <c r="G513" s="94" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="H513" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I513" s="94" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J513" s="52">
         <v>40</v>
@@ -51547,10 +51541,10 @@
         <v>108</v>
       </c>
       <c r="G514" s="94" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H514" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I514" s="94" t="s">
         <v>128</v>
@@ -51639,10 +51633,10 @@
         <v>108</v>
       </c>
       <c r="G515" s="94" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H515" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I515" s="94" t="s">
         <v>128</v>
@@ -51729,10 +51723,10 @@
         <v>108</v>
       </c>
       <c r="G516" s="94" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H516" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I516" s="94" t="s">
         <v>128</v>
@@ -51819,13 +51813,13 @@
         <v>108</v>
       </c>
       <c r="G517" s="94" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="H517" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I517" s="94" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J517" s="52"/>
       <c r="K517" s="52"/>
@@ -51911,10 +51905,10 @@
         <v>108</v>
       </c>
       <c r="G518" s="94" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H518" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I518" s="94" t="s">
         <v>128</v>
@@ -52001,10 +51995,10 @@
         <v>109</v>
       </c>
       <c r="G519" s="94" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H519" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I519" s="94" t="s">
         <v>128</v>
@@ -52095,10 +52089,10 @@
         <v>108</v>
       </c>
       <c r="G520" s="94" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="H520" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I520" s="94" t="s">
         <v>128</v>
@@ -52189,10 +52183,10 @@
         <v>109</v>
       </c>
       <c r="G521" s="94" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H521" s="94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I521" s="94" t="s">
         <v>128</v>
@@ -52281,13 +52275,13 @@
         <v>108</v>
       </c>
       <c r="G522" s="94" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H522" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I522" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J522" s="52"/>
       <c r="K522" s="52"/>
@@ -52373,13 +52367,13 @@
         <v>108</v>
       </c>
       <c r="G523" s="94" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H523" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I523" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J523" s="52">
         <v>12</v>
@@ -52465,13 +52459,13 @@
         <v>108</v>
       </c>
       <c r="G524" s="94" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H524" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I524" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J524" s="52"/>
       <c r="K524" s="52">
@@ -52557,13 +52551,13 @@
         <v>108</v>
       </c>
       <c r="G525" s="94" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H525" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I525" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J525" s="52">
         <v>40</v>
@@ -52647,13 +52641,13 @@
         <v>108</v>
       </c>
       <c r="G526" s="94" t="s">
+        <v>505</v>
+      </c>
+      <c r="H526" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I526" s="94" t="s">
         <v>508</v>
-      </c>
-      <c r="H526" s="94" t="s">
-        <v>438</v>
-      </c>
-      <c r="I526" s="94" t="s">
-        <v>511</v>
       </c>
       <c r="J526" s="52">
         <v>40</v>
@@ -52741,13 +52735,13 @@
         <v>108</v>
       </c>
       <c r="G527" s="94" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H527" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I527" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J527" s="52">
         <v>40</v>
@@ -52834,10 +52828,10 @@
         <v>139</v>
       </c>
       <c r="H528" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I528" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J528" s="52">
         <v>10</v>
@@ -52921,13 +52915,13 @@
         <v>108</v>
       </c>
       <c r="G529" s="94" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H529" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I529" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J529" s="52">
         <v>10</v>
@@ -53011,13 +53005,13 @@
         <v>108</v>
       </c>
       <c r="G530" s="94" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="H530" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I530" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J530" s="52">
         <v>10</v>
@@ -53101,13 +53095,13 @@
         <v>109</v>
       </c>
       <c r="G531" s="94" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H531" s="94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I531" s="94" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J531" s="52"/>
       <c r="K531" s="52">
@@ -53193,13 +53187,13 @@
         <v>87</v>
       </c>
       <c r="G532" s="94" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H532" s="94" t="s">
         <v>89</v>
       </c>
       <c r="I532" s="94" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J532" s="52"/>
       <c r="K532" s="52">
@@ -53296,13 +53290,13 @@
         <v>109</v>
       </c>
       <c r="G533" s="94" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H533" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I533" s="94" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J533" s="52"/>
       <c r="K533" s="52">
@@ -53390,13 +53384,13 @@
         <v>108</v>
       </c>
       <c r="G534" s="94" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H534" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I534" s="94" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J534" s="52">
         <v>40</v>
@@ -53480,13 +53474,13 @@
         <v>108</v>
       </c>
       <c r="G535" s="94" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="H535" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I535" s="94" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J535" s="52"/>
       <c r="K535" s="52"/>
@@ -53575,10 +53569,10 @@
         <v>142</v>
       </c>
       <c r="H536" s="94" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I536" s="94" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J536" s="52"/>
       <c r="K536" s="52"/>
@@ -53662,13 +53656,13 @@
         <v>108</v>
       </c>
       <c r="G537" s="94" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H537" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I537" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J537" s="52"/>
       <c r="K537" s="52"/>
@@ -53754,13 +53748,13 @@
         <v>108</v>
       </c>
       <c r="G538" s="94" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H538" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I538" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J538" s="52"/>
       <c r="K538" s="52"/>
@@ -53846,13 +53840,13 @@
         <v>109</v>
       </c>
       <c r="G539" s="94" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H539" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I539" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J539" s="52"/>
       <c r="K539" s="52">
@@ -53938,13 +53932,13 @@
         <v>108</v>
       </c>
       <c r="G540" s="94" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H540" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I540" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J540" s="52"/>
       <c r="K540" s="52"/>
@@ -54030,13 +54024,13 @@
         <v>108</v>
       </c>
       <c r="G541" s="94" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="H541" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I541" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J541" s="52"/>
       <c r="K541" s="52"/>
@@ -54122,13 +54116,13 @@
         <v>108</v>
       </c>
       <c r="G542" s="94" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H542" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I542" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J542" s="52"/>
       <c r="K542" s="52"/>
@@ -54214,13 +54208,13 @@
         <v>109</v>
       </c>
       <c r="G543" s="94" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H543" s="94" t="s">
         <v>112</v>
       </c>
       <c r="I543" s="94" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J543" s="52"/>
       <c r="K543" s="52">
@@ -54306,7 +54300,7 @@
         <v>108</v>
       </c>
       <c r="G544" s="94" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H544" s="94" t="s">
         <v>129</v>
@@ -54396,7 +54390,7 @@
         <v>109</v>
       </c>
       <c r="G545" s="94" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H545" s="94" t="s">
         <v>129</v>
@@ -54488,7 +54482,7 @@
         <v>109</v>
       </c>
       <c r="G546" s="94" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H546" s="94" t="s">
         <v>129</v>
@@ -54578,7 +54572,7 @@
         <v>108</v>
       </c>
       <c r="G547" s="94" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H547" s="94" t="s">
         <v>129</v>
@@ -54668,7 +54662,7 @@
         <v>108</v>
       </c>
       <c r="G548" s="94" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H548" s="94" t="s">
         <v>129</v>
@@ -54940,7 +54934,7 @@
         <v>109</v>
       </c>
       <c r="G551" s="94" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H551" s="94" t="s">
         <v>129</v>
@@ -55030,7 +55024,7 @@
         <v>109</v>
       </c>
       <c r="G552" s="94" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="H552" s="94" t="s">
         <v>129</v>
@@ -58025,13 +58019,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58044,14 +58039,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58087,7 +58081,7 @@
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E5" s="129"/>
       <c r="F5" s="129"/>

--- a/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CAA96E-6D5B-4D6A-84C4-61266E848539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826269E6-C4DA-4564-AC24-5389B4DE37A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3377" uniqueCount="619">
   <si>
     <t>Date</t>
   </si>
@@ -1803,6 +1803,90 @@
   <si>
     <t xml:space="preserve">Al Mazz Cash &amp; Carry </t>
   </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders Al Fateh </t>
+  </si>
+  <si>
+    <t>Attari Darbar Ferozpur Road</t>
+  </si>
+  <si>
+    <t>Jalal Sons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Faisal Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheen Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SM Rise Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khan Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D Mart </t>
+  </si>
+  <si>
+    <t>Safe Cash &amp; Carry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.B Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t>Behria Nasheman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canal Park </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakher Groccery </t>
+  </si>
+  <si>
+    <t>Malik store</t>
+  </si>
+  <si>
+    <t>Saleem Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khalil Bakers </t>
+  </si>
+  <si>
+    <t>Jaan Store</t>
+  </si>
+  <si>
+    <t>Yaseen Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bin Sohan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irfan Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rahat Bakers </t>
+  </si>
+  <si>
+    <t>Ishfaq Store</t>
+  </si>
+  <si>
+    <t>Iqbal Mart</t>
+  </si>
+  <si>
+    <t>Euro K-2</t>
+  </si>
+  <si>
+    <t>Euro D-2</t>
+  </si>
+  <si>
+    <t>Defence Road</t>
+  </si>
+  <si>
+    <t>Rehmat Chowk</t>
+  </si>
 </sst>
 </file>
 
@@ -3181,7 +3265,9 @@
       <c r="H1" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J1" s="42"/>
       <c r="K1" s="119" t="s">
         <v>8</v>
@@ -61234,33 +61320,61 @@
       <c r="AP629" s="7"/>
     </row>
     <row r="630" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A630" s="94"/>
-      <c r="B630" s="76"/>
-      <c r="C630" s="94"/>
-      <c r="D630" s="102"/>
-      <c r="E630" s="94"/>
-      <c r="F630" s="94"/>
-      <c r="G630" s="94"/>
-      <c r="H630" s="94"/>
-      <c r="I630" s="94"/>
+      <c r="A630" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B630" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C630" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D630" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E630" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F630" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G630" s="94" t="s">
+        <v>591</v>
+      </c>
+      <c r="H630" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I630" s="94" t="s">
+        <v>592</v>
+      </c>
       <c r="J630" s="52"/>
-      <c r="K630" s="52"/>
-      <c r="L630" s="52"/>
+      <c r="K630" s="52">
+        <v>1189</v>
+      </c>
+      <c r="L630" s="52">
+        <v>1395</v>
+      </c>
       <c r="M630" s="52"/>
       <c r="N630" s="104">
         <f t="shared" si="150"/>
-        <v>0</v>
-      </c>
-      <c r="O630" s="52"/>
-      <c r="P630" s="52"/>
-      <c r="Q630" s="52"/>
+        <v>2584</v>
+      </c>
+      <c r="O630" s="52">
+        <v>2398</v>
+      </c>
+      <c r="P630" s="52">
+        <v>2397</v>
+      </c>
+      <c r="Q630" s="52">
+        <v>4800</v>
+      </c>
       <c r="R630" s="104">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>9595</v>
       </c>
       <c r="S630" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>12179</v>
       </c>
       <c r="AB630" s="111"/>
       <c r="AC630" s="111"/>
@@ -61276,33 +61390,61 @@
       <c r="AP630" s="7"/>
     </row>
     <row r="631" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A631" s="94"/>
-      <c r="B631" s="76"/>
-      <c r="C631" s="94"/>
-      <c r="D631" s="102"/>
-      <c r="E631" s="94"/>
-      <c r="F631" s="94"/>
-      <c r="G631" s="94"/>
-      <c r="H631" s="94"/>
-      <c r="I631" s="94"/>
+      <c r="A631" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B631" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C631" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D631" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E631" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F631" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G631" s="94" t="s">
+        <v>593</v>
+      </c>
+      <c r="H631" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I631" s="94" t="s">
+        <v>405</v>
+      </c>
       <c r="J631" s="52"/>
-      <c r="K631" s="52"/>
-      <c r="L631" s="52"/>
+      <c r="K631" s="52">
+        <v>40</v>
+      </c>
+      <c r="L631" s="52">
+        <v>40</v>
+      </c>
       <c r="M631" s="52"/>
       <c r="N631" s="104">
         <f t="shared" si="150"/>
-        <v>0</v>
-      </c>
-      <c r="O631" s="52"/>
-      <c r="P631" s="52"/>
-      <c r="Q631" s="52"/>
+        <v>80</v>
+      </c>
+      <c r="O631" s="52">
+        <v>40</v>
+      </c>
+      <c r="P631" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q631" s="52">
+        <v>40</v>
+      </c>
       <c r="R631" s="104">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S631" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB631" s="111"/>
       <c r="AC631" s="111"/>
@@ -61318,16 +61460,36 @@
       <c r="AP631" s="7"/>
     </row>
     <row r="632" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A632" s="94"/>
-      <c r="B632" s="76"/>
-      <c r="C632" s="94"/>
-      <c r="D632" s="102"/>
-      <c r="E632" s="94"/>
-      <c r="F632" s="94"/>
-      <c r="G632" s="94"/>
-      <c r="H632" s="94"/>
-      <c r="I632" s="94"/>
-      <c r="J632" s="52"/>
+      <c r="A632" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B632" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C632" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D632" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E632" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F632" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G632" s="94" t="s">
+        <v>594</v>
+      </c>
+      <c r="H632" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I632" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J632" s="52">
+        <v>40</v>
+      </c>
       <c r="K632" s="52"/>
       <c r="L632" s="52"/>
       <c r="M632" s="52"/>
@@ -61335,16 +61497,18 @@
         <f t="shared" si="150"/>
         <v>0</v>
       </c>
-      <c r="O632" s="52"/>
+      <c r="O632" s="52">
+        <v>40</v>
+      </c>
       <c r="P632" s="52"/>
       <c r="Q632" s="52"/>
       <c r="R632" s="104">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S632" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB632" s="111"/>
       <c r="AC632" s="111"/>
@@ -61360,16 +61524,36 @@
       <c r="AP632" s="7"/>
     </row>
     <row r="633" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A633" s="94"/>
-      <c r="B633" s="76"/>
-      <c r="C633" s="94"/>
-      <c r="D633" s="102"/>
-      <c r="E633" s="94"/>
-      <c r="F633" s="94"/>
-      <c r="G633" s="94"/>
-      <c r="H633" s="94"/>
-      <c r="I633" s="94"/>
-      <c r="J633" s="52"/>
+      <c r="A633" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B633" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C633" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D633" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E633" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F633" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G633" s="94" t="s">
+        <v>595</v>
+      </c>
+      <c r="H633" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I633" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J633" s="52">
+        <v>20</v>
+      </c>
       <c r="K633" s="52"/>
       <c r="L633" s="52"/>
       <c r="M633" s="52"/>
@@ -61386,7 +61570,7 @@
       </c>
       <c r="S633" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB633" s="111"/>
       <c r="AC633" s="111"/>
@@ -61402,15 +61586,33 @@
       <c r="AP633" s="7"/>
     </row>
     <row r="634" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A634" s="94"/>
-      <c r="B634" s="76"/>
-      <c r="C634" s="94"/>
-      <c r="D634" s="102"/>
-      <c r="E634" s="94"/>
-      <c r="F634" s="94"/>
-      <c r="G634" s="94"/>
-      <c r="H634" s="94"/>
-      <c r="I634" s="94"/>
+      <c r="A634" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B634" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C634" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D634" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E634" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F634" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G634" s="94" t="s">
+        <v>596</v>
+      </c>
+      <c r="H634" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I634" s="94" t="s">
+        <v>603</v>
+      </c>
       <c r="J634" s="52"/>
       <c r="K634" s="52"/>
       <c r="L634" s="52"/>
@@ -61419,16 +61621,20 @@
         <f t="shared" si="150"/>
         <v>0</v>
       </c>
-      <c r="O634" s="52"/>
-      <c r="P634" s="52"/>
+      <c r="O634" s="52">
+        <v>40</v>
+      </c>
+      <c r="P634" s="52">
+        <v>40</v>
+      </c>
       <c r="Q634" s="52"/>
       <c r="R634" s="104">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S634" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB634" s="111"/>
       <c r="AC634" s="111"/>
@@ -61444,16 +61650,36 @@
       <c r="AP634" s="7"/>
     </row>
     <row r="635" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A635" s="94"/>
-      <c r="B635" s="76"/>
-      <c r="C635" s="94"/>
-      <c r="D635" s="102"/>
-      <c r="E635" s="94"/>
-      <c r="F635" s="94"/>
-      <c r="G635" s="94"/>
-      <c r="H635" s="94"/>
-      <c r="I635" s="94"/>
-      <c r="J635" s="52"/>
+      <c r="A635" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B635" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C635" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D635" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E635" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F635" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G635" s="94" t="s">
+        <v>597</v>
+      </c>
+      <c r="H635" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I635" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J635" s="52">
+        <v>40</v>
+      </c>
       <c r="K635" s="52"/>
       <c r="L635" s="52"/>
       <c r="M635" s="52"/>
@@ -61470,7 +61696,7 @@
       </c>
       <c r="S635" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB635" s="111"/>
       <c r="AC635" s="111"/>
@@ -61486,16 +61712,36 @@
       <c r="AP635" s="7"/>
     </row>
     <row r="636" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A636" s="94"/>
-      <c r="B636" s="76"/>
-      <c r="C636" s="94"/>
-      <c r="D636" s="102"/>
-      <c r="E636" s="94"/>
-      <c r="F636" s="94"/>
-      <c r="G636" s="94"/>
-      <c r="H636" s="94"/>
-      <c r="I636" s="94"/>
-      <c r="J636" s="52"/>
+      <c r="A636" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B636" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C636" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D636" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E636" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F636" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G636" s="94" t="s">
+        <v>598</v>
+      </c>
+      <c r="H636" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I636" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J636" s="52">
+        <v>40</v>
+      </c>
       <c r="K636" s="52"/>
       <c r="L636" s="52"/>
       <c r="M636" s="52"/>
@@ -61512,7 +61758,7 @@
       </c>
       <c r="S636" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB636" s="111"/>
       <c r="AC636" s="111"/>
@@ -61528,16 +61774,36 @@
       <c r="AP636" s="7"/>
     </row>
     <row r="637" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A637" s="94"/>
-      <c r="B637" s="76"/>
-      <c r="C637" s="94"/>
-      <c r="D637" s="102"/>
-      <c r="E637" s="94"/>
-      <c r="F637" s="94"/>
-      <c r="G637" s="94"/>
-      <c r="H637" s="94"/>
-      <c r="I637" s="94"/>
-      <c r="J637" s="52"/>
+      <c r="A637" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B637" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C637" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D637" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E637" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F637" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G637" s="94" t="s">
+        <v>599</v>
+      </c>
+      <c r="H637" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I637" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J637" s="52">
+        <v>40</v>
+      </c>
       <c r="K637" s="52"/>
       <c r="L637" s="52"/>
       <c r="M637" s="52"/>
@@ -61545,16 +61811,20 @@
         <f t="shared" si="150"/>
         <v>0</v>
       </c>
-      <c r="O637" s="52"/>
+      <c r="O637" s="52">
+        <v>40</v>
+      </c>
       <c r="P637" s="52"/>
-      <c r="Q637" s="52"/>
+      <c r="Q637" s="52">
+        <v>40</v>
+      </c>
       <c r="R637" s="104">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S637" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB637" s="111"/>
       <c r="AC637" s="111"/>
@@ -61570,16 +61840,36 @@
       <c r="AP637" s="7"/>
     </row>
     <row r="638" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A638" s="94"/>
-      <c r="B638" s="76"/>
-      <c r="C638" s="94"/>
-      <c r="D638" s="102"/>
-      <c r="E638" s="94"/>
-      <c r="F638" s="94"/>
-      <c r="G638" s="94"/>
-      <c r="H638" s="94"/>
-      <c r="I638" s="94"/>
-      <c r="J638" s="52"/>
+      <c r="A638" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B638" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C638" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D638" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E638" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F638" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G638" s="94" t="s">
+        <v>600</v>
+      </c>
+      <c r="H638" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I638" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J638" s="52">
+        <v>40</v>
+      </c>
       <c r="K638" s="52"/>
       <c r="L638" s="52"/>
       <c r="M638" s="52"/>
@@ -61596,7 +61886,7 @@
       </c>
       <c r="S638" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB638" s="111"/>
       <c r="AC638" s="111"/>
@@ -61612,22 +61902,46 @@
       <c r="AP638" s="7"/>
     </row>
     <row r="639" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A639" s="94"/>
-      <c r="B639" s="76"/>
-      <c r="C639" s="94"/>
-      <c r="D639" s="102"/>
-      <c r="E639" s="94"/>
-      <c r="F639" s="94"/>
-      <c r="G639" s="94"/>
-      <c r="H639" s="94"/>
-      <c r="I639" s="94"/>
-      <c r="J639" s="52"/>
-      <c r="K639" s="52"/>
-      <c r="L639" s="52"/>
+      <c r="A639" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B639" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C639" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D639" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E639" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F639" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G639" s="94" t="s">
+        <v>601</v>
+      </c>
+      <c r="H639" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="I639" s="94" t="s">
+        <v>602</v>
+      </c>
+      <c r="J639" s="52">
+        <v>200</v>
+      </c>
+      <c r="K639" s="52">
+        <v>80</v>
+      </c>
+      <c r="L639" s="52">
+        <v>80</v>
+      </c>
       <c r="M639" s="52"/>
       <c r="N639" s="104">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="O639" s="52"/>
       <c r="P639" s="52"/>
@@ -61638,7 +61952,7 @@
       </c>
       <c r="S639" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="AB639" s="111"/>
       <c r="AC639" s="111"/>
@@ -61654,16 +61968,36 @@
       <c r="AP639" s="7"/>
     </row>
     <row r="640" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A640" s="94"/>
-      <c r="B640" s="76"/>
-      <c r="C640" s="94"/>
-      <c r="D640" s="102"/>
-      <c r="E640" s="94"/>
-      <c r="F640" s="94"/>
-      <c r="G640" s="94"/>
-      <c r="H640" s="94"/>
-      <c r="I640" s="94"/>
-      <c r="J640" s="52"/>
+      <c r="A640" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B640" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C640" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D640" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E640" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F640" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G640" s="94" t="s">
+        <v>299</v>
+      </c>
+      <c r="H640" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I640" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J640" s="52">
+        <v>80</v>
+      </c>
       <c r="K640" s="52"/>
       <c r="L640" s="52"/>
       <c r="M640" s="52"/>
@@ -61680,7 +62014,7 @@
       </c>
       <c r="S640" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB640" s="111"/>
       <c r="AC640" s="111"/>
@@ -61696,15 +62030,33 @@
       <c r="AP640" s="7"/>
     </row>
     <row r="641" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A641" s="94"/>
-      <c r="B641" s="76"/>
-      <c r="C641" s="94"/>
-      <c r="D641" s="102"/>
-      <c r="E641" s="94"/>
-      <c r="F641" s="94"/>
-      <c r="G641" s="94"/>
-      <c r="H641" s="94"/>
-      <c r="I641" s="94"/>
+      <c r="A641" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B641" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C641" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D641" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E641" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F641" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G641" s="94" t="s">
+        <v>604</v>
+      </c>
+      <c r="H641" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I641" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J641" s="52"/>
       <c r="K641" s="52"/>
       <c r="L641" s="52"/>
@@ -61715,14 +62067,16 @@
       </c>
       <c r="O641" s="52"/>
       <c r="P641" s="52"/>
-      <c r="Q641" s="52"/>
+      <c r="Q641" s="52">
+        <v>6</v>
+      </c>
       <c r="R641" s="104">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S641" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB641" s="111"/>
       <c r="AC641" s="111"/>
@@ -61738,22 +62092,44 @@
       <c r="AP641" s="7"/>
     </row>
     <row r="642" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A642" s="94"/>
-      <c r="B642" s="76"/>
-      <c r="C642" s="94"/>
-      <c r="D642" s="102"/>
-      <c r="E642" s="94"/>
-      <c r="F642" s="94"/>
-      <c r="G642" s="94"/>
-      <c r="H642" s="94"/>
-      <c r="I642" s="94"/>
+      <c r="A642" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B642" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C642" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D642" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E642" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F642" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G642" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="H642" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I642" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J642" s="52"/>
-      <c r="K642" s="52"/>
-      <c r="L642" s="52"/>
+      <c r="K642" s="52">
+        <v>6</v>
+      </c>
+      <c r="L642" s="52">
+        <v>6</v>
+      </c>
       <c r="M642" s="52"/>
       <c r="N642" s="104">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O642" s="52"/>
       <c r="P642" s="52"/>
@@ -61764,7 +62140,7 @@
       </c>
       <c r="S642" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB642" s="111"/>
       <c r="AC642" s="111"/>
@@ -61780,16 +62156,36 @@
       <c r="AP642" s="7"/>
     </row>
     <row r="643" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A643" s="94"/>
-      <c r="B643" s="76"/>
-      <c r="C643" s="94"/>
-      <c r="D643" s="102"/>
-      <c r="E643" s="94"/>
-      <c r="F643" s="94"/>
-      <c r="G643" s="94"/>
-      <c r="H643" s="94"/>
-      <c r="I643" s="94"/>
-      <c r="J643" s="52"/>
+      <c r="A643" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B643" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C643" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D643" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E643" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F643" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G643" s="94" t="s">
+        <v>605</v>
+      </c>
+      <c r="H643" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I643" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J643" s="52">
+        <v>12</v>
+      </c>
       <c r="K643" s="52"/>
       <c r="L643" s="52"/>
       <c r="M643" s="52"/>
@@ -61806,7 +62202,7 @@
       </c>
       <c r="S643" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB643" s="111"/>
       <c r="AC643" s="111"/>
@@ -61822,15 +62218,33 @@
       <c r="AP643" s="7"/>
     </row>
     <row r="644" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A644" s="94"/>
-      <c r="B644" s="76"/>
-      <c r="C644" s="94"/>
-      <c r="D644" s="102"/>
-      <c r="E644" s="94"/>
-      <c r="F644" s="94"/>
-      <c r="G644" s="94"/>
-      <c r="H644" s="94"/>
-      <c r="I644" s="94"/>
+      <c r="A644" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B644" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C644" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D644" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E644" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F644" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G644" s="94" t="s">
+        <v>606</v>
+      </c>
+      <c r="H644" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I644" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J644" s="52"/>
       <c r="K644" s="52"/>
       <c r="L644" s="52"/>
@@ -61841,14 +62255,16 @@
       </c>
       <c r="O644" s="52"/>
       <c r="P644" s="52"/>
-      <c r="Q644" s="52"/>
+      <c r="Q644" s="52">
+        <v>6</v>
+      </c>
       <c r="R644" s="104">
         <f t="shared" ref="R644:R687" si="152">SUM(O644:Q644)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S644" s="86">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB644" s="111"/>
       <c r="AC644" s="111"/>
@@ -61864,15 +62280,33 @@
       <c r="AP644" s="7"/>
     </row>
     <row r="645" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A645" s="94"/>
-      <c r="B645" s="76"/>
-      <c r="C645" s="94"/>
-      <c r="D645" s="102"/>
-      <c r="E645" s="94"/>
-      <c r="F645" s="94"/>
-      <c r="G645" s="94"/>
-      <c r="H645" s="94"/>
-      <c r="I645" s="94"/>
+      <c r="A645" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B645" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C645" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D645" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E645" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F645" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G645" s="94" t="s">
+        <v>607</v>
+      </c>
+      <c r="H645" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I645" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J645" s="52"/>
       <c r="K645" s="52"/>
       <c r="L645" s="52"/>
@@ -61881,16 +62315,18 @@
         <f t="shared" ref="N645:N672" si="153">K645+L645+M645</f>
         <v>0</v>
       </c>
-      <c r="O645" s="52"/>
+      <c r="O645" s="52">
+        <v>6</v>
+      </c>
       <c r="P645" s="52"/>
       <c r="Q645" s="52"/>
       <c r="R645" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S645" s="86">
         <f t="shared" ref="S645:S671" si="154">R645+N645+J645</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB645" s="111"/>
       <c r="AC645" s="111"/>
@@ -61906,15 +62342,33 @@
       <c r="AP645" s="7"/>
     </row>
     <row r="646" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A646" s="94"/>
-      <c r="B646" s="76"/>
-      <c r="C646" s="94"/>
-      <c r="D646" s="102"/>
-      <c r="E646" s="94"/>
-      <c r="F646" s="94"/>
-      <c r="G646" s="94"/>
-      <c r="H646" s="94"/>
-      <c r="I646" s="94"/>
+      <c r="A646" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B646" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C646" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D646" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E646" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F646" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G646" s="94" t="s">
+        <v>608</v>
+      </c>
+      <c r="H646" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I646" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J646" s="52"/>
       <c r="K646" s="52"/>
       <c r="L646" s="52"/>
@@ -61924,15 +62378,17 @@
         <v>0</v>
       </c>
       <c r="O646" s="52"/>
-      <c r="P646" s="52"/>
+      <c r="P646" s="52">
+        <v>6</v>
+      </c>
       <c r="Q646" s="52"/>
       <c r="R646" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S646" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB646" s="111"/>
       <c r="AC646" s="111"/>
@@ -61948,16 +62404,36 @@
       <c r="AP646" s="7"/>
     </row>
     <row r="647" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A647" s="94"/>
-      <c r="B647" s="76"/>
-      <c r="C647" s="94"/>
-      <c r="D647" s="102"/>
-      <c r="E647" s="94"/>
-      <c r="F647" s="94"/>
-      <c r="G647" s="94"/>
-      <c r="H647" s="94"/>
-      <c r="I647" s="94"/>
-      <c r="J647" s="52"/>
+      <c r="A647" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B647" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C647" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D647" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E647" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F647" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G647" s="94" t="s">
+        <v>609</v>
+      </c>
+      <c r="H647" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I647" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J647" s="52">
+        <v>10</v>
+      </c>
       <c r="K647" s="52"/>
       <c r="L647" s="52"/>
       <c r="M647" s="52"/>
@@ -61974,7 +62450,7 @@
       </c>
       <c r="S647" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB647" s="111"/>
       <c r="AC647" s="111"/>
@@ -61990,16 +62466,36 @@
       <c r="AP647" s="7"/>
     </row>
     <row r="648" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A648" s="94"/>
-      <c r="B648" s="76"/>
-      <c r="C648" s="94"/>
-      <c r="D648" s="102"/>
-      <c r="E648" s="94"/>
-      <c r="F648" s="94"/>
-      <c r="G648" s="94"/>
-      <c r="H648" s="94"/>
-      <c r="I648" s="94"/>
-      <c r="J648" s="52"/>
+      <c r="A648" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B648" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C648" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D648" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E648" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F648" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G648" s="94" t="s">
+        <v>133</v>
+      </c>
+      <c r="H648" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I648" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J648" s="52">
+        <v>10</v>
+      </c>
       <c r="K648" s="52"/>
       <c r="L648" s="52"/>
       <c r="M648" s="52"/>
@@ -62016,7 +62512,7 @@
       </c>
       <c r="S648" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB648" s="111"/>
       <c r="AC648" s="111"/>
@@ -62032,16 +62528,36 @@
       <c r="AP648" s="7"/>
     </row>
     <row r="649" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A649" s="94"/>
-      <c r="B649" s="76"/>
-      <c r="C649" s="94"/>
-      <c r="D649" s="102"/>
-      <c r="E649" s="94"/>
-      <c r="F649" s="94"/>
-      <c r="G649" s="94"/>
-      <c r="H649" s="94"/>
-      <c r="I649" s="94"/>
-      <c r="J649" s="52"/>
+      <c r="A649" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B649" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C649" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D649" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E649" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F649" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G649" s="94" t="s">
+        <v>269</v>
+      </c>
+      <c r="H649" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I649" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J649" s="52">
+        <v>10</v>
+      </c>
       <c r="K649" s="52"/>
       <c r="L649" s="52"/>
       <c r="M649" s="52"/>
@@ -62058,7 +62574,7 @@
       </c>
       <c r="S649" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB649" s="111"/>
       <c r="AC649" s="111"/>
@@ -62074,33 +62590,61 @@
       <c r="AP649" s="7"/>
     </row>
     <row r="650" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A650" s="94"/>
-      <c r="B650" s="76"/>
-      <c r="C650" s="94"/>
-      <c r="D650" s="102"/>
-      <c r="E650" s="94"/>
-      <c r="F650" s="94"/>
-      <c r="G650" s="94"/>
-      <c r="H650" s="94"/>
-      <c r="I650" s="94"/>
+      <c r="A650" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B650" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C650" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D650" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E650" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F650" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G650" s="94" t="s">
+        <v>610</v>
+      </c>
+      <c r="H650" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I650" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J650" s="52"/>
-      <c r="K650" s="52"/>
-      <c r="L650" s="52"/>
+      <c r="K650" s="52">
+        <v>40</v>
+      </c>
+      <c r="L650" s="52">
+        <v>40</v>
+      </c>
       <c r="M650" s="52"/>
       <c r="N650" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O650" s="52"/>
-      <c r="P650" s="52"/>
-      <c r="Q650" s="52"/>
+        <v>80</v>
+      </c>
+      <c r="O650" s="52">
+        <v>80</v>
+      </c>
+      <c r="P650" s="52">
+        <v>80</v>
+      </c>
+      <c r="Q650" s="52">
+        <v>160</v>
+      </c>
       <c r="R650" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="S650" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AB650" s="111"/>
       <c r="AC650" s="111"/>
@@ -62116,16 +62660,36 @@
       <c r="AP650" s="7"/>
     </row>
     <row r="651" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A651" s="94"/>
-      <c r="B651" s="76"/>
-      <c r="C651" s="94"/>
-      <c r="D651" s="102"/>
-      <c r="E651" s="94"/>
-      <c r="F651" s="94"/>
-      <c r="G651" s="94"/>
-      <c r="H651" s="94"/>
-      <c r="I651" s="94"/>
-      <c r="J651" s="52"/>
+      <c r="A651" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B651" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C651" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D651" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E651" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F651" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G651" s="94" t="s">
+        <v>611</v>
+      </c>
+      <c r="H651" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I651" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J651" s="52">
+        <v>10</v>
+      </c>
       <c r="K651" s="52"/>
       <c r="L651" s="52"/>
       <c r="M651" s="52"/>
@@ -62142,7 +62706,7 @@
       </c>
       <c r="S651" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB651" s="111"/>
       <c r="AC651" s="111"/>
@@ -62158,16 +62722,36 @@
       <c r="AP651" s="7"/>
     </row>
     <row r="652" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A652" s="94"/>
-      <c r="B652" s="76"/>
-      <c r="C652" s="94"/>
-      <c r="D652" s="102"/>
-      <c r="E652" s="94"/>
-      <c r="F652" s="94"/>
-      <c r="G652" s="94"/>
-      <c r="H652" s="94"/>
-      <c r="I652" s="94"/>
-      <c r="J652" s="52"/>
+      <c r="A652" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B652" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C652" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D652" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E652" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F652" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G652" s="94" t="s">
+        <v>612</v>
+      </c>
+      <c r="H652" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I652" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J652" s="52">
+        <v>10</v>
+      </c>
       <c r="K652" s="52"/>
       <c r="L652" s="52"/>
       <c r="M652" s="52"/>
@@ -62184,7 +62768,7 @@
       </c>
       <c r="S652" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB652" s="111"/>
       <c r="AC652" s="111"/>
@@ -62200,16 +62784,36 @@
       <c r="AP652" s="7"/>
     </row>
     <row r="653" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A653" s="94"/>
-      <c r="B653" s="76"/>
-      <c r="C653" s="94"/>
-      <c r="D653" s="102"/>
-      <c r="E653" s="94"/>
-      <c r="F653" s="94"/>
-      <c r="G653" s="94"/>
-      <c r="H653" s="94"/>
-      <c r="I653" s="94"/>
-      <c r="J653" s="52"/>
+      <c r="A653" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B653" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C653" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D653" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E653" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F653" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G653" s="94" t="s">
+        <v>613</v>
+      </c>
+      <c r="H653" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I653" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J653" s="52">
+        <v>10</v>
+      </c>
       <c r="K653" s="52"/>
       <c r="L653" s="52"/>
       <c r="M653" s="52"/>
@@ -62226,7 +62830,7 @@
       </c>
       <c r="S653" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB653" s="111"/>
       <c r="AC653" s="111"/>
@@ -62242,16 +62846,36 @@
       <c r="AP653" s="7"/>
     </row>
     <row r="654" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A654" s="94"/>
-      <c r="B654" s="76"/>
-      <c r="C654" s="94"/>
-      <c r="D654" s="102"/>
-      <c r="E654" s="94"/>
-      <c r="F654" s="94"/>
-      <c r="G654" s="94"/>
-      <c r="H654" s="94"/>
-      <c r="I654" s="94"/>
-      <c r="J654" s="52"/>
+      <c r="A654" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B654" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C654" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D654" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E654" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F654" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G654" s="94" t="s">
+        <v>614</v>
+      </c>
+      <c r="H654" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I654" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J654" s="52">
+        <v>10</v>
+      </c>
       <c r="K654" s="52"/>
       <c r="L654" s="52"/>
       <c r="M654" s="52"/>
@@ -62268,7 +62892,7 @@
       </c>
       <c r="S654" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB654" s="111"/>
       <c r="AC654" s="111"/>
@@ -62284,33 +62908,63 @@
       <c r="AP654" s="7"/>
     </row>
     <row r="655" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A655" s="94"/>
-      <c r="B655" s="76"/>
-      <c r="C655" s="94"/>
-      <c r="D655" s="102"/>
-      <c r="E655" s="94"/>
-      <c r="F655" s="94"/>
-      <c r="G655" s="94"/>
-      <c r="H655" s="94"/>
-      <c r="I655" s="94"/>
-      <c r="J655" s="52"/>
-      <c r="K655" s="52"/>
-      <c r="L655" s="52"/>
+      <c r="A655" s="85">
+        <v>46223</v>
+      </c>
+      <c r="B655" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C655" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D655" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E655" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F655" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G655" s="94" t="s">
+        <v>440</v>
+      </c>
+      <c r="H655" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I655" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J655" s="52">
+        <v>40</v>
+      </c>
+      <c r="K655" s="52">
+        <v>20</v>
+      </c>
+      <c r="L655" s="52">
+        <v>20</v>
+      </c>
       <c r="M655" s="52"/>
       <c r="N655" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O655" s="52"/>
-      <c r="P655" s="52"/>
-      <c r="Q655" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O655" s="52">
+        <v>40</v>
+      </c>
+      <c r="P655" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q655" s="52">
+        <v>40</v>
+      </c>
       <c r="R655" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S655" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB655" s="111"/>
       <c r="AC655" s="111"/>
@@ -62326,33 +62980,61 @@
       <c r="AP655" s="7"/>
     </row>
     <row r="656" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A656" s="94"/>
-      <c r="B656" s="76"/>
-      <c r="C656" s="94"/>
-      <c r="D656" s="102"/>
-      <c r="E656" s="94"/>
-      <c r="F656" s="94"/>
-      <c r="G656" s="94"/>
-      <c r="H656" s="94"/>
-      <c r="I656" s="94"/>
+      <c r="A656" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B656" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C656" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D656" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E656" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F656" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G656" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H656" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I656" s="94" t="s">
+        <v>568</v>
+      </c>
       <c r="J656" s="52"/>
-      <c r="K656" s="52"/>
-      <c r="L656" s="52"/>
+      <c r="K656" s="52">
+        <v>40</v>
+      </c>
+      <c r="L656" s="52">
+        <v>400</v>
+      </c>
       <c r="M656" s="52"/>
       <c r="N656" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O656" s="52"/>
-      <c r="P656" s="52"/>
-      <c r="Q656" s="52"/>
+        <v>440</v>
+      </c>
+      <c r="O656" s="52">
+        <v>160</v>
+      </c>
+      <c r="P656" s="52">
+        <v>320</v>
+      </c>
+      <c r="Q656" s="52">
+        <v>200</v>
+      </c>
       <c r="R656" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="S656" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="AB656" s="111"/>
       <c r="AC656" s="111"/>
@@ -62368,33 +63050,61 @@
       <c r="AP656" s="7"/>
     </row>
     <row r="657" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A657" s="94"/>
-      <c r="B657" s="76"/>
-      <c r="C657" s="94"/>
-      <c r="D657" s="102"/>
-      <c r="E657" s="94"/>
-      <c r="F657" s="94"/>
-      <c r="G657" s="94"/>
-      <c r="H657" s="94"/>
-      <c r="I657" s="94"/>
+      <c r="A657" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B657" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C657" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D657" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E657" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F657" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G657" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H657" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I657" s="94" t="s">
+        <v>617</v>
+      </c>
       <c r="J657" s="52"/>
-      <c r="K657" s="52"/>
-      <c r="L657" s="52"/>
+      <c r="K657" s="52">
+        <v>200</v>
+      </c>
+      <c r="L657" s="52">
+        <v>320</v>
+      </c>
       <c r="M657" s="52"/>
       <c r="N657" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O657" s="52"/>
-      <c r="P657" s="52"/>
-      <c r="Q657" s="52"/>
+        <v>520</v>
+      </c>
+      <c r="O657" s="52">
+        <v>320</v>
+      </c>
+      <c r="P657" s="52">
+        <v>400</v>
+      </c>
+      <c r="Q657" s="52">
+        <v>520</v>
+      </c>
       <c r="R657" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="S657" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="AB657" s="111"/>
       <c r="AC657" s="111"/>
@@ -62410,33 +63120,61 @@
       <c r="AP657" s="7"/>
     </row>
     <row r="658" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A658" s="94"/>
-      <c r="B658" s="76"/>
-      <c r="C658" s="94"/>
-      <c r="D658" s="102"/>
-      <c r="E658" s="94"/>
-      <c r="F658" s="94"/>
-      <c r="G658" s="94"/>
-      <c r="H658" s="94"/>
-      <c r="I658" s="94"/>
+      <c r="A658" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B658" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C658" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D658" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E658" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F658" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G658" s="94" t="s">
+        <v>615</v>
+      </c>
+      <c r="H658" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I658" s="94" t="s">
+        <v>618</v>
+      </c>
       <c r="J658" s="52"/>
-      <c r="K658" s="52"/>
-      <c r="L658" s="52"/>
+      <c r="K658" s="52">
+        <v>240</v>
+      </c>
+      <c r="L658" s="52">
+        <v>240</v>
+      </c>
       <c r="M658" s="52"/>
       <c r="N658" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O658" s="52"/>
-      <c r="P658" s="52"/>
-      <c r="Q658" s="52"/>
+        <v>480</v>
+      </c>
+      <c r="O658" s="52">
+        <v>240</v>
+      </c>
+      <c r="P658" s="52">
+        <v>240</v>
+      </c>
+      <c r="Q658" s="52">
+        <v>240</v>
+      </c>
       <c r="R658" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="S658" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AB658" s="111"/>
       <c r="AC658" s="111"/>
@@ -62452,33 +63190,61 @@
       <c r="AP658" s="7"/>
     </row>
     <row r="659" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A659" s="94"/>
-      <c r="B659" s="76"/>
-      <c r="C659" s="94"/>
-      <c r="D659" s="102"/>
-      <c r="E659" s="94"/>
-      <c r="F659" s="94"/>
-      <c r="G659" s="94"/>
-      <c r="H659" s="94"/>
-      <c r="I659" s="94"/>
+      <c r="A659" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B659" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C659" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D659" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E659" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F659" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G659" s="94" t="s">
+        <v>616</v>
+      </c>
+      <c r="H659" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I659" s="94" t="s">
+        <v>568</v>
+      </c>
       <c r="J659" s="52"/>
-      <c r="K659" s="52"/>
-      <c r="L659" s="52"/>
+      <c r="K659" s="52">
+        <v>200</v>
+      </c>
+      <c r="L659" s="52">
+        <v>200</v>
+      </c>
       <c r="M659" s="52"/>
       <c r="N659" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O659" s="52"/>
-      <c r="P659" s="52"/>
-      <c r="Q659" s="52"/>
+        <v>400</v>
+      </c>
+      <c r="O659" s="52">
+        <v>200</v>
+      </c>
+      <c r="P659" s="52">
+        <v>200</v>
+      </c>
+      <c r="Q659" s="52">
+        <v>200</v>
+      </c>
       <c r="R659" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S659" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB659" s="111"/>
       <c r="AC659" s="111"/>
@@ -62494,33 +63260,61 @@
       <c r="AP659" s="7"/>
     </row>
     <row r="660" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A660" s="94"/>
-      <c r="B660" s="76"/>
-      <c r="C660" s="94"/>
-      <c r="D660" s="102"/>
-      <c r="E660" s="94"/>
-      <c r="F660" s="94"/>
-      <c r="G660" s="94"/>
-      <c r="H660" s="94"/>
-      <c r="I660" s="94"/>
+      <c r="A660" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B660" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C660" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D660" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E660" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F660" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G660" s="94" t="s">
+        <v>593</v>
+      </c>
+      <c r="H660" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I660" s="94" t="s">
+        <v>448</v>
+      </c>
       <c r="J660" s="52"/>
-      <c r="K660" s="52"/>
-      <c r="L660" s="52"/>
+      <c r="K660" s="52">
+        <v>80</v>
+      </c>
+      <c r="L660" s="52">
+        <v>80</v>
+      </c>
       <c r="M660" s="52"/>
       <c r="N660" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O660" s="52"/>
-      <c r="P660" s="52"/>
-      <c r="Q660" s="52"/>
+        <v>160</v>
+      </c>
+      <c r="O660" s="52">
+        <v>80</v>
+      </c>
+      <c r="P660" s="52">
+        <v>80</v>
+      </c>
+      <c r="Q660" s="52">
+        <v>120</v>
+      </c>
       <c r="R660" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S660" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="AB660" s="111"/>
       <c r="AC660" s="111"/>
@@ -62536,33 +63330,63 @@
       <c r="AP660" s="7"/>
     </row>
     <row r="661" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A661" s="94"/>
-      <c r="B661" s="76"/>
-      <c r="C661" s="94"/>
-      <c r="D661" s="102"/>
-      <c r="E661" s="94"/>
-      <c r="F661" s="94"/>
-      <c r="G661" s="94"/>
-      <c r="H661" s="94"/>
-      <c r="I661" s="94"/>
-      <c r="J661" s="52"/>
-      <c r="K661" s="52"/>
-      <c r="L661" s="52"/>
+      <c r="A661" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B661" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C661" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D661" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E661" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F661" s="94" t="s">
+        <v>367</v>
+      </c>
+      <c r="G661" s="94" t="s">
+        <v>420</v>
+      </c>
+      <c r="H661" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I661" s="94" t="s">
+        <v>247</v>
+      </c>
+      <c r="J661" s="52">
+        <v>4000</v>
+      </c>
+      <c r="K661" s="52">
+        <v>600</v>
+      </c>
+      <c r="L661" s="52">
+        <v>800</v>
+      </c>
       <c r="M661" s="52"/>
       <c r="N661" s="104">
         <f t="shared" si="153"/>
-        <v>0</v>
-      </c>
-      <c r="O661" s="52"/>
-      <c r="P661" s="52"/>
-      <c r="Q661" s="52"/>
+        <v>1400</v>
+      </c>
+      <c r="O661" s="52">
+        <v>2800</v>
+      </c>
+      <c r="P661" s="52">
+        <v>1200</v>
+      </c>
+      <c r="Q661" s="52">
+        <v>2600</v>
+      </c>
       <c r="R661" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="S661" s="86">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AB661" s="111"/>
       <c r="AC661" s="111"/>
@@ -62578,12 +63402,24 @@
       <c r="AP661" s="7"/>
     </row>
     <row r="662" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A662" s="94"/>
-      <c r="B662" s="76"/>
-      <c r="C662" s="94"/>
-      <c r="D662" s="102"/>
-      <c r="E662" s="94"/>
-      <c r="F662" s="94"/>
+      <c r="A662" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B662" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C662" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D662" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E662" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F662" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G662" s="94"/>
       <c r="H662" s="94"/>
       <c r="I662" s="94"/>
@@ -62620,12 +63456,24 @@
       <c r="AP662" s="7"/>
     </row>
     <row r="663" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A663" s="94"/>
-      <c r="B663" s="76"/>
-      <c r="C663" s="94"/>
-      <c r="D663" s="102"/>
-      <c r="E663" s="94"/>
-      <c r="F663" s="94"/>
+      <c r="A663" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B663" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C663" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D663" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E663" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F663" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G663" s="94"/>
       <c r="H663" s="94"/>
       <c r="I663" s="94"/>
@@ -62662,12 +63510,24 @@
       <c r="AP663" s="7"/>
     </row>
     <row r="664" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A664" s="94"/>
-      <c r="B664" s="76"/>
-      <c r="C664" s="94"/>
-      <c r="D664" s="102"/>
-      <c r="E664" s="94"/>
-      <c r="F664" s="94"/>
+      <c r="A664" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B664" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C664" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D664" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E664" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F664" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G664" s="94"/>
       <c r="H664" s="94"/>
       <c r="I664" s="94"/>
@@ -62704,12 +63564,24 @@
       <c r="AP664" s="7"/>
     </row>
     <row r="665" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A665" s="94"/>
-      <c r="B665" s="76"/>
-      <c r="C665" s="94"/>
-      <c r="D665" s="102"/>
-      <c r="E665" s="94"/>
-      <c r="F665" s="94"/>
+      <c r="A665" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B665" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C665" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D665" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E665" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F665" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G665" s="94"/>
       <c r="H665" s="94"/>
       <c r="I665" s="94"/>
@@ -62746,12 +63618,24 @@
       <c r="AP665" s="7"/>
     </row>
     <row r="666" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A666" s="94"/>
-      <c r="B666" s="76"/>
-      <c r="C666" s="94"/>
-      <c r="D666" s="102"/>
-      <c r="E666" s="94"/>
-      <c r="F666" s="94"/>
+      <c r="A666" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B666" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C666" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D666" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E666" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F666" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G666" s="94"/>
       <c r="H666" s="94"/>
       <c r="I666" s="94"/>
@@ -62788,12 +63672,24 @@
       <c r="AP666" s="7"/>
     </row>
     <row r="667" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A667" s="94"/>
-      <c r="B667" s="76"/>
-      <c r="C667" s="94"/>
-      <c r="D667" s="102"/>
-      <c r="E667" s="94"/>
-      <c r="F667" s="94"/>
+      <c r="A667" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B667" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C667" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D667" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E667" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F667" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G667" s="94"/>
       <c r="H667" s="94"/>
       <c r="I667" s="94"/>
@@ -62830,12 +63726,24 @@
       <c r="AP667" s="7"/>
     </row>
     <row r="668" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A668" s="94"/>
-      <c r="B668" s="76"/>
-      <c r="C668" s="94"/>
-      <c r="D668" s="102"/>
-      <c r="E668" s="94"/>
-      <c r="F668" s="94"/>
+      <c r="A668" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B668" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C668" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D668" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E668" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F668" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G668" s="94"/>
       <c r="H668" s="94"/>
       <c r="I668" s="94"/>
@@ -62872,12 +63780,24 @@
       <c r="AP668" s="7"/>
     </row>
     <row r="669" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A669" s="94"/>
-      <c r="B669" s="76"/>
-      <c r="C669" s="94"/>
-      <c r="D669" s="102"/>
-      <c r="E669" s="94"/>
-      <c r="F669" s="94"/>
+      <c r="A669" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B669" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C669" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D669" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E669" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F669" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G669" s="94"/>
       <c r="H669" s="94"/>
       <c r="I669" s="94"/>
@@ -62914,12 +63834,24 @@
       <c r="AP669" s="7"/>
     </row>
     <row r="670" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A670" s="94"/>
-      <c r="B670" s="76"/>
-      <c r="C670" s="94"/>
-      <c r="D670" s="102"/>
-      <c r="E670" s="94"/>
-      <c r="F670" s="94"/>
+      <c r="A670" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B670" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C670" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D670" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E670" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F670" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G670" s="94"/>
       <c r="H670" s="94"/>
       <c r="I670" s="94"/>
@@ -62956,12 +63888,24 @@
       <c r="AP670" s="7"/>
     </row>
     <row r="671" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A671" s="94"/>
-      <c r="B671" s="76"/>
-      <c r="C671" s="94"/>
-      <c r="D671" s="102"/>
-      <c r="E671" s="94"/>
-      <c r="F671" s="94"/>
+      <c r="A671" s="85">
+        <v>46224</v>
+      </c>
+      <c r="B671" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C671" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D671" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E671" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F671" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="G671" s="94"/>
       <c r="H671" s="94"/>
       <c r="I671" s="94"/>
@@ -63848,15 +64792,15 @@
       <c r="A693" s="3"/>
       <c r="J693" s="107">
         <f>SUM(J3:J692)</f>
-        <v>12778</v>
+        <v>17400</v>
       </c>
       <c r="K693" s="107">
         <f t="shared" ref="K693:S693" si="158">SUM(K3:K692)</f>
-        <v>8977</v>
+        <v>11712</v>
       </c>
       <c r="L693" s="107">
         <f t="shared" si="158"/>
-        <v>8161</v>
+        <v>11782</v>
       </c>
       <c r="M693" s="107">
         <f t="shared" si="158"/>
@@ -63864,27 +64808,27 @@
       </c>
       <c r="N693" s="107">
         <f t="shared" si="158"/>
-        <v>17138</v>
+        <v>23494</v>
       </c>
       <c r="O693" s="107">
         <f t="shared" si="158"/>
-        <v>14917</v>
+        <v>21401</v>
       </c>
       <c r="P693" s="107">
         <f t="shared" si="158"/>
-        <v>10913</v>
+        <v>15956</v>
       </c>
       <c r="Q693" s="107">
         <f t="shared" si="158"/>
-        <v>16208</v>
+        <v>25180</v>
       </c>
       <c r="R693" s="107">
         <f t="shared" si="158"/>
-        <v>42038</v>
+        <v>62537</v>
       </c>
       <c r="S693" s="107">
         <f t="shared" si="158"/>
-        <v>71954</v>
+        <v>103431</v>
       </c>
       <c r="AP693" s="7"/>
     </row>
@@ -63951,15 +64895,15 @@
       </c>
       <c r="J696" s="47">
         <f>J693/40</f>
-        <v>319.45</v>
+        <v>435</v>
       </c>
       <c r="K696" s="109">
         <f t="shared" ref="K696:S696" si="159">K693/40</f>
-        <v>224.42500000000001</v>
+        <v>292.8</v>
       </c>
       <c r="L696" s="109">
         <f t="shared" si="159"/>
-        <v>204.02500000000001</v>
+        <v>294.55</v>
       </c>
       <c r="M696" s="109">
         <f t="shared" si="159"/>
@@ -63967,27 +64911,27 @@
       </c>
       <c r="N696" s="47">
         <f t="shared" si="159"/>
-        <v>428.45</v>
+        <v>587.35</v>
       </c>
       <c r="O696" s="109">
         <f t="shared" si="159"/>
-        <v>372.92500000000001</v>
+        <v>535.02499999999998</v>
       </c>
       <c r="P696" s="109">
         <f t="shared" si="159"/>
-        <v>272.82499999999999</v>
+        <v>398.9</v>
       </c>
       <c r="Q696" s="109">
         <f t="shared" si="159"/>
-        <v>405.2</v>
+        <v>629.5</v>
       </c>
       <c r="R696" s="47">
         <f t="shared" si="159"/>
-        <v>1050.95</v>
+        <v>1563.425</v>
       </c>
       <c r="S696" s="109">
         <f t="shared" si="159"/>
-        <v>1798.85</v>
+        <v>2585.7750000000001</v>
       </c>
       <c r="T696" s="54">
         <f t="shared" ref="T696:AF696" si="160">+T433/40</f>
@@ -64052,7 +64996,7 @@
     <row r="698" spans="1:42" x14ac:dyDescent="0.35">
       <c r="S698" s="53">
         <f>S696+W696+AA696</f>
-        <v>1798.85</v>
+        <v>2585.7750000000001</v>
       </c>
       <c r="X698" t="s">
         <v>50</v>
@@ -64180,11 +65124,11 @@
       </c>
       <c r="G7" s="16">
         <f>'STT Report'!Q696+'STT Report'!Z696</f>
-        <v>405.2</v>
+        <v>629.5</v>
       </c>
       <c r="H7" s="17">
         <f>E7+F7-G7</f>
-        <v>914.8</v>
+        <v>690.5</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -64199,11 +65143,11 @@
       </c>
       <c r="G8" s="16">
         <f>'STT Report'!P696+'STT Report'!Y696</f>
-        <v>272.82499999999999</v>
+        <v>398.9</v>
       </c>
       <c r="H8" s="17">
         <f>E8+F8-G8</f>
-        <v>70.175000000000011</v>
+        <v>-55.899999999999977</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -64218,11 +65162,11 @@
       </c>
       <c r="G9" s="16">
         <f>'STT Report'!O696+'STT Report'!X696</f>
-        <v>372.92500000000001</v>
+        <v>535.02499999999998</v>
       </c>
       <c r="H9" s="17">
         <f>E9+F9-G9</f>
-        <v>555.07500000000005</v>
+        <v>392.97500000000002</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -64239,11 +65183,11 @@
       </c>
       <c r="G10" s="22">
         <f>SUM(G7:G9)</f>
-        <v>1050.95</v>
+        <v>1563.4250000000002</v>
       </c>
       <c r="H10" s="23">
         <f>SUM(H7:H9)</f>
-        <v>1540.05</v>
+        <v>1027.575</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -64256,11 +65200,11 @@
       <c r="F11" s="15"/>
       <c r="G11" s="44">
         <f>'STT Report'!J696</f>
-        <v>319.45</v>
+        <v>435</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1333.55</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -64297,11 +65241,11 @@
       </c>
       <c r="G14" s="20">
         <f>SUM(G11:G13)</f>
-        <v>319.45</v>
+        <v>435</v>
       </c>
       <c r="H14" s="23">
         <f>SUM(H11:H13)</f>
-        <v>1333.55</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -64331,11 +65275,11 @@
       <c r="F16" s="18"/>
       <c r="G16" s="16">
         <f>'STT Report'!L696+'STT Report'!U696</f>
-        <v>204.02500000000001</v>
+        <v>294.55</v>
       </c>
       <c r="H16" s="17">
         <f>E16+F16-G16</f>
-        <v>62.974999999999994</v>
+        <v>-27.550000000000011</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -64348,11 +65292,11 @@
       <c r="F17" s="18"/>
       <c r="G17" s="16">
         <f>'STT Report'!K696+'STT Report'!T696</f>
-        <v>224.42500000000001</v>
+        <v>292.8</v>
       </c>
       <c r="H17" s="17">
         <f>E17+F17-G17</f>
-        <v>15.574999999999989</v>
+        <v>-52.800000000000011</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -64369,11 +65313,11 @@
       </c>
       <c r="G18" s="22">
         <f>SUM(G15:G17)</f>
-        <v>428.45000000000005</v>
+        <v>587.35</v>
       </c>
       <c r="H18" s="23">
         <f>SUM(H15:H17)</f>
-        <v>78.549999999999983</v>
+        <v>-80.350000000000023</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -64390,11 +65334,11 @@
       </c>
       <c r="G19" s="25">
         <f>G10+G14+G18</f>
-        <v>1798.8500000000001</v>
+        <v>2585.7750000000001</v>
       </c>
       <c r="H19" s="27">
         <f>H10+H14+H18</f>
-        <v>2952.15</v>
+        <v>2165.2249999999999</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">

--- a/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2327089F-9A9B-45ED-AE99-672573CB0E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457BA334-DA35-44A6-895E-C3199BC0FC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3839" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4067" uniqueCount="699">
   <si>
     <t>Date</t>
   </si>
@@ -2049,6 +2049,84 @@
   <si>
     <t>EME</t>
   </si>
+  <si>
+    <t>umair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satara Bakers </t>
+  </si>
+  <si>
+    <t>Sadar Bazar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">shadbagh </t>
+  </si>
+  <si>
+    <t>behria Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faisal Town </t>
+  </si>
+  <si>
+    <t>Shere Rubani Store</t>
+  </si>
+  <si>
+    <t>Bakhtawer Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madina Bakers </t>
+  </si>
+  <si>
+    <t>Bhai Bhai Medical Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calevery Ground </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al hamd Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marhaba </t>
+  </si>
+  <si>
+    <t>Punjab Coporative</t>
+  </si>
+  <si>
+    <t>Fakhar Store</t>
+  </si>
+  <si>
+    <t>MM Store</t>
+  </si>
+  <si>
+    <t>Sahdra</t>
+  </si>
+  <si>
+    <t>Umaima Super Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaudry Frozen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">China Groccery </t>
+  </si>
+  <si>
+    <t>Dua Book store</t>
+  </si>
+  <si>
+    <t>M Sultan GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajwa Atta Chaki </t>
+  </si>
+  <si>
+    <t>Ghazi Road</t>
+  </si>
 </sst>
 </file>
 
@@ -2995,10 +3073,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3007,16 +3088,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3403,47 +3481,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="123" t="s">
+      <c r="A1" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="C1" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="E1" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="F1" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="G1" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="123" t="s">
+      <c r="H1" s="119" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J1" s="42"/>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="125" t="s">
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="121" t="s">
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="122" t="s">
         <v>10</v>
       </c>
       <c r="T1" s="124" t="s">
@@ -3458,61 +3536,61 @@
       <c r="Y1" s="124"/>
       <c r="Z1" s="124"/>
       <c r="AA1" s="124"/>
-      <c r="AB1" s="121" t="s">
+      <c r="AB1" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="121" t="s">
+      <c r="AC1" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="121" t="s">
+      <c r="AD1" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="121" t="s">
+      <c r="AE1" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="121" t="s">
+      <c r="AF1" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="121" t="s">
+      <c r="AG1" s="122" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="84">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="121" t="s">
+      <c r="AI1" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="121" t="s">
+      <c r="AJ1" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="121" t="s">
+      <c r="AK1" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="121" t="s">
+      <c r="AL1" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="121" t="s">
+      <c r="AM1" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="119" t="s">
+      <c r="AN1" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="119" t="s">
+      <c r="AO1" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="121" t="s">
+      <c r="AP1" s="122" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="123"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
+      <c r="A2" s="119"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3543,7 +3621,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="122"/>
+      <c r="S2" s="123"/>
       <c r="T2" s="83" t="s">
         <v>73</v>
       </c>
@@ -3568,23 +3646,23 @@
       <c r="AA2" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="123"/>
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
       <c r="AH2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="120"/>
-      <c r="AO2" s="120"/>
-      <c r="AP2" s="122"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="123"/>
+      <c r="AL2" s="123"/>
+      <c r="AM2" s="123"/>
+      <c r="AN2" s="126"/>
+      <c r="AO2" s="126"/>
+      <c r="AP2" s="123"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="85">
@@ -66584,7 +66662,7 @@
       <c r="L709" s="52"/>
       <c r="M709" s="52"/>
       <c r="N709" s="104">
-        <f t="shared" ref="N709:N736" si="155">K709+L709+M709</f>
+        <f t="shared" ref="N709:N743" si="155">K709+L709+M709</f>
         <v>0</v>
       </c>
       <c r="O709" s="52">
@@ -66599,7 +66677,7 @@
         <v>16</v>
       </c>
       <c r="S709" s="86">
-        <f t="shared" ref="S709:S750" si="156">R709+N709+J709</f>
+        <f t="shared" ref="S709:S772" si="156">R709+N709+J709</f>
         <v>16</v>
       </c>
       <c r="AB709" s="111"/>
@@ -68320,9 +68398,15 @@
       <c r="F735" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G735" s="94"/>
-      <c r="H735" s="94"/>
-      <c r="I735" s="94"/>
+      <c r="G735" s="94" t="s">
+        <v>546</v>
+      </c>
+      <c r="H735" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="I735" s="94" t="s">
+        <v>135</v>
+      </c>
       <c r="J735" s="52"/>
       <c r="K735" s="52"/>
       <c r="L735" s="52"/>
@@ -68331,16 +68415,22 @@
         <f t="shared" si="155"/>
         <v>0</v>
       </c>
-      <c r="O735" s="52"/>
-      <c r="P735" s="52"/>
-      <c r="Q735" s="52"/>
+      <c r="O735" s="52">
+        <v>40</v>
+      </c>
+      <c r="P735" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q735" s="52">
+        <v>120</v>
+      </c>
       <c r="R735" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="S735" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB735" s="111"/>
       <c r="AC735" s="111"/>
@@ -68374,27 +68464,45 @@
       <c r="F736" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G736" s="94"/>
-      <c r="H736" s="94"/>
-      <c r="I736" s="94"/>
-      <c r="J736" s="52"/>
-      <c r="K736" s="52"/>
-      <c r="L736" s="52"/>
+      <c r="G736" s="94" t="s">
+        <v>548</v>
+      </c>
+      <c r="H736" s="94" t="s">
+        <v>673</v>
+      </c>
+      <c r="I736" s="94" t="s">
+        <v>434</v>
+      </c>
+      <c r="J736" s="52">
+        <v>112</v>
+      </c>
+      <c r="K736" s="52">
+        <v>20</v>
+      </c>
+      <c r="L736" s="52">
+        <v>20</v>
+      </c>
       <c r="M736" s="52"/>
       <c r="N736" s="104">
         <f t="shared" si="155"/>
-        <v>0</v>
-      </c>
-      <c r="O736" s="52"/>
-      <c r="P736" s="52"/>
-      <c r="Q736" s="52"/>
+        <v>40</v>
+      </c>
+      <c r="O736" s="52">
+        <v>93</v>
+      </c>
+      <c r="P736" s="52">
+        <v>139</v>
+      </c>
+      <c r="Q736" s="52">
+        <v>178</v>
+      </c>
       <c r="R736" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="S736" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="AB736" s="111"/>
       <c r="AC736" s="111"/>
@@ -68411,7 +68519,7 @@
     </row>
     <row r="737" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A737" s="85">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B737" s="51" t="s">
         <v>85</v>
@@ -68428,24 +68536,43 @@
       <c r="F737" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G737" s="94"/>
-      <c r="H737" s="94"/>
-      <c r="I737" s="94"/>
+      <c r="G737" s="94" t="s">
+        <v>674</v>
+      </c>
+      <c r="H737" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I737" s="94" t="s">
+        <v>675</v>
+      </c>
       <c r="J737" s="52"/>
-      <c r="K737" s="52"/>
-      <c r="L737" s="52"/>
+      <c r="K737" s="52">
+        <v>40</v>
+      </c>
+      <c r="L737" s="52">
+        <v>40</v>
+      </c>
       <c r="M737" s="52"/>
-      <c r="N737" s="103"/>
-      <c r="O737" s="52"/>
-      <c r="P737" s="52"/>
-      <c r="Q737" s="52"/>
+      <c r="N737" s="103">
+        <f t="shared" si="155"/>
+        <v>80</v>
+      </c>
+      <c r="O737" s="52">
+        <v>40</v>
+      </c>
+      <c r="P737" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q737" s="52">
+        <v>40</v>
+      </c>
       <c r="R737" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S737" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB737" s="111"/>
       <c r="AC737" s="111"/>
@@ -68462,7 +68589,7 @@
     </row>
     <row r="738" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A738" s="85">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B738" s="51" t="s">
         <v>85</v>
@@ -68477,26 +68604,47 @@
         <v>86</v>
       </c>
       <c r="F738" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="G738" s="94"/>
-      <c r="H738" s="94"/>
-      <c r="I738" s="94"/>
-      <c r="J738" s="52"/>
-      <c r="K738" s="52"/>
-      <c r="L738" s="52"/>
+        <v>87</v>
+      </c>
+      <c r="G738" s="94" t="s">
+        <v>443</v>
+      </c>
+      <c r="H738" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I738" s="94" t="s">
+        <v>447</v>
+      </c>
+      <c r="J738" s="52">
+        <v>200</v>
+      </c>
+      <c r="K738" s="52">
+        <v>200</v>
+      </c>
+      <c r="L738" s="52">
+        <v>200</v>
+      </c>
       <c r="M738" s="52"/>
-      <c r="N738" s="103"/>
-      <c r="O738" s="52"/>
-      <c r="P738" s="52"/>
-      <c r="Q738" s="52"/>
+      <c r="N738" s="103">
+        <f t="shared" si="155"/>
+        <v>400</v>
+      </c>
+      <c r="O738" s="52">
+        <v>200</v>
+      </c>
+      <c r="P738" s="52">
+        <v>200</v>
+      </c>
+      <c r="Q738" s="52">
+        <v>200</v>
+      </c>
       <c r="R738" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S738" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AB738" s="111"/>
       <c r="AC738" s="111"/>
@@ -68513,7 +68661,7 @@
     </row>
     <row r="739" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A739" s="85">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B739" s="51" t="s">
         <v>85</v>
@@ -68528,26 +68676,41 @@
         <v>86</v>
       </c>
       <c r="F739" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="G739" s="94"/>
-      <c r="H739" s="94"/>
-      <c r="I739" s="94"/>
+        <v>87</v>
+      </c>
+      <c r="G739" s="94" t="s">
+        <v>532</v>
+      </c>
+      <c r="H739" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I739" s="94" t="s">
+        <v>243</v>
+      </c>
       <c r="J739" s="52"/>
       <c r="K739" s="52"/>
       <c r="L739" s="52"/>
       <c r="M739" s="52"/>
-      <c r="N739" s="103"/>
-      <c r="O739" s="52"/>
-      <c r="P739" s="52"/>
-      <c r="Q739" s="52"/>
+      <c r="N739" s="103">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+      <c r="O739" s="52">
+        <v>120</v>
+      </c>
+      <c r="P739" s="52">
+        <v>120</v>
+      </c>
+      <c r="Q739" s="52">
+        <v>80</v>
+      </c>
       <c r="R739" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="S739" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AB739" s="111"/>
       <c r="AC739" s="111"/>
@@ -68564,7 +68727,7 @@
     </row>
     <row r="740" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A740" s="85">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B740" s="51" t="s">
         <v>85</v>
@@ -68579,26 +68742,37 @@
         <v>86</v>
       </c>
       <c r="F740" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="G740" s="94"/>
-      <c r="H740" s="94"/>
-      <c r="I740" s="94"/>
+        <v>87</v>
+      </c>
+      <c r="G740" s="94" t="s">
+        <v>676</v>
+      </c>
+      <c r="H740" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I740" s="94" t="s">
+        <v>677</v>
+      </c>
       <c r="J740" s="52"/>
       <c r="K740" s="52"/>
       <c r="L740" s="52"/>
       <c r="M740" s="52"/>
-      <c r="N740" s="103"/>
+      <c r="N740" s="103">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
       <c r="O740" s="52"/>
-      <c r="P740" s="52"/>
+      <c r="P740" s="52">
+        <v>80</v>
+      </c>
       <c r="Q740" s="52"/>
       <c r="R740" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S740" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB740" s="111"/>
       <c r="AC740" s="111"/>
@@ -68615,7 +68789,7 @@
     </row>
     <row r="741" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A741" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B741" s="51" t="s">
         <v>85</v>
@@ -68630,26 +68804,39 @@
         <v>86</v>
       </c>
       <c r="F741" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="G741" s="94"/>
-      <c r="H741" s="94"/>
-      <c r="I741" s="94"/>
+        <v>87</v>
+      </c>
+      <c r="G741" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H741" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I741" s="94" t="s">
+        <v>568</v>
+      </c>
       <c r="J741" s="52"/>
-      <c r="K741" s="52"/>
+      <c r="K741" s="52">
+        <v>40</v>
+      </c>
       <c r="L741" s="52"/>
       <c r="M741" s="52"/>
-      <c r="N741" s="103"/>
+      <c r="N741" s="103">
+        <f t="shared" si="155"/>
+        <v>40</v>
+      </c>
       <c r="O741" s="52"/>
       <c r="P741" s="52"/>
-      <c r="Q741" s="52"/>
+      <c r="Q741" s="52">
+        <v>40</v>
+      </c>
       <c r="R741" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S741" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB741" s="111"/>
       <c r="AC741" s="111"/>
@@ -68666,7 +68853,7 @@
     </row>
     <row r="742" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A742" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B742" s="51" t="s">
         <v>85</v>
@@ -68681,26 +68868,45 @@
         <v>86</v>
       </c>
       <c r="F742" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="G742" s="94"/>
-      <c r="H742" s="94"/>
-      <c r="I742" s="94"/>
+        <v>87</v>
+      </c>
+      <c r="G742" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H742" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I742" s="94" t="s">
+        <v>678</v>
+      </c>
       <c r="J742" s="52"/>
-      <c r="K742" s="52"/>
-      <c r="L742" s="52"/>
+      <c r="K742" s="52">
+        <v>40</v>
+      </c>
+      <c r="L742" s="52">
+        <v>40</v>
+      </c>
       <c r="M742" s="52"/>
-      <c r="N742" s="103"/>
-      <c r="O742" s="52"/>
-      <c r="P742" s="52"/>
-      <c r="Q742" s="52"/>
+      <c r="N742" s="103">
+        <f t="shared" si="155"/>
+        <v>80</v>
+      </c>
+      <c r="O742" s="52">
+        <v>37</v>
+      </c>
+      <c r="P742" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q742" s="52">
+        <v>79</v>
+      </c>
       <c r="R742" s="104">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="S742" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="AB742" s="111"/>
       <c r="AC742" s="111"/>
@@ -68717,7 +68923,7 @@
     </row>
     <row r="743" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A743" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B743" s="51" t="s">
         <v>85</v>
@@ -68732,23 +68938,43 @@
         <v>86</v>
       </c>
       <c r="F743" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="G743" s="94"/>
-      <c r="H743" s="94"/>
-      <c r="I743" s="94"/>
+        <v>87</v>
+      </c>
+      <c r="G743" s="94" t="s">
+        <v>531</v>
+      </c>
+      <c r="H743" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I743" s="94" t="s">
+        <v>679</v>
+      </c>
       <c r="J743" s="52"/>
-      <c r="K743" s="52"/>
+      <c r="K743" s="52">
+        <v>40</v>
+      </c>
       <c r="L743" s="52"/>
       <c r="M743" s="52"/>
-      <c r="N743" s="103"/>
-      <c r="O743" s="52"/>
-      <c r="P743" s="52"/>
-      <c r="Q743" s="52"/>
-      <c r="R743" s="103"/>
+      <c r="N743" s="103">
+        <f t="shared" ref="N743:N786" si="157">K743+L743+M743</f>
+        <v>40</v>
+      </c>
+      <c r="O743" s="52">
+        <v>40</v>
+      </c>
+      <c r="P743" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q743" s="52">
+        <v>40</v>
+      </c>
+      <c r="R743" s="104">
+        <f t="shared" ref="R743:R777" si="158">SUM(O743:Q743)</f>
+        <v>120</v>
+      </c>
       <c r="S743" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB743" s="111"/>
       <c r="AC743" s="111"/>
@@ -68765,7 +68991,7 @@
     </row>
     <row r="744" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A744" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B744" s="51" t="s">
         <v>85</v>
@@ -68782,21 +69008,41 @@
       <c r="F744" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G744" s="94"/>
-      <c r="H744" s="94"/>
-      <c r="I744" s="94"/>
-      <c r="J744" s="52"/>
+      <c r="G744" s="94" t="s">
+        <v>680</v>
+      </c>
+      <c r="H744" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I744" s="94" t="s">
+        <v>684</v>
+      </c>
+      <c r="J744" s="52">
+        <v>20</v>
+      </c>
       <c r="K744" s="52"/>
       <c r="L744" s="52"/>
       <c r="M744" s="52"/>
-      <c r="N744" s="103"/>
-      <c r="O744" s="52"/>
-      <c r="P744" s="52"/>
-      <c r="Q744" s="52"/>
-      <c r="R744" s="103"/>
+      <c r="N744" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O744" s="52">
+        <v>15</v>
+      </c>
+      <c r="P744" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q744" s="52">
+        <v>15</v>
+      </c>
+      <c r="R744" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
       <c r="S744" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB744" s="111"/>
       <c r="AC744" s="111"/>
@@ -68813,7 +69059,7 @@
     </row>
     <row r="745" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A745" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B745" s="51" t="s">
         <v>85</v>
@@ -68830,21 +69076,39 @@
       <c r="F745" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G745" s="94"/>
-      <c r="H745" s="94"/>
-      <c r="I745" s="94"/>
-      <c r="J745" s="52"/>
+      <c r="G745" s="94" t="s">
+        <v>681</v>
+      </c>
+      <c r="H745" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I745" s="94" t="s">
+        <v>684</v>
+      </c>
+      <c r="J745" s="52">
+        <v>16</v>
+      </c>
       <c r="K745" s="52"/>
       <c r="L745" s="52"/>
       <c r="M745" s="52"/>
-      <c r="N745" s="103"/>
+      <c r="N745" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O745" s="52"/>
-      <c r="P745" s="52"/>
-      <c r="Q745" s="52"/>
-      <c r="R745" s="103"/>
+      <c r="P745" s="52">
+        <v>12</v>
+      </c>
+      <c r="Q745" s="52">
+        <v>12</v>
+      </c>
+      <c r="R745" s="104">
+        <f t="shared" si="158"/>
+        <v>24</v>
+      </c>
       <c r="S745" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB745" s="111"/>
       <c r="AC745" s="111"/>
@@ -68861,7 +69125,7 @@
     </row>
     <row r="746" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A746" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B746" s="51" t="s">
         <v>85</v>
@@ -68878,21 +69142,41 @@
       <c r="F746" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G746" s="94"/>
-      <c r="H746" s="94"/>
-      <c r="I746" s="94"/>
-      <c r="J746" s="52"/>
-      <c r="K746" s="52"/>
-      <c r="L746" s="52"/>
+      <c r="G746" s="94" t="s">
+        <v>574</v>
+      </c>
+      <c r="H746" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I746" s="94" t="s">
+        <v>684</v>
+      </c>
+      <c r="J746" s="52">
+        <v>20</v>
+      </c>
+      <c r="K746" s="52">
+        <v>12</v>
+      </c>
+      <c r="L746" s="52">
+        <v>12</v>
+      </c>
       <c r="M746" s="52"/>
-      <c r="N746" s="103"/>
-      <c r="O746" s="52"/>
+      <c r="N746" s="103">
+        <f t="shared" si="157"/>
+        <v>24</v>
+      </c>
+      <c r="O746" s="52">
+        <v>12</v>
+      </c>
       <c r="P746" s="52"/>
       <c r="Q746" s="52"/>
-      <c r="R746" s="103"/>
+      <c r="R746" s="104">
+        <f t="shared" si="158"/>
+        <v>12</v>
+      </c>
       <c r="S746" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AB746" s="111"/>
       <c r="AC746" s="111"/>
@@ -68909,7 +69193,7 @@
     </row>
     <row r="747" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A747" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B747" s="51" t="s">
         <v>85</v>
@@ -68926,21 +69210,39 @@
       <c r="F747" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G747" s="94"/>
-      <c r="H747" s="94"/>
-      <c r="I747" s="94"/>
+      <c r="G747" s="94" t="s">
+        <v>573</v>
+      </c>
+      <c r="H747" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I747" s="94" t="s">
+        <v>684</v>
+      </c>
       <c r="J747" s="52"/>
-      <c r="K747" s="52"/>
+      <c r="K747" s="52">
+        <v>40</v>
+      </c>
       <c r="L747" s="52"/>
       <c r="M747" s="52"/>
-      <c r="N747" s="103"/>
-      <c r="O747" s="52"/>
-      <c r="P747" s="52"/>
+      <c r="N747" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O747" s="52">
+        <v>40</v>
+      </c>
+      <c r="P747" s="52">
+        <v>40</v>
+      </c>
       <c r="Q747" s="52"/>
-      <c r="R747" s="103"/>
+      <c r="R747" s="104">
+        <f t="shared" si="158"/>
+        <v>80</v>
+      </c>
       <c r="S747" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB747" s="111"/>
       <c r="AC747" s="111"/>
@@ -68957,7 +69259,7 @@
     </row>
     <row r="748" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A748" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B748" s="51" t="s">
         <v>85</v>
@@ -68974,21 +69276,35 @@
       <c r="F748" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G748" s="94"/>
-      <c r="H748" s="94"/>
-      <c r="I748" s="94"/>
-      <c r="J748" s="52"/>
+      <c r="G748" s="94" t="s">
+        <v>682</v>
+      </c>
+      <c r="H748" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I748" s="94" t="s">
+        <v>684</v>
+      </c>
+      <c r="J748" s="52">
+        <v>40</v>
+      </c>
       <c r="K748" s="52"/>
       <c r="L748" s="52"/>
       <c r="M748" s="52"/>
-      <c r="N748" s="103"/>
+      <c r="N748" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O748" s="52"/>
       <c r="P748" s="52"/>
       <c r="Q748" s="52"/>
-      <c r="R748" s="103"/>
+      <c r="R748" s="104">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
       <c r="S748" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB748" s="111"/>
       <c r="AC748" s="111"/>
@@ -69005,7 +69321,7 @@
     </row>
     <row r="749" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A749" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B749" s="51" t="s">
         <v>85</v>
@@ -69022,21 +69338,35 @@
       <c r="F749" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G749" s="94"/>
-      <c r="H749" s="94"/>
-      <c r="I749" s="94"/>
-      <c r="J749" s="52"/>
+      <c r="G749" s="94" t="s">
+        <v>683</v>
+      </c>
+      <c r="H749" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I749" s="94" t="s">
+        <v>684</v>
+      </c>
+      <c r="J749" s="52">
+        <v>12</v>
+      </c>
       <c r="K749" s="52"/>
       <c r="L749" s="52"/>
       <c r="M749" s="52"/>
-      <c r="N749" s="103"/>
+      <c r="N749" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O749" s="52"/>
       <c r="P749" s="52"/>
       <c r="Q749" s="52"/>
-      <c r="R749" s="103"/>
+      <c r="R749" s="104">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
       <c r="S749" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB749" s="111"/>
       <c r="AC749" s="111"/>
@@ -69053,7 +69383,7 @@
     </row>
     <row r="750" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A750" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B750" s="51" t="s">
         <v>85</v>
@@ -69070,21 +69400,45 @@
       <c r="F750" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G750" s="94"/>
-      <c r="H750" s="94"/>
-      <c r="I750" s="94"/>
-      <c r="J750" s="52"/>
-      <c r="K750" s="52"/>
-      <c r="L750" s="52"/>
+      <c r="G750" s="94" t="s">
+        <v>382</v>
+      </c>
+      <c r="H750" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I750" s="94" t="s">
+        <v>684</v>
+      </c>
+      <c r="J750" s="52">
+        <v>16</v>
+      </c>
+      <c r="K750" s="52">
+        <v>12</v>
+      </c>
+      <c r="L750" s="52">
+        <v>12</v>
+      </c>
       <c r="M750" s="52"/>
-      <c r="N750" s="103"/>
-      <c r="O750" s="52"/>
-      <c r="P750" s="52"/>
-      <c r="Q750" s="52"/>
-      <c r="R750" s="103"/>
+      <c r="N750" s="103">
+        <f t="shared" si="157"/>
+        <v>24</v>
+      </c>
+      <c r="O750" s="52">
+        <v>15</v>
+      </c>
+      <c r="P750" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q750" s="52">
+        <v>15</v>
+      </c>
+      <c r="R750" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
       <c r="S750" s="86">
         <f t="shared" si="156"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB750" s="111"/>
       <c r="AC750" s="111"/>
@@ -69101,7 +69455,7 @@
     </row>
     <row r="751" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A751" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B751" s="51" t="s">
         <v>85</v>
@@ -69118,19 +69472,42 @@
       <c r="F751" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G751" s="94"/>
-      <c r="H751" s="94"/>
-      <c r="I751" s="94"/>
-      <c r="J751" s="52"/>
+      <c r="G751" s="94" t="s">
+        <v>685</v>
+      </c>
+      <c r="H751" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I751" s="94" t="s">
+        <v>688</v>
+      </c>
+      <c r="J751" s="52">
+        <v>40</v>
+      </c>
       <c r="K751" s="52"/>
       <c r="L751" s="52"/>
       <c r="M751" s="52"/>
-      <c r="N751" s="103"/>
-      <c r="O751" s="52"/>
-      <c r="P751" s="52"/>
-      <c r="Q751" s="52"/>
-      <c r="R751" s="103"/>
-      <c r="S751" s="95"/>
+      <c r="N751" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O751" s="52">
+        <v>15</v>
+      </c>
+      <c r="P751" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q751" s="52">
+        <v>15</v>
+      </c>
+      <c r="R751" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S751" s="86">
+        <f t="shared" si="156"/>
+        <v>80</v>
+      </c>
       <c r="AB751" s="111"/>
       <c r="AC751" s="111"/>
       <c r="AD751" s="111"/>
@@ -69146,7 +69523,7 @@
     </row>
     <row r="752" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A752" s="85">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B752" s="51" t="s">
         <v>85</v>
@@ -69163,19 +69540,40 @@
       <c r="F752" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="G752" s="94"/>
-      <c r="H752" s="94"/>
-      <c r="I752" s="94"/>
+      <c r="G752" s="94" t="s">
+        <v>210</v>
+      </c>
+      <c r="H752" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I752" s="94" t="s">
+        <v>688</v>
+      </c>
       <c r="J752" s="52"/>
       <c r="K752" s="52"/>
       <c r="L752" s="52"/>
       <c r="M752" s="52"/>
-      <c r="N752" s="103"/>
-      <c r="O752" s="52"/>
-      <c r="P752" s="52"/>
-      <c r="Q752" s="52"/>
-      <c r="R752" s="103"/>
-      <c r="S752" s="95"/>
+      <c r="N752" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O752" s="52">
+        <v>15</v>
+      </c>
+      <c r="P752" s="52">
+        <v>15</v>
+      </c>
+      <c r="Q752" s="52">
+        <v>10</v>
+      </c>
+      <c r="R752" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S752" s="86">
+        <f t="shared" si="156"/>
+        <v>40</v>
+      </c>
       <c r="AB752" s="111"/>
       <c r="AC752" s="111"/>
       <c r="AD752" s="111"/>
@@ -69190,25 +69588,60 @@
       <c r="AP752" s="7"/>
     </row>
     <row r="753" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A753" s="94"/>
-      <c r="B753" s="76"/>
-      <c r="C753" s="94"/>
-      <c r="D753" s="102"/>
-      <c r="E753" s="94"/>
-      <c r="F753" s="94"/>
-      <c r="G753" s="94"/>
-      <c r="H753" s="94"/>
-      <c r="I753" s="94"/>
-      <c r="J753" s="52"/>
+      <c r="A753" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B753" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C753" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D753" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E753" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F753" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G753" s="94" t="s">
+        <v>209</v>
+      </c>
+      <c r="H753" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I753" s="94" t="s">
+        <v>688</v>
+      </c>
+      <c r="J753" s="52">
+        <v>40</v>
+      </c>
       <c r="K753" s="52"/>
       <c r="L753" s="52"/>
       <c r="M753" s="52"/>
-      <c r="N753" s="103"/>
-      <c r="O753" s="52"/>
-      <c r="P753" s="52"/>
-      <c r="Q753" s="52"/>
-      <c r="R753" s="103"/>
-      <c r="S753" s="95"/>
+      <c r="N753" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O753" s="52">
+        <v>40</v>
+      </c>
+      <c r="P753" s="52">
+        <v>40</v>
+      </c>
+      <c r="Q753" s="52">
+        <v>40</v>
+      </c>
+      <c r="R753" s="104">
+        <f t="shared" si="158"/>
+        <v>120</v>
+      </c>
+      <c r="S753" s="86">
+        <f t="shared" si="156"/>
+        <v>160</v>
+      </c>
       <c r="AB753" s="111"/>
       <c r="AC753" s="111"/>
       <c r="AD753" s="111"/>
@@ -69223,25 +69656,62 @@
       <c r="AP753" s="7"/>
     </row>
     <row r="754" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A754" s="94"/>
-      <c r="B754" s="76"/>
-      <c r="C754" s="94"/>
-      <c r="D754" s="102"/>
-      <c r="E754" s="94"/>
-      <c r="F754" s="94"/>
-      <c r="G754" s="94"/>
-      <c r="H754" s="94"/>
-      <c r="I754" s="94"/>
+      <c r="A754" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B754" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C754" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D754" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E754" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F754" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G754" s="94" t="s">
+        <v>686</v>
+      </c>
+      <c r="H754" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I754" s="94" t="s">
+        <v>688</v>
+      </c>
       <c r="J754" s="52"/>
-      <c r="K754" s="52"/>
-      <c r="L754" s="52"/>
+      <c r="K754" s="52">
+        <v>12</v>
+      </c>
+      <c r="L754" s="52">
+        <v>12</v>
+      </c>
       <c r="M754" s="52"/>
-      <c r="N754" s="103"/>
-      <c r="O754" s="52"/>
-      <c r="P754" s="52"/>
-      <c r="Q754" s="52"/>
-      <c r="R754" s="103"/>
-      <c r="S754" s="95"/>
+      <c r="N754" s="103">
+        <f t="shared" si="157"/>
+        <v>24</v>
+      </c>
+      <c r="O754" s="52">
+        <v>6</v>
+      </c>
+      <c r="P754" s="52">
+        <v>6</v>
+      </c>
+      <c r="Q754" s="52">
+        <v>6</v>
+      </c>
+      <c r="R754" s="104">
+        <f t="shared" si="158"/>
+        <v>18</v>
+      </c>
+      <c r="S754" s="86">
+        <f t="shared" si="156"/>
+        <v>42</v>
+      </c>
       <c r="AB754" s="111"/>
       <c r="AC754" s="111"/>
       <c r="AD754" s="111"/>
@@ -69256,25 +69726,58 @@
       <c r="AP754" s="7"/>
     </row>
     <row r="755" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A755" s="94"/>
-      <c r="B755" s="76"/>
-      <c r="C755" s="94"/>
-      <c r="D755" s="102"/>
-      <c r="E755" s="94"/>
-      <c r="F755" s="94"/>
-      <c r="G755" s="94"/>
-      <c r="H755" s="94"/>
-      <c r="I755" s="94"/>
+      <c r="A755" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B755" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C755" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D755" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E755" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F755" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G755" s="94" t="s">
+        <v>687</v>
+      </c>
+      <c r="H755" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I755" s="94" t="s">
+        <v>688</v>
+      </c>
       <c r="J755" s="52"/>
       <c r="K755" s="52"/>
       <c r="L755" s="52"/>
       <c r="M755" s="52"/>
-      <c r="N755" s="103"/>
-      <c r="O755" s="52"/>
-      <c r="P755" s="52"/>
-      <c r="Q755" s="52"/>
-      <c r="R755" s="103"/>
-      <c r="S755" s="95"/>
+      <c r="N755" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O755" s="52">
+        <v>15</v>
+      </c>
+      <c r="P755" s="52">
+        <v>15</v>
+      </c>
+      <c r="Q755" s="52">
+        <v>10</v>
+      </c>
+      <c r="R755" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S755" s="86">
+        <f t="shared" si="156"/>
+        <v>40</v>
+      </c>
       <c r="AB755" s="111"/>
       <c r="AC755" s="111"/>
       <c r="AD755" s="111"/>
@@ -69289,25 +69792,54 @@
       <c r="AP755" s="7"/>
     </row>
     <row r="756" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A756" s="94"/>
-      <c r="B756" s="76"/>
-      <c r="C756" s="94"/>
-      <c r="D756" s="102"/>
-      <c r="E756" s="94"/>
-      <c r="F756" s="94"/>
-      <c r="G756" s="94"/>
-      <c r="H756" s="94"/>
-      <c r="I756" s="94"/>
-      <c r="J756" s="52"/>
+      <c r="A756" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B756" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C756" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D756" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E756" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F756" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G756" s="94" t="s">
+        <v>689</v>
+      </c>
+      <c r="H756" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I756" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J756" s="52">
+        <v>10</v>
+      </c>
       <c r="K756" s="52"/>
       <c r="L756" s="52"/>
       <c r="M756" s="52"/>
-      <c r="N756" s="103"/>
+      <c r="N756" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O756" s="52"/>
       <c r="P756" s="52"/>
       <c r="Q756" s="52"/>
-      <c r="R756" s="103"/>
-      <c r="S756" s="95"/>
+      <c r="R756" s="104">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+      <c r="S756" s="86">
+        <f t="shared" si="156"/>
+        <v>10</v>
+      </c>
       <c r="AB756" s="111"/>
       <c r="AC756" s="111"/>
       <c r="AD756" s="111"/>
@@ -69322,25 +69854,54 @@
       <c r="AP756" s="7"/>
     </row>
     <row r="757" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A757" s="94"/>
-      <c r="B757" s="76"/>
-      <c r="C757" s="94"/>
-      <c r="D757" s="102"/>
-      <c r="E757" s="94"/>
-      <c r="F757" s="94"/>
-      <c r="G757" s="94"/>
-      <c r="H757" s="94"/>
-      <c r="I757" s="94"/>
-      <c r="J757" s="52"/>
+      <c r="A757" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B757" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C757" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D757" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E757" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F757" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G757" s="94" t="s">
+        <v>322</v>
+      </c>
+      <c r="H757" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I757" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J757" s="52">
+        <v>10</v>
+      </c>
       <c r="K757" s="52"/>
       <c r="L757" s="52"/>
       <c r="M757" s="52"/>
-      <c r="N757" s="103"/>
+      <c r="N757" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O757" s="52"/>
       <c r="P757" s="52"/>
       <c r="Q757" s="52"/>
-      <c r="R757" s="103"/>
-      <c r="S757" s="95"/>
+      <c r="R757" s="104">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+      <c r="S757" s="86">
+        <f t="shared" si="156"/>
+        <v>10</v>
+      </c>
       <c r="AB757" s="111"/>
       <c r="AC757" s="111"/>
       <c r="AD757" s="111"/>
@@ -69355,25 +69916,60 @@
       <c r="AP757" s="7"/>
     </row>
     <row r="758" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A758" s="94"/>
-      <c r="B758" s="76"/>
-      <c r="C758" s="94"/>
-      <c r="D758" s="102"/>
-      <c r="E758" s="94"/>
-      <c r="F758" s="94"/>
-      <c r="G758" s="94"/>
-      <c r="H758" s="94"/>
-      <c r="I758" s="94"/>
+      <c r="A758" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B758" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C758" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D758" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E758" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F758" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G758" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="H758" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I758" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J758" s="52"/>
-      <c r="K758" s="52"/>
-      <c r="L758" s="52"/>
+      <c r="K758" s="52">
+        <v>20</v>
+      </c>
+      <c r="L758" s="52">
+        <v>20</v>
+      </c>
       <c r="M758" s="52"/>
-      <c r="N758" s="103"/>
+      <c r="N758" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
       <c r="O758" s="52"/>
-      <c r="P758" s="52"/>
-      <c r="Q758" s="52"/>
-      <c r="R758" s="103"/>
-      <c r="S758" s="95"/>
+      <c r="P758" s="52">
+        <v>20</v>
+      </c>
+      <c r="Q758" s="52">
+        <v>20</v>
+      </c>
+      <c r="R758" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S758" s="86">
+        <f t="shared" si="156"/>
+        <v>80</v>
+      </c>
       <c r="AB758" s="111"/>
       <c r="AC758" s="111"/>
       <c r="AD758" s="111"/>
@@ -69388,25 +69984,64 @@
       <c r="AP758" s="7"/>
     </row>
     <row r="759" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A759" s="94"/>
-      <c r="B759" s="76"/>
-      <c r="C759" s="94"/>
-      <c r="D759" s="102"/>
-      <c r="E759" s="94"/>
-      <c r="F759" s="94"/>
-      <c r="G759" s="94"/>
-      <c r="H759" s="94"/>
-      <c r="I759" s="94"/>
-      <c r="J759" s="52"/>
-      <c r="K759" s="52"/>
-      <c r="L759" s="52"/>
+      <c r="A759" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B759" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C759" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D759" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E759" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F759" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G759" s="94" t="s">
+        <v>690</v>
+      </c>
+      <c r="H759" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I759" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J759" s="52">
+        <v>40</v>
+      </c>
+      <c r="K759" s="52">
+        <v>20</v>
+      </c>
+      <c r="L759" s="52">
+        <v>20</v>
+      </c>
       <c r="M759" s="52"/>
-      <c r="N759" s="103"/>
-      <c r="O759" s="52"/>
-      <c r="P759" s="52"/>
-      <c r="Q759" s="52"/>
-      <c r="R759" s="103"/>
-      <c r="S759" s="95"/>
+      <c r="N759" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O759" s="52">
+        <v>15</v>
+      </c>
+      <c r="P759" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q759" s="52">
+        <v>15</v>
+      </c>
+      <c r="R759" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S759" s="86">
+        <f t="shared" si="156"/>
+        <v>120</v>
+      </c>
       <c r="AB759" s="111"/>
       <c r="AC759" s="111"/>
       <c r="AD759" s="111"/>
@@ -69421,25 +70056,64 @@
       <c r="AP759" s="7"/>
     </row>
     <row r="760" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A760" s="94"/>
-      <c r="B760" s="76"/>
-      <c r="C760" s="94"/>
-      <c r="D760" s="102"/>
-      <c r="E760" s="94"/>
-      <c r="F760" s="94"/>
-      <c r="G760" s="94"/>
-      <c r="H760" s="94"/>
-      <c r="I760" s="94"/>
-      <c r="J760" s="52"/>
-      <c r="K760" s="52"/>
-      <c r="L760" s="52"/>
+      <c r="A760" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B760" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C760" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D760" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E760" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F760" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G760" s="94" t="s">
+        <v>440</v>
+      </c>
+      <c r="H760" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I760" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J760" s="52">
+        <v>80</v>
+      </c>
+      <c r="K760" s="52">
+        <v>20</v>
+      </c>
+      <c r="L760" s="52">
+        <v>20</v>
+      </c>
       <c r="M760" s="52"/>
-      <c r="N760" s="103"/>
-      <c r="O760" s="52"/>
-      <c r="P760" s="52"/>
-      <c r="Q760" s="52"/>
-      <c r="R760" s="103"/>
-      <c r="S760" s="95"/>
+      <c r="N760" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O760" s="52">
+        <v>20</v>
+      </c>
+      <c r="P760" s="52">
+        <v>20</v>
+      </c>
+      <c r="Q760" s="52">
+        <v>40</v>
+      </c>
+      <c r="R760" s="104">
+        <f t="shared" si="158"/>
+        <v>80</v>
+      </c>
+      <c r="S760" s="86">
+        <f t="shared" si="156"/>
+        <v>200</v>
+      </c>
       <c r="AB760" s="111"/>
       <c r="AC760" s="111"/>
       <c r="AD760" s="111"/>
@@ -69454,25 +70128,54 @@
       <c r="AP760" s="7"/>
     </row>
     <row r="761" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A761" s="94"/>
-      <c r="B761" s="76"/>
-      <c r="C761" s="94"/>
-      <c r="D761" s="102"/>
-      <c r="E761" s="94"/>
-      <c r="F761" s="94"/>
-      <c r="G761" s="94"/>
-      <c r="H761" s="94"/>
-      <c r="I761" s="94"/>
-      <c r="J761" s="52"/>
+      <c r="A761" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B761" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C761" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D761" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E761" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F761" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G761" s="94" t="s">
+        <v>605</v>
+      </c>
+      <c r="H761" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I761" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J761" s="52">
+        <v>10</v>
+      </c>
       <c r="K761" s="52"/>
       <c r="L761" s="52"/>
       <c r="M761" s="52"/>
-      <c r="N761" s="103"/>
+      <c r="N761" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O761" s="52"/>
       <c r="P761" s="52"/>
       <c r="Q761" s="52"/>
-      <c r="R761" s="103"/>
-      <c r="S761" s="95"/>
+      <c r="R761" s="104">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+      <c r="S761" s="86">
+        <f t="shared" si="156"/>
+        <v>10</v>
+      </c>
       <c r="AB761" s="111"/>
       <c r="AC761" s="111"/>
       <c r="AD761" s="111"/>
@@ -69487,25 +70190,54 @@
       <c r="AP761" s="7"/>
     </row>
     <row r="762" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A762" s="94"/>
-      <c r="B762" s="76"/>
-      <c r="C762" s="94"/>
-      <c r="D762" s="102"/>
-      <c r="E762" s="94"/>
-      <c r="F762" s="94"/>
-      <c r="G762" s="94"/>
-      <c r="H762" s="94"/>
-      <c r="I762" s="94"/>
-      <c r="J762" s="52"/>
+      <c r="A762" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B762" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C762" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D762" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E762" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F762" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G762" s="94" t="s">
+        <v>609</v>
+      </c>
+      <c r="H762" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I762" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="J762" s="52">
+        <v>10</v>
+      </c>
       <c r="K762" s="52"/>
       <c r="L762" s="52"/>
       <c r="M762" s="52"/>
-      <c r="N762" s="103"/>
+      <c r="N762" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O762" s="52"/>
       <c r="P762" s="52"/>
       <c r="Q762" s="52"/>
-      <c r="R762" s="103"/>
-      <c r="S762" s="95"/>
+      <c r="R762" s="104">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+      <c r="S762" s="86">
+        <f t="shared" si="156"/>
+        <v>10</v>
+      </c>
       <c r="AB762" s="111"/>
       <c r="AC762" s="111"/>
       <c r="AD762" s="111"/>
@@ -69520,25 +70252,58 @@
       <c r="AP762" s="7"/>
     </row>
     <row r="763" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A763" s="94"/>
-      <c r="B763" s="76"/>
-      <c r="C763" s="94"/>
-      <c r="D763" s="102"/>
-      <c r="E763" s="94"/>
-      <c r="F763" s="94"/>
-      <c r="G763" s="94"/>
-      <c r="H763" s="94"/>
-      <c r="I763" s="94"/>
+      <c r="A763" s="85">
+        <v>46230</v>
+      </c>
+      <c r="B763" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C763" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D763" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E763" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F763" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G763" s="94" t="s">
+        <v>635</v>
+      </c>
+      <c r="H763" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I763" s="94" t="s">
+        <v>273</v>
+      </c>
       <c r="J763" s="52"/>
       <c r="K763" s="52"/>
       <c r="L763" s="52"/>
       <c r="M763" s="52"/>
-      <c r="N763" s="103"/>
-      <c r="O763" s="52"/>
-      <c r="P763" s="52"/>
-      <c r="Q763" s="52"/>
-      <c r="R763" s="103"/>
-      <c r="S763" s="95"/>
+      <c r="N763" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O763" s="52">
+        <v>15</v>
+      </c>
+      <c r="P763" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q763" s="52">
+        <v>15</v>
+      </c>
+      <c r="R763" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S763" s="86">
+        <f t="shared" si="156"/>
+        <v>40</v>
+      </c>
       <c r="AB763" s="111"/>
       <c r="AC763" s="111"/>
       <c r="AD763" s="111"/>
@@ -69553,25 +70318,62 @@
       <c r="AP763" s="7"/>
     </row>
     <row r="764" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A764" s="94"/>
-      <c r="B764" s="76"/>
-      <c r="C764" s="94"/>
-      <c r="D764" s="102"/>
-      <c r="E764" s="94"/>
-      <c r="F764" s="94"/>
-      <c r="G764" s="94"/>
-      <c r="H764" s="94"/>
-      <c r="I764" s="94"/>
+      <c r="A764" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B764" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C764" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D764" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E764" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F764" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G764" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H764" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I764" s="94" t="s">
+        <v>691</v>
+      </c>
       <c r="J764" s="52"/>
-      <c r="K764" s="52"/>
-      <c r="L764" s="52"/>
+      <c r="K764" s="52">
+        <v>40</v>
+      </c>
+      <c r="L764" s="52">
+        <v>40</v>
+      </c>
       <c r="M764" s="52"/>
-      <c r="N764" s="103"/>
-      <c r="O764" s="52"/>
-      <c r="P764" s="52"/>
-      <c r="Q764" s="52"/>
-      <c r="R764" s="103"/>
-      <c r="S764" s="95"/>
+      <c r="N764" s="103">
+        <f t="shared" si="157"/>
+        <v>80</v>
+      </c>
+      <c r="O764" s="52">
+        <v>40</v>
+      </c>
+      <c r="P764" s="52">
+        <v>200</v>
+      </c>
+      <c r="Q764" s="52">
+        <v>120</v>
+      </c>
+      <c r="R764" s="104">
+        <f t="shared" si="158"/>
+        <v>360</v>
+      </c>
+      <c r="S764" s="86">
+        <f t="shared" si="156"/>
+        <v>440</v>
+      </c>
       <c r="AB764" s="111"/>
       <c r="AC764" s="111"/>
       <c r="AD764" s="111"/>
@@ -69586,25 +70388,60 @@
       <c r="AP764" s="7"/>
     </row>
     <row r="765" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A765" s="94"/>
-      <c r="B765" s="76"/>
-      <c r="C765" s="94"/>
-      <c r="D765" s="102"/>
-      <c r="E765" s="94"/>
-      <c r="F765" s="94"/>
-      <c r="G765" s="94"/>
-      <c r="H765" s="94"/>
-      <c r="I765" s="94"/>
+      <c r="A765" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B765" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C765" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D765" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E765" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F765" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G765" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H765" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I765" s="94" t="s">
+        <v>527</v>
+      </c>
       <c r="J765" s="52"/>
       <c r="K765" s="52"/>
-      <c r="L765" s="52"/>
+      <c r="L765" s="52">
+        <v>40</v>
+      </c>
       <c r="M765" s="52"/>
-      <c r="N765" s="103"/>
-      <c r="O765" s="52"/>
-      <c r="P765" s="52"/>
-      <c r="Q765" s="52"/>
-      <c r="R765" s="103"/>
-      <c r="S765" s="95"/>
+      <c r="N765" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O765" s="52">
+        <v>80</v>
+      </c>
+      <c r="P765" s="52">
+        <v>80</v>
+      </c>
+      <c r="Q765" s="52">
+        <v>40</v>
+      </c>
+      <c r="R765" s="104">
+        <f t="shared" si="158"/>
+        <v>200</v>
+      </c>
+      <c r="S765" s="86">
+        <f t="shared" si="156"/>
+        <v>240</v>
+      </c>
       <c r="AB765" s="111"/>
       <c r="AC765" s="111"/>
       <c r="AD765" s="111"/>
@@ -69619,25 +70456,60 @@
       <c r="AP765" s="7"/>
     </row>
     <row r="766" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A766" s="94"/>
-      <c r="B766" s="76"/>
-      <c r="C766" s="94"/>
-      <c r="D766" s="102"/>
-      <c r="E766" s="94"/>
-      <c r="F766" s="94"/>
-      <c r="G766" s="94"/>
-      <c r="H766" s="94"/>
-      <c r="I766" s="94"/>
+      <c r="A766" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B766" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C766" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D766" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E766" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F766" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G766" s="94" t="s">
+        <v>425</v>
+      </c>
+      <c r="H766" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I766" s="94" t="s">
+        <v>528</v>
+      </c>
       <c r="J766" s="52"/>
-      <c r="K766" s="52"/>
-      <c r="L766" s="52"/>
+      <c r="K766" s="52">
+        <v>200</v>
+      </c>
+      <c r="L766" s="52">
+        <v>200</v>
+      </c>
       <c r="M766" s="52"/>
-      <c r="N766" s="103"/>
-      <c r="O766" s="52"/>
-      <c r="P766" s="52"/>
+      <c r="N766" s="103">
+        <f t="shared" si="157"/>
+        <v>400</v>
+      </c>
+      <c r="O766" s="52">
+        <v>120</v>
+      </c>
+      <c r="P766" s="52">
+        <v>40</v>
+      </c>
       <c r="Q766" s="52"/>
-      <c r="R766" s="103"/>
-      <c r="S766" s="95"/>
+      <c r="R766" s="104">
+        <f t="shared" si="158"/>
+        <v>160</v>
+      </c>
+      <c r="S766" s="86">
+        <f t="shared" si="156"/>
+        <v>560</v>
+      </c>
       <c r="AB766" s="111"/>
       <c r="AC766" s="111"/>
       <c r="AD766" s="111"/>
@@ -69652,25 +70524,62 @@
       <c r="AP766" s="7"/>
     </row>
     <row r="767" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A767" s="94"/>
-      <c r="B767" s="76"/>
-      <c r="C767" s="94"/>
-      <c r="D767" s="102"/>
-      <c r="E767" s="94"/>
-      <c r="F767" s="94"/>
-      <c r="G767" s="94"/>
-      <c r="H767" s="94"/>
-      <c r="I767" s="94"/>
+      <c r="A767" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B767" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C767" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D767" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E767" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F767" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G767" s="94" t="s">
+        <v>240</v>
+      </c>
+      <c r="H767" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I767" s="94" t="s">
+        <v>94</v>
+      </c>
       <c r="J767" s="52"/>
-      <c r="K767" s="52"/>
-      <c r="L767" s="52"/>
+      <c r="K767" s="52">
+        <v>80</v>
+      </c>
+      <c r="L767" s="52">
+        <v>40</v>
+      </c>
       <c r="M767" s="52"/>
-      <c r="N767" s="103"/>
-      <c r="O767" s="52"/>
-      <c r="P767" s="52"/>
-      <c r="Q767" s="52"/>
-      <c r="R767" s="103"/>
-      <c r="S767" s="95"/>
+      <c r="N767" s="103">
+        <f t="shared" si="157"/>
+        <v>120</v>
+      </c>
+      <c r="O767" s="52">
+        <v>240</v>
+      </c>
+      <c r="P767" s="52">
+        <v>240</v>
+      </c>
+      <c r="Q767" s="52">
+        <v>320</v>
+      </c>
+      <c r="R767" s="104">
+        <f t="shared" si="158"/>
+        <v>800</v>
+      </c>
+      <c r="S767" s="86">
+        <f t="shared" si="156"/>
+        <v>920</v>
+      </c>
       <c r="AB767" s="111"/>
       <c r="AC767" s="111"/>
       <c r="AD767" s="111"/>
@@ -69685,25 +70594,60 @@
       <c r="AP767" s="7"/>
     </row>
     <row r="768" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A768" s="94"/>
-      <c r="B768" s="76"/>
-      <c r="C768" s="94"/>
-      <c r="D768" s="102"/>
-      <c r="E768" s="94"/>
-      <c r="F768" s="94"/>
-      <c r="G768" s="94"/>
-      <c r="H768" s="94"/>
-      <c r="I768" s="94"/>
-      <c r="J768" s="52"/>
+      <c r="A768" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B768" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C768" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D768" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E768" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F768" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G768" s="94" t="s">
+        <v>440</v>
+      </c>
+      <c r="H768" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I768" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="J768" s="52">
+        <v>40</v>
+      </c>
       <c r="K768" s="52"/>
       <c r="L768" s="52"/>
       <c r="M768" s="52"/>
-      <c r="N768" s="103"/>
-      <c r="O768" s="52"/>
-      <c r="P768" s="52"/>
-      <c r="Q768" s="52"/>
-      <c r="R768" s="103"/>
-      <c r="S768" s="95"/>
+      <c r="N768" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O768" s="52">
+        <v>10</v>
+      </c>
+      <c r="P768" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q768" s="52">
+        <v>20</v>
+      </c>
+      <c r="R768" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S768" s="86">
+        <f t="shared" si="156"/>
+        <v>80</v>
+      </c>
       <c r="AB768" s="111"/>
       <c r="AC768" s="111"/>
       <c r="AD768" s="111"/>
@@ -69718,25 +70662,60 @@
       <c r="AP768" s="7"/>
     </row>
     <row r="769" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A769" s="94"/>
-      <c r="B769" s="76"/>
-      <c r="C769" s="94"/>
-      <c r="D769" s="102"/>
-      <c r="E769" s="94"/>
-      <c r="F769" s="94"/>
-      <c r="G769" s="94"/>
-      <c r="H769" s="94"/>
-      <c r="I769" s="94"/>
-      <c r="J769" s="52"/>
-      <c r="K769" s="52"/>
+      <c r="A769" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B769" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C769" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D769" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E769" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F769" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G769" s="94" t="s">
+        <v>692</v>
+      </c>
+      <c r="H769" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I769" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="J769" s="52">
+        <v>40</v>
+      </c>
+      <c r="K769" s="52">
+        <v>40</v>
+      </c>
       <c r="L769" s="52"/>
       <c r="M769" s="52"/>
-      <c r="N769" s="103"/>
-      <c r="O769" s="52"/>
+      <c r="N769" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O769" s="52">
+        <v>40</v>
+      </c>
       <c r="P769" s="52"/>
-      <c r="Q769" s="52"/>
-      <c r="R769" s="103"/>
-      <c r="S769" s="95"/>
+      <c r="Q769" s="52">
+        <v>40</v>
+      </c>
+      <c r="R769" s="104">
+        <f t="shared" si="158"/>
+        <v>80</v>
+      </c>
+      <c r="S769" s="86">
+        <f t="shared" si="156"/>
+        <v>160</v>
+      </c>
       <c r="AB769" s="111"/>
       <c r="AC769" s="111"/>
       <c r="AD769" s="111"/>
@@ -69751,25 +70730,62 @@
       <c r="AP769" s="7"/>
     </row>
     <row r="770" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A770" s="94"/>
-      <c r="B770" s="76"/>
-      <c r="C770" s="94"/>
-      <c r="D770" s="102"/>
-      <c r="E770" s="94"/>
-      <c r="F770" s="94"/>
-      <c r="G770" s="94"/>
-      <c r="H770" s="94"/>
-      <c r="I770" s="94"/>
-      <c r="J770" s="52"/>
-      <c r="K770" s="52"/>
-      <c r="L770" s="52"/>
+      <c r="A770" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B770" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C770" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D770" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E770" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F770" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G770" s="94" t="s">
+        <v>489</v>
+      </c>
+      <c r="H770" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I770" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="J770" s="52">
+        <v>12</v>
+      </c>
+      <c r="K770" s="52">
+        <v>12</v>
+      </c>
+      <c r="L770" s="52">
+        <v>12</v>
+      </c>
       <c r="M770" s="52"/>
-      <c r="N770" s="103"/>
-      <c r="O770" s="52"/>
-      <c r="P770" s="52"/>
+      <c r="N770" s="103">
+        <f t="shared" si="157"/>
+        <v>24</v>
+      </c>
+      <c r="O770" s="52">
+        <v>12</v>
+      </c>
+      <c r="P770" s="52">
+        <v>6</v>
+      </c>
       <c r="Q770" s="52"/>
-      <c r="R770" s="103"/>
-      <c r="S770" s="95"/>
+      <c r="R770" s="104">
+        <f t="shared" si="158"/>
+        <v>18</v>
+      </c>
+      <c r="S770" s="86">
+        <f t="shared" si="156"/>
+        <v>54</v>
+      </c>
       <c r="AB770" s="111"/>
       <c r="AC770" s="111"/>
       <c r="AD770" s="111"/>
@@ -69784,25 +70800,62 @@
       <c r="AP770" s="7"/>
     </row>
     <row r="771" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A771" s="94"/>
-      <c r="B771" s="76"/>
-      <c r="C771" s="94"/>
-      <c r="D771" s="102"/>
-      <c r="E771" s="94"/>
-      <c r="F771" s="94"/>
-      <c r="G771" s="94"/>
-      <c r="H771" s="94"/>
-      <c r="I771" s="94"/>
-      <c r="J771" s="52"/>
-      <c r="K771" s="52"/>
+      <c r="A771" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B771" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C771" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D771" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E771" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F771" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G771" s="94" t="s">
+        <v>693</v>
+      </c>
+      <c r="H771" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="I771" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="J771" s="52">
+        <v>20</v>
+      </c>
+      <c r="K771" s="52">
+        <v>20</v>
+      </c>
       <c r="L771" s="52"/>
       <c r="M771" s="52"/>
-      <c r="N771" s="103"/>
-      <c r="O771" s="52"/>
-      <c r="P771" s="52"/>
-      <c r="Q771" s="52"/>
-      <c r="R771" s="103"/>
-      <c r="S771" s="95"/>
+      <c r="N771" s="103">
+        <f t="shared" si="157"/>
+        <v>20</v>
+      </c>
+      <c r="O771" s="52">
+        <v>20</v>
+      </c>
+      <c r="P771" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q771" s="52">
+        <v>10</v>
+      </c>
+      <c r="R771" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S771" s="86">
+        <f t="shared" si="156"/>
+        <v>80</v>
+      </c>
       <c r="AB771" s="111"/>
       <c r="AC771" s="111"/>
       <c r="AD771" s="111"/>
@@ -69817,25 +70870,56 @@
       <c r="AP771" s="7"/>
     </row>
     <row r="772" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A772" s="94"/>
-      <c r="B772" s="76"/>
-      <c r="C772" s="94"/>
-      <c r="D772" s="102"/>
-      <c r="E772" s="94"/>
-      <c r="F772" s="94"/>
-      <c r="G772" s="94"/>
-      <c r="H772" s="94"/>
-      <c r="I772" s="94"/>
-      <c r="J772" s="52"/>
+      <c r="A772" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B772" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C772" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D772" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E772" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F772" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G772" s="94" t="s">
+        <v>694</v>
+      </c>
+      <c r="H772" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I772" s="94" t="s">
+        <v>698</v>
+      </c>
+      <c r="J772" s="52">
+        <v>20</v>
+      </c>
       <c r="K772" s="52"/>
       <c r="L772" s="52"/>
       <c r="M772" s="52"/>
-      <c r="N772" s="103"/>
+      <c r="N772" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O772" s="52"/>
       <c r="P772" s="52"/>
-      <c r="Q772" s="52"/>
-      <c r="R772" s="103"/>
-      <c r="S772" s="95"/>
+      <c r="Q772" s="52">
+        <v>20</v>
+      </c>
+      <c r="R772" s="104">
+        <f t="shared" si="158"/>
+        <v>20</v>
+      </c>
+      <c r="S772" s="86">
+        <f t="shared" si="156"/>
+        <v>40</v>
+      </c>
       <c r="AB772" s="111"/>
       <c r="AC772" s="111"/>
       <c r="AD772" s="111"/>
@@ -69850,25 +70934,58 @@
       <c r="AP772" s="7"/>
     </row>
     <row r="773" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A773" s="94"/>
-      <c r="B773" s="76"/>
-      <c r="C773" s="94"/>
-      <c r="D773" s="102"/>
-      <c r="E773" s="94"/>
-      <c r="F773" s="94"/>
-      <c r="G773" s="94"/>
-      <c r="H773" s="94"/>
-      <c r="I773" s="94"/>
-      <c r="J773" s="52"/>
+      <c r="A773" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B773" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C773" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D773" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E773" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F773" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G773" s="94" t="s">
+        <v>695</v>
+      </c>
+      <c r="H773" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I773" s="94" t="s">
+        <v>698</v>
+      </c>
+      <c r="J773" s="52">
+        <v>12</v>
+      </c>
       <c r="K773" s="52"/>
       <c r="L773" s="52"/>
       <c r="M773" s="52"/>
-      <c r="N773" s="103"/>
-      <c r="O773" s="52"/>
-      <c r="P773" s="52"/>
+      <c r="N773" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O773" s="52">
+        <v>12</v>
+      </c>
+      <c r="P773" s="52">
+        <v>12</v>
+      </c>
       <c r="Q773" s="52"/>
-      <c r="R773" s="103"/>
-      <c r="S773" s="95"/>
+      <c r="R773" s="104">
+        <f t="shared" si="158"/>
+        <v>24</v>
+      </c>
+      <c r="S773" s="86">
+        <f t="shared" ref="S773:S779" si="159">R773+N773+J773</f>
+        <v>36</v>
+      </c>
       <c r="AB773" s="111"/>
       <c r="AC773" s="111"/>
       <c r="AD773" s="111"/>
@@ -69883,25 +71000,54 @@
       <c r="AP773" s="7"/>
     </row>
     <row r="774" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A774" s="94"/>
-      <c r="B774" s="76"/>
-      <c r="C774" s="94"/>
-      <c r="D774" s="102"/>
-      <c r="E774" s="94"/>
-      <c r="F774" s="94"/>
-      <c r="G774" s="94"/>
-      <c r="H774" s="94"/>
-      <c r="I774" s="94"/>
+      <c r="A774" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B774" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C774" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D774" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E774" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F774" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G774" s="94" t="s">
+        <v>696</v>
+      </c>
+      <c r="H774" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I774" s="94" t="s">
+        <v>698</v>
+      </c>
       <c r="J774" s="52"/>
       <c r="K774" s="52"/>
       <c r="L774" s="52"/>
       <c r="M774" s="52"/>
-      <c r="N774" s="103"/>
-      <c r="O774" s="52"/>
+      <c r="N774" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O774" s="52">
+        <v>40</v>
+      </c>
       <c r="P774" s="52"/>
       <c r="Q774" s="52"/>
-      <c r="R774" s="103"/>
-      <c r="S774" s="95"/>
+      <c r="R774" s="104">
+        <f t="shared" si="158"/>
+        <v>40</v>
+      </c>
+      <c r="S774" s="86">
+        <f t="shared" si="159"/>
+        <v>40</v>
+      </c>
       <c r="AB774" s="111"/>
       <c r="AC774" s="111"/>
       <c r="AD774" s="111"/>
@@ -69916,25 +71062,64 @@
       <c r="AP774" s="7"/>
     </row>
     <row r="775" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A775" s="94"/>
-      <c r="B775" s="76"/>
-      <c r="C775" s="94"/>
-      <c r="D775" s="102"/>
-      <c r="E775" s="94"/>
-      <c r="F775" s="94"/>
-      <c r="G775" s="94"/>
-      <c r="H775" s="94"/>
-      <c r="I775" s="94"/>
-      <c r="J775" s="52"/>
-      <c r="K775" s="52"/>
-      <c r="L775" s="52"/>
+      <c r="A775" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B775" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C775" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D775" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E775" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F775" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G775" s="94" t="s">
+        <v>697</v>
+      </c>
+      <c r="H775" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="I775" s="94" t="s">
+        <v>698</v>
+      </c>
+      <c r="J775" s="52">
+        <v>80</v>
+      </c>
+      <c r="K775" s="52">
+        <v>40</v>
+      </c>
+      <c r="L775" s="52">
+        <v>80</v>
+      </c>
       <c r="M775" s="52"/>
-      <c r="N775" s="103"/>
-      <c r="O775" s="52"/>
-      <c r="P775" s="52"/>
-      <c r="Q775" s="52"/>
-      <c r="R775" s="103"/>
-      <c r="S775" s="95"/>
+      <c r="N775" s="103">
+        <f t="shared" si="157"/>
+        <v>120</v>
+      </c>
+      <c r="O775" s="52">
+        <v>40</v>
+      </c>
+      <c r="P775" s="52">
+        <v>80</v>
+      </c>
+      <c r="Q775" s="52">
+        <v>80</v>
+      </c>
+      <c r="R775" s="104">
+        <f t="shared" si="158"/>
+        <v>200</v>
+      </c>
+      <c r="S775" s="86">
+        <f t="shared" si="159"/>
+        <v>400</v>
+      </c>
       <c r="AB775" s="111"/>
       <c r="AC775" s="111"/>
       <c r="AD775" s="111"/>
@@ -69949,25 +71134,60 @@
       <c r="AP775" s="7"/>
     </row>
     <row r="776" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A776" s="94"/>
-      <c r="B776" s="76"/>
-      <c r="C776" s="94"/>
-      <c r="D776" s="102"/>
-      <c r="E776" s="94"/>
-      <c r="F776" s="94"/>
-      <c r="G776" s="94"/>
-      <c r="H776" s="94"/>
-      <c r="I776" s="94"/>
+      <c r="A776" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B776" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C776" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D776" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E776" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F776" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G776" s="94" t="s">
+        <v>545</v>
+      </c>
+      <c r="H776" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I776" s="94" t="s">
+        <v>152</v>
+      </c>
       <c r="J776" s="52"/>
-      <c r="K776" s="52"/>
+      <c r="K776" s="52">
+        <v>10</v>
+      </c>
       <c r="L776" s="52"/>
       <c r="M776" s="52"/>
-      <c r="N776" s="103"/>
-      <c r="O776" s="52"/>
-      <c r="P776" s="52"/>
-      <c r="Q776" s="52"/>
-      <c r="R776" s="103"/>
-      <c r="S776" s="95"/>
+      <c r="N776" s="103">
+        <f t="shared" si="157"/>
+        <v>10</v>
+      </c>
+      <c r="O776" s="52">
+        <v>15</v>
+      </c>
+      <c r="P776" s="52">
+        <v>15</v>
+      </c>
+      <c r="Q776" s="52">
+        <v>15</v>
+      </c>
+      <c r="R776" s="104">
+        <f t="shared" si="158"/>
+        <v>45</v>
+      </c>
+      <c r="S776" s="86">
+        <f t="shared" si="159"/>
+        <v>55</v>
+      </c>
       <c r="AB776" s="111"/>
       <c r="AC776" s="111"/>
       <c r="AD776" s="111"/>
@@ -69982,25 +71202,58 @@
       <c r="AP776" s="7"/>
     </row>
     <row r="777" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A777" s="94"/>
-      <c r="B777" s="76"/>
-      <c r="C777" s="94"/>
-      <c r="D777" s="102"/>
-      <c r="E777" s="94"/>
-      <c r="F777" s="94"/>
-      <c r="G777" s="94"/>
-      <c r="H777" s="94"/>
-      <c r="I777" s="94"/>
+      <c r="A777" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B777" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C777" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D777" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E777" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F777" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G777" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="H777" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I777" s="94" t="s">
+        <v>152</v>
+      </c>
       <c r="J777" s="52"/>
       <c r="K777" s="52"/>
       <c r="L777" s="52"/>
       <c r="M777" s="52"/>
-      <c r="N777" s="103"/>
-      <c r="O777" s="52"/>
-      <c r="P777" s="52"/>
-      <c r="Q777" s="52"/>
-      <c r="R777" s="103"/>
-      <c r="S777" s="95"/>
+      <c r="N777" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="O777" s="52">
+        <v>15</v>
+      </c>
+      <c r="P777" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q777" s="52">
+        <v>15</v>
+      </c>
+      <c r="R777" s="104">
+        <f t="shared" ref="R777:R795" si="160">SUM(O777:Q777)</f>
+        <v>40</v>
+      </c>
+      <c r="S777" s="86">
+        <f t="shared" ref="S777:S795" si="161">R777+N777+J777</f>
+        <v>40</v>
+      </c>
       <c r="AB777" s="111"/>
       <c r="AC777" s="111"/>
       <c r="AD777" s="111"/>
@@ -70015,25 +71268,64 @@
       <c r="AP777" s="7"/>
     </row>
     <row r="778" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A778" s="94"/>
-      <c r="B778" s="76"/>
-      <c r="C778" s="94"/>
-      <c r="D778" s="102"/>
-      <c r="E778" s="94"/>
-      <c r="F778" s="94"/>
-      <c r="G778" s="94"/>
-      <c r="H778" s="94"/>
-      <c r="I778" s="94"/>
-      <c r="J778" s="52"/>
-      <c r="K778" s="52"/>
-      <c r="L778" s="52"/>
+      <c r="A778" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B778" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C778" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D778" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E778" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F778" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G778" s="94" t="s">
+        <v>556</v>
+      </c>
+      <c r="H778" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I778" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="J778" s="52">
+        <v>40</v>
+      </c>
+      <c r="K778" s="52">
+        <v>20</v>
+      </c>
+      <c r="L778" s="52">
+        <v>20</v>
+      </c>
       <c r="M778" s="52"/>
-      <c r="N778" s="103"/>
-      <c r="O778" s="52"/>
-      <c r="P778" s="52"/>
-      <c r="Q778" s="52"/>
-      <c r="R778" s="103"/>
-      <c r="S778" s="95"/>
+      <c r="N778" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O778" s="52">
+        <v>15</v>
+      </c>
+      <c r="P778" s="52">
+        <v>10</v>
+      </c>
+      <c r="Q778" s="52">
+        <v>15</v>
+      </c>
+      <c r="R778" s="104">
+        <f t="shared" si="160"/>
+        <v>40</v>
+      </c>
+      <c r="S778" s="86">
+        <f t="shared" si="161"/>
+        <v>120</v>
+      </c>
       <c r="AB778" s="111"/>
       <c r="AC778" s="111"/>
       <c r="AD778" s="111"/>
@@ -70048,25 +71340,54 @@
       <c r="AP778" s="7"/>
     </row>
     <row r="779" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A779" s="94"/>
-      <c r="B779" s="76"/>
-      <c r="C779" s="94"/>
-      <c r="D779" s="102"/>
-      <c r="E779" s="94"/>
-      <c r="F779" s="94"/>
-      <c r="G779" s="94"/>
-      <c r="H779" s="94"/>
-      <c r="I779" s="94"/>
+      <c r="A779" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B779" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C779" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D779" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E779" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F779" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G779" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="H779" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I779" s="94" t="s">
+        <v>152</v>
+      </c>
       <c r="J779" s="52"/>
       <c r="K779" s="52"/>
       <c r="L779" s="52"/>
       <c r="M779" s="52"/>
-      <c r="N779" s="103"/>
+      <c r="N779" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O779" s="52"/>
-      <c r="P779" s="52"/>
+      <c r="P779" s="52">
+        <v>20</v>
+      </c>
       <c r="Q779" s="52"/>
-      <c r="R779" s="103"/>
-      <c r="S779" s="95"/>
+      <c r="R779" s="104">
+        <f t="shared" si="160"/>
+        <v>20</v>
+      </c>
+      <c r="S779" s="86">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
       <c r="AB779" s="111"/>
       <c r="AC779" s="111"/>
       <c r="AD779" s="111"/>
@@ -70081,25 +71402,54 @@
       <c r="AP779" s="7"/>
     </row>
     <row r="780" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A780" s="94"/>
-      <c r="B780" s="76"/>
-      <c r="C780" s="94"/>
-      <c r="D780" s="102"/>
-      <c r="E780" s="94"/>
-      <c r="F780" s="94"/>
-      <c r="G780" s="94"/>
-      <c r="H780" s="94"/>
-      <c r="I780" s="94"/>
+      <c r="A780" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B780" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C780" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D780" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E780" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F780" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G780" s="94" t="s">
+        <v>513</v>
+      </c>
+      <c r="H780" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I780" s="94" t="s">
+        <v>152</v>
+      </c>
       <c r="J780" s="52"/>
       <c r="K780" s="52"/>
       <c r="L780" s="52"/>
       <c r="M780" s="52"/>
-      <c r="N780" s="103"/>
+      <c r="N780" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O780" s="52"/>
-      <c r="P780" s="52"/>
+      <c r="P780" s="52">
+        <v>20</v>
+      </c>
       <c r="Q780" s="52"/>
-      <c r="R780" s="103"/>
-      <c r="S780" s="95"/>
+      <c r="R780" s="104">
+        <f t="shared" si="160"/>
+        <v>20</v>
+      </c>
+      <c r="S780" s="86">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
       <c r="AB780" s="111"/>
       <c r="AC780" s="111"/>
       <c r="AD780" s="111"/>
@@ -70114,25 +71464,64 @@
       <c r="AP780" s="7"/>
     </row>
     <row r="781" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A781" s="94"/>
-      <c r="B781" s="76"/>
-      <c r="C781" s="94"/>
-      <c r="D781" s="102"/>
-      <c r="E781" s="94"/>
-      <c r="F781" s="94"/>
-      <c r="G781" s="94"/>
-      <c r="H781" s="94"/>
-      <c r="I781" s="94"/>
-      <c r="J781" s="52"/>
-      <c r="K781" s="52"/>
-      <c r="L781" s="52"/>
+      <c r="A781" s="85">
+        <v>46231</v>
+      </c>
+      <c r="B781" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C781" s="97">
+        <v>61123995.678571403</v>
+      </c>
+      <c r="D781" s="97">
+        <v>87119.5</v>
+      </c>
+      <c r="E781" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F781" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="G781" s="94" t="s">
+        <v>344</v>
+      </c>
+      <c r="H781" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I781" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="J781" s="52">
+        <v>40</v>
+      </c>
+      <c r="K781" s="52">
+        <v>20</v>
+      </c>
+      <c r="L781" s="52">
+        <v>20</v>
+      </c>
       <c r="M781" s="52"/>
-      <c r="N781" s="103"/>
-      <c r="O781" s="52"/>
-      <c r="P781" s="52"/>
-      <c r="Q781" s="52"/>
-      <c r="R781" s="103"/>
-      <c r="S781" s="95"/>
+      <c r="N781" s="103">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="O781" s="52">
+        <v>50</v>
+      </c>
+      <c r="P781" s="52">
+        <v>50</v>
+      </c>
+      <c r="Q781" s="52">
+        <v>60</v>
+      </c>
+      <c r="R781" s="104">
+        <f t="shared" si="160"/>
+        <v>160</v>
+      </c>
+      <c r="S781" s="86">
+        <f t="shared" si="161"/>
+        <v>240</v>
+      </c>
       <c r="AB781" s="111"/>
       <c r="AC781" s="111"/>
       <c r="AD781" s="111"/>
@@ -70160,12 +71549,21 @@
       <c r="K782" s="52"/>
       <c r="L782" s="52"/>
       <c r="M782" s="52"/>
-      <c r="N782" s="103"/>
+      <c r="N782" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O782" s="52"/>
       <c r="P782" s="52"/>
       <c r="Q782" s="52"/>
-      <c r="R782" s="103"/>
-      <c r="S782" s="95"/>
+      <c r="R782" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S782" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB782" s="111"/>
       <c r="AC782" s="111"/>
       <c r="AD782" s="111"/>
@@ -70193,12 +71591,21 @@
       <c r="K783" s="52"/>
       <c r="L783" s="52"/>
       <c r="M783" s="52"/>
-      <c r="N783" s="103"/>
+      <c r="N783" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O783" s="52"/>
       <c r="P783" s="52"/>
       <c r="Q783" s="52"/>
-      <c r="R783" s="103"/>
-      <c r="S783" s="95"/>
+      <c r="R783" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S783" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB783" s="111"/>
       <c r="AC783" s="111"/>
       <c r="AD783" s="111"/>
@@ -70226,12 +71633,21 @@
       <c r="K784" s="52"/>
       <c r="L784" s="52"/>
       <c r="M784" s="52"/>
-      <c r="N784" s="103"/>
+      <c r="N784" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O784" s="52"/>
       <c r="P784" s="52"/>
       <c r="Q784" s="52"/>
-      <c r="R784" s="103"/>
-      <c r="S784" s="95"/>
+      <c r="R784" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S784" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB784" s="111"/>
       <c r="AC784" s="111"/>
       <c r="AD784" s="111"/>
@@ -70259,12 +71675,21 @@
       <c r="K785" s="52"/>
       <c r="L785" s="52"/>
       <c r="M785" s="52"/>
-      <c r="N785" s="103"/>
+      <c r="N785" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O785" s="52"/>
       <c r="P785" s="52"/>
       <c r="Q785" s="52"/>
-      <c r="R785" s="103"/>
-      <c r="S785" s="95"/>
+      <c r="R785" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S785" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB785" s="111"/>
       <c r="AC785" s="111"/>
       <c r="AD785" s="111"/>
@@ -70292,12 +71717,21 @@
       <c r="K786" s="52"/>
       <c r="L786" s="52"/>
       <c r="M786" s="52"/>
-      <c r="N786" s="103"/>
+      <c r="N786" s="103">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
       <c r="O786" s="52"/>
       <c r="P786" s="52"/>
       <c r="Q786" s="52"/>
-      <c r="R786" s="103"/>
-      <c r="S786" s="95"/>
+      <c r="R786" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S786" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB786" s="111"/>
       <c r="AC786" s="111"/>
       <c r="AD786" s="111"/>
@@ -70329,8 +71763,14 @@
       <c r="O787" s="52"/>
       <c r="P787" s="52"/>
       <c r="Q787" s="52"/>
-      <c r="R787" s="103"/>
-      <c r="S787" s="95"/>
+      <c r="R787" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S787" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB787" s="111"/>
       <c r="AC787" s="111"/>
       <c r="AD787" s="111"/>
@@ -70362,8 +71802,14 @@
       <c r="O788" s="52"/>
       <c r="P788" s="52"/>
       <c r="Q788" s="52"/>
-      <c r="R788" s="103"/>
-      <c r="S788" s="95"/>
+      <c r="R788" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S788" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB788" s="111"/>
       <c r="AC788" s="111"/>
       <c r="AD788" s="111"/>
@@ -70395,8 +71841,14 @@
       <c r="O789" s="52"/>
       <c r="P789" s="52"/>
       <c r="Q789" s="52"/>
-      <c r="R789" s="103"/>
-      <c r="S789" s="95"/>
+      <c r="R789" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S789" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB789" s="111"/>
       <c r="AC789" s="111"/>
       <c r="AD789" s="111"/>
@@ -70428,8 +71880,14 @@
       <c r="O790" s="52"/>
       <c r="P790" s="52"/>
       <c r="Q790" s="52"/>
-      <c r="R790" s="103"/>
-      <c r="S790" s="95"/>
+      <c r="R790" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S790" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB790" s="111"/>
       <c r="AC790" s="111"/>
       <c r="AD790" s="111"/>
@@ -70461,8 +71919,14 @@
       <c r="O791" s="52"/>
       <c r="P791" s="52"/>
       <c r="Q791" s="52"/>
-      <c r="R791" s="103"/>
-      <c r="S791" s="95"/>
+      <c r="R791" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S791" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB791" s="111"/>
       <c r="AC791" s="111"/>
       <c r="AD791" s="111"/>
@@ -70494,8 +71958,14 @@
       <c r="O792" s="52"/>
       <c r="P792" s="52"/>
       <c r="Q792" s="52"/>
-      <c r="R792" s="103"/>
-      <c r="S792" s="95"/>
+      <c r="R792" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S792" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB792" s="111"/>
       <c r="AC792" s="111"/>
       <c r="AD792" s="111"/>
@@ -70527,8 +71997,14 @@
       <c r="O793" s="52"/>
       <c r="P793" s="52"/>
       <c r="Q793" s="52"/>
-      <c r="R793" s="103"/>
-      <c r="S793" s="95"/>
+      <c r="R793" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S793" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB793" s="111"/>
       <c r="AC793" s="111"/>
       <c r="AD793" s="111"/>
@@ -70560,8 +72036,14 @@
       <c r="O794" s="52"/>
       <c r="P794" s="52"/>
       <c r="Q794" s="52"/>
-      <c r="R794" s="103"/>
-      <c r="S794" s="95"/>
+      <c r="R794" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S794" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB794" s="111"/>
       <c r="AC794" s="111"/>
       <c r="AD794" s="111"/>
@@ -70593,8 +72075,14 @@
       <c r="O795" s="52"/>
       <c r="P795" s="52"/>
       <c r="Q795" s="52"/>
-      <c r="R795" s="103"/>
-      <c r="S795" s="95"/>
+      <c r="R795" s="104">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S795" s="86">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
       <c r="AB795" s="111"/>
       <c r="AC795" s="111"/>
       <c r="AD795" s="111"/>
@@ -72648,18 +74136,18 @@
       <c r="L857" s="52"/>
       <c r="M857" s="52"/>
       <c r="N857" s="104">
-        <f t="shared" ref="N857:N860" si="157">K857+L857+M857</f>
+        <f t="shared" ref="N857:N860" si="162">K857+L857+M857</f>
         <v>0</v>
       </c>
       <c r="O857" s="52"/>
       <c r="P857" s="52"/>
       <c r="Q857" s="52"/>
       <c r="R857" s="104">
-        <f t="shared" ref="R857:R860" si="158">SUM(O857:Q857)</f>
+        <f t="shared" ref="R857:R860" si="163">SUM(O857:Q857)</f>
         <v>0</v>
       </c>
       <c r="S857" s="86">
-        <f t="shared" ref="S857:S860" si="159">R857+N857+J857</f>
+        <f t="shared" ref="S857:S860" si="164">R857+N857+J857</f>
         <v>0</v>
       </c>
       <c r="AB857" s="88">
@@ -72718,18 +74206,18 @@
       <c r="L858" s="52"/>
       <c r="M858" s="52"/>
       <c r="N858" s="104">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0</v>
       </c>
       <c r="O858" s="52"/>
       <c r="P858" s="52"/>
       <c r="Q858" s="52"/>
       <c r="R858" s="104">
-        <f t="shared" si="158"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="S858" s="86">
-        <f t="shared" si="159"/>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="AB858" s="88">
@@ -72788,18 +74276,18 @@
       <c r="L859" s="52"/>
       <c r="M859" s="52"/>
       <c r="N859" s="104">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0</v>
       </c>
       <c r="O859" s="52"/>
       <c r="P859" s="52"/>
       <c r="Q859" s="52"/>
       <c r="R859" s="104">
-        <f t="shared" si="158"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="S859" s="86">
-        <f t="shared" si="159"/>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="AB859" s="88">
@@ -72852,18 +74340,18 @@
       <c r="L860" s="108"/>
       <c r="M860" s="108"/>
       <c r="N860" s="104">
-        <f t="shared" si="157"/>
+        <f t="shared" si="162"/>
         <v>0</v>
       </c>
       <c r="O860" s="108"/>
       <c r="P860" s="108"/>
       <c r="Q860" s="108"/>
       <c r="R860" s="104">
-        <f t="shared" si="158"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="S860" s="86">
-        <f t="shared" si="159"/>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="AP860" s="7"/>
@@ -72872,43 +74360,43 @@
       <c r="A861" s="3"/>
       <c r="J861" s="107">
         <f>SUM(J3:J860)</f>
-        <v>18358</v>
+        <v>19338</v>
       </c>
       <c r="K861" s="107">
-        <f t="shared" ref="K861:S861" si="160">SUM(K3:K860)</f>
-        <v>12787</v>
+        <f t="shared" ref="K861:S861" si="165">SUM(K3:K860)</f>
+        <v>13785</v>
       </c>
       <c r="L861" s="107">
-        <f t="shared" si="160"/>
-        <v>12832</v>
+        <f t="shared" si="165"/>
+        <v>13680</v>
       </c>
       <c r="M861" s="107">
-        <f t="shared" si="160"/>
+        <f t="shared" si="165"/>
         <v>0</v>
       </c>
       <c r="N861" s="107">
-        <f t="shared" si="160"/>
-        <v>25619</v>
+        <f t="shared" si="165"/>
+        <v>27465</v>
       </c>
       <c r="O861" s="107">
-        <f t="shared" si="160"/>
-        <v>22552</v>
+        <f t="shared" si="165"/>
+        <v>24094</v>
       </c>
       <c r="P861" s="107">
-        <f t="shared" si="160"/>
-        <v>17154</v>
+        <f t="shared" si="165"/>
+        <v>18834</v>
       </c>
       <c r="Q861" s="107">
-        <f t="shared" si="160"/>
-        <v>27130</v>
+        <f t="shared" si="165"/>
+        <v>28875</v>
       </c>
       <c r="R861" s="107">
-        <f t="shared" si="160"/>
-        <v>66836</v>
+        <f t="shared" si="165"/>
+        <v>71803</v>
       </c>
       <c r="S861" s="107">
-        <f t="shared" si="160"/>
-        <v>110813</v>
+        <f t="shared" si="165"/>
+        <v>118606</v>
       </c>
       <c r="AP861" s="7"/>
     </row>
@@ -72975,91 +74463,91 @@
       </c>
       <c r="J864" s="47">
         <f>J861/40</f>
-        <v>458.95</v>
+        <v>483.45</v>
       </c>
       <c r="K864" s="109">
-        <f t="shared" ref="K864:S864" si="161">K861/40</f>
-        <v>319.67500000000001</v>
+        <f t="shared" ref="K864:S864" si="166">K861/40</f>
+        <v>344.625</v>
       </c>
       <c r="L864" s="109">
-        <f t="shared" si="161"/>
-        <v>320.8</v>
+        <f t="shared" si="166"/>
+        <v>342</v>
       </c>
       <c r="M864" s="109">
-        <f t="shared" si="161"/>
+        <f t="shared" si="166"/>
         <v>0</v>
       </c>
       <c r="N864" s="47">
-        <f t="shared" si="161"/>
-        <v>640.47500000000002</v>
+        <f t="shared" si="166"/>
+        <v>686.625</v>
       </c>
       <c r="O864" s="109">
-        <f t="shared" si="161"/>
-        <v>563.79999999999995</v>
+        <f t="shared" si="166"/>
+        <v>602.35</v>
       </c>
       <c r="P864" s="109">
-        <f t="shared" si="161"/>
-        <v>428.85</v>
+        <f t="shared" si="166"/>
+        <v>470.85</v>
       </c>
       <c r="Q864" s="109">
-        <f t="shared" si="161"/>
-        <v>678.25</v>
+        <f t="shared" si="166"/>
+        <v>721.875</v>
       </c>
       <c r="R864" s="47">
-        <f t="shared" si="161"/>
-        <v>1670.9</v>
+        <f t="shared" si="166"/>
+        <v>1795.075</v>
       </c>
       <c r="S864" s="109">
-        <f t="shared" si="161"/>
-        <v>2770.3249999999998</v>
+        <f t="shared" si="166"/>
+        <v>2965.15</v>
       </c>
       <c r="T864" s="54">
-        <f t="shared" ref="T864:AF864" si="162">+T433/40</f>
+        <f t="shared" ref="T864:AF864" si="167">+T433/40</f>
         <v>0</v>
       </c>
       <c r="U864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="V864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="W864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="X864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="Y864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="Z864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AA864" s="54">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AB864" s="55"/>
       <c r="AC864" s="43">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AD864" s="43">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AE864" s="43">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>84640.158687499978</v>
       </c>
       <c r="AF864" s="43">
-        <f t="shared" si="162"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AG864" s="43"/>
@@ -73076,7 +74564,7 @@
     <row r="866" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S866" s="53">
         <f>S864+W864+AA864</f>
-        <v>2770.3249999999998</v>
+        <v>2965.15</v>
       </c>
       <c r="X866" t="s">
         <v>50</v>
@@ -73106,13 +74594,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -73125,14 +74614,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -73204,11 +74692,11 @@
       </c>
       <c r="G7" s="16">
         <f>'STT Report'!Q864+'STT Report'!Z864</f>
-        <v>678.25</v>
+        <v>721.875</v>
       </c>
       <c r="H7" s="17">
         <f>E7+F7-G7</f>
-        <v>641.75</v>
+        <v>598.125</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -73223,11 +74711,11 @@
       </c>
       <c r="G8" s="16">
         <f>'STT Report'!P864+'STT Report'!Y864</f>
-        <v>428.85</v>
+        <v>470.85</v>
       </c>
       <c r="H8" s="17">
         <f>E8+F8-G8</f>
-        <v>-85.850000000000023</v>
+        <v>-127.85000000000002</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -73242,11 +74730,11 @@
       </c>
       <c r="G9" s="16">
         <f>'STT Report'!O864+'STT Report'!X864</f>
-        <v>563.79999999999995</v>
+        <v>602.35</v>
       </c>
       <c r="H9" s="17">
         <f>E9+F9-G9</f>
-        <v>364.20000000000005</v>
+        <v>325.64999999999998</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -73263,11 +74751,11 @@
       </c>
       <c r="G10" s="22">
         <f>SUM(G7:G9)</f>
-        <v>1670.8999999999999</v>
+        <v>1795.0749999999998</v>
       </c>
       <c r="H10" s="23">
         <f>SUM(H7:H9)</f>
-        <v>920.1</v>
+        <v>795.92499999999995</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -73280,11 +74768,11 @@
       <c r="F11" s="15"/>
       <c r="G11" s="44">
         <f>'STT Report'!J864</f>
-        <v>458.95</v>
+        <v>483.45</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1194.05</v>
+        <v>1169.55</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -73321,11 +74809,11 @@
       </c>
       <c r="G14" s="20">
         <f>SUM(G11:G13)</f>
-        <v>458.95</v>
+        <v>483.45</v>
       </c>
       <c r="H14" s="23">
         <f>SUM(H11:H13)</f>
-        <v>1194.05</v>
+        <v>1169.55</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -73355,11 +74843,11 @@
       <c r="F16" s="18"/>
       <c r="G16" s="16">
         <f>'STT Report'!L864+'STT Report'!U864</f>
-        <v>320.8</v>
+        <v>342</v>
       </c>
       <c r="H16" s="17">
         <f>E16+F16-G16</f>
-        <v>-53.800000000000011</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -73372,11 +74860,11 @@
       <c r="F17" s="18"/>
       <c r="G17" s="16">
         <f>'STT Report'!K864+'STT Report'!T864</f>
-        <v>319.67500000000001</v>
+        <v>344.625</v>
       </c>
       <c r="H17" s="17">
         <f>E17+F17-G17</f>
-        <v>-79.675000000000011</v>
+        <v>-104.625</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -73393,11 +74881,11 @@
       </c>
       <c r="G18" s="22">
         <f>SUM(G15:G17)</f>
-        <v>640.47500000000002</v>
+        <v>686.625</v>
       </c>
       <c r="H18" s="23">
         <f>SUM(H15:H17)</f>
-        <v>-133.47500000000002</v>
+        <v>-179.625</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -73414,11 +74902,11 @@
       </c>
       <c r="G19" s="25">
         <f>G10+G14+G18</f>
-        <v>2770.3249999999998</v>
+        <v>2965.1499999999996</v>
       </c>
       <c r="H19" s="27">
         <f>H10+H14+H18</f>
-        <v>1980.6750000000002</v>
+        <v>1785.85</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
